--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726748</v>
+        <v>129728258</v>
       </c>
       <c r="B5" t="n">
-        <v>78088</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492403</v>
+        <v>492272</v>
       </c>
       <c r="R5" t="n">
-        <v>7135004</v>
+        <v>7135018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1094,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:04</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129728258</v>
+        <v>129726742</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492272</v>
+        <v>492287</v>
       </c>
       <c r="R6" t="n">
-        <v>7135018</v>
+        <v>7135066</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,14 +1196,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,57 +1223,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728238</v>
+        <v>129728249</v>
       </c>
       <c r="B7" t="n">
-        <v>80208</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492287</v>
+        <v>492618</v>
       </c>
       <c r="R7" t="n">
-        <v>7135150</v>
+        <v>7134954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,14 +1311,45 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1332,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726742</v>
+        <v>129728237</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>80182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,34 +1377,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492287</v>
+        <v>492236</v>
       </c>
       <c r="R8" t="n">
-        <v>7135066</v>
+        <v>7135034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,19 +1441,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,28 +1457,54 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728249</v>
+        <v>129726748</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>78089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,37 +1512,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492618</v>
+        <v>492403</v>
       </c>
       <c r="R9" t="n">
-        <v>7134954</v>
+        <v>7135004</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,14 +1569,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,76 +1590,50 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726749</v>
+        <v>129728238</v>
       </c>
       <c r="B10" t="n">
-        <v>83044</v>
+        <v>80209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1605,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492403</v>
+        <v>492287</v>
       </c>
       <c r="R10" t="n">
-        <v>7135004</v>
+        <v>7135150</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,19 +1676,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129728237</v>
+        <v>129726749</v>
       </c>
       <c r="B11" t="n">
-        <v>80181</v>
+        <v>83045</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,41 +1716,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492236</v>
+        <v>492403</v>
       </c>
       <c r="R11" t="n">
-        <v>7135034</v>
+        <v>7135004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,14 +1773,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en klen levande sälg.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,44 +1794,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
         <v>129728251</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>129728261</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,65 +2045,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129728244</v>
+        <v>129726752</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492133</v>
+        <v>492482</v>
       </c>
       <c r="R14" t="n">
-        <v>7135159</v>
+        <v>7134934</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,14 +2113,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,89 +2134,63 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129728247</v>
+        <v>129726741</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492455</v>
+        <v>492282</v>
       </c>
       <c r="R15" t="n">
-        <v>7134922</v>
+        <v>7135069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,14 +2220,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,34 +2241,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726752</v>
+        <v>129726738</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>83045</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,21 +2270,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2336,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492482</v>
+        <v>492242</v>
       </c>
       <c r="R16" t="n">
-        <v>7134934</v>
+        <v>7135130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,45 +2366,65 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726741</v>
+        <v>129728247</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492282</v>
+        <v>492455</v>
       </c>
       <c r="R17" t="n">
-        <v>7135069</v>
+        <v>7134922</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,19 +2454,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,63 +2470,89 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726738</v>
+        <v>129728244</v>
       </c>
       <c r="B18" t="n">
-        <v>83044</v>
+        <v>98769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492242</v>
+        <v>492133</v>
       </c>
       <c r="R18" t="n">
-        <v>7135130</v>
+        <v>7135159</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,19 +2582,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:30</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,83 +2598,69 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129728246</v>
+        <v>129726723</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492341</v>
+        <v>492370</v>
       </c>
       <c r="R19" t="n">
-        <v>7134976</v>
+        <v>7135127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,14 +2690,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,34 +2711,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726723</v>
+        <v>129726744</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492370</v>
+        <v>492318</v>
       </c>
       <c r="R20" t="n">
-        <v>7135127</v>
+        <v>7135032</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2820,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2857,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726744</v>
+        <v>129726736</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>83045</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,21 +2847,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2892,10 +2871,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492318</v>
+        <v>492194</v>
       </c>
       <c r="R21" t="n">
-        <v>7135032</v>
+        <v>7135150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,7 +2906,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2916,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,45 +2943,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726736</v>
+        <v>129728246</v>
       </c>
       <c r="B22" t="n">
-        <v>83044</v>
+        <v>98769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492194</v>
+        <v>492341</v>
       </c>
       <c r="R22" t="n">
-        <v>7135150</v>
+        <v>7134976</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3032,19 +3031,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3053,18 +3047,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
         <v>129726716</v>
       </c>
       <c r="B23" t="n">
-        <v>97645</v>
+        <v>97646</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>129728252</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3280,10 +3280,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129728242</v>
+        <v>129728245</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492205</v>
+        <v>492204</v>
       </c>
       <c r="R25" t="n">
-        <v>7135151</v>
+        <v>7135099</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,10 +3408,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129728245</v>
+        <v>129728242</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492204</v>
+        <v>492205</v>
       </c>
       <c r="R26" t="n">
-        <v>7135099</v>
+        <v>7135151</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
+          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,7 +3539,7 @@
         <v>129726732</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>129728257</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>129726754</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>129726719</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,32 +3959,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726737</v>
+        <v>129726726</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>91761</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492228</v>
+        <v>492285</v>
       </c>
       <c r="R31" t="n">
-        <v>7135126</v>
+        <v>7135248</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,32 +4066,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726726</v>
+        <v>129726737</v>
       </c>
       <c r="B32" t="n">
-        <v>91760</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492285</v>
+        <v>492228</v>
       </c>
       <c r="R32" t="n">
-        <v>7135248</v>
+        <v>7135126</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4176,7 +4176,7 @@
         <v>129726722</v>
       </c>
       <c r="B33" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>129728254</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>129728255</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>129728256</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>129726729</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>129726750</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>129726720</v>
       </c>
       <c r="B39" t="n">
-        <v>78088</v>
+        <v>78089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>129728243</v>
       </c>
       <c r="B40" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>129728236</v>
       </c>
       <c r="B41" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>129726735</v>
       </c>
       <c r="B42" t="n">
-        <v>83039</v>
+        <v>83040</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>129728253</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>129726740</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>129728234</v>
       </c>
       <c r="B45" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5625,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129726717</v>
+        <v>129726733</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5636,21 +5636,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492583</v>
+        <v>492186</v>
       </c>
       <c r="R46" t="n">
-        <v>7134977</v>
+        <v>7135180</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5732,10 +5732,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129726751</v>
+        <v>129726717</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492457</v>
+        <v>492583</v>
       </c>
       <c r="R47" t="n">
-        <v>7134957</v>
+        <v>7134977</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129726733</v>
+        <v>129726751</v>
       </c>
       <c r="B48" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5850,21 +5850,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492186</v>
+        <v>492457</v>
       </c>
       <c r="R48" t="n">
-        <v>7135180</v>
+        <v>7134957</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5949,7 +5949,7 @@
         <v>129728241</v>
       </c>
       <c r="B49" t="n">
-        <v>80208</v>
+        <v>80209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>129728262</v>
       </c>
       <c r="B50" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>129726721</v>
       </c>
       <c r="B51" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>129726718</v>
       </c>
       <c r="B52" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>129726727</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>129726747</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>129728248</v>
       </c>
       <c r="B55" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>129728260</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>129726731</v>
       </c>
       <c r="B57" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>129726734</v>
       </c>
       <c r="B58" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>129726728</v>
       </c>
       <c r="B59" t="n">
-        <v>78088</v>
+        <v>78089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7150,10 +7150,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726753</v>
+        <v>129728250</v>
       </c>
       <c r="B60" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7161,21 +7161,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492496</v>
+        <v>492572</v>
       </c>
       <c r="R60" t="n">
-        <v>7134904</v>
+        <v>7135009</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7218,19 +7218,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>08:40</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7245,22 +7240,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129728250</v>
+        <v>129726725</v>
       </c>
       <c r="B61" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7292,10 +7287,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492572</v>
+        <v>492304</v>
       </c>
       <c r="R61" t="n">
-        <v>7135009</v>
+        <v>7135246</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7325,14 +7320,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7347,22 +7347,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726725</v>
+        <v>129726753</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492304</v>
+        <v>492496</v>
       </c>
       <c r="R62" t="n">
-        <v>7135246</v>
+        <v>7134904</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7469,7 +7469,7 @@
         <v>129728239</v>
       </c>
       <c r="B63" t="n">
-        <v>80208</v>
+        <v>80209</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,32 +7568,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726730</v>
+        <v>129728259</v>
       </c>
       <c r="B64" t="n">
-        <v>92305</v>
+        <v>79076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492124</v>
+        <v>492317</v>
       </c>
       <c r="R64" t="n">
-        <v>7135171</v>
+        <v>7134999</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7636,19 +7636,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:53</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7663,22 +7658,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129726724</v>
+        <v>129726745</v>
       </c>
       <c r="B65" t="n">
-        <v>57895</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7686,43 +7681,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492343</v>
+        <v>492367</v>
       </c>
       <c r="R65" t="n">
-        <v>7135242</v>
+        <v>7135038</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7754,7 +7740,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7764,7 +7750,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7791,32 +7777,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129728259</v>
+        <v>129728240</v>
       </c>
       <c r="B66" t="n">
-        <v>79075</v>
+        <v>80209</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7826,10 +7812,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492317</v>
+        <v>492405</v>
       </c>
       <c r="R66" t="n">
-        <v>7134999</v>
+        <v>7134981</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7866,7 +7852,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7893,10 +7879,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129726745</v>
+        <v>129726724</v>
       </c>
       <c r="B67" t="n">
-        <v>79075</v>
+        <v>57896</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7904,34 +7890,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492367</v>
+        <v>492343</v>
       </c>
       <c r="R67" t="n">
-        <v>7135038</v>
+        <v>7135242</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7963,7 +7958,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7973,7 +7968,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8000,10 +7995,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129728240</v>
+        <v>129726730</v>
       </c>
       <c r="B68" t="n">
-        <v>80208</v>
+        <v>92306</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8011,21 +8006,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6461</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8035,10 +8030,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492405</v>
+        <v>492124</v>
       </c>
       <c r="R68" t="n">
-        <v>7134981</v>
+        <v>7135171</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8068,14 +8063,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8090,22 +8090,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730573</v>
+        <v>129730672</v>
       </c>
       <c r="B69" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492062</v>
+        <v>492334</v>
       </c>
       <c r="R69" t="n">
-        <v>7135100</v>
+        <v>7135092</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,11 +8173,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8204,10 +8199,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730598</v>
+        <v>129730573</v>
       </c>
       <c r="B70" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8239,10 +8234,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492220</v>
+        <v>492062</v>
       </c>
       <c r="R70" t="n">
-        <v>7135003</v>
+        <v>7135100</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8279,7 +8274,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8306,10 +8301,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730615</v>
+        <v>129730584</v>
       </c>
       <c r="B71" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8341,10 +8336,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492345</v>
+        <v>492107</v>
       </c>
       <c r="R71" t="n">
-        <v>7134961</v>
+        <v>7135052</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8381,7 +8376,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8408,10 +8403,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730584</v>
+        <v>129730598</v>
       </c>
       <c r="B72" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8443,10 +8438,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492107</v>
+        <v>492220</v>
       </c>
       <c r="R72" t="n">
-        <v>7135052</v>
+        <v>7135003</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8510,10 +8505,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730658</v>
+        <v>129730615</v>
       </c>
       <c r="B73" t="n">
-        <v>57895</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8521,21 +8516,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8545,10 +8540,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492464</v>
+        <v>492345</v>
       </c>
       <c r="R73" t="n">
-        <v>7135049</v>
+        <v>7134961</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8585,7 +8580,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8612,10 +8607,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730672</v>
+        <v>129730658</v>
       </c>
       <c r="B74" t="n">
-        <v>79075</v>
+        <v>57896</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8623,21 +8618,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8647,10 +8642,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492334</v>
+        <v>492464</v>
       </c>
       <c r="R74" t="n">
-        <v>7135092</v>
+        <v>7135049</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8683,6 +8678,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8712,7 +8712,7 @@
         <v>129730671</v>
       </c>
       <c r="B75" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8806,10 +8806,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129730645</v>
+        <v>129730629</v>
       </c>
       <c r="B76" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>492464</v>
+        <v>492369</v>
       </c>
       <c r="R76" t="n">
-        <v>7134870</v>
+        <v>7134915</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8911,7 +8911,7 @@
         <v>129730637</v>
       </c>
       <c r="B77" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>129730551</v>
       </c>
       <c r="B78" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129730629</v>
+        <v>129730645</v>
       </c>
       <c r="B79" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>492369</v>
+        <v>492464</v>
       </c>
       <c r="R79" t="n">
-        <v>7134915</v>
+        <v>7134870</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9214,32 +9214,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730665</v>
+        <v>129730675</v>
       </c>
       <c r="B80" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492046</v>
+        <v>492075</v>
       </c>
       <c r="R80" t="n">
-        <v>7135177</v>
+        <v>7135214</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9285,11 +9285,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>8st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,10 +9311,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730675</v>
+        <v>129730635</v>
       </c>
       <c r="B81" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9327,21 +9322,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9346,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492075</v>
+        <v>492424</v>
       </c>
       <c r="R81" t="n">
-        <v>7135214</v>
+        <v>7134911</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9387,6 +9382,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9413,10 +9413,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730603</v>
+        <v>129730639</v>
       </c>
       <c r="B82" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492265</v>
+        <v>492439</v>
       </c>
       <c r="R82" t="n">
-        <v>7134987</v>
+        <v>7134899</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>129730562</v>
       </c>
       <c r="B83" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9617,10 +9617,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730594</v>
+        <v>129730575</v>
       </c>
       <c r="B84" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492205</v>
+        <v>492063</v>
       </c>
       <c r="R84" t="n">
-        <v>7135012</v>
+        <v>7135101</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9692,7 +9692,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9719,10 +9719,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730599</v>
+        <v>129730603</v>
       </c>
       <c r="B85" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492216</v>
+        <v>492265</v>
       </c>
       <c r="R85" t="n">
-        <v>7135002</v>
+        <v>7134987</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9821,10 +9821,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129730639</v>
+        <v>129730594</v>
       </c>
       <c r="B86" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492439</v>
+        <v>492205</v>
       </c>
       <c r="R86" t="n">
-        <v>7134899</v>
+        <v>7135012</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9923,10 +9923,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129730635</v>
+        <v>129730599</v>
       </c>
       <c r="B87" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9958,10 +9958,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492424</v>
+        <v>492216</v>
       </c>
       <c r="R87" t="n">
-        <v>7134911</v>
+        <v>7135002</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10025,10 +10025,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730575</v>
+        <v>129730630</v>
       </c>
       <c r="B88" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492063</v>
+        <v>492411</v>
       </c>
       <c r="R88" t="n">
-        <v>7135101</v>
+        <v>7134926</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10127,32 +10127,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129730630</v>
+        <v>129730665</v>
       </c>
       <c r="B89" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10162,10 +10162,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492411</v>
+        <v>492046</v>
       </c>
       <c r="R89" t="n">
-        <v>7134926</v>
+        <v>7135177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10229,32 +10229,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129730663</v>
+        <v>129730583</v>
       </c>
       <c r="B90" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492070</v>
+        <v>492105</v>
       </c>
       <c r="R90" t="n">
-        <v>7135173</v>
+        <v>7135051</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>14st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,10 +10331,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129730583</v>
+        <v>129730625</v>
       </c>
       <c r="B91" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492105</v>
+        <v>492367</v>
       </c>
       <c r="R91" t="n">
-        <v>7135051</v>
+        <v>7134920</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10433,10 +10433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129730625</v>
+        <v>129730565</v>
       </c>
       <c r="B92" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>492367</v>
+        <v>492040</v>
       </c>
       <c r="R92" t="n">
-        <v>7134920</v>
+        <v>7135117</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10535,32 +10535,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129730565</v>
+        <v>129730663</v>
       </c>
       <c r="B93" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>492040</v>
+        <v>492070</v>
       </c>
       <c r="R93" t="n">
-        <v>7135117</v>
+        <v>7135173</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>14st</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129730662</v>
+        <v>129730522</v>
       </c>
       <c r="B94" t="n">
-        <v>78088</v>
+        <v>97015</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>53</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10672,10 +10672,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492166</v>
+        <v>492217</v>
       </c>
       <c r="R94" t="n">
-        <v>7135239</v>
+        <v>7135249</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10734,10 +10734,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730522</v>
+        <v>129730650</v>
       </c>
       <c r="B95" t="n">
-        <v>97014</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10745,21 +10745,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10769,10 +10769,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492217</v>
+        <v>492473</v>
       </c>
       <c r="R95" t="n">
-        <v>7135249</v>
+        <v>7134864</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10805,6 +10805,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10831,10 +10836,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730650</v>
+        <v>129730661</v>
       </c>
       <c r="B96" t="n">
-        <v>57735</v>
+        <v>91608</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10842,23 +10847,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10866,10 +10867,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492473</v>
+        <v>492069</v>
       </c>
       <c r="R96" t="n">
-        <v>7134864</v>
+        <v>7135162</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10896,17 +10897,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10915,6 +10911,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10933,10 +10930,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730619</v>
+        <v>129730606</v>
       </c>
       <c r="B97" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10968,10 +10965,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492353</v>
+        <v>492303</v>
       </c>
       <c r="R97" t="n">
-        <v>7134945</v>
+        <v>7134972</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11008,7 +11005,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11035,10 +11032,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129730606</v>
+        <v>129730619</v>
       </c>
       <c r="B98" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11070,10 +11067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492303</v>
+        <v>492353</v>
       </c>
       <c r="R98" t="n">
-        <v>7134972</v>
+        <v>7134945</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11110,7 +11107,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11137,10 +11134,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730569</v>
+        <v>129730604</v>
       </c>
       <c r="B99" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11172,10 +11169,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492054</v>
+        <v>492297</v>
       </c>
       <c r="R99" t="n">
-        <v>7135107</v>
+        <v>7134975</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11212,7 +11209,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11239,10 +11236,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730604</v>
+        <v>129730569</v>
       </c>
       <c r="B100" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11274,10 +11271,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492297</v>
+        <v>492054</v>
       </c>
       <c r="R100" t="n">
-        <v>7134975</v>
+        <v>7135107</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11314,7 +11311,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11341,10 +11338,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730661</v>
+        <v>129730662</v>
       </c>
       <c r="B101" t="n">
-        <v>91607</v>
+        <v>78089</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11352,19 +11349,23 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11372,10 +11373,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492069</v>
+        <v>492166</v>
       </c>
       <c r="R101" t="n">
-        <v>7135162</v>
+        <v>7135239</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11402,12 +11403,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11416,7 +11417,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730523</v>
+        <v>129730656</v>
       </c>
       <c r="B102" t="n">
-        <v>97014</v>
+        <v>57736</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11446,21 +11446,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492316</v>
+        <v>492466</v>
       </c>
       <c r="R102" t="n">
-        <v>7135071</v>
+        <v>7134851</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11506,6 +11506,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11532,10 +11537,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730640</v>
+        <v>129730602</v>
       </c>
       <c r="B103" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11567,10 +11572,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492444</v>
+        <v>492245</v>
       </c>
       <c r="R103" t="n">
-        <v>7134887</v>
+        <v>7134995</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,10 +11639,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730602</v>
+        <v>129730640</v>
       </c>
       <c r="B104" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11669,10 +11674,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492245</v>
+        <v>492444</v>
       </c>
       <c r="R104" t="n">
-        <v>7134995</v>
+        <v>7134887</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11736,10 +11741,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730656</v>
+        <v>129730523</v>
       </c>
       <c r="B105" t="n">
-        <v>57735</v>
+        <v>97015</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11747,21 +11752,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11771,10 +11776,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>492466</v>
+        <v>492316</v>
       </c>
       <c r="R105" t="n">
-        <v>7134851</v>
+        <v>7135071</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11807,11 +11812,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11838,10 +11838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730521</v>
+        <v>129730529</v>
       </c>
       <c r="B106" t="n">
-        <v>83044</v>
+        <v>57736</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492100</v>
+        <v>492088</v>
       </c>
       <c r="R106" t="n">
-        <v>7135216</v>
+        <v>7135198</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11909,6 +11909,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11935,10 +11940,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730559</v>
+        <v>129730631</v>
       </c>
       <c r="B107" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11970,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492032</v>
+        <v>492409</v>
       </c>
       <c r="R107" t="n">
-        <v>7135120</v>
+        <v>7134918</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12010,7 +12015,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12037,10 +12042,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730529</v>
+        <v>129730532</v>
       </c>
       <c r="B108" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12072,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492088</v>
+        <v>492082</v>
       </c>
       <c r="R108" t="n">
-        <v>7135198</v>
+        <v>7135294</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12112,7 +12117,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12139,10 +12144,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730532</v>
+        <v>129730576</v>
       </c>
       <c r="B109" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12174,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492082</v>
+        <v>492066</v>
       </c>
       <c r="R109" t="n">
-        <v>7135294</v>
+        <v>7135093</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12214,7 +12219,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,10 +12246,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730631</v>
+        <v>129730559</v>
       </c>
       <c r="B110" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12276,10 +12281,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492409</v>
+        <v>492032</v>
       </c>
       <c r="R110" t="n">
-        <v>7134918</v>
+        <v>7135120</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12316,7 +12321,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12343,10 +12348,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730576</v>
+        <v>129730521</v>
       </c>
       <c r="B111" t="n">
-        <v>57735</v>
+        <v>83045</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12354,21 +12359,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12378,10 +12383,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492066</v>
+        <v>492100</v>
       </c>
       <c r="R111" t="n">
-        <v>7135093</v>
+        <v>7135216</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12414,11 +12419,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12448,7 +12448,7 @@
         <v>129730526</v>
       </c>
       <c r="B112" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12542,10 +12542,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730617</v>
+        <v>129730528</v>
       </c>
       <c r="B113" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12577,10 +12577,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492349</v>
+        <v>492476</v>
       </c>
       <c r="R113" t="n">
-        <v>7134943</v>
+        <v>7135072</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12617,7 +12617,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12644,10 +12644,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730624</v>
+        <v>129730632</v>
       </c>
       <c r="B114" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12679,10 +12679,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492366</v>
+        <v>492414</v>
       </c>
       <c r="R114" t="n">
-        <v>7134921</v>
+        <v>7134915</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12746,10 +12746,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730528</v>
+        <v>129730608</v>
       </c>
       <c r="B115" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12781,10 +12781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492476</v>
+        <v>492316</v>
       </c>
       <c r="R115" t="n">
-        <v>7135072</v>
+        <v>7134971</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12848,10 +12848,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730597</v>
+        <v>129730617</v>
       </c>
       <c r="B116" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12883,10 +12883,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>492213</v>
+        <v>492349</v>
       </c>
       <c r="R116" t="n">
-        <v>7135010</v>
+        <v>7134943</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12953,7 +12953,7 @@
         <v>129730579</v>
       </c>
       <c r="B117" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13052,10 +13052,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730632</v>
+        <v>129730624</v>
       </c>
       <c r="B118" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13087,10 +13087,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492414</v>
+        <v>492366</v>
       </c>
       <c r="R118" t="n">
-        <v>7134915</v>
+        <v>7134921</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13154,10 +13154,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730608</v>
+        <v>129730597</v>
       </c>
       <c r="B119" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13189,10 +13189,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492316</v>
+        <v>492213</v>
       </c>
       <c r="R119" t="n">
-        <v>7134971</v>
+        <v>7135010</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13259,7 +13259,7 @@
         <v>129730673</v>
       </c>
       <c r="B120" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13353,10 +13353,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730585</v>
+        <v>129730587</v>
       </c>
       <c r="B121" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>492123</v>
+        <v>492125</v>
       </c>
       <c r="R121" t="n">
         <v>7135047</v>
@@ -13455,10 +13455,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730582</v>
+        <v>129730568</v>
       </c>
       <c r="B122" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13490,10 +13490,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492094</v>
+        <v>492044</v>
       </c>
       <c r="R122" t="n">
-        <v>7135060</v>
+        <v>7135114</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13557,10 +13557,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730657</v>
+        <v>129730582</v>
       </c>
       <c r="B123" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13592,10 +13592,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492468</v>
+        <v>492094</v>
       </c>
       <c r="R123" t="n">
-        <v>7134848</v>
+        <v>7135060</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13659,10 +13659,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730587</v>
+        <v>129730585</v>
       </c>
       <c r="B124" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492125</v>
+        <v>492123</v>
       </c>
       <c r="R124" t="n">
         <v>7135047</v>
@@ -13761,10 +13761,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730568</v>
+        <v>129730657</v>
       </c>
       <c r="B125" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492044</v>
+        <v>492468</v>
       </c>
       <c r="R125" t="n">
-        <v>7135114</v>
+        <v>7134848</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13863,10 +13863,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730618</v>
+        <v>129730614</v>
       </c>
       <c r="B126" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13898,10 +13898,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492350</v>
+        <v>492342</v>
       </c>
       <c r="R126" t="n">
-        <v>7134947</v>
+        <v>7134966</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13965,10 +13965,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730614</v>
+        <v>129730618</v>
       </c>
       <c r="B127" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14000,10 +14000,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>492342</v>
+        <v>492350</v>
       </c>
       <c r="R127" t="n">
-        <v>7134966</v>
+        <v>7134947</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14067,10 +14067,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730539</v>
+        <v>129730563</v>
       </c>
       <c r="B128" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14102,10 +14102,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>492011</v>
+        <v>492037</v>
       </c>
       <c r="R128" t="n">
-        <v>7135206</v>
+        <v>7135119</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14169,10 +14169,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730563</v>
+        <v>129730643</v>
       </c>
       <c r="B129" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>492037</v>
+        <v>492464</v>
       </c>
       <c r="R129" t="n">
-        <v>7135119</v>
+        <v>7134867</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14271,10 +14271,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730643</v>
+        <v>129730561</v>
       </c>
       <c r="B130" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14306,10 +14306,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>492464</v>
+        <v>492039</v>
       </c>
       <c r="R130" t="n">
-        <v>7134867</v>
+        <v>7135123</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14373,10 +14373,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730561</v>
+        <v>129730539</v>
       </c>
       <c r="B131" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14408,10 +14408,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>492039</v>
+        <v>492011</v>
       </c>
       <c r="R131" t="n">
-        <v>7135123</v>
+        <v>7135206</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14478,7 +14478,7 @@
         <v>129730670</v>
       </c>
       <c r="B132" t="n">
-        <v>91760</v>
+        <v>91761</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14572,10 +14572,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730531</v>
+        <v>129730545</v>
       </c>
       <c r="B133" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>492083</v>
+        <v>491983</v>
       </c>
       <c r="R133" t="n">
-        <v>7135291</v>
+        <v>7135171</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14674,10 +14674,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730574</v>
+        <v>129730531</v>
       </c>
       <c r="B134" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>492062</v>
+        <v>492083</v>
       </c>
       <c r="R134" t="n">
-        <v>7135103</v>
+        <v>7135291</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14776,10 +14776,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730545</v>
+        <v>129730580</v>
       </c>
       <c r="B135" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491983</v>
+        <v>492077</v>
       </c>
       <c r="R135" t="n">
-        <v>7135171</v>
+        <v>7135066</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14878,10 +14878,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730580</v>
+        <v>129730574</v>
       </c>
       <c r="B136" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492077</v>
+        <v>492062</v>
       </c>
       <c r="R136" t="n">
-        <v>7135066</v>
+        <v>7135103</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14980,32 +14980,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129730620</v>
+        <v>129730669</v>
       </c>
       <c r="B137" t="n">
-        <v>57735</v>
+        <v>91761</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15015,10 +15015,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>492351</v>
+        <v>492248</v>
       </c>
       <c r="R137" t="n">
-        <v>7134938</v>
+        <v>7135292</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15051,11 +15051,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15082,10 +15077,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730535</v>
+        <v>129730646</v>
       </c>
       <c r="B138" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15117,10 +15112,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>492065</v>
+        <v>492465</v>
       </c>
       <c r="R138" t="n">
-        <v>7135257</v>
+        <v>7134871</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15187,7 +15182,7 @@
         <v>129730541</v>
       </c>
       <c r="B139" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15286,10 +15281,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730646</v>
+        <v>129730535</v>
       </c>
       <c r="B140" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15321,10 +15316,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492465</v>
+        <v>492065</v>
       </c>
       <c r="R140" t="n">
-        <v>7134871</v>
+        <v>7135257</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15388,32 +15383,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730669</v>
+        <v>129730620</v>
       </c>
       <c r="B141" t="n">
-        <v>91760</v>
+        <v>57736</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15423,10 +15418,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492248</v>
+        <v>492351</v>
       </c>
       <c r="R141" t="n">
-        <v>7135292</v>
+        <v>7134938</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15459,6 +15454,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15485,32 +15485,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730648</v>
+        <v>129730524</v>
       </c>
       <c r="B142" t="n">
-        <v>57735</v>
+        <v>91552</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492457</v>
+        <v>492271</v>
       </c>
       <c r="R142" t="n">
-        <v>7134863</v>
+        <v>7135240</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15556,11 +15556,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15587,10 +15582,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730616</v>
+        <v>129730655</v>
       </c>
       <c r="B143" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15622,10 +15617,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492343</v>
+        <v>492460</v>
       </c>
       <c r="R143" t="n">
-        <v>7134960</v>
+        <v>7134849</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15689,10 +15684,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730593</v>
+        <v>129730558</v>
       </c>
       <c r="B144" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15724,10 +15719,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>492199</v>
+        <v>492028</v>
       </c>
       <c r="R144" t="n">
-        <v>7135015</v>
+        <v>7135126</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15764,7 +15759,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15791,10 +15786,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730578</v>
+        <v>129730609</v>
       </c>
       <c r="B145" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15826,10 +15821,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>492086</v>
+        <v>492330</v>
       </c>
       <c r="R145" t="n">
-        <v>7135087</v>
+        <v>7134971</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15866,7 +15861,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15893,10 +15888,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730609</v>
+        <v>129730616</v>
       </c>
       <c r="B146" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15928,10 +15923,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>492330</v>
+        <v>492343</v>
       </c>
       <c r="R146" t="n">
-        <v>7134971</v>
+        <v>7134960</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15968,7 +15963,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15995,10 +15990,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730549</v>
+        <v>129730595</v>
       </c>
       <c r="B147" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16030,10 +16025,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491986</v>
+        <v>492208</v>
       </c>
       <c r="R147" t="n">
-        <v>7135153</v>
+        <v>7135012</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16070,7 +16065,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16097,10 +16092,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730655</v>
+        <v>129730549</v>
       </c>
       <c r="B148" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16132,10 +16127,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>492460</v>
+        <v>491986</v>
       </c>
       <c r="R148" t="n">
-        <v>7134849</v>
+        <v>7135153</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16199,10 +16194,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730595</v>
+        <v>129730648</v>
       </c>
       <c r="B149" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16234,10 +16229,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>492208</v>
+        <v>492457</v>
       </c>
       <c r="R149" t="n">
-        <v>7135012</v>
+        <v>7134863</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16301,10 +16296,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730558</v>
+        <v>129730593</v>
       </c>
       <c r="B150" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16336,10 +16331,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>492028</v>
+        <v>492199</v>
       </c>
       <c r="R150" t="n">
-        <v>7135126</v>
+        <v>7135015</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16376,7 +16371,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16403,10 +16398,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730525</v>
+        <v>129730578</v>
       </c>
       <c r="B151" t="n">
-        <v>90619</v>
+        <v>57736</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16414,21 +16409,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16438,10 +16433,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>492390</v>
+        <v>492086</v>
       </c>
       <c r="R151" t="n">
-        <v>7135053</v>
+        <v>7135087</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16474,6 +16469,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16500,32 +16500,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730524</v>
+        <v>129730525</v>
       </c>
       <c r="B152" t="n">
-        <v>91551</v>
+        <v>90620</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16535,10 +16535,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492271</v>
+        <v>492390</v>
       </c>
       <c r="R152" t="n">
-        <v>7135240</v>
+        <v>7135053</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16597,10 +16597,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730668</v>
+        <v>129730601</v>
       </c>
       <c r="B153" t="n">
-        <v>56916</v>
+        <v>57736</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16608,16 +16608,16 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>492293</v>
+        <v>492240</v>
       </c>
       <c r="R153" t="n">
-        <v>7134991</v>
+        <v>7134998</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16668,6 +16668,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16694,10 +16699,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730667</v>
+        <v>129730552</v>
       </c>
       <c r="B154" t="n">
-        <v>56916</v>
+        <v>57736</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16705,16 +16710,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -16729,10 +16734,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>492088</v>
+        <v>492001</v>
       </c>
       <c r="R154" t="n">
-        <v>7135189</v>
+        <v>7135144</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16765,6 +16770,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16791,10 +16801,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730544</v>
+        <v>129730571</v>
       </c>
       <c r="B155" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16826,10 +16836,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>491998</v>
+        <v>492057</v>
       </c>
       <c r="R155" t="n">
-        <v>7135201</v>
+        <v>7135106</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16866,7 +16876,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16893,10 +16903,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129730590</v>
+        <v>129730544</v>
       </c>
       <c r="B156" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16928,10 +16938,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>492184</v>
+        <v>491998</v>
       </c>
       <c r="R156" t="n">
-        <v>7135029</v>
+        <v>7135201</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16995,10 +17005,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730601</v>
+        <v>129730564</v>
       </c>
       <c r="B157" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17030,10 +17040,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>492240</v>
+        <v>492039</v>
       </c>
       <c r="R157" t="n">
-        <v>7134998</v>
+        <v>7135120</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17070,7 +17080,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17097,10 +17107,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730552</v>
+        <v>129730590</v>
       </c>
       <c r="B158" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17132,10 +17142,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>492001</v>
+        <v>492184</v>
       </c>
       <c r="R158" t="n">
-        <v>7135144</v>
+        <v>7135029</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17199,10 +17209,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730564</v>
+        <v>129730634</v>
       </c>
       <c r="B159" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17234,10 +17244,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>492039</v>
+        <v>492423</v>
       </c>
       <c r="R159" t="n">
-        <v>7135120</v>
+        <v>7134915</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17301,10 +17311,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730571</v>
+        <v>129730668</v>
       </c>
       <c r="B160" t="n">
-        <v>57735</v>
+        <v>56917</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17312,16 +17322,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -17336,10 +17346,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>492057</v>
+        <v>492293</v>
       </c>
       <c r="R160" t="n">
-        <v>7135106</v>
+        <v>7134991</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17372,11 +17382,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17403,10 +17408,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129730634</v>
+        <v>129730667</v>
       </c>
       <c r="B161" t="n">
-        <v>57735</v>
+        <v>56917</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17414,16 +17419,16 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -17438,10 +17443,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>492423</v>
+        <v>492088</v>
       </c>
       <c r="R161" t="n">
-        <v>7134915</v>
+        <v>7135189</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17474,11 +17479,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17505,10 +17505,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730527</v>
+        <v>129730547</v>
       </c>
       <c r="B162" t="n">
-        <v>90619</v>
+        <v>57736</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17516,21 +17516,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17540,10 +17540,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>492267</v>
+        <v>491981</v>
       </c>
       <c r="R162" t="n">
-        <v>7135233</v>
+        <v>7135158</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17576,6 +17576,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17602,10 +17607,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730547</v>
+        <v>129730546</v>
       </c>
       <c r="B163" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17637,7 +17642,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>491981</v>
+        <v>491985</v>
       </c>
       <c r="R163" t="n">
         <v>7135158</v>
@@ -17677,7 +17682,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17707,7 +17712,7 @@
         <v>129730556</v>
       </c>
       <c r="B164" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17806,10 +17811,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730591</v>
+        <v>129730592</v>
       </c>
       <c r="B165" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17841,7 +17846,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>492194</v>
+        <v>492195</v>
       </c>
       <c r="R165" t="n">
         <v>7135016</v>
@@ -17881,7 +17886,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17908,10 +17913,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730546</v>
+        <v>129730591</v>
       </c>
       <c r="B166" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17943,10 +17948,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>491985</v>
+        <v>492194</v>
       </c>
       <c r="R166" t="n">
-        <v>7135158</v>
+        <v>7135016</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17983,7 +17988,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18010,10 +18015,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730592</v>
+        <v>129730527</v>
       </c>
       <c r="B167" t="n">
-        <v>57735</v>
+        <v>90620</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18021,21 +18026,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18045,10 +18050,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492195</v>
+        <v>492267</v>
       </c>
       <c r="R167" t="n">
-        <v>7135016</v>
+        <v>7135233</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18081,11 +18086,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18112,10 +18112,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129730554</v>
+        <v>129730652</v>
       </c>
       <c r="B168" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18147,10 +18147,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>492027</v>
+        <v>492473</v>
       </c>
       <c r="R168" t="n">
-        <v>7135130</v>
+        <v>7134862</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18217,7 +18217,7 @@
         <v>129730605</v>
       </c>
       <c r="B169" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18316,10 +18316,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129730652</v>
+        <v>129730554</v>
       </c>
       <c r="B170" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18351,10 +18351,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>492473</v>
+        <v>492027</v>
       </c>
       <c r="R170" t="n">
-        <v>7134862</v>
+        <v>7135130</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18421,7 +18421,7 @@
         <v>129730588</v>
       </c>
       <c r="B171" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18520,10 +18520,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129730530</v>
+        <v>129730567</v>
       </c>
       <c r="B172" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18555,10 +18555,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>492078</v>
+        <v>492043</v>
       </c>
       <c r="R172" t="n">
-        <v>7135290</v>
+        <v>7135115</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18622,10 +18622,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129730567</v>
+        <v>129730649</v>
       </c>
       <c r="B173" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>492043</v>
+        <v>492466</v>
       </c>
       <c r="R173" t="n">
-        <v>7135115</v>
+        <v>7134866</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18727,7 +18727,7 @@
         <v>129730555</v>
       </c>
       <c r="B174" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18826,10 +18826,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129730649</v>
+        <v>129730581</v>
       </c>
       <c r="B175" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>492466</v>
+        <v>492090</v>
       </c>
       <c r="R175" t="n">
-        <v>7134866</v>
+        <v>7135062</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18928,10 +18928,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129730581</v>
+        <v>129730530</v>
       </c>
       <c r="B176" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18963,10 +18963,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>492090</v>
+        <v>492078</v>
       </c>
       <c r="R176" t="n">
-        <v>7135062</v>
+        <v>7135290</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19030,10 +19030,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129730607</v>
+        <v>129730586</v>
       </c>
       <c r="B177" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19065,10 +19065,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>492312</v>
+        <v>492124</v>
       </c>
       <c r="R177" t="n">
-        <v>7134971</v>
+        <v>7135046</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19132,10 +19132,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129730644</v>
+        <v>129730612</v>
       </c>
       <c r="B178" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19167,10 +19167,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>492462</v>
+        <v>492333</v>
       </c>
       <c r="R178" t="n">
-        <v>7134869</v>
+        <v>7134969</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19234,10 +19234,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129730612</v>
+        <v>129730623</v>
       </c>
       <c r="B179" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19269,10 +19269,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>492333</v>
+        <v>492353</v>
       </c>
       <c r="R179" t="n">
-        <v>7134969</v>
+        <v>7134936</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19336,10 +19336,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129730586</v>
+        <v>129730607</v>
       </c>
       <c r="B180" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19371,10 +19371,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>492124</v>
+        <v>492312</v>
       </c>
       <c r="R180" t="n">
-        <v>7135046</v>
+        <v>7134971</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19438,10 +19438,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129730623</v>
+        <v>129730610</v>
       </c>
       <c r="B181" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>492353</v>
+        <v>492330</v>
       </c>
       <c r="R181" t="n">
-        <v>7134936</v>
+        <v>7134972</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19540,10 +19540,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129730610</v>
+        <v>129730644</v>
       </c>
       <c r="B182" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>492330</v>
+        <v>492462</v>
       </c>
       <c r="R182" t="n">
-        <v>7134972</v>
+        <v>7134869</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19642,10 +19642,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129730550</v>
+        <v>129730557</v>
       </c>
       <c r="B183" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19677,10 +19677,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>491991</v>
+        <v>492026</v>
       </c>
       <c r="R183" t="n">
-        <v>7135149</v>
+        <v>7135131</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19717,7 +19717,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19744,10 +19744,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129730653</v>
+        <v>129730537</v>
       </c>
       <c r="B184" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19779,10 +19779,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>492468</v>
+        <v>492037</v>
       </c>
       <c r="R184" t="n">
-        <v>7134851</v>
+        <v>7135230</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19846,10 +19846,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129730577</v>
+        <v>129730572</v>
       </c>
       <c r="B185" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>492066</v>
+        <v>492060</v>
       </c>
       <c r="R185" t="n">
-        <v>7135097</v>
+        <v>7135105</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19948,10 +19948,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730636</v>
+        <v>129730653</v>
       </c>
       <c r="B186" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19983,10 +19983,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492435</v>
+        <v>492468</v>
       </c>
       <c r="R186" t="n">
-        <v>7134917</v>
+        <v>7134851</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20023,7 +20023,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20050,10 +20050,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730557</v>
+        <v>129730636</v>
       </c>
       <c r="B187" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20085,10 +20085,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>492026</v>
+        <v>492435</v>
       </c>
       <c r="R187" t="n">
-        <v>7135131</v>
+        <v>7134917</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20152,10 +20152,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730537</v>
+        <v>129730550</v>
       </c>
       <c r="B188" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20187,10 +20187,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>492037</v>
+        <v>491991</v>
       </c>
       <c r="R188" t="n">
-        <v>7135230</v>
+        <v>7135149</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20254,10 +20254,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129730654</v>
+        <v>129730577</v>
       </c>
       <c r="B189" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20289,10 +20289,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>492462</v>
+        <v>492066</v>
       </c>
       <c r="R189" t="n">
-        <v>7134847</v>
+        <v>7135097</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20329,7 +20329,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20356,10 +20356,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730572</v>
+        <v>129730654</v>
       </c>
       <c r="B190" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20391,10 +20391,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>492060</v>
+        <v>492462</v>
       </c>
       <c r="R190" t="n">
-        <v>7135105</v>
+        <v>7134847</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20461,7 +20461,7 @@
         <v>129730660</v>
       </c>
       <c r="B191" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>129730674</v>
       </c>
       <c r="B192" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20649,10 +20649,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730641</v>
+        <v>129730596</v>
       </c>
       <c r="B193" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492462</v>
+        <v>492210</v>
       </c>
       <c r="R193" t="n">
-        <v>7134883</v>
+        <v>7135013</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20754,7 +20754,7 @@
         <v>129730621</v>
       </c>
       <c r="B194" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20853,10 +20853,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730613</v>
+        <v>129730553</v>
       </c>
       <c r="B195" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20888,10 +20888,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492341</v>
+        <v>492008</v>
       </c>
       <c r="R195" t="n">
-        <v>7134968</v>
+        <v>7135137</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20955,10 +20955,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730570</v>
+        <v>129730642</v>
       </c>
       <c r="B196" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20990,10 +20990,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492057</v>
+        <v>492466</v>
       </c>
       <c r="R196" t="n">
-        <v>7135109</v>
+        <v>7134877</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21057,10 +21057,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129730642</v>
+        <v>129730613</v>
       </c>
       <c r="B197" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21092,10 +21092,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>492466</v>
+        <v>492341</v>
       </c>
       <c r="R197" t="n">
-        <v>7134877</v>
+        <v>7134968</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21159,10 +21159,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730560</v>
+        <v>129730600</v>
       </c>
       <c r="B198" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21194,10 +21194,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492037</v>
+        <v>492239</v>
       </c>
       <c r="R198" t="n">
-        <v>7135124</v>
+        <v>7134997</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21261,10 +21261,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730651</v>
+        <v>129730560</v>
       </c>
       <c r="B199" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21296,10 +21296,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492474</v>
+        <v>492037</v>
       </c>
       <c r="R199" t="n">
-        <v>7134863</v>
+        <v>7135124</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21363,10 +21363,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730553</v>
+        <v>129730570</v>
       </c>
       <c r="B200" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21398,10 +21398,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492008</v>
+        <v>492057</v>
       </c>
       <c r="R200" t="n">
-        <v>7135137</v>
+        <v>7135109</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21465,10 +21465,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730600</v>
+        <v>129730641</v>
       </c>
       <c r="B201" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21500,10 +21500,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492239</v>
+        <v>492462</v>
       </c>
       <c r="R201" t="n">
-        <v>7134997</v>
+        <v>7134883</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21567,10 +21567,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730596</v>
+        <v>129730651</v>
       </c>
       <c r="B202" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492210</v>
+        <v>492474</v>
       </c>
       <c r="R202" t="n">
-        <v>7135013</v>
+        <v>7134863</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21672,7 +21672,7 @@
         <v>129730666</v>
       </c>
       <c r="B203" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -2622,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726723</v>
+        <v>129726736</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>83045</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492370</v>
+        <v>492194</v>
       </c>
       <c r="R19" t="n">
-        <v>7135127</v>
+        <v>7135150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,45 +2729,65 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726744</v>
+        <v>129728246</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492318</v>
+        <v>492341</v>
       </c>
       <c r="R20" t="n">
-        <v>7135032</v>
+        <v>7134976</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2797,19 +2817,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:14</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,50 +2833,56 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726736</v>
+        <v>129726716</v>
       </c>
       <c r="B21" t="n">
-        <v>83045</v>
+        <v>97646</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2871,10 +2892,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492194</v>
+        <v>492599</v>
       </c>
       <c r="R21" t="n">
-        <v>7135150</v>
+        <v>7134962</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2916,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2943,65 +2964,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129728246</v>
+        <v>129726723</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492341</v>
+        <v>492370</v>
       </c>
       <c r="R22" t="n">
-        <v>7134976</v>
+        <v>7135127</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,14 +3032,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,56 +3053,50 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726716</v>
+        <v>129726744</v>
       </c>
       <c r="B23" t="n">
-        <v>97646</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492599</v>
+        <v>492318</v>
       </c>
       <c r="R23" t="n">
-        <v>7134962</v>
+        <v>7135032</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4284,45 +4284,65 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129728254</v>
+        <v>129728243</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492116</v>
+        <v>492168</v>
       </c>
       <c r="R34" t="n">
-        <v>7135129</v>
+        <v>7135133</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4359,7 +4379,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4368,8 +4388,14 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4386,10 +4412,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129728255</v>
+        <v>129726720</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>78089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,21 +4423,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4421,10 +4447,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492112</v>
+        <v>492458</v>
       </c>
       <c r="R35" t="n">
-        <v>7135077</v>
+        <v>7135104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4454,14 +4480,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4476,19 +4507,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129728256</v>
+        <v>129728254</v>
       </c>
       <c r="B36" t="n">
         <v>79076</v>
@@ -4523,10 +4554,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492217</v>
+        <v>492116</v>
       </c>
       <c r="R36" t="n">
-        <v>7135029</v>
+        <v>7135129</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4621,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726729</v>
+        <v>129728255</v>
       </c>
       <c r="B37" t="n">
         <v>79076</v>
@@ -4625,10 +4656,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492180</v>
+        <v>492112</v>
       </c>
       <c r="R37" t="n">
-        <v>7135242</v>
+        <v>7135077</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4658,19 +4689,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4685,19 +4711,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726750</v>
+        <v>129728256</v>
       </c>
       <c r="B38" t="n">
         <v>79076</v>
@@ -4732,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492416</v>
+        <v>492217</v>
       </c>
       <c r="R38" t="n">
-        <v>7135000</v>
+        <v>7135029</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4765,19 +4791,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:01</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:01</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4792,22 +4813,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726720</v>
+        <v>129726729</v>
       </c>
       <c r="B39" t="n">
-        <v>78089</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4815,21 +4836,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4839,10 +4860,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492458</v>
+        <v>492180</v>
       </c>
       <c r="R39" t="n">
-        <v>7135104</v>
+        <v>7135242</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4874,7 +4895,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4884,7 +4905,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4911,65 +4932,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129728243</v>
+        <v>129726750</v>
       </c>
       <c r="B40" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492168</v>
+        <v>492416</v>
       </c>
       <c r="R40" t="n">
-        <v>7135133</v>
+        <v>7135000</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4999,14 +5000,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5015,76 +5021,63 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129728236</v>
+        <v>129726735</v>
       </c>
       <c r="B41" t="n">
-        <v>80210</v>
+        <v>83040</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492236</v>
+        <v>492209</v>
       </c>
       <c r="R41" t="n">
-        <v>7135033</v>
+        <v>7135176</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5114,14 +5107,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På en klen levande sälg.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5130,89 +5128,70 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129726735</v>
+        <v>129728236</v>
       </c>
       <c r="B42" t="n">
-        <v>83040</v>
+        <v>80210</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>310</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492209</v>
+        <v>492236</v>
       </c>
       <c r="R42" t="n">
-        <v>7135176</v>
+        <v>7135033</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5242,19 +5221,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:39</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:39</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5263,18 +5237,44 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5946,45 +5946,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129728241</v>
+        <v>129728262</v>
       </c>
       <c r="B49" t="n">
-        <v>80209</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492451</v>
+        <v>492479</v>
       </c>
       <c r="R49" t="n">
-        <v>7134904</v>
+        <v>7134899</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6019,14 +6022,45 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6043,7 +6077,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129728262</v>
+        <v>129726721</v>
       </c>
       <c r="B50" t="n">
         <v>79076</v>
@@ -6072,19 +6106,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492479</v>
+        <v>492421</v>
       </c>
       <c r="R50" t="n">
-        <v>7134899</v>
+        <v>7135113</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6114,14 +6145,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran i gammal barrblandskog.</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6130,76 +6166,50 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129726721</v>
+        <v>129728241</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>80209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6209,10 +6219,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492421</v>
+        <v>492451</v>
       </c>
       <c r="R51" t="n">
-        <v>7135113</v>
+        <v>7134904</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6242,19 +6252,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6269,12 +6269,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -7043,10 +7043,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129726728</v>
+        <v>129728250</v>
       </c>
       <c r="B59" t="n">
-        <v>78089</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7054,21 +7054,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492179</v>
+        <v>492572</v>
       </c>
       <c r="R59" t="n">
-        <v>7135241</v>
+        <v>7135009</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7111,19 +7111,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7138,19 +7133,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129728250</v>
+        <v>129726725</v>
       </c>
       <c r="B60" t="n">
         <v>79076</v>
@@ -7185,10 +7180,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492572</v>
+        <v>492304</v>
       </c>
       <c r="R60" t="n">
-        <v>7135009</v>
+        <v>7135246</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7218,14 +7213,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7240,22 +7240,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129726725</v>
+        <v>129726753</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7263,21 +7263,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492304</v>
+        <v>492496</v>
       </c>
       <c r="R61" t="n">
-        <v>7135246</v>
+        <v>7134904</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726753</v>
+        <v>129726728</v>
       </c>
       <c r="B62" t="n">
-        <v>78834</v>
+        <v>78089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492496</v>
+        <v>492179</v>
       </c>
       <c r="R62" t="n">
-        <v>7134904</v>
+        <v>7135241</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7777,45 +7777,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129728240</v>
+        <v>129726724</v>
       </c>
       <c r="B66" t="n">
-        <v>80209</v>
+        <v>57896</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492405</v>
+        <v>492343</v>
       </c>
       <c r="R66" t="n">
-        <v>7134981</v>
+        <v>7135242</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7845,14 +7854,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7867,66 +7881,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129726724</v>
+        <v>129726730</v>
       </c>
       <c r="B67" t="n">
-        <v>57896</v>
+        <v>92306</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492343</v>
+        <v>492124</v>
       </c>
       <c r="R67" t="n">
-        <v>7135242</v>
+        <v>7135171</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7958,7 +7963,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7968,7 +7973,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7995,10 +8000,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726730</v>
+        <v>129728240</v>
       </c>
       <c r="B68" t="n">
-        <v>92306</v>
+        <v>80209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8006,21 +8011,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8030,10 +8035,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492124</v>
+        <v>492405</v>
       </c>
       <c r="R68" t="n">
-        <v>7135171</v>
+        <v>7134981</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8063,19 +8068,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:53</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8090,12 +8090,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -9214,32 +9214,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730675</v>
+        <v>129730665</v>
       </c>
       <c r="B80" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492075</v>
+        <v>492046</v>
       </c>
       <c r="R80" t="n">
-        <v>7135214</v>
+        <v>7135177</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9285,6 +9285,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9311,10 +9316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730635</v>
+        <v>129730675</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9322,21 +9327,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9346,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492424</v>
+        <v>492075</v>
       </c>
       <c r="R81" t="n">
-        <v>7134911</v>
+        <v>7135214</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9382,11 +9387,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9413,7 +9413,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730639</v>
+        <v>129730635</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492439</v>
+        <v>492424</v>
       </c>
       <c r="R82" t="n">
-        <v>7134899</v>
+        <v>7134911</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9515,7 +9515,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730562</v>
+        <v>129730639</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492037</v>
+        <v>492439</v>
       </c>
       <c r="R83" t="n">
-        <v>7135120</v>
+        <v>7134899</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9617,7 +9617,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730575</v>
+        <v>129730562</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492063</v>
+        <v>492037</v>
       </c>
       <c r="R84" t="n">
-        <v>7135101</v>
+        <v>7135120</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9692,7 +9692,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9719,7 +9719,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730603</v>
+        <v>129730575</v>
       </c>
       <c r="B85" t="n">
         <v>57736</v>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492265</v>
+        <v>492063</v>
       </c>
       <c r="R85" t="n">
-        <v>7134987</v>
+        <v>7135101</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9821,7 +9821,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129730594</v>
+        <v>129730603</v>
       </c>
       <c r="B86" t="n">
         <v>57736</v>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492205</v>
+        <v>492265</v>
       </c>
       <c r="R86" t="n">
-        <v>7135012</v>
+        <v>7134987</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9923,7 +9923,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129730599</v>
+        <v>129730594</v>
       </c>
       <c r="B87" t="n">
         <v>57736</v>
@@ -9958,10 +9958,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492216</v>
+        <v>492205</v>
       </c>
       <c r="R87" t="n">
-        <v>7135002</v>
+        <v>7135012</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10025,7 +10025,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730630</v>
+        <v>129730599</v>
       </c>
       <c r="B88" t="n">
         <v>57736</v>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492411</v>
+        <v>492216</v>
       </c>
       <c r="R88" t="n">
-        <v>7134926</v>
+        <v>7135002</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10127,32 +10127,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129730665</v>
+        <v>129730630</v>
       </c>
       <c r="B89" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10162,10 +10162,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492046</v>
+        <v>492411</v>
       </c>
       <c r="R89" t="n">
-        <v>7135177</v>
+        <v>7134926</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>8st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10734,7 +10734,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730650</v>
+        <v>129730606</v>
       </c>
       <c r="B95" t="n">
         <v>57736</v>
@@ -10769,10 +10769,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492473</v>
+        <v>492303</v>
       </c>
       <c r="R95" t="n">
-        <v>7134864</v>
+        <v>7134972</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730606</v>
+        <v>129730619</v>
       </c>
       <c r="B97" t="n">
         <v>57736</v>
@@ -10965,10 +10965,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492303</v>
+        <v>492353</v>
       </c>
       <c r="R97" t="n">
-        <v>7134972</v>
+        <v>7134945</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11032,7 +11032,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129730619</v>
+        <v>129730650</v>
       </c>
       <c r="B98" t="n">
         <v>57736</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492353</v>
+        <v>492473</v>
       </c>
       <c r="R98" t="n">
-        <v>7134945</v>
+        <v>7134864</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11838,10 +11838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730529</v>
+        <v>129730521</v>
       </c>
       <c r="B106" t="n">
-        <v>57736</v>
+        <v>83045</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492088</v>
+        <v>492100</v>
       </c>
       <c r="R106" t="n">
-        <v>7135198</v>
+        <v>7135216</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11909,11 +11909,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11940,7 +11935,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730631</v>
+        <v>129730529</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11975,10 +11970,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492409</v>
+        <v>492088</v>
       </c>
       <c r="R107" t="n">
-        <v>7134918</v>
+        <v>7135198</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12015,7 +12010,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12042,7 +12037,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730532</v>
+        <v>129730631</v>
       </c>
       <c r="B108" t="n">
         <v>57736</v>
@@ -12077,10 +12072,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492082</v>
+        <v>492409</v>
       </c>
       <c r="R108" t="n">
-        <v>7135294</v>
+        <v>7134918</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12144,7 +12139,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730576</v>
+        <v>129730532</v>
       </c>
       <c r="B109" t="n">
         <v>57736</v>
@@ -12179,10 +12174,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492066</v>
+        <v>492082</v>
       </c>
       <c r="R109" t="n">
-        <v>7135093</v>
+        <v>7135294</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12219,7 +12214,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12246,7 +12241,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730559</v>
+        <v>129730576</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12281,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492032</v>
+        <v>492066</v>
       </c>
       <c r="R110" t="n">
-        <v>7135120</v>
+        <v>7135093</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12348,10 +12343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730521</v>
+        <v>129730559</v>
       </c>
       <c r="B111" t="n">
-        <v>83045</v>
+        <v>57736</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12359,21 +12354,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12383,10 +12378,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492100</v>
+        <v>492032</v>
       </c>
       <c r="R111" t="n">
-        <v>7135216</v>
+        <v>7135120</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12419,6 +12414,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14475,32 +14475,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730670</v>
+        <v>129730545</v>
       </c>
       <c r="B132" t="n">
-        <v>91761</v>
+        <v>57736</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>492219</v>
+        <v>491983</v>
       </c>
       <c r="R132" t="n">
-        <v>7135247</v>
+        <v>7135171</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14546,6 +14546,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14572,7 +14577,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730545</v>
+        <v>129730531</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -14607,10 +14612,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491983</v>
+        <v>492083</v>
       </c>
       <c r="R133" t="n">
-        <v>7135171</v>
+        <v>7135291</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14674,7 +14679,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730531</v>
+        <v>129730580</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -14709,10 +14714,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>492083</v>
+        <v>492077</v>
       </c>
       <c r="R134" t="n">
-        <v>7135291</v>
+        <v>7135066</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14776,7 +14781,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730580</v>
+        <v>129730574</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -14811,10 +14816,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>492077</v>
+        <v>492062</v>
       </c>
       <c r="R135" t="n">
-        <v>7135066</v>
+        <v>7135103</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14878,32 +14883,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730574</v>
+        <v>129730670</v>
       </c>
       <c r="B136" t="n">
-        <v>57736</v>
+        <v>91761</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14913,10 +14918,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492062</v>
+        <v>492219</v>
       </c>
       <c r="R136" t="n">
-        <v>7135103</v>
+        <v>7135247</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14949,11 +14954,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14980,32 +14980,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129730669</v>
+        <v>129730646</v>
       </c>
       <c r="B137" t="n">
-        <v>91761</v>
+        <v>57736</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15015,10 +15015,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>492248</v>
+        <v>492465</v>
       </c>
       <c r="R137" t="n">
-        <v>7135292</v>
+        <v>7134871</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15051,6 +15051,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15077,7 +15082,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730646</v>
+        <v>129730541</v>
       </c>
       <c r="B138" t="n">
         <v>57736</v>
@@ -15112,10 +15117,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>492465</v>
+        <v>492004</v>
       </c>
       <c r="R138" t="n">
-        <v>7134871</v>
+        <v>7135207</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15179,7 +15184,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730541</v>
+        <v>129730535</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -15214,10 +15219,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492004</v>
+        <v>492065</v>
       </c>
       <c r="R139" t="n">
-        <v>7135207</v>
+        <v>7135257</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15281,7 +15286,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730535</v>
+        <v>129730620</v>
       </c>
       <c r="B140" t="n">
         <v>57736</v>
@@ -15316,10 +15321,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492065</v>
+        <v>492351</v>
       </c>
       <c r="R140" t="n">
-        <v>7135257</v>
+        <v>7134938</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15383,32 +15388,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730620</v>
+        <v>129730669</v>
       </c>
       <c r="B141" t="n">
-        <v>57736</v>
+        <v>91761</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15418,10 +15423,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492351</v>
+        <v>492248</v>
       </c>
       <c r="R141" t="n">
-        <v>7134938</v>
+        <v>7135292</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15454,11 +15459,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17505,10 +17505,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730547</v>
+        <v>129730527</v>
       </c>
       <c r="B162" t="n">
-        <v>57736</v>
+        <v>90620</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17516,21 +17516,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17540,10 +17540,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>491981</v>
+        <v>492267</v>
       </c>
       <c r="R162" t="n">
-        <v>7135158</v>
+        <v>7135233</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17576,11 +17576,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17607,7 +17602,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730546</v>
+        <v>129730547</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -17642,7 +17637,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>491985</v>
+        <v>491981</v>
       </c>
       <c r="R163" t="n">
         <v>7135158</v>
@@ -17682,7 +17677,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17709,7 +17704,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730556</v>
+        <v>129730546</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -17744,10 +17739,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>492024</v>
+        <v>491985</v>
       </c>
       <c r="R164" t="n">
-        <v>7135131</v>
+        <v>7135158</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17784,7 +17779,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17811,7 +17806,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730592</v>
+        <v>129730556</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -17846,10 +17841,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>492195</v>
+        <v>492024</v>
       </c>
       <c r="R165" t="n">
-        <v>7135016</v>
+        <v>7135131</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17886,7 +17881,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17913,7 +17908,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730591</v>
+        <v>129730592</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -17948,7 +17943,7 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>492194</v>
+        <v>492195</v>
       </c>
       <c r="R166" t="n">
         <v>7135016</v>
@@ -17988,7 +17983,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18015,10 +18010,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730527</v>
+        <v>129730591</v>
       </c>
       <c r="B167" t="n">
-        <v>90620</v>
+        <v>57736</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18026,21 +18021,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18050,10 +18045,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492267</v>
+        <v>492194</v>
       </c>
       <c r="R167" t="n">
-        <v>7135233</v>
+        <v>7135016</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18086,6 +18081,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19642,10 +19642,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129730557</v>
+        <v>129730660</v>
       </c>
       <c r="B183" t="n">
-        <v>57736</v>
+        <v>91608</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19653,23 +19653,19 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
@@ -19677,10 +19673,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>492026</v>
+        <v>492059</v>
       </c>
       <c r="R183" t="n">
-        <v>7135131</v>
+        <v>7135168</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19707,17 +19703,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19726,6 +19717,7 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19744,7 +19736,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129730537</v>
+        <v>129730557</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -19779,10 +19771,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>492037</v>
+        <v>492026</v>
       </c>
       <c r="R184" t="n">
-        <v>7135230</v>
+        <v>7135131</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19846,7 +19838,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129730572</v>
+        <v>129730537</v>
       </c>
       <c r="B185" t="n">
         <v>57736</v>
@@ -19881,10 +19873,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>492060</v>
+        <v>492037</v>
       </c>
       <c r="R185" t="n">
-        <v>7135105</v>
+        <v>7135230</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19921,7 +19913,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19948,7 +19940,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730653</v>
+        <v>129730572</v>
       </c>
       <c r="B186" t="n">
         <v>57736</v>
@@ -19983,10 +19975,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492468</v>
+        <v>492060</v>
       </c>
       <c r="R186" t="n">
-        <v>7134851</v>
+        <v>7135105</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20023,7 +20015,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20050,7 +20042,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730636</v>
+        <v>129730653</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -20085,10 +20077,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>492435</v>
+        <v>492468</v>
       </c>
       <c r="R187" t="n">
-        <v>7134917</v>
+        <v>7134851</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20125,7 +20117,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20152,7 +20144,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730550</v>
+        <v>129730636</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -20187,10 +20179,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>491991</v>
+        <v>492435</v>
       </c>
       <c r="R188" t="n">
-        <v>7135149</v>
+        <v>7134917</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20254,7 +20246,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129730577</v>
+        <v>129730550</v>
       </c>
       <c r="B189" t="n">
         <v>57736</v>
@@ -20289,10 +20281,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>492066</v>
+        <v>491991</v>
       </c>
       <c r="R189" t="n">
-        <v>7135097</v>
+        <v>7135149</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20329,7 +20321,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20356,7 +20348,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730654</v>
+        <v>129730577</v>
       </c>
       <c r="B190" t="n">
         <v>57736</v>
@@ -20391,10 +20383,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>492462</v>
+        <v>492066</v>
       </c>
       <c r="R190" t="n">
-        <v>7134847</v>
+        <v>7135097</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20431,7 +20423,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20458,10 +20450,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129730660</v>
+        <v>129730654</v>
       </c>
       <c r="B191" t="n">
-        <v>91608</v>
+        <v>57736</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20469,19 +20461,23 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
@@ -20489,10 +20485,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>492059</v>
+        <v>492462</v>
       </c>
       <c r="R191" t="n">
-        <v>7135168</v>
+        <v>7134847</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20519,12 +20515,17 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20533,7 +20534,6 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728258</v>
+        <v>129728237</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>80187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,34 +1037,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492272</v>
+        <v>492236</v>
       </c>
       <c r="R5" t="n">
-        <v>7135018</v>
+        <v>7135034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1108,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,8 +1117,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,32 +1161,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726742</v>
+        <v>129728238</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>80214</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,7 +1199,7 @@
         <v>492287</v>
       </c>
       <c r="R6" t="n">
-        <v>7135066</v>
+        <v>7135150</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1229,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1246,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728249</v>
+        <v>129728258</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,19 +1287,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492618</v>
+        <v>492272</v>
       </c>
       <c r="R7" t="n">
-        <v>7134954</v>
+        <v>7135018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,7 +1333,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,34 +1342,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1366,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728237</v>
+        <v>129726742</v>
       </c>
       <c r="B8" t="n">
-        <v>80182</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,41 +1371,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492236</v>
+        <v>492287</v>
       </c>
       <c r="R8" t="n">
-        <v>7135034</v>
+        <v>7135066</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,14 +1428,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På en klen levande sälg.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,54 +1449,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726748</v>
+        <v>129728249</v>
       </c>
       <c r="B9" t="n">
-        <v>78089</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,34 +1478,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492403</v>
+        <v>492618</v>
       </c>
       <c r="R9" t="n">
-        <v>7135004</v>
+        <v>7134954</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,19 +1538,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:04</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,50 +1554,76 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129728238</v>
+        <v>129726749</v>
       </c>
       <c r="B10" t="n">
-        <v>80209</v>
+        <v>83050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492287</v>
+        <v>492403</v>
       </c>
       <c r="R10" t="n">
-        <v>7135150</v>
+        <v>7135004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,9 +1666,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726749</v>
+        <v>129726748</v>
       </c>
       <c r="B11" t="n">
-        <v>83045</v>
+        <v>78094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,7 +1815,7 @@
         <v>129728251</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>129728261</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>129726752</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>129726741</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129726738</v>
       </c>
       <c r="B16" t="n">
-        <v>83045</v>
+        <v>83050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>129728247</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129728244</v>
       </c>
       <c r="B18" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726736</v>
+        <v>129726723</v>
       </c>
       <c r="B19" t="n">
-        <v>83045</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492194</v>
+        <v>492370</v>
       </c>
       <c r="R19" t="n">
-        <v>7135150</v>
+        <v>7135127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,65 +2729,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129728246</v>
+        <v>129726744</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492341</v>
+        <v>492318</v>
       </c>
       <c r="R20" t="n">
-        <v>7134976</v>
+        <v>7135032</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,14 +2797,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,56 +2818,50 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726716</v>
+        <v>129726736</v>
       </c>
       <c r="B21" t="n">
-        <v>97646</v>
+        <v>83050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2892,10 +2871,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492599</v>
+        <v>492194</v>
       </c>
       <c r="R21" t="n">
-        <v>7134962</v>
+        <v>7135150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,7 +2906,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2916,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,45 +2943,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726723</v>
+        <v>129728246</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492370</v>
+        <v>492341</v>
       </c>
       <c r="R22" t="n">
-        <v>7135127</v>
+        <v>7134976</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3032,19 +3031,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3053,50 +3047,56 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726744</v>
+        <v>129726716</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>97651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492318</v>
+        <v>492599</v>
       </c>
       <c r="R23" t="n">
-        <v>7135032</v>
+        <v>7134962</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3181,7 +3181,7 @@
         <v>129728252</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>129728245</v>
       </c>
       <c r="B25" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>129728242</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129726732</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>129728257</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>129726754</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>129726719</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,32 +3959,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726726</v>
+        <v>129726737</v>
       </c>
       <c r="B31" t="n">
-        <v>91761</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492285</v>
+        <v>492228</v>
       </c>
       <c r="R31" t="n">
-        <v>7135248</v>
+        <v>7135126</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,45 +4066,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726737</v>
+        <v>129726722</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492228</v>
+        <v>492376</v>
       </c>
       <c r="R32" t="n">
-        <v>7135126</v>
+        <v>7135128</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4146,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4173,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726722</v>
+        <v>129726726</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>91766</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4184,38 +4188,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492376</v>
+        <v>492285</v>
       </c>
       <c r="R33" t="n">
-        <v>7135128</v>
+        <v>7135248</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4287,7 +4287,7 @@
         <v>129728243</v>
       </c>
       <c r="B34" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>129726720</v>
       </c>
       <c r="B35" t="n">
-        <v>78089</v>
+        <v>78094</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>129728254</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>129728255</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>129728256</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>129726729</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>129726750</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>129726735</v>
       </c>
       <c r="B41" t="n">
-        <v>83040</v>
+        <v>83045</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>129728236</v>
       </c>
       <c r="B42" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>129728253</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>129726740</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>129728234</v>
       </c>
       <c r="B45" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>129726733</v>
       </c>
       <c r="B46" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>129726717</v>
       </c>
       <c r="B47" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>129726751</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5946,48 +5946,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129728262</v>
+        <v>129728241</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>80214</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492479</v>
+        <v>492451</v>
       </c>
       <c r="R49" t="n">
-        <v>7134899</v>
+        <v>7134904</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6022,45 +6019,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran i gammal barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6077,10 +6043,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129726721</v>
+        <v>129728262</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6106,16 +6072,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492421</v>
+        <v>492479</v>
       </c>
       <c r="R50" t="n">
-        <v>7135113</v>
+        <v>7134899</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6145,19 +6114,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,50 +6130,76 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129728241</v>
+        <v>129726721</v>
       </c>
       <c r="B51" t="n">
-        <v>80209</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6219,10 +6209,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492451</v>
+        <v>492421</v>
       </c>
       <c r="R51" t="n">
-        <v>7134904</v>
+        <v>7135113</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6252,9 +6242,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6269,12 +6269,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6284,7 +6284,7 @@
         <v>129726718</v>
       </c>
       <c r="B52" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>129726727</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>129726747</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6602,65 +6602,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129728248</v>
+        <v>129728260</v>
       </c>
       <c r="B55" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492492</v>
+        <v>492378</v>
       </c>
       <c r="R55" t="n">
-        <v>7134909</v>
+        <v>7134955</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6697,7 +6677,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6706,14 +6686,8 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6730,10 +6704,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129728260</v>
+        <v>129726731</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6765,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492378</v>
+        <v>492137</v>
       </c>
       <c r="R56" t="n">
-        <v>7134955</v>
+        <v>7135201</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6798,14 +6772,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6820,22 +6799,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129726731</v>
+        <v>129726734</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>91613</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6843,23 +6822,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6867,10 +6842,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492137</v>
+        <v>492211</v>
       </c>
       <c r="R57" t="n">
-        <v>7135201</v>
+        <v>7135170</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6902,7 +6877,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6912,7 +6887,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6921,6 +6896,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6939,41 +6915,65 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129726734</v>
+        <v>129728248</v>
       </c>
       <c r="B58" t="n">
-        <v>91608</v>
+        <v>98774</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492211</v>
+        <v>492492</v>
       </c>
       <c r="R58" t="n">
-        <v>7135170</v>
+        <v>7134909</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7003,19 +7003,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7028,15 +7023,20 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
         <v>129728250</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>129726725</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7252,10 +7252,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129726753</v>
+        <v>129726728</v>
       </c>
       <c r="B61" t="n">
-        <v>78834</v>
+        <v>78094</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7263,21 +7263,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492496</v>
+        <v>492179</v>
       </c>
       <c r="R61" t="n">
-        <v>7134904</v>
+        <v>7135241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726728</v>
+        <v>129726753</v>
       </c>
       <c r="B62" t="n">
-        <v>78089</v>
+        <v>78839</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492179</v>
+        <v>492496</v>
       </c>
       <c r="R62" t="n">
-        <v>7135241</v>
+        <v>7134904</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7469,7 +7469,7 @@
         <v>129728239</v>
       </c>
       <c r="B63" t="n">
-        <v>80209</v>
+        <v>80214</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,32 +7568,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129728259</v>
+        <v>129726730</v>
       </c>
       <c r="B64" t="n">
-        <v>79076</v>
+        <v>92311</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492317</v>
+        <v>492124</v>
       </c>
       <c r="R64" t="n">
-        <v>7134999</v>
+        <v>7135171</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7636,14 +7636,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7658,22 +7663,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129726745</v>
+        <v>129728259</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7705,10 +7710,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492367</v>
+        <v>492317</v>
       </c>
       <c r="R65" t="n">
-        <v>7135038</v>
+        <v>7134999</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7738,19 +7743,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:12</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7765,22 +7765,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129726724</v>
+        <v>129726745</v>
       </c>
       <c r="B66" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7788,43 +7788,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492343</v>
+        <v>492367</v>
       </c>
       <c r="R66" t="n">
-        <v>7135242</v>
+        <v>7135038</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7856,7 +7847,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7866,7 +7857,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7893,10 +7884,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129726730</v>
+        <v>129728240</v>
       </c>
       <c r="B67" t="n">
-        <v>92306</v>
+        <v>80214</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7904,21 +7895,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7928,10 +7919,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492124</v>
+        <v>492405</v>
       </c>
       <c r="R67" t="n">
-        <v>7135171</v>
+        <v>7134981</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7961,19 +7952,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:53</t>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7988,57 +7974,66 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129728240</v>
+        <v>129726724</v>
       </c>
       <c r="B68" t="n">
-        <v>80209</v>
+        <v>57896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492405</v>
+        <v>492343</v>
       </c>
       <c r="R68" t="n">
-        <v>7134981</v>
+        <v>7135242</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8068,14 +8063,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8090,22 +8090,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730672</v>
+        <v>129730573</v>
       </c>
       <c r="B69" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492334</v>
+        <v>492062</v>
       </c>
       <c r="R69" t="n">
-        <v>7135092</v>
+        <v>7135100</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,6 +8173,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8199,7 +8204,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730573</v>
+        <v>129730584</v>
       </c>
       <c r="B70" t="n">
         <v>57736</v>
@@ -8234,10 +8239,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492062</v>
+        <v>492107</v>
       </c>
       <c r="R70" t="n">
-        <v>7135100</v>
+        <v>7135052</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8274,7 +8279,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8301,7 +8306,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730584</v>
+        <v>129730598</v>
       </c>
       <c r="B71" t="n">
         <v>57736</v>
@@ -8336,10 +8341,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492107</v>
+        <v>492220</v>
       </c>
       <c r="R71" t="n">
-        <v>7135052</v>
+        <v>7135003</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8403,7 +8408,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730598</v>
+        <v>129730615</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -8438,10 +8443,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492220</v>
+        <v>492345</v>
       </c>
       <c r="R72" t="n">
-        <v>7135003</v>
+        <v>7134961</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8478,7 +8483,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8505,10 +8510,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730615</v>
+        <v>129730658</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8516,21 +8521,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8540,10 +8545,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492345</v>
+        <v>492464</v>
       </c>
       <c r="R73" t="n">
-        <v>7134961</v>
+        <v>7135049</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8580,7 +8585,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8607,10 +8612,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730658</v>
+        <v>129730672</v>
       </c>
       <c r="B74" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8618,21 +8623,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8642,10 +8647,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492464</v>
+        <v>492334</v>
       </c>
       <c r="R74" t="n">
-        <v>7135049</v>
+        <v>7135092</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8678,11 +8683,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8712,7 +8712,7 @@
         <v>129730671</v>
       </c>
       <c r="B75" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9214,32 +9214,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730665</v>
+        <v>129730635</v>
       </c>
       <c r="B80" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492046</v>
+        <v>492424</v>
       </c>
       <c r="R80" t="n">
-        <v>7135177</v>
+        <v>7134911</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>8st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730675</v>
+        <v>129730639</v>
       </c>
       <c r="B81" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9327,21 +9327,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492075</v>
+        <v>492439</v>
       </c>
       <c r="R81" t="n">
-        <v>7135214</v>
+        <v>7134899</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9387,6 +9387,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9413,7 +9418,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730635</v>
+        <v>129730562</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -9448,10 +9453,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492424</v>
+        <v>492037</v>
       </c>
       <c r="R82" t="n">
-        <v>7134911</v>
+        <v>7135120</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9515,7 +9520,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730639</v>
+        <v>129730575</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -9550,10 +9555,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492439</v>
+        <v>492063</v>
       </c>
       <c r="R83" t="n">
-        <v>7134899</v>
+        <v>7135101</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9590,7 +9595,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9617,7 +9622,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730562</v>
+        <v>129730603</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -9652,10 +9657,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492037</v>
+        <v>492265</v>
       </c>
       <c r="R84" t="n">
-        <v>7135120</v>
+        <v>7134987</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9719,7 +9724,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730575</v>
+        <v>129730594</v>
       </c>
       <c r="B85" t="n">
         <v>57736</v>
@@ -9754,10 +9759,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492063</v>
+        <v>492205</v>
       </c>
       <c r="R85" t="n">
-        <v>7135101</v>
+        <v>7135012</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9794,7 +9799,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9821,7 +9826,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129730603</v>
+        <v>129730599</v>
       </c>
       <c r="B86" t="n">
         <v>57736</v>
@@ -9856,10 +9861,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492265</v>
+        <v>492216</v>
       </c>
       <c r="R86" t="n">
-        <v>7134987</v>
+        <v>7135002</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9896,7 +9901,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9923,7 +9928,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129730594</v>
+        <v>129730630</v>
       </c>
       <c r="B87" t="n">
         <v>57736</v>
@@ -9958,10 +9963,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492205</v>
+        <v>492411</v>
       </c>
       <c r="R87" t="n">
-        <v>7135012</v>
+        <v>7134926</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10025,10 +10030,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730599</v>
+        <v>129730675</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,21 +10041,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10060,10 +10065,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492216</v>
+        <v>492075</v>
       </c>
       <c r="R88" t="n">
-        <v>7135002</v>
+        <v>7135214</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10096,11 +10101,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10127,32 +10127,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129730630</v>
+        <v>129730665</v>
       </c>
       <c r="B89" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10162,10 +10162,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492411</v>
+        <v>492046</v>
       </c>
       <c r="R89" t="n">
-        <v>7134926</v>
+        <v>7135177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10538,7 +10538,7 @@
         <v>129730663</v>
       </c>
       <c r="B93" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129730522</v>
+        <v>129730606</v>
       </c>
       <c r="B94" t="n">
-        <v>97015</v>
+        <v>57736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10672,10 +10672,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492217</v>
+        <v>492303</v>
       </c>
       <c r="R94" t="n">
-        <v>7135249</v>
+        <v>7134972</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10708,6 +10708,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10734,7 +10739,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730606</v>
+        <v>129730619</v>
       </c>
       <c r="B95" t="n">
         <v>57736</v>
@@ -10769,10 +10774,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492303</v>
+        <v>492353</v>
       </c>
       <c r="R95" t="n">
-        <v>7134972</v>
+        <v>7134945</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10809,7 +10814,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10836,10 +10841,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730661</v>
+        <v>129730650</v>
       </c>
       <c r="B96" t="n">
-        <v>91608</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10847,19 +10852,23 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10867,10 +10876,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492069</v>
+        <v>492473</v>
       </c>
       <c r="R96" t="n">
-        <v>7135162</v>
+        <v>7134864</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10897,12 +10906,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10911,7 +10925,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10930,7 +10943,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730619</v>
+        <v>129730604</v>
       </c>
       <c r="B97" t="n">
         <v>57736</v>
@@ -10965,10 +10978,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492353</v>
+        <v>492297</v>
       </c>
       <c r="R97" t="n">
-        <v>7134945</v>
+        <v>7134975</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11005,7 +11018,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11032,7 +11045,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129730650</v>
+        <v>129730569</v>
       </c>
       <c r="B98" t="n">
         <v>57736</v>
@@ -11067,10 +11080,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492473</v>
+        <v>492054</v>
       </c>
       <c r="R98" t="n">
-        <v>7134864</v>
+        <v>7135107</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11107,7 +11120,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11134,10 +11147,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730604</v>
+        <v>129730522</v>
       </c>
       <c r="B99" t="n">
-        <v>57736</v>
+        <v>97020</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11145,21 +11158,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11169,10 +11182,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492297</v>
+        <v>492217</v>
       </c>
       <c r="R99" t="n">
-        <v>7134975</v>
+        <v>7135249</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11205,11 +11218,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11236,10 +11244,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730569</v>
+        <v>129730661</v>
       </c>
       <c r="B100" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11247,23 +11255,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11271,10 +11275,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492054</v>
+        <v>492069</v>
       </c>
       <c r="R100" t="n">
-        <v>7135107</v>
+        <v>7135162</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11301,17 +11305,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11320,6 +11319,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11341,7 +11341,7 @@
         <v>129730662</v>
       </c>
       <c r="B101" t="n">
-        <v>78089</v>
+        <v>78094</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730656</v>
+        <v>129730523</v>
       </c>
       <c r="B102" t="n">
-        <v>57736</v>
+        <v>97020</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11446,21 +11446,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492466</v>
+        <v>492316</v>
       </c>
       <c r="R102" t="n">
-        <v>7134851</v>
+        <v>7135071</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11506,11 +11506,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11537,7 +11532,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730602</v>
+        <v>129730656</v>
       </c>
       <c r="B103" t="n">
         <v>57736</v>
@@ -11572,10 +11567,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492245</v>
+        <v>492466</v>
       </c>
       <c r="R103" t="n">
-        <v>7134995</v>
+        <v>7134851</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11612,7 +11607,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11639,7 +11634,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730640</v>
+        <v>129730602</v>
       </c>
       <c r="B104" t="n">
         <v>57736</v>
@@ -11674,10 +11669,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492444</v>
+        <v>492245</v>
       </c>
       <c r="R104" t="n">
-        <v>7134887</v>
+        <v>7134995</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11741,10 +11736,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730523</v>
+        <v>129730640</v>
       </c>
       <c r="B105" t="n">
-        <v>97015</v>
+        <v>57736</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11752,21 +11747,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11776,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>492316</v>
+        <v>492444</v>
       </c>
       <c r="R105" t="n">
-        <v>7135071</v>
+        <v>7134887</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11812,6 +11807,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11841,7 +11841,7 @@
         <v>129730521</v>
       </c>
       <c r="B106" t="n">
-        <v>83045</v>
+        <v>83050</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129730526</v>
+        <v>129730528</v>
       </c>
       <c r="B112" t="n">
-        <v>90620</v>
+        <v>57736</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12456,21 +12456,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>492395</v>
+        <v>492476</v>
       </c>
       <c r="R112" t="n">
-        <v>7135064</v>
+        <v>7135072</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12516,6 +12516,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12542,7 +12547,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730528</v>
+        <v>129730632</v>
       </c>
       <c r="B113" t="n">
         <v>57736</v>
@@ -12577,10 +12582,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492476</v>
+        <v>492414</v>
       </c>
       <c r="R113" t="n">
-        <v>7135072</v>
+        <v>7134915</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12644,7 +12649,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730632</v>
+        <v>129730608</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -12679,10 +12684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492414</v>
+        <v>492316</v>
       </c>
       <c r="R114" t="n">
-        <v>7134915</v>
+        <v>7134971</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12746,7 +12751,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730608</v>
+        <v>129730617</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -12781,10 +12786,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492316</v>
+        <v>492349</v>
       </c>
       <c r="R115" t="n">
-        <v>7134971</v>
+        <v>7134943</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12821,7 +12826,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12848,7 +12853,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730617</v>
+        <v>129730579</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -12883,10 +12888,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>492349</v>
+        <v>492080</v>
       </c>
       <c r="R116" t="n">
-        <v>7134943</v>
+        <v>7135064</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12923,7 +12928,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12950,7 +12955,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730579</v>
+        <v>129730624</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -12985,10 +12990,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492080</v>
+        <v>492366</v>
       </c>
       <c r="R117" t="n">
-        <v>7135064</v>
+        <v>7134921</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13052,7 +13057,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730624</v>
+        <v>129730597</v>
       </c>
       <c r="B118" t="n">
         <v>57736</v>
@@ -13087,10 +13092,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492366</v>
+        <v>492213</v>
       </c>
       <c r="R118" t="n">
-        <v>7134921</v>
+        <v>7135010</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13154,10 +13159,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730597</v>
+        <v>129730526</v>
       </c>
       <c r="B119" t="n">
-        <v>57736</v>
+        <v>90625</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13165,21 +13170,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13189,10 +13194,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492213</v>
+        <v>492395</v>
       </c>
       <c r="R119" t="n">
-        <v>7135010</v>
+        <v>7135064</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13225,11 +13230,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13259,7 +13259,7 @@
         <v>129730673</v>
       </c>
       <c r="B120" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>129730670</v>
       </c>
       <c r="B136" t="n">
-        <v>91761</v>
+        <v>91766</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>129730669</v>
       </c>
       <c r="B141" t="n">
-        <v>91761</v>
+        <v>91766</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15485,32 +15485,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730524</v>
+        <v>129730525</v>
       </c>
       <c r="B142" t="n">
-        <v>91552</v>
+        <v>90625</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492271</v>
+        <v>492390</v>
       </c>
       <c r="R142" t="n">
-        <v>7135240</v>
+        <v>7135053</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15582,32 +15582,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730655</v>
+        <v>129730524</v>
       </c>
       <c r="B143" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15617,10 +15617,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492460</v>
+        <v>492271</v>
       </c>
       <c r="R143" t="n">
-        <v>7134849</v>
+        <v>7135240</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15653,11 +15653,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15684,7 +15679,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730558</v>
+        <v>129730655</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -15719,10 +15714,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>492028</v>
+        <v>492460</v>
       </c>
       <c r="R144" t="n">
-        <v>7135126</v>
+        <v>7134849</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15759,7 +15754,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15786,7 +15781,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730609</v>
+        <v>129730558</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -15821,10 +15816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>492330</v>
+        <v>492028</v>
       </c>
       <c r="R145" t="n">
-        <v>7134971</v>
+        <v>7135126</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15888,7 +15883,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730616</v>
+        <v>129730609</v>
       </c>
       <c r="B146" t="n">
         <v>57736</v>
@@ -15923,10 +15918,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>492343</v>
+        <v>492330</v>
       </c>
       <c r="R146" t="n">
-        <v>7134960</v>
+        <v>7134971</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15963,7 +15958,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15990,7 +15985,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730595</v>
+        <v>129730616</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -16025,10 +16020,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>492208</v>
+        <v>492343</v>
       </c>
       <c r="R147" t="n">
-        <v>7135012</v>
+        <v>7134960</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16065,7 +16060,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16092,7 +16087,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730549</v>
+        <v>129730595</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -16127,10 +16122,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491986</v>
+        <v>492208</v>
       </c>
       <c r="R148" t="n">
-        <v>7135153</v>
+        <v>7135012</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16167,7 +16162,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16194,7 +16189,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730648</v>
+        <v>129730549</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -16229,10 +16224,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>492457</v>
+        <v>491986</v>
       </c>
       <c r="R149" t="n">
-        <v>7134863</v>
+        <v>7135153</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16269,7 +16264,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16296,7 +16291,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730593</v>
+        <v>129730648</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -16331,10 +16326,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>492199</v>
+        <v>492457</v>
       </c>
       <c r="R150" t="n">
-        <v>7135015</v>
+        <v>7134863</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16371,7 +16366,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16398,7 +16393,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730578</v>
+        <v>129730593</v>
       </c>
       <c r="B151" t="n">
         <v>57736</v>
@@ -16433,10 +16428,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>492086</v>
+        <v>492199</v>
       </c>
       <c r="R151" t="n">
-        <v>7135087</v>
+        <v>7135015</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16500,10 +16495,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730525</v>
+        <v>129730578</v>
       </c>
       <c r="B152" t="n">
-        <v>90620</v>
+        <v>57736</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16511,21 +16506,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16535,10 +16530,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492390</v>
+        <v>492086</v>
       </c>
       <c r="R152" t="n">
-        <v>7135053</v>
+        <v>7135087</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16571,6 +16566,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17508,7 +17508,7 @@
         <v>129730527</v>
       </c>
       <c r="B162" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>129730660</v>
       </c>
       <c r="B183" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>129730674</v>
       </c>
       <c r="B192" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20649,32 +20649,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730596</v>
+        <v>129730666</v>
       </c>
       <c r="B193" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492210</v>
+        <v>492253</v>
       </c>
       <c r="R193" t="n">
-        <v>7135013</v>
+        <v>7135293</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>7st</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20751,7 +20751,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730621</v>
+        <v>129730553</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -20786,10 +20786,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492355</v>
+        <v>492008</v>
       </c>
       <c r="R194" t="n">
-        <v>7134935</v>
+        <v>7135137</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20853,7 +20853,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730553</v>
+        <v>129730642</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -20888,10 +20888,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492008</v>
+        <v>492466</v>
       </c>
       <c r="R195" t="n">
-        <v>7135137</v>
+        <v>7134877</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20955,7 +20955,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730642</v>
+        <v>129730596</v>
       </c>
       <c r="B196" t="n">
         <v>57736</v>
@@ -20990,10 +20990,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492466</v>
+        <v>492210</v>
       </c>
       <c r="R196" t="n">
-        <v>7134877</v>
+        <v>7135013</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21030,7 +21030,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21567,7 +21567,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730651</v>
+        <v>129730621</v>
       </c>
       <c r="B202" t="n">
         <v>57736</v>
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492474</v>
+        <v>492355</v>
       </c>
       <c r="R202" t="n">
-        <v>7134863</v>
+        <v>7134935</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21642,7 +21642,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21669,32 +21669,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129730666</v>
+        <v>129730651</v>
       </c>
       <c r="B203" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21704,10 +21704,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>492253</v>
+        <v>492474</v>
       </c>
       <c r="R203" t="n">
-        <v>7135293</v>
+        <v>7134863</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21744,7 +21744,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>7st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD203" t="b">

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -2045,45 +2045,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726752</v>
+        <v>129728247</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492482</v>
+        <v>492455</v>
       </c>
       <c r="R14" t="n">
-        <v>7134934</v>
+        <v>7134922</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,19 +2133,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>08:50</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,63 +2149,89 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726741</v>
+        <v>129728244</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492282</v>
+        <v>492133</v>
       </c>
       <c r="R15" t="n">
-        <v>7135069</v>
+        <v>7135159</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,19 +2261,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,28 +2277,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726738</v>
+        <v>129726752</v>
       </c>
       <c r="B16" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,21 +2312,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,10 +2336,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492242</v>
+        <v>492482</v>
       </c>
       <c r="R16" t="n">
-        <v>7135130</v>
+        <v>7134934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,65 +2408,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129728247</v>
+        <v>129726741</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492455</v>
+        <v>492282</v>
       </c>
       <c r="R17" t="n">
-        <v>7134922</v>
+        <v>7135069</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,14 +2476,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,89 +2497,63 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129728244</v>
+        <v>129726738</v>
       </c>
       <c r="B18" t="n">
-        <v>98774</v>
+        <v>83050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492133</v>
+        <v>492242</v>
       </c>
       <c r="R18" t="n">
-        <v>7135159</v>
+        <v>7135130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2582,14 +2583,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,24 +2604,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3959,32 +3959,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726737</v>
+        <v>129726726</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>91766</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492228</v>
+        <v>492285</v>
       </c>
       <c r="R31" t="n">
-        <v>7135126</v>
+        <v>7135248</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,49 +4066,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726722</v>
+        <v>129726737</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492376</v>
+        <v>492228</v>
       </c>
       <c r="R32" t="n">
-        <v>7135128</v>
+        <v>7135126</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4140,7 +4136,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4146,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,10 +4173,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726726</v>
+        <v>129726722</v>
       </c>
       <c r="B33" t="n">
-        <v>91766</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,34 +4184,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492285</v>
+        <v>492376</v>
       </c>
       <c r="R33" t="n">
-        <v>7135248</v>
+        <v>7135128</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,65 +4284,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129728243</v>
+        <v>129728256</v>
       </c>
       <c r="B34" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492168</v>
+        <v>492217</v>
       </c>
       <c r="R34" t="n">
-        <v>7135133</v>
+        <v>7135029</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4379,7 +4359,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4388,14 +4368,8 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4412,10 +4386,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726720</v>
+        <v>129726729</v>
       </c>
       <c r="B35" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4423,21 +4397,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4447,10 +4421,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492458</v>
+        <v>492180</v>
       </c>
       <c r="R35" t="n">
-        <v>7135104</v>
+        <v>7135242</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4482,7 +4456,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4492,7 +4466,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4519,7 +4493,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129728254</v>
+        <v>129726750</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4554,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492116</v>
+        <v>492416</v>
       </c>
       <c r="R36" t="n">
-        <v>7135129</v>
+        <v>7135000</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4587,14 +4561,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4609,57 +4588,77 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129728255</v>
+        <v>129728243</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492112</v>
+        <v>492168</v>
       </c>
       <c r="R37" t="n">
-        <v>7135077</v>
+        <v>7135133</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4696,7 +4695,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4705,8 +4704,14 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4723,10 +4728,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129728256</v>
+        <v>129726720</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,21 +4739,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4758,10 +4763,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492217</v>
+        <v>492458</v>
       </c>
       <c r="R38" t="n">
-        <v>7135029</v>
+        <v>7135104</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4791,14 +4796,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4813,19 +4823,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726729</v>
+        <v>129728254</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4860,10 +4870,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492180</v>
+        <v>492116</v>
       </c>
       <c r="R39" t="n">
-        <v>7135242</v>
+        <v>7135129</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4893,19 +4903,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4920,19 +4925,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129726750</v>
+        <v>129728255</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4967,10 +4972,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492416</v>
+        <v>492112</v>
       </c>
       <c r="R40" t="n">
-        <v>7135000</v>
+        <v>7135077</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5000,19 +5005,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:01</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:01</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5027,12 +5027,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5732,7 +5732,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129726717</v>
+        <v>129726751</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492583</v>
+        <v>492457</v>
       </c>
       <c r="R47" t="n">
-        <v>7134977</v>
+        <v>7134957</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5839,7 +5839,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129726751</v>
+        <v>129726717</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492457</v>
+        <v>492583</v>
       </c>
       <c r="R48" t="n">
-        <v>7134957</v>
+        <v>7134977</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6602,45 +6602,65 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129728260</v>
+        <v>129728248</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492378</v>
+        <v>492492</v>
       </c>
       <c r="R55" t="n">
-        <v>7134955</v>
+        <v>7134909</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6677,7 +6697,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6686,8 +6706,14 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6915,65 +6941,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129728248</v>
+        <v>129728260</v>
       </c>
       <c r="B58" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492492</v>
+        <v>492378</v>
       </c>
       <c r="R58" t="n">
-        <v>7134909</v>
+        <v>7134955</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7010,7 +7016,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7019,14 +7025,8 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7568,32 +7568,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726730</v>
+        <v>129728259</v>
       </c>
       <c r="B64" t="n">
-        <v>92311</v>
+        <v>79081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492124</v>
+        <v>492317</v>
       </c>
       <c r="R64" t="n">
-        <v>7135171</v>
+        <v>7134999</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7636,19 +7636,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:53</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7663,19 +7658,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129728259</v>
+        <v>129726745</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7710,10 +7705,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492317</v>
+        <v>492367</v>
       </c>
       <c r="R65" t="n">
-        <v>7134999</v>
+        <v>7135038</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7743,14 +7738,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7765,22 +7765,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129726745</v>
+        <v>129726724</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7788,34 +7788,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492367</v>
+        <v>492343</v>
       </c>
       <c r="R66" t="n">
-        <v>7135038</v>
+        <v>7135242</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7847,7 +7856,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7857,7 +7866,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7986,54 +7995,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726724</v>
+        <v>129726730</v>
       </c>
       <c r="B68" t="n">
-        <v>57896</v>
+        <v>92311</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492343</v>
+        <v>492124</v>
       </c>
       <c r="R68" t="n">
-        <v>7135242</v>
+        <v>7135171</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730573</v>
+        <v>129730672</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492062</v>
+        <v>492334</v>
       </c>
       <c r="R69" t="n">
-        <v>7135100</v>
+        <v>7135092</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,11 +8173,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8306,7 +8301,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730598</v>
+        <v>129730615</v>
       </c>
       <c r="B71" t="n">
         <v>57736</v>
@@ -8341,10 +8336,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492220</v>
+        <v>492345</v>
       </c>
       <c r="R71" t="n">
-        <v>7135003</v>
+        <v>7134961</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8381,7 +8376,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8408,7 +8403,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730615</v>
+        <v>129730573</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -8443,10 +8438,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492345</v>
+        <v>492062</v>
       </c>
       <c r="R72" t="n">
-        <v>7134961</v>
+        <v>7135100</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8510,10 +8505,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730658</v>
+        <v>129730598</v>
       </c>
       <c r="B73" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8521,21 +8516,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8545,10 +8540,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492464</v>
+        <v>492220</v>
       </c>
       <c r="R73" t="n">
-        <v>7135049</v>
+        <v>7135003</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8585,7 +8580,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8612,10 +8607,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730672</v>
+        <v>129730658</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8623,21 +8618,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8647,10 +8642,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492334</v>
+        <v>492464</v>
       </c>
       <c r="R74" t="n">
-        <v>7135092</v>
+        <v>7135049</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8683,6 +8678,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129730671</v>
+        <v>129730637</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>492379</v>
+        <v>492431</v>
       </c>
       <c r="R75" t="n">
-        <v>7135129</v>
+        <v>7134907</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8780,6 +8780,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8806,7 +8811,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129730629</v>
+        <v>129730551</v>
       </c>
       <c r="B76" t="n">
         <v>57736</v>
@@ -8841,10 +8846,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>492369</v>
+        <v>491997</v>
       </c>
       <c r="R76" t="n">
-        <v>7134915</v>
+        <v>7135143</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8908,7 +8913,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129730637</v>
+        <v>129730645</v>
       </c>
       <c r="B77" t="n">
         <v>57736</v>
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>492431</v>
+        <v>492464</v>
       </c>
       <c r="R77" t="n">
-        <v>7134907</v>
+        <v>7134870</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8983,7 +8988,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9010,10 +9015,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129730551</v>
+        <v>129730671</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9021,21 +9026,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9045,10 +9050,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>491997</v>
+        <v>492379</v>
       </c>
       <c r="R78" t="n">
-        <v>7135143</v>
+        <v>7135129</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9081,11 +9086,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9112,7 +9112,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129730645</v>
+        <v>129730629</v>
       </c>
       <c r="B79" t="n">
         <v>57736</v>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>492464</v>
+        <v>492369</v>
       </c>
       <c r="R79" t="n">
-        <v>7134870</v>
+        <v>7134915</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9214,10 +9214,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730635</v>
+        <v>129730675</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9225,21 +9225,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492424</v>
+        <v>492075</v>
       </c>
       <c r="R80" t="n">
-        <v>7134911</v>
+        <v>7135214</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9285,11 +9285,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,7 +9311,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730639</v>
+        <v>129730635</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -9351,10 +9346,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492439</v>
+        <v>492424</v>
       </c>
       <c r="R81" t="n">
-        <v>7134899</v>
+        <v>7134911</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9418,7 +9413,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730562</v>
+        <v>129730575</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -9453,10 +9448,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492037</v>
+        <v>492063</v>
       </c>
       <c r="R82" t="n">
-        <v>7135120</v>
+        <v>7135101</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9493,7 +9488,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9520,7 +9515,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730575</v>
+        <v>129730639</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -9555,10 +9550,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492063</v>
+        <v>492439</v>
       </c>
       <c r="R83" t="n">
-        <v>7135101</v>
+        <v>7134899</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9595,7 +9590,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10030,10 +10025,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730675</v>
+        <v>129730562</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10041,21 +10036,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10065,10 +10060,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492075</v>
+        <v>492037</v>
       </c>
       <c r="R88" t="n">
-        <v>7135214</v>
+        <v>7135120</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10101,6 +10096,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10229,7 +10229,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129730583</v>
+        <v>129730625</v>
       </c>
       <c r="B90" t="n">
         <v>57736</v>
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492105</v>
+        <v>492367</v>
       </c>
       <c r="R90" t="n">
-        <v>7135051</v>
+        <v>7134920</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10331,7 +10331,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129730625</v>
+        <v>129730565</v>
       </c>
       <c r="B91" t="n">
         <v>57736</v>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492367</v>
+        <v>492040</v>
       </c>
       <c r="R91" t="n">
-        <v>7134920</v>
+        <v>7135117</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10433,7 +10433,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129730565</v>
+        <v>129730583</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>492040</v>
+        <v>492105</v>
       </c>
       <c r="R92" t="n">
-        <v>7135117</v>
+        <v>7135051</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129730606</v>
+        <v>129730522</v>
       </c>
       <c r="B94" t="n">
-        <v>57736</v>
+        <v>97020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10672,10 +10672,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492303</v>
+        <v>492217</v>
       </c>
       <c r="R94" t="n">
-        <v>7134972</v>
+        <v>7135249</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10708,11 +10708,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10739,10 +10734,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730619</v>
+        <v>129730661</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10750,23 +10745,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10774,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492353</v>
+        <v>492069</v>
       </c>
       <c r="R95" t="n">
-        <v>7134945</v>
+        <v>7135162</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10804,17 +10795,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10823,6 +10809,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10841,7 +10828,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730650</v>
+        <v>129730619</v>
       </c>
       <c r="B96" t="n">
         <v>57736</v>
@@ -10876,10 +10863,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492473</v>
+        <v>492353</v>
       </c>
       <c r="R96" t="n">
-        <v>7134864</v>
+        <v>7134945</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10916,7 +10903,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10943,7 +10930,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730604</v>
+        <v>129730650</v>
       </c>
       <c r="B97" t="n">
         <v>57736</v>
@@ -10978,10 +10965,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492297</v>
+        <v>492473</v>
       </c>
       <c r="R97" t="n">
-        <v>7134975</v>
+        <v>7134864</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11147,10 +11134,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730522</v>
+        <v>129730606</v>
       </c>
       <c r="B99" t="n">
-        <v>97020</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11158,21 +11145,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11182,10 +11169,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492217</v>
+        <v>492303</v>
       </c>
       <c r="R99" t="n">
-        <v>7135249</v>
+        <v>7134972</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11218,6 +11205,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11244,10 +11236,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730661</v>
+        <v>129730604</v>
       </c>
       <c r="B100" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11255,19 +11247,23 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11275,10 +11271,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492069</v>
+        <v>492297</v>
       </c>
       <c r="R100" t="n">
-        <v>7135162</v>
+        <v>7134975</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11305,12 +11301,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11319,7 +11320,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730523</v>
+        <v>129730656</v>
       </c>
       <c r="B102" t="n">
-        <v>97020</v>
+        <v>57736</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11446,21 +11446,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492316</v>
+        <v>492466</v>
       </c>
       <c r="R102" t="n">
-        <v>7135071</v>
+        <v>7134851</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11506,6 +11506,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11532,10 +11537,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730656</v>
+        <v>129730523</v>
       </c>
       <c r="B103" t="n">
-        <v>57736</v>
+        <v>97020</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11543,21 +11548,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11567,10 +11572,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492466</v>
+        <v>492316</v>
       </c>
       <c r="R103" t="n">
-        <v>7134851</v>
+        <v>7135071</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11603,11 +11608,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11838,10 +11838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730521</v>
+        <v>129730529</v>
       </c>
       <c r="B106" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492100</v>
+        <v>492088</v>
       </c>
       <c r="R106" t="n">
-        <v>7135216</v>
+        <v>7135198</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11909,6 +11909,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11935,7 +11940,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730529</v>
+        <v>129730532</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11970,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492088</v>
+        <v>492082</v>
       </c>
       <c r="R107" t="n">
-        <v>7135198</v>
+        <v>7135294</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12010,7 +12015,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12037,7 +12042,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730631</v>
+        <v>129730576</v>
       </c>
       <c r="B108" t="n">
         <v>57736</v>
@@ -12072,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492409</v>
+        <v>492066</v>
       </c>
       <c r="R108" t="n">
-        <v>7134918</v>
+        <v>7135093</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12112,7 +12117,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12139,7 +12144,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730532</v>
+        <v>129730559</v>
       </c>
       <c r="B109" t="n">
         <v>57736</v>
@@ -12174,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492082</v>
+        <v>492032</v>
       </c>
       <c r="R109" t="n">
-        <v>7135294</v>
+        <v>7135120</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12214,7 +12219,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,10 +12246,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730576</v>
+        <v>129730521</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>83050</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12252,21 +12257,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12276,10 +12281,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492066</v>
+        <v>492100</v>
       </c>
       <c r="R110" t="n">
-        <v>7135093</v>
+        <v>7135216</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12312,11 +12317,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12343,7 +12343,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730559</v>
+        <v>129730631</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492032</v>
+        <v>492409</v>
       </c>
       <c r="R111" t="n">
-        <v>7135120</v>
+        <v>7134918</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12547,7 +12547,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730632</v>
+        <v>129730617</v>
       </c>
       <c r="B113" t="n">
         <v>57736</v>
@@ -12582,10 +12582,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492414</v>
+        <v>492349</v>
       </c>
       <c r="R113" t="n">
-        <v>7134915</v>
+        <v>7134943</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12649,7 +12649,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730608</v>
+        <v>129730579</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -12684,10 +12684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492316</v>
+        <v>492080</v>
       </c>
       <c r="R114" t="n">
-        <v>7134971</v>
+        <v>7135064</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12751,7 +12751,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730617</v>
+        <v>129730624</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -12786,10 +12786,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492349</v>
+        <v>492366</v>
       </c>
       <c r="R115" t="n">
-        <v>7134943</v>
+        <v>7134921</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12853,7 +12853,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730579</v>
+        <v>129730632</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -12888,10 +12888,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>492080</v>
+        <v>492414</v>
       </c>
       <c r="R116" t="n">
-        <v>7135064</v>
+        <v>7134915</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12955,7 +12955,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730624</v>
+        <v>129730608</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -12990,10 +12990,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492366</v>
+        <v>492316</v>
       </c>
       <c r="R117" t="n">
-        <v>7134921</v>
+        <v>7134971</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13256,10 +13256,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129730673</v>
+        <v>129730568</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13267,21 +13267,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>492342</v>
+        <v>492044</v>
       </c>
       <c r="R120" t="n">
-        <v>7135223</v>
+        <v>7135114</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13327,6 +13327,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13353,7 +13358,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730587</v>
+        <v>129730585</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -13388,7 +13393,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>492125</v>
+        <v>492123</v>
       </c>
       <c r="R121" t="n">
         <v>7135047</v>
@@ -13455,7 +13460,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730568</v>
+        <v>129730657</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -13490,10 +13495,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492044</v>
+        <v>492468</v>
       </c>
       <c r="R122" t="n">
-        <v>7135114</v>
+        <v>7134848</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13557,7 +13562,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730582</v>
+        <v>129730614</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -13592,10 +13597,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492094</v>
+        <v>492342</v>
       </c>
       <c r="R123" t="n">
-        <v>7135060</v>
+        <v>7134966</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13632,7 +13637,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13659,7 +13664,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730585</v>
+        <v>129730618</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -13694,10 +13699,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492123</v>
+        <v>492350</v>
       </c>
       <c r="R124" t="n">
-        <v>7135047</v>
+        <v>7134947</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13734,7 +13739,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13761,7 +13766,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730657</v>
+        <v>129730587</v>
       </c>
       <c r="B125" t="n">
         <v>57736</v>
@@ -13796,10 +13801,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492468</v>
+        <v>492125</v>
       </c>
       <c r="R125" t="n">
-        <v>7134848</v>
+        <v>7135047</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13863,7 +13868,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730614</v>
+        <v>129730582</v>
       </c>
       <c r="B126" t="n">
         <v>57736</v>
@@ -13898,10 +13903,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492342</v>
+        <v>492094</v>
       </c>
       <c r="R126" t="n">
-        <v>7134966</v>
+        <v>7135060</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13938,7 +13943,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13965,10 +13970,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730618</v>
+        <v>129730673</v>
       </c>
       <c r="B127" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13976,21 +13981,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14000,10 +14005,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>492350</v>
+        <v>492342</v>
       </c>
       <c r="R127" t="n">
-        <v>7134947</v>
+        <v>7135223</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14036,11 +14041,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14067,7 +14067,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730563</v>
+        <v>129730539</v>
       </c>
       <c r="B128" t="n">
         <v>57736</v>
@@ -14102,10 +14102,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>492037</v>
+        <v>492011</v>
       </c>
       <c r="R128" t="n">
-        <v>7135119</v>
+        <v>7135206</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14169,7 +14169,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730643</v>
+        <v>129730563</v>
       </c>
       <c r="B129" t="n">
         <v>57736</v>
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>492464</v>
+        <v>492037</v>
       </c>
       <c r="R129" t="n">
-        <v>7134867</v>
+        <v>7135119</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14271,7 +14271,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730561</v>
+        <v>129730643</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -14306,10 +14306,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>492039</v>
+        <v>492464</v>
       </c>
       <c r="R130" t="n">
-        <v>7135123</v>
+        <v>7134867</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14373,7 +14373,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730539</v>
+        <v>129730561</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -14408,10 +14408,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>492011</v>
+        <v>492039</v>
       </c>
       <c r="R131" t="n">
-        <v>7135206</v>
+        <v>7135123</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14475,32 +14475,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730545</v>
+        <v>129730670</v>
       </c>
       <c r="B132" t="n">
-        <v>57736</v>
+        <v>91766</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491983</v>
+        <v>492219</v>
       </c>
       <c r="R132" t="n">
-        <v>7135171</v>
+        <v>7135247</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14546,11 +14546,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14577,7 +14572,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730531</v>
+        <v>129730580</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -14612,10 +14607,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>492083</v>
+        <v>492077</v>
       </c>
       <c r="R133" t="n">
-        <v>7135291</v>
+        <v>7135066</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14679,7 +14674,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730580</v>
+        <v>129730545</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -14714,10 +14709,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>492077</v>
+        <v>491983</v>
       </c>
       <c r="R134" t="n">
-        <v>7135066</v>
+        <v>7135171</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14781,7 +14776,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730574</v>
+        <v>129730531</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -14816,10 +14811,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>492062</v>
+        <v>492083</v>
       </c>
       <c r="R135" t="n">
-        <v>7135103</v>
+        <v>7135291</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14883,32 +14878,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730670</v>
+        <v>129730574</v>
       </c>
       <c r="B136" t="n">
-        <v>91766</v>
+        <v>57736</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14918,10 +14913,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492219</v>
+        <v>492062</v>
       </c>
       <c r="R136" t="n">
-        <v>7135247</v>
+        <v>7135103</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14954,6 +14949,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15184,7 +15184,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730535</v>
+        <v>129730620</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -15219,10 +15219,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492065</v>
+        <v>492351</v>
       </c>
       <c r="R139" t="n">
-        <v>7135257</v>
+        <v>7134938</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15286,32 +15286,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730620</v>
+        <v>129730669</v>
       </c>
       <c r="B140" t="n">
-        <v>57736</v>
+        <v>91766</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15321,10 +15321,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492351</v>
+        <v>492248</v>
       </c>
       <c r="R140" t="n">
-        <v>7134938</v>
+        <v>7135292</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15357,11 +15357,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15388,32 +15383,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730669</v>
+        <v>129730535</v>
       </c>
       <c r="B141" t="n">
-        <v>91766</v>
+        <v>57736</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15423,10 +15418,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492248</v>
+        <v>492065</v>
       </c>
       <c r="R141" t="n">
-        <v>7135292</v>
+        <v>7135257</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15459,6 +15454,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15485,10 +15485,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730525</v>
+        <v>129730609</v>
       </c>
       <c r="B142" t="n">
-        <v>90625</v>
+        <v>57736</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15496,21 +15496,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492390</v>
+        <v>492330</v>
       </c>
       <c r="R142" t="n">
-        <v>7135053</v>
+        <v>7134971</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15556,6 +15556,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15582,32 +15587,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730524</v>
+        <v>129730616</v>
       </c>
       <c r="B143" t="n">
-        <v>91557</v>
+        <v>57736</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15617,10 +15622,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492271</v>
+        <v>492343</v>
       </c>
       <c r="R143" t="n">
-        <v>7135240</v>
+        <v>7134960</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15653,6 +15658,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15679,7 +15689,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730655</v>
+        <v>129730549</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -15714,10 +15724,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>492460</v>
+        <v>491986</v>
       </c>
       <c r="R144" t="n">
-        <v>7134849</v>
+        <v>7135153</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15781,7 +15791,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730558</v>
+        <v>129730578</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -15816,10 +15826,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>492028</v>
+        <v>492086</v>
       </c>
       <c r="R145" t="n">
-        <v>7135126</v>
+        <v>7135087</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15856,7 +15866,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15883,10 +15893,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730609</v>
+        <v>129730525</v>
       </c>
       <c r="B146" t="n">
-        <v>57736</v>
+        <v>90625</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15894,21 +15904,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15918,10 +15928,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>492330</v>
+        <v>492390</v>
       </c>
       <c r="R146" t="n">
-        <v>7134971</v>
+        <v>7135053</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15954,11 +15964,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15985,32 +15990,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730616</v>
+        <v>129730524</v>
       </c>
       <c r="B147" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16020,10 +16025,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>492343</v>
+        <v>492271</v>
       </c>
       <c r="R147" t="n">
-        <v>7134960</v>
+        <v>7135240</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16056,11 +16061,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16087,7 +16087,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730595</v>
+        <v>129730655</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>492208</v>
+        <v>492460</v>
       </c>
       <c r="R148" t="n">
-        <v>7135012</v>
+        <v>7134849</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16189,7 +16189,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730549</v>
+        <v>129730558</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -16224,10 +16224,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491986</v>
+        <v>492028</v>
       </c>
       <c r="R149" t="n">
-        <v>7135153</v>
+        <v>7135126</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16291,7 +16291,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730648</v>
+        <v>129730595</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -16326,10 +16326,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>492457</v>
+        <v>492208</v>
       </c>
       <c r="R150" t="n">
-        <v>7134863</v>
+        <v>7135012</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16393,7 +16393,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730593</v>
+        <v>129730648</v>
       </c>
       <c r="B151" t="n">
         <v>57736</v>
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>492199</v>
+        <v>492457</v>
       </c>
       <c r="R151" t="n">
-        <v>7135015</v>
+        <v>7134863</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16495,7 +16495,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730578</v>
+        <v>129730593</v>
       </c>
       <c r="B152" t="n">
         <v>57736</v>
@@ -16530,10 +16530,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492086</v>
+        <v>492199</v>
       </c>
       <c r="R152" t="n">
-        <v>7135087</v>
+        <v>7135015</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16597,7 +16597,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730601</v>
+        <v>129730571</v>
       </c>
       <c r="B153" t="n">
         <v>57736</v>
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>492240</v>
+        <v>492057</v>
       </c>
       <c r="R153" t="n">
-        <v>7134998</v>
+        <v>7135106</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16699,7 +16699,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730552</v>
+        <v>129730544</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -16734,10 +16734,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>492001</v>
+        <v>491998</v>
       </c>
       <c r="R154" t="n">
-        <v>7135144</v>
+        <v>7135201</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16801,7 +16801,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730571</v>
+        <v>129730564</v>
       </c>
       <c r="B155" t="n">
         <v>57736</v>
@@ -16836,10 +16836,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>492057</v>
+        <v>492039</v>
       </c>
       <c r="R155" t="n">
-        <v>7135106</v>
+        <v>7135120</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16903,7 +16903,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129730544</v>
+        <v>129730590</v>
       </c>
       <c r="B156" t="n">
         <v>57736</v>
@@ -16938,10 +16938,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>491998</v>
+        <v>492184</v>
       </c>
       <c r="R156" t="n">
-        <v>7135201</v>
+        <v>7135029</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17005,7 +17005,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730564</v>
+        <v>129730634</v>
       </c>
       <c r="B157" t="n">
         <v>57736</v>
@@ -17040,10 +17040,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>492039</v>
+        <v>492423</v>
       </c>
       <c r="R157" t="n">
-        <v>7135120</v>
+        <v>7134915</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17107,7 +17107,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730590</v>
+        <v>129730601</v>
       </c>
       <c r="B158" t="n">
         <v>57736</v>
@@ -17142,10 +17142,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>492184</v>
+        <v>492240</v>
       </c>
       <c r="R158" t="n">
-        <v>7135029</v>
+        <v>7134998</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17182,7 +17182,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17209,7 +17209,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730634</v>
+        <v>129730552</v>
       </c>
       <c r="B159" t="n">
         <v>57736</v>
@@ -17244,10 +17244,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>492423</v>
+        <v>492001</v>
       </c>
       <c r="R159" t="n">
-        <v>7134915</v>
+        <v>7135144</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17505,10 +17505,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730527</v>
+        <v>129730547</v>
       </c>
       <c r="B162" t="n">
-        <v>90625</v>
+        <v>57736</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17516,21 +17516,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17540,10 +17540,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>492267</v>
+        <v>491981</v>
       </c>
       <c r="R162" t="n">
-        <v>7135233</v>
+        <v>7135158</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17576,6 +17576,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17602,7 +17607,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730547</v>
+        <v>129730546</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -17637,7 +17642,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>491981</v>
+        <v>491985</v>
       </c>
       <c r="R163" t="n">
         <v>7135158</v>
@@ -17677,7 +17682,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17704,7 +17709,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730546</v>
+        <v>129730556</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -17739,10 +17744,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>491985</v>
+        <v>492024</v>
       </c>
       <c r="R164" t="n">
-        <v>7135158</v>
+        <v>7135131</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17779,7 +17784,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17806,7 +17811,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730556</v>
+        <v>129730591</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -17841,10 +17846,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>492024</v>
+        <v>492194</v>
       </c>
       <c r="R165" t="n">
-        <v>7135131</v>
+        <v>7135016</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17908,10 +17913,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730592</v>
+        <v>129730527</v>
       </c>
       <c r="B166" t="n">
-        <v>57736</v>
+        <v>90625</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17919,21 +17924,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17943,10 +17948,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>492195</v>
+        <v>492267</v>
       </c>
       <c r="R166" t="n">
-        <v>7135016</v>
+        <v>7135233</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17979,11 +17984,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18010,7 +18010,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730591</v>
+        <v>129730592</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -18045,7 +18045,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492194</v>
+        <v>492195</v>
       </c>
       <c r="R167" t="n">
         <v>7135016</v>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18520,7 +18520,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129730567</v>
+        <v>129730649</v>
       </c>
       <c r="B172" t="n">
         <v>57736</v>
@@ -18555,10 +18555,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>492043</v>
+        <v>492466</v>
       </c>
       <c r="R172" t="n">
-        <v>7135115</v>
+        <v>7134866</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18622,7 +18622,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129730649</v>
+        <v>129730555</v>
       </c>
       <c r="B173" t="n">
         <v>57736</v>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>492466</v>
+        <v>492031</v>
       </c>
       <c r="R173" t="n">
-        <v>7134866</v>
+        <v>7135128</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18724,7 +18724,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129730555</v>
+        <v>129730581</v>
       </c>
       <c r="B174" t="n">
         <v>57736</v>
@@ -18759,10 +18759,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>492031</v>
+        <v>492090</v>
       </c>
       <c r="R174" t="n">
-        <v>7135128</v>
+        <v>7135062</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18799,7 +18799,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18826,7 +18826,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129730581</v>
+        <v>129730530</v>
       </c>
       <c r="B175" t="n">
         <v>57736</v>
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>492090</v>
+        <v>492078</v>
       </c>
       <c r="R175" t="n">
-        <v>7135062</v>
+        <v>7135290</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18928,7 +18928,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129730530</v>
+        <v>129730567</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -18963,10 +18963,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>492078</v>
+        <v>492043</v>
       </c>
       <c r="R176" t="n">
-        <v>7135290</v>
+        <v>7135115</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19642,10 +19642,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129730660</v>
+        <v>129730557</v>
       </c>
       <c r="B183" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19653,19 +19653,23 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
@@ -19673,10 +19677,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>492059</v>
+        <v>492026</v>
       </c>
       <c r="R183" t="n">
-        <v>7135168</v>
+        <v>7135131</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19703,12 +19707,17 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19717,7 +19726,6 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19736,7 +19744,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129730557</v>
+        <v>129730537</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -19771,10 +19779,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>492026</v>
+        <v>492037</v>
       </c>
       <c r="R184" t="n">
-        <v>7135131</v>
+        <v>7135230</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19838,7 +19846,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129730537</v>
+        <v>129730653</v>
       </c>
       <c r="B185" t="n">
         <v>57736</v>
@@ -19873,10 +19881,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>492037</v>
+        <v>492468</v>
       </c>
       <c r="R185" t="n">
-        <v>7135230</v>
+        <v>7134851</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19940,7 +19948,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730572</v>
+        <v>129730636</v>
       </c>
       <c r="B186" t="n">
         <v>57736</v>
@@ -19975,10 +19983,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492060</v>
+        <v>492435</v>
       </c>
       <c r="R186" t="n">
-        <v>7135105</v>
+        <v>7134917</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20042,7 +20050,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730653</v>
+        <v>129730577</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -20077,10 +20085,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>492468</v>
+        <v>492066</v>
       </c>
       <c r="R187" t="n">
-        <v>7134851</v>
+        <v>7135097</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20144,7 +20152,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730636</v>
+        <v>129730654</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -20179,10 +20187,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>492435</v>
+        <v>492462</v>
       </c>
       <c r="R188" t="n">
-        <v>7134917</v>
+        <v>7134847</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20246,10 +20254,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129730550</v>
+        <v>129730660</v>
       </c>
       <c r="B189" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20257,23 +20265,19 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
@@ -20281,10 +20285,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>491991</v>
+        <v>492059</v>
       </c>
       <c r="R189" t="n">
-        <v>7135149</v>
+        <v>7135168</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20311,17 +20315,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20330,6 +20329,7 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -20348,7 +20348,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730577</v>
+        <v>129730572</v>
       </c>
       <c r="B190" t="n">
         <v>57736</v>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>492066</v>
+        <v>492060</v>
       </c>
       <c r="R190" t="n">
-        <v>7135097</v>
+        <v>7135105</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20450,7 +20450,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129730654</v>
+        <v>129730550</v>
       </c>
       <c r="B191" t="n">
         <v>57736</v>
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>492462</v>
+        <v>491991</v>
       </c>
       <c r="R191" t="n">
-        <v>7134847</v>
+        <v>7135149</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20649,32 +20649,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730666</v>
+        <v>129730600</v>
       </c>
       <c r="B193" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492253</v>
+        <v>492239</v>
       </c>
       <c r="R193" t="n">
-        <v>7135293</v>
+        <v>7134997</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>7st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21159,7 +21159,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730600</v>
+        <v>129730560</v>
       </c>
       <c r="B198" t="n">
         <v>57736</v>
@@ -21194,10 +21194,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492239</v>
+        <v>492037</v>
       </c>
       <c r="R198" t="n">
-        <v>7134997</v>
+        <v>7135124</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21261,7 +21261,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730560</v>
+        <v>129730570</v>
       </c>
       <c r="B199" t="n">
         <v>57736</v>
@@ -21296,10 +21296,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492037</v>
+        <v>492057</v>
       </c>
       <c r="R199" t="n">
-        <v>7135124</v>
+        <v>7135109</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21363,7 +21363,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730570</v>
+        <v>129730641</v>
       </c>
       <c r="B200" t="n">
         <v>57736</v>
@@ -21398,10 +21398,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492057</v>
+        <v>492462</v>
       </c>
       <c r="R200" t="n">
-        <v>7135109</v>
+        <v>7134883</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21465,7 +21465,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730641</v>
+        <v>129730621</v>
       </c>
       <c r="B201" t="n">
         <v>57736</v>
@@ -21500,10 +21500,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492462</v>
+        <v>492355</v>
       </c>
       <c r="R201" t="n">
-        <v>7134883</v>
+        <v>7134935</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21567,7 +21567,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730621</v>
+        <v>129730651</v>
       </c>
       <c r="B202" t="n">
         <v>57736</v>
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492355</v>
+        <v>492474</v>
       </c>
       <c r="R202" t="n">
-        <v>7134935</v>
+        <v>7134863</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21642,7 +21642,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21669,32 +21669,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129730651</v>
+        <v>129730666</v>
       </c>
       <c r="B203" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21704,10 +21704,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>492474</v>
+        <v>492253</v>
       </c>
       <c r="R203" t="n">
-        <v>7134863</v>
+        <v>7135293</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21744,7 +21744,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>7st</t>
         </is>
       </c>
       <c r="AD203" t="b">

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY203"/>
+  <dimension ref="A1:AY204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728237</v>
+        <v>129726748</v>
       </c>
       <c r="B5" t="n">
-        <v>80187</v>
+        <v>78094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,41 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492236</v>
+        <v>492403</v>
       </c>
       <c r="R5" t="n">
-        <v>7135034</v>
+        <v>7135004</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,14 +1094,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en klen levande sälg.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,76 +1115,50 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129728238</v>
+        <v>129728258</v>
       </c>
       <c r="B6" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492287</v>
+        <v>492272</v>
       </c>
       <c r="R6" t="n">
-        <v>7135150</v>
+        <v>7135018</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,6 +1204,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728258</v>
+        <v>129726742</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1293,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492272</v>
+        <v>492287</v>
       </c>
       <c r="R7" t="n">
-        <v>7135018</v>
+        <v>7135066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,14 +1303,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,19 +1330,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726742</v>
+        <v>129728249</v>
       </c>
       <c r="B8" t="n">
         <v>79081</v>
@@ -1389,16 +1371,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492287</v>
+        <v>492618</v>
       </c>
       <c r="R8" t="n">
-        <v>7135066</v>
+        <v>7134954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,19 +1413,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,28 +1429,54 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728249</v>
+        <v>129728237</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,26 +1484,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1505,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492618</v>
+        <v>492236</v>
       </c>
       <c r="R9" t="n">
-        <v>7134954</v>
+        <v>7135034</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1555,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,22 +1575,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1705,32 +1715,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726748</v>
+        <v>129728238</v>
       </c>
       <c r="B11" t="n">
-        <v>78094</v>
+        <v>80214</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1740,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492403</v>
+        <v>492287</v>
       </c>
       <c r="R11" t="n">
-        <v>7135004</v>
+        <v>7135150</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,19 +1783,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,12 +1800,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2045,65 +2045,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129728247</v>
+        <v>129726741</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492455</v>
+        <v>492282</v>
       </c>
       <c r="R14" t="n">
-        <v>7134922</v>
+        <v>7135069</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,14 +2113,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,89 +2134,63 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129728244</v>
+        <v>129726752</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492133</v>
+        <v>492482</v>
       </c>
       <c r="R15" t="n">
-        <v>7135159</v>
+        <v>7134934</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,14 +2220,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,34 +2241,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726752</v>
+        <v>129726738</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,21 +2270,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2336,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492482</v>
+        <v>492242</v>
       </c>
       <c r="R16" t="n">
-        <v>7134934</v>
+        <v>7135130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,45 +2366,65 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726741</v>
+        <v>129728247</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492282</v>
+        <v>492455</v>
       </c>
       <c r="R17" t="n">
-        <v>7135069</v>
+        <v>7134922</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,19 +2454,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,63 +2470,89 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726738</v>
+        <v>129728244</v>
       </c>
       <c r="B18" t="n">
-        <v>83050</v>
+        <v>98774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492242</v>
+        <v>492133</v>
       </c>
       <c r="R18" t="n">
-        <v>7135130</v>
+        <v>7135159</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,19 +2582,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:30</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,18 +2598,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2943,65 +2943,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129728246</v>
+        <v>129726716</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>97651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492341</v>
+        <v>492599</v>
       </c>
       <c r="R22" t="n">
-        <v>7134976</v>
+        <v>7134962</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,14 +3011,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,69 +3032,83 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726716</v>
+        <v>129728246</v>
       </c>
       <c r="B23" t="n">
-        <v>97651</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492599</v>
+        <v>492341</v>
       </c>
       <c r="R23" t="n">
-        <v>7134962</v>
+        <v>7134976</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,19 +3138,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:13</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,63 +3154,89 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129728252</v>
+        <v>129728245</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492377</v>
+        <v>492204</v>
       </c>
       <c r="R24" t="n">
-        <v>7135110</v>
+        <v>7135099</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3253,7 +3273,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,8 +3282,14 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3280,7 +3306,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129728245</v>
+        <v>129728242</v>
       </c>
       <c r="B25" t="n">
         <v>98774</v>
@@ -3310,7 +3336,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3335,10 +3361,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492204</v>
+        <v>492205</v>
       </c>
       <c r="R25" t="n">
-        <v>7135099</v>
+        <v>7135151</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,7 +3401,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
+          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,65 +3434,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129728242</v>
+        <v>129728252</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492205</v>
+        <v>492377</v>
       </c>
       <c r="R26" t="n">
-        <v>7135151</v>
+        <v>7135110</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3503,7 +3509,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3512,14 +3518,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3536,7 +3536,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129726732</v>
+        <v>129728257</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492176</v>
+        <v>492250</v>
       </c>
       <c r="R27" t="n">
-        <v>7135178</v>
+        <v>7135035</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3604,19 +3604,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,19 +3626,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129728257</v>
+        <v>129726719</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3678,10 +3673,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492250</v>
+        <v>492458</v>
       </c>
       <c r="R28" t="n">
-        <v>7135035</v>
+        <v>7135104</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3711,14 +3706,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3733,19 +3733,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129726754</v>
+        <v>129726732</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492511</v>
+        <v>492176</v>
       </c>
       <c r="R29" t="n">
-        <v>7134902</v>
+        <v>7135178</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3852,7 +3852,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726719</v>
+        <v>129726754</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492458</v>
+        <v>492511</v>
       </c>
       <c r="R30" t="n">
-        <v>7135104</v>
+        <v>7134902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3959,32 +3959,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726726</v>
+        <v>129726737</v>
       </c>
       <c r="B31" t="n">
-        <v>91766</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492285</v>
+        <v>492228</v>
       </c>
       <c r="R31" t="n">
-        <v>7135248</v>
+        <v>7135126</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,45 +4066,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726737</v>
+        <v>129726722</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492228</v>
+        <v>492376</v>
       </c>
       <c r="R32" t="n">
-        <v>7135126</v>
+        <v>7135128</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4146,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4173,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726722</v>
+        <v>129726726</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>91766</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4184,38 +4188,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492376</v>
+        <v>492285</v>
       </c>
       <c r="R33" t="n">
-        <v>7135128</v>
+        <v>7135248</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,7 +4284,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129728256</v>
+        <v>129728254</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492217</v>
+        <v>492116</v>
       </c>
       <c r="R34" t="n">
-        <v>7135029</v>
+        <v>7135129</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4493,7 +4493,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726750</v>
+        <v>129728255</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492416</v>
+        <v>492112</v>
       </c>
       <c r="R36" t="n">
-        <v>7135000</v>
+        <v>7135077</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4561,19 +4561,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:01</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:01</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,77 +4583,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129728243</v>
+        <v>129728256</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492168</v>
+        <v>492217</v>
       </c>
       <c r="R37" t="n">
-        <v>7135133</v>
+        <v>7135029</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4695,7 +4670,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4704,14 +4679,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4728,10 +4697,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726720</v>
+        <v>129726750</v>
       </c>
       <c r="B38" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4739,21 +4708,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4763,10 +4732,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492458</v>
+        <v>492416</v>
       </c>
       <c r="R38" t="n">
-        <v>7135104</v>
+        <v>7135000</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4798,7 +4767,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4808,7 +4777,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,45 +4804,65 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129728254</v>
+        <v>129728243</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492116</v>
+        <v>492168</v>
       </c>
       <c r="R39" t="n">
-        <v>7135129</v>
+        <v>7135133</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4910,7 +4899,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4919,8 +4908,14 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4937,10 +4932,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129728255</v>
+        <v>129726720</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4948,21 +4943,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4972,10 +4967,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492112</v>
+        <v>492458</v>
       </c>
       <c r="R40" t="n">
-        <v>7135077</v>
+        <v>7135104</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5005,14 +5000,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5027,12 +5027,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129728253</v>
+        <v>129726740</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492341</v>
+        <v>492268</v>
       </c>
       <c r="R43" t="n">
-        <v>7135150</v>
+        <v>7135143</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5349,14 +5349,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5371,19 +5376,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726740</v>
+        <v>129728253</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5418,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492268</v>
+        <v>492341</v>
       </c>
       <c r="R44" t="n">
-        <v>7135143</v>
+        <v>7135150</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5451,19 +5456,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:25</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5478,12 +5478,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5946,45 +5946,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129728241</v>
+        <v>129728262</v>
       </c>
       <c r="B49" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492451</v>
+        <v>492479</v>
       </c>
       <c r="R49" t="n">
-        <v>7134904</v>
+        <v>7134899</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6019,14 +6022,45 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6043,7 +6077,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129728262</v>
+        <v>129726721</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -6072,19 +6106,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492479</v>
+        <v>492421</v>
       </c>
       <c r="R50" t="n">
-        <v>7134899</v>
+        <v>7135113</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6114,14 +6145,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran i gammal barrblandskog.</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6130,76 +6166,50 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129726721</v>
+        <v>129728241</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6209,10 +6219,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492421</v>
+        <v>492451</v>
       </c>
       <c r="R51" t="n">
-        <v>7135113</v>
+        <v>7134904</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6242,19 +6252,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6269,19 +6269,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129726718</v>
+        <v>129726727</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492543</v>
+        <v>492258</v>
       </c>
       <c r="R52" t="n">
-        <v>7135091</v>
+        <v>7135232</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6388,7 +6388,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129726727</v>
+        <v>129726718</v>
       </c>
       <c r="B53" t="n">
         <v>79081</v>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492258</v>
+        <v>492543</v>
       </c>
       <c r="R53" t="n">
-        <v>7135232</v>
+        <v>7135091</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6602,65 +6602,41 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129728248</v>
+        <v>129726734</v>
       </c>
       <c r="B55" t="n">
-        <v>98774</v>
+        <v>91613</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492492</v>
+        <v>492211</v>
       </c>
       <c r="R55" t="n">
-        <v>7134909</v>
+        <v>7135170</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6690,14 +6666,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6710,27 +6691,22 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129726731</v>
+        <v>129728260</v>
       </c>
       <c r="B56" t="n">
         <v>79081</v>
@@ -6765,10 +6741,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492137</v>
+        <v>492378</v>
       </c>
       <c r="R56" t="n">
-        <v>7135201</v>
+        <v>7134955</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6798,19 +6774,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:48</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6825,22 +6796,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129726734</v>
+        <v>129726731</v>
       </c>
       <c r="B57" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6848,19 +6819,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6868,10 +6843,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492211</v>
+        <v>492137</v>
       </c>
       <c r="R57" t="n">
-        <v>7135170</v>
+        <v>7135201</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6903,7 +6878,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6913,7 +6888,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6922,7 +6897,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6941,45 +6915,65 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129728260</v>
+        <v>129728248</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492378</v>
+        <v>492492</v>
       </c>
       <c r="R58" t="n">
-        <v>7134955</v>
+        <v>7134909</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7016,7 +7010,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7025,8 +7019,14 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7043,10 +7043,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129728250</v>
+        <v>129726728</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7054,21 +7054,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492572</v>
+        <v>492179</v>
       </c>
       <c r="R59" t="n">
-        <v>7135009</v>
+        <v>7135241</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7111,14 +7111,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7133,22 +7138,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726725</v>
+        <v>129726753</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,21 +7161,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7180,10 +7185,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492304</v>
+        <v>492496</v>
       </c>
       <c r="R60" t="n">
-        <v>7135246</v>
+        <v>7134904</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7215,7 +7220,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7225,7 +7230,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7252,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129726728</v>
+        <v>129728250</v>
       </c>
       <c r="B61" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7263,21 +7268,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7287,10 +7292,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492179</v>
+        <v>492572</v>
       </c>
       <c r="R61" t="n">
-        <v>7135241</v>
+        <v>7135009</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7320,19 +7325,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7347,22 +7347,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726753</v>
+        <v>129726725</v>
       </c>
       <c r="B62" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492496</v>
+        <v>492304</v>
       </c>
       <c r="R62" t="n">
-        <v>7134904</v>
+        <v>7135246</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7568,32 +7568,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129728259</v>
+        <v>129726730</v>
       </c>
       <c r="B64" t="n">
-        <v>79081</v>
+        <v>92311</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492317</v>
+        <v>492124</v>
       </c>
       <c r="R64" t="n">
-        <v>7134999</v>
+        <v>7135171</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7636,14 +7636,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7658,44 +7663,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129726745</v>
+        <v>129728240</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7705,10 +7710,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492367</v>
+        <v>492405</v>
       </c>
       <c r="R65" t="n">
-        <v>7135038</v>
+        <v>7134981</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7738,19 +7743,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:12</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7765,22 +7765,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129726724</v>
+        <v>129728259</v>
       </c>
       <c r="B66" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7788,43 +7788,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492343</v>
+        <v>492317</v>
       </c>
       <c r="R66" t="n">
-        <v>7135242</v>
+        <v>7134999</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7854,19 +7845,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:28</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7881,44 +7867,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129728240</v>
+        <v>129726745</v>
       </c>
       <c r="B67" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7928,10 +7914,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492405</v>
+        <v>492367</v>
       </c>
       <c r="R67" t="n">
-        <v>7134981</v>
+        <v>7135038</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7961,14 +7947,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7983,57 +7974,66 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726730</v>
+        <v>129726724</v>
       </c>
       <c r="B68" t="n">
-        <v>92311</v>
+        <v>57896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492124</v>
+        <v>492343</v>
       </c>
       <c r="R68" t="n">
-        <v>7135171</v>
+        <v>7135242</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730672</v>
+        <v>129730658</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492334</v>
+        <v>492464</v>
       </c>
       <c r="R69" t="n">
-        <v>7135092</v>
+        <v>7135049</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,6 +8173,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8199,7 +8204,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730584</v>
+        <v>129730615</v>
       </c>
       <c r="B70" t="n">
         <v>57736</v>
@@ -8234,10 +8239,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492107</v>
+        <v>492345</v>
       </c>
       <c r="R70" t="n">
-        <v>7135052</v>
+        <v>7134961</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8274,7 +8279,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8301,10 +8306,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730615</v>
+        <v>129730672</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8312,21 +8317,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8336,10 +8341,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492345</v>
+        <v>492334</v>
       </c>
       <c r="R71" t="n">
-        <v>7134961</v>
+        <v>7135092</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8372,11 +8377,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8505,7 +8505,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730598</v>
+        <v>129730584</v>
       </c>
       <c r="B73" t="n">
         <v>57736</v>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492220</v>
+        <v>492107</v>
       </c>
       <c r="R73" t="n">
-        <v>7135003</v>
+        <v>7135052</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730658</v>
+        <v>129730598</v>
       </c>
       <c r="B74" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492464</v>
+        <v>492220</v>
       </c>
       <c r="R74" t="n">
-        <v>7135049</v>
+        <v>7135003</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8913,10 +8913,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129730645</v>
+        <v>129730671</v>
       </c>
       <c r="B77" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8924,21 +8924,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>492464</v>
+        <v>492379</v>
       </c>
       <c r="R77" t="n">
-        <v>7134870</v>
+        <v>7135129</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8984,11 +8984,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9015,10 +9010,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129730671</v>
+        <v>129730629</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9026,21 +9021,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9050,10 +9045,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>492379</v>
+        <v>492369</v>
       </c>
       <c r="R78" t="n">
-        <v>7135129</v>
+        <v>7134915</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9086,6 +9081,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9112,7 +9112,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129730629</v>
+        <v>129730645</v>
       </c>
       <c r="B79" t="n">
         <v>57736</v>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>492369</v>
+        <v>492464</v>
       </c>
       <c r="R79" t="n">
-        <v>7134915</v>
+        <v>7134870</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9214,10 +9214,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730675</v>
+        <v>129730594</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9225,21 +9225,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492075</v>
+        <v>492205</v>
       </c>
       <c r="R80" t="n">
-        <v>7135214</v>
+        <v>7135012</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9285,6 +9285,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9311,7 +9316,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730635</v>
+        <v>129730630</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -9346,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492424</v>
+        <v>492411</v>
       </c>
       <c r="R81" t="n">
-        <v>7134911</v>
+        <v>7134926</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9413,7 +9418,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730575</v>
+        <v>129730635</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -9448,10 +9453,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492063</v>
+        <v>492424</v>
       </c>
       <c r="R82" t="n">
-        <v>7135101</v>
+        <v>7134911</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9488,7 +9493,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9617,7 +9622,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730603</v>
+        <v>129730562</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -9652,10 +9657,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492265</v>
+        <v>492037</v>
       </c>
       <c r="R84" t="n">
-        <v>7134987</v>
+        <v>7135120</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9719,7 +9724,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730594</v>
+        <v>129730575</v>
       </c>
       <c r="B85" t="n">
         <v>57736</v>
@@ -9754,10 +9759,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492205</v>
+        <v>492063</v>
       </c>
       <c r="R85" t="n">
-        <v>7135012</v>
+        <v>7135101</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9794,7 +9799,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9821,7 +9826,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129730599</v>
+        <v>129730603</v>
       </c>
       <c r="B86" t="n">
         <v>57736</v>
@@ -9856,10 +9861,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492216</v>
+        <v>492265</v>
       </c>
       <c r="R86" t="n">
-        <v>7135002</v>
+        <v>7134987</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9896,7 +9901,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9923,7 +9928,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129730630</v>
+        <v>129730599</v>
       </c>
       <c r="B87" t="n">
         <v>57736</v>
@@ -9958,10 +9963,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492411</v>
+        <v>492216</v>
       </c>
       <c r="R87" t="n">
-        <v>7134926</v>
+        <v>7135002</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9998,7 +10003,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10025,32 +10030,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730562</v>
+        <v>129730665</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10060,10 +10065,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492037</v>
+        <v>492046</v>
       </c>
       <c r="R88" t="n">
-        <v>7135120</v>
+        <v>7135177</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10100,7 +10105,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10127,32 +10132,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129730665</v>
+        <v>129730675</v>
       </c>
       <c r="B89" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10162,10 +10167,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492046</v>
+        <v>492075</v>
       </c>
       <c r="R89" t="n">
-        <v>7135177</v>
+        <v>7135214</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10198,11 +10203,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>8st</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10331,7 +10331,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129730565</v>
+        <v>129730583</v>
       </c>
       <c r="B91" t="n">
         <v>57736</v>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492040</v>
+        <v>492105</v>
       </c>
       <c r="R91" t="n">
-        <v>7135117</v>
+        <v>7135051</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10433,7 +10433,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129730583</v>
+        <v>129730565</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>492105</v>
+        <v>492040</v>
       </c>
       <c r="R92" t="n">
-        <v>7135051</v>
+        <v>7135117</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129730522</v>
+        <v>129730661</v>
       </c>
       <c r="B94" t="n">
-        <v>97020</v>
+        <v>91613</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,23 +10648,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10672,10 +10668,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492217</v>
+        <v>492069</v>
       </c>
       <c r="R94" t="n">
-        <v>7135249</v>
+        <v>7135162</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10702,12 +10698,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10716,6 +10712,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10734,10 +10731,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730661</v>
+        <v>129730619</v>
       </c>
       <c r="B95" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10745,19 +10742,23 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10765,10 +10766,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492069</v>
+        <v>492353</v>
       </c>
       <c r="R95" t="n">
-        <v>7135162</v>
+        <v>7134945</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10795,12 +10796,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10809,7 +10815,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10828,7 +10833,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730619</v>
+        <v>129730604</v>
       </c>
       <c r="B96" t="n">
         <v>57736</v>
@@ -10863,10 +10868,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492353</v>
+        <v>492297</v>
       </c>
       <c r="R96" t="n">
-        <v>7134945</v>
+        <v>7134975</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10903,7 +10908,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10930,10 +10935,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730650</v>
+        <v>129730522</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>97020</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10941,21 +10946,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10965,10 +10970,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492473</v>
+        <v>492217</v>
       </c>
       <c r="R97" t="n">
-        <v>7134864</v>
+        <v>7135249</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11001,11 +11006,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11032,7 +11032,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129730569</v>
+        <v>129730606</v>
       </c>
       <c r="B98" t="n">
         <v>57736</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492054</v>
+        <v>492303</v>
       </c>
       <c r="R98" t="n">
-        <v>7135107</v>
+        <v>7134972</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11134,7 +11134,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730606</v>
+        <v>129730569</v>
       </c>
       <c r="B99" t="n">
         <v>57736</v>
@@ -11169,10 +11169,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492303</v>
+        <v>492054</v>
       </c>
       <c r="R99" t="n">
-        <v>7134972</v>
+        <v>7135107</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11236,7 +11236,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730604</v>
+        <v>129730650</v>
       </c>
       <c r="B100" t="n">
         <v>57736</v>
@@ -11271,10 +11271,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492297</v>
+        <v>492473</v>
       </c>
       <c r="R100" t="n">
-        <v>7134975</v>
+        <v>7134864</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730656</v>
+        <v>129730523</v>
       </c>
       <c r="B102" t="n">
-        <v>57736</v>
+        <v>97020</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11446,21 +11446,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492466</v>
+        <v>492316</v>
       </c>
       <c r="R102" t="n">
-        <v>7134851</v>
+        <v>7135071</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11506,11 +11506,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11537,10 +11532,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730523</v>
+        <v>129730640</v>
       </c>
       <c r="B103" t="n">
-        <v>97020</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11548,21 +11543,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11572,10 +11567,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492316</v>
+        <v>492444</v>
       </c>
       <c r="R103" t="n">
-        <v>7135071</v>
+        <v>7134887</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11608,6 +11603,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11634,7 +11634,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730602</v>
+        <v>129730656</v>
       </c>
       <c r="B104" t="n">
         <v>57736</v>
@@ -11669,10 +11669,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492245</v>
+        <v>492466</v>
       </c>
       <c r="R104" t="n">
-        <v>7134995</v>
+        <v>7134851</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11736,7 +11736,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730640</v>
+        <v>129730602</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>492444</v>
+        <v>492245</v>
       </c>
       <c r="R105" t="n">
-        <v>7134887</v>
+        <v>7134995</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11838,10 +11838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730529</v>
+        <v>129730521</v>
       </c>
       <c r="B106" t="n">
-        <v>57736</v>
+        <v>83050</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492088</v>
+        <v>492100</v>
       </c>
       <c r="R106" t="n">
-        <v>7135198</v>
+        <v>7135216</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11909,11 +11909,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11940,7 +11935,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730532</v>
+        <v>129730529</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11975,10 +11970,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492082</v>
+        <v>492088</v>
       </c>
       <c r="R107" t="n">
-        <v>7135294</v>
+        <v>7135198</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12015,7 +12010,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12042,7 +12037,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730576</v>
+        <v>129730631</v>
       </c>
       <c r="B108" t="n">
         <v>57736</v>
@@ -12077,10 +12072,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492066</v>
+        <v>492409</v>
       </c>
       <c r="R108" t="n">
-        <v>7135093</v>
+        <v>7134918</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12117,7 +12112,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12144,7 +12139,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730559</v>
+        <v>129730532</v>
       </c>
       <c r="B109" t="n">
         <v>57736</v>
@@ -12179,10 +12174,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492032</v>
+        <v>492082</v>
       </c>
       <c r="R109" t="n">
-        <v>7135120</v>
+        <v>7135294</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12219,7 +12214,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12246,10 +12241,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730521</v>
+        <v>129730576</v>
       </c>
       <c r="B110" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12257,21 +12252,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12281,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492100</v>
+        <v>492066</v>
       </c>
       <c r="R110" t="n">
-        <v>7135216</v>
+        <v>7135093</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12317,6 +12312,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12343,7 +12343,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730631</v>
+        <v>129730559</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492409</v>
+        <v>492032</v>
       </c>
       <c r="R111" t="n">
-        <v>7134918</v>
+        <v>7135120</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129730528</v>
+        <v>129730526</v>
       </c>
       <c r="B112" t="n">
-        <v>57736</v>
+        <v>90625</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12456,21 +12456,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>492476</v>
+        <v>492395</v>
       </c>
       <c r="R112" t="n">
-        <v>7135072</v>
+        <v>7135064</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12516,11 +12516,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12751,7 +12746,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730624</v>
+        <v>129730528</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -12786,10 +12781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492366</v>
+        <v>492476</v>
       </c>
       <c r="R115" t="n">
-        <v>7134921</v>
+        <v>7135072</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13057,7 +13052,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730597</v>
+        <v>129730624</v>
       </c>
       <c r="B118" t="n">
         <v>57736</v>
@@ -13092,10 +13087,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492213</v>
+        <v>492366</v>
       </c>
       <c r="R118" t="n">
-        <v>7135010</v>
+        <v>7134921</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13159,10 +13154,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730526</v>
+        <v>129730597</v>
       </c>
       <c r="B119" t="n">
-        <v>90625</v>
+        <v>57736</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13170,21 +13165,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13194,10 +13189,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492395</v>
+        <v>492213</v>
       </c>
       <c r="R119" t="n">
-        <v>7135064</v>
+        <v>7135010</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13230,6 +13225,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13256,10 +13256,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129730568</v>
+        <v>129730673</v>
       </c>
       <c r="B120" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13267,21 +13267,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>492044</v>
+        <v>492342</v>
       </c>
       <c r="R120" t="n">
-        <v>7135114</v>
+        <v>7135223</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13327,11 +13327,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13358,7 +13353,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730585</v>
+        <v>129730587</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -13393,7 +13388,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>492123</v>
+        <v>492125</v>
       </c>
       <c r="R121" t="n">
         <v>7135047</v>
@@ -13460,7 +13455,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730657</v>
+        <v>129730614</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -13495,10 +13490,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492468</v>
+        <v>492342</v>
       </c>
       <c r="R122" t="n">
-        <v>7134848</v>
+        <v>7134966</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13562,7 +13557,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730614</v>
+        <v>129730618</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -13597,10 +13592,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492342</v>
+        <v>492350</v>
       </c>
       <c r="R123" t="n">
-        <v>7134966</v>
+        <v>7134947</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13637,7 +13632,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13664,7 +13659,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730618</v>
+        <v>129730568</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -13699,10 +13694,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492350</v>
+        <v>492044</v>
       </c>
       <c r="R124" t="n">
-        <v>7134947</v>
+        <v>7135114</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13739,7 +13734,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13766,7 +13761,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730587</v>
+        <v>129730582</v>
       </c>
       <c r="B125" t="n">
         <v>57736</v>
@@ -13801,10 +13796,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492125</v>
+        <v>492094</v>
       </c>
       <c r="R125" t="n">
-        <v>7135047</v>
+        <v>7135060</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13841,7 +13836,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13868,7 +13863,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730582</v>
+        <v>129730585</v>
       </c>
       <c r="B126" t="n">
         <v>57736</v>
@@ -13903,10 +13898,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492094</v>
+        <v>492123</v>
       </c>
       <c r="R126" t="n">
-        <v>7135060</v>
+        <v>7135047</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13943,7 +13938,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13970,10 +13965,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730673</v>
+        <v>129730657</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13981,21 +13976,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14005,10 +14000,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>492342</v>
+        <v>492468</v>
       </c>
       <c r="R127" t="n">
-        <v>7135223</v>
+        <v>7134848</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14041,6 +14036,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14067,7 +14067,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730539</v>
+        <v>129730643</v>
       </c>
       <c r="B128" t="n">
         <v>57736</v>
@@ -14102,10 +14102,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>492011</v>
+        <v>492464</v>
       </c>
       <c r="R128" t="n">
-        <v>7135206</v>
+        <v>7134867</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14142,7 +14142,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14169,7 +14169,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730563</v>
+        <v>129730561</v>
       </c>
       <c r="B129" t="n">
         <v>57736</v>
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>492037</v>
+        <v>492039</v>
       </c>
       <c r="R129" t="n">
-        <v>7135119</v>
+        <v>7135123</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730643</v>
+        <v>129730539</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -14306,10 +14306,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>492464</v>
+        <v>492011</v>
       </c>
       <c r="R130" t="n">
-        <v>7134867</v>
+        <v>7135206</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14373,7 +14373,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730561</v>
+        <v>129730563</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -14408,10 +14408,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>492039</v>
+        <v>492037</v>
       </c>
       <c r="R131" t="n">
-        <v>7135123</v>
+        <v>7135119</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14572,7 +14572,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730580</v>
+        <v>129730545</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>492077</v>
+        <v>491983</v>
       </c>
       <c r="R133" t="n">
-        <v>7135066</v>
+        <v>7135171</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14674,7 +14674,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730545</v>
+        <v>129730531</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>491983</v>
+        <v>492083</v>
       </c>
       <c r="R134" t="n">
-        <v>7135171</v>
+        <v>7135291</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14776,7 +14776,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730531</v>
+        <v>129730574</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>492083</v>
+        <v>492062</v>
       </c>
       <c r="R135" t="n">
-        <v>7135291</v>
+        <v>7135103</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14878,7 +14878,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730574</v>
+        <v>129730580</v>
       </c>
       <c r="B136" t="n">
         <v>57736</v>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492062</v>
+        <v>492077</v>
       </c>
       <c r="R136" t="n">
-        <v>7135103</v>
+        <v>7135066</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14980,32 +14980,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129730646</v>
+        <v>129730669</v>
       </c>
       <c r="B137" t="n">
-        <v>57736</v>
+        <v>91766</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15015,10 +15015,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>492465</v>
+        <v>492248</v>
       </c>
       <c r="R137" t="n">
-        <v>7134871</v>
+        <v>7135292</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15051,11 +15051,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15082,7 +15077,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730541</v>
+        <v>129730646</v>
       </c>
       <c r="B138" t="n">
         <v>57736</v>
@@ -15117,10 +15112,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>492004</v>
+        <v>492465</v>
       </c>
       <c r="R138" t="n">
-        <v>7135207</v>
+        <v>7134871</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15184,7 +15179,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730620</v>
+        <v>129730541</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -15219,10 +15214,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492351</v>
+        <v>492004</v>
       </c>
       <c r="R139" t="n">
-        <v>7134938</v>
+        <v>7135207</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15286,32 +15281,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730669</v>
+        <v>129730535</v>
       </c>
       <c r="B140" t="n">
-        <v>91766</v>
+        <v>57736</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15321,10 +15316,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492248</v>
+        <v>492065</v>
       </c>
       <c r="R140" t="n">
-        <v>7135292</v>
+        <v>7135257</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15357,6 +15352,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15383,7 +15383,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730535</v>
+        <v>129730620</v>
       </c>
       <c r="B141" t="n">
         <v>57736</v>
@@ -15418,10 +15418,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492065</v>
+        <v>492351</v>
       </c>
       <c r="R141" t="n">
-        <v>7135257</v>
+        <v>7134938</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15485,10 +15485,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730609</v>
+        <v>129730525</v>
       </c>
       <c r="B142" t="n">
-        <v>57736</v>
+        <v>90625</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15496,21 +15496,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492330</v>
+        <v>492390</v>
       </c>
       <c r="R142" t="n">
-        <v>7134971</v>
+        <v>7135053</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15556,11 +15556,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15587,32 +15582,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730616</v>
+        <v>129730524</v>
       </c>
       <c r="B143" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15622,10 +15617,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492343</v>
+        <v>492271</v>
       </c>
       <c r="R143" t="n">
-        <v>7134960</v>
+        <v>7135240</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15658,11 +15653,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15689,7 +15679,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730549</v>
+        <v>129730616</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -15724,10 +15714,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>491986</v>
+        <v>492343</v>
       </c>
       <c r="R144" t="n">
-        <v>7135153</v>
+        <v>7134960</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15791,7 +15781,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730578</v>
+        <v>129730655</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -15826,10 +15816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>492086</v>
+        <v>492460</v>
       </c>
       <c r="R145" t="n">
-        <v>7135087</v>
+        <v>7134849</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15893,10 +15883,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730525</v>
+        <v>129730609</v>
       </c>
       <c r="B146" t="n">
-        <v>90625</v>
+        <v>57736</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15904,21 +15894,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15928,10 +15918,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>492390</v>
+        <v>492330</v>
       </c>
       <c r="R146" t="n">
-        <v>7135053</v>
+        <v>7134971</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15964,6 +15954,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15990,32 +15985,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730524</v>
+        <v>129730595</v>
       </c>
       <c r="B147" t="n">
-        <v>91557</v>
+        <v>57736</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16025,10 +16020,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>492271</v>
+        <v>492208</v>
       </c>
       <c r="R147" t="n">
-        <v>7135240</v>
+        <v>7135012</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16061,6 +16056,11 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16087,7 +16087,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730655</v>
+        <v>129730549</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>492460</v>
+        <v>491986</v>
       </c>
       <c r="R148" t="n">
-        <v>7134849</v>
+        <v>7135153</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16189,7 +16189,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730558</v>
+        <v>129730648</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -16224,10 +16224,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>492028</v>
+        <v>492457</v>
       </c>
       <c r="R149" t="n">
-        <v>7135126</v>
+        <v>7134863</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16291,7 +16291,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730595</v>
+        <v>129730593</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -16326,10 +16326,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>492208</v>
+        <v>492199</v>
       </c>
       <c r="R150" t="n">
-        <v>7135012</v>
+        <v>7135015</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16393,7 +16393,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730648</v>
+        <v>129730578</v>
       </c>
       <c r="B151" t="n">
         <v>57736</v>
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>492457</v>
+        <v>492086</v>
       </c>
       <c r="R151" t="n">
-        <v>7134863</v>
+        <v>7135087</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16495,7 +16495,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730593</v>
+        <v>129730558</v>
       </c>
       <c r="B152" t="n">
         <v>57736</v>
@@ -16530,10 +16530,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492199</v>
+        <v>492028</v>
       </c>
       <c r="R152" t="n">
-        <v>7135015</v>
+        <v>7135126</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16597,7 +16597,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730571</v>
+        <v>129730601</v>
       </c>
       <c r="B153" t="n">
         <v>57736</v>
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>492057</v>
+        <v>492240</v>
       </c>
       <c r="R153" t="n">
-        <v>7135106</v>
+        <v>7134998</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16699,7 +16699,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730544</v>
+        <v>129730552</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -16734,10 +16734,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>491998</v>
+        <v>492001</v>
       </c>
       <c r="R154" t="n">
-        <v>7135201</v>
+        <v>7135144</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16801,10 +16801,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730564</v>
+        <v>129730668</v>
       </c>
       <c r="B155" t="n">
-        <v>57736</v>
+        <v>56917</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16812,16 +16812,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -16836,10 +16836,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>492039</v>
+        <v>492293</v>
       </c>
       <c r="R155" t="n">
-        <v>7135120</v>
+        <v>7134991</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16872,11 +16872,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16903,10 +16898,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129730590</v>
+        <v>129730667</v>
       </c>
       <c r="B156" t="n">
-        <v>57736</v>
+        <v>56917</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16914,16 +16909,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -16938,10 +16933,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>492184</v>
+        <v>492088</v>
       </c>
       <c r="R156" t="n">
-        <v>7135029</v>
+        <v>7135189</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16974,11 +16969,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17005,7 +16995,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730634</v>
+        <v>129730571</v>
       </c>
       <c r="B157" t="n">
         <v>57736</v>
@@ -17040,10 +17030,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>492423</v>
+        <v>492057</v>
       </c>
       <c r="R157" t="n">
-        <v>7134915</v>
+        <v>7135106</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17080,7 +17070,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17107,7 +17097,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730601</v>
+        <v>129730544</v>
       </c>
       <c r="B158" t="n">
         <v>57736</v>
@@ -17142,10 +17132,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>492240</v>
+        <v>491998</v>
       </c>
       <c r="R158" t="n">
-        <v>7134998</v>
+        <v>7135201</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17182,7 +17172,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17209,7 +17199,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730552</v>
+        <v>129730564</v>
       </c>
       <c r="B159" t="n">
         <v>57736</v>
@@ -17244,10 +17234,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>492001</v>
+        <v>492039</v>
       </c>
       <c r="R159" t="n">
-        <v>7135144</v>
+        <v>7135120</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17311,10 +17301,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730668</v>
+        <v>129730590</v>
       </c>
       <c r="B160" t="n">
-        <v>56917</v>
+        <v>57736</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17322,16 +17312,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -17346,10 +17336,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>492293</v>
+        <v>492184</v>
       </c>
       <c r="R160" t="n">
-        <v>7134991</v>
+        <v>7135029</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17382,6 +17372,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17408,10 +17403,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129730667</v>
+        <v>129730634</v>
       </c>
       <c r="B161" t="n">
-        <v>56917</v>
+        <v>57736</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17419,16 +17414,16 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -17443,10 +17438,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>492088</v>
+        <v>492423</v>
       </c>
       <c r="R161" t="n">
-        <v>7135189</v>
+        <v>7134915</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17479,6 +17474,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17505,7 +17505,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730547</v>
+        <v>129730546</v>
       </c>
       <c r="B162" t="n">
         <v>57736</v>
@@ -17540,7 +17540,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>491981</v>
+        <v>491985</v>
       </c>
       <c r="R162" t="n">
         <v>7135158</v>
@@ -17580,7 +17580,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17607,7 +17607,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730546</v>
+        <v>129730592</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -17642,10 +17642,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>491985</v>
+        <v>492195</v>
       </c>
       <c r="R163" t="n">
-        <v>7135158</v>
+        <v>7135016</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17709,7 +17709,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730556</v>
+        <v>129730591</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -17744,10 +17744,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>492024</v>
+        <v>492194</v>
       </c>
       <c r="R164" t="n">
-        <v>7135131</v>
+        <v>7135016</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17811,10 +17811,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730591</v>
+        <v>129730527</v>
       </c>
       <c r="B165" t="n">
-        <v>57736</v>
+        <v>90625</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17822,21 +17822,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17846,10 +17846,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>492194</v>
+        <v>492267</v>
       </c>
       <c r="R165" t="n">
-        <v>7135016</v>
+        <v>7135233</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17882,11 +17882,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17913,10 +17908,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730527</v>
+        <v>129730556</v>
       </c>
       <c r="B166" t="n">
-        <v>90625</v>
+        <v>57736</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17924,21 +17919,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17948,10 +17943,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>492267</v>
+        <v>492024</v>
       </c>
       <c r="R166" t="n">
-        <v>7135233</v>
+        <v>7135131</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17984,6 +17979,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18010,7 +18010,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730592</v>
+        <v>129730547</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -18045,10 +18045,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492195</v>
+        <v>491981</v>
       </c>
       <c r="R167" t="n">
-        <v>7135016</v>
+        <v>7135158</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18520,7 +18520,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129730649</v>
+        <v>129730555</v>
       </c>
       <c r="B172" t="n">
         <v>57736</v>
@@ -18555,10 +18555,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>492466</v>
+        <v>492031</v>
       </c>
       <c r="R172" t="n">
-        <v>7134866</v>
+        <v>7135128</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18622,7 +18622,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129730555</v>
+        <v>129730567</v>
       </c>
       <c r="B173" t="n">
         <v>57736</v>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>492031</v>
+        <v>492043</v>
       </c>
       <c r="R173" t="n">
-        <v>7135128</v>
+        <v>7135115</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18724,7 +18724,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129730581</v>
+        <v>129730649</v>
       </c>
       <c r="B174" t="n">
         <v>57736</v>
@@ -18759,10 +18759,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>492090</v>
+        <v>492466</v>
       </c>
       <c r="R174" t="n">
-        <v>7135062</v>
+        <v>7134866</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18799,7 +18799,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18826,7 +18826,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129730530</v>
+        <v>129730581</v>
       </c>
       <c r="B175" t="n">
         <v>57736</v>
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>492078</v>
+        <v>492090</v>
       </c>
       <c r="R175" t="n">
-        <v>7135290</v>
+        <v>7135062</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18928,7 +18928,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129730567</v>
+        <v>129730530</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -18963,10 +18963,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>492043</v>
+        <v>492078</v>
       </c>
       <c r="R176" t="n">
-        <v>7135115</v>
+        <v>7135290</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19642,10 +19642,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129730557</v>
+        <v>129730660</v>
       </c>
       <c r="B183" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19653,23 +19653,19 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
@@ -19677,10 +19673,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>492026</v>
+        <v>492059</v>
       </c>
       <c r="R183" t="n">
-        <v>7135131</v>
+        <v>7135168</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19707,17 +19703,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19726,6 +19717,7 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19744,7 +19736,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129730537</v>
+        <v>129730653</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -19779,10 +19771,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>492037</v>
+        <v>492468</v>
       </c>
       <c r="R184" t="n">
-        <v>7135230</v>
+        <v>7134851</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19846,7 +19838,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129730653</v>
+        <v>129730537</v>
       </c>
       <c r="B185" t="n">
         <v>57736</v>
@@ -19881,10 +19873,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>492468</v>
+        <v>492037</v>
       </c>
       <c r="R185" t="n">
-        <v>7134851</v>
+        <v>7135230</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19948,7 +19940,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730636</v>
+        <v>129730572</v>
       </c>
       <c r="B186" t="n">
         <v>57736</v>
@@ -19983,10 +19975,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492435</v>
+        <v>492060</v>
       </c>
       <c r="R186" t="n">
-        <v>7134917</v>
+        <v>7135105</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20050,7 +20042,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730577</v>
+        <v>129730636</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -20085,10 +20077,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>492066</v>
+        <v>492435</v>
       </c>
       <c r="R187" t="n">
-        <v>7135097</v>
+        <v>7134917</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20125,7 +20117,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20152,7 +20144,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730654</v>
+        <v>129730577</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -20187,10 +20179,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>492462</v>
+        <v>492066</v>
       </c>
       <c r="R188" t="n">
-        <v>7134847</v>
+        <v>7135097</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20227,7 +20219,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20254,10 +20246,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129730660</v>
+        <v>129730654</v>
       </c>
       <c r="B189" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20265,19 +20257,23 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
@@ -20285,10 +20281,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>492059</v>
+        <v>492462</v>
       </c>
       <c r="R189" t="n">
-        <v>7135168</v>
+        <v>7134847</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20315,12 +20311,17 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20329,7 +20330,6 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -20348,7 +20348,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730572</v>
+        <v>129730557</v>
       </c>
       <c r="B190" t="n">
         <v>57736</v>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>492060</v>
+        <v>492026</v>
       </c>
       <c r="R190" t="n">
-        <v>7135105</v>
+        <v>7135131</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20552,10 +20552,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129730674</v>
+        <v>129730651</v>
       </c>
       <c r="B192" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20563,21 +20563,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20587,10 +20587,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>492084</v>
+        <v>492474</v>
       </c>
       <c r="R192" t="n">
-        <v>7135198</v>
+        <v>7134863</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20623,6 +20623,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20649,7 +20654,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730600</v>
+        <v>129730642</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -20684,10 +20689,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492239</v>
+        <v>492466</v>
       </c>
       <c r="R193" t="n">
-        <v>7134997</v>
+        <v>7134877</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20751,7 +20756,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730553</v>
+        <v>129730600</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -20786,10 +20791,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492008</v>
+        <v>492239</v>
       </c>
       <c r="R194" t="n">
-        <v>7135137</v>
+        <v>7134997</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20853,7 +20858,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730642</v>
+        <v>129730560</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -20888,10 +20893,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492466</v>
+        <v>492037</v>
       </c>
       <c r="R195" t="n">
-        <v>7134877</v>
+        <v>7135124</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20928,7 +20933,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20955,10 +20960,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730596</v>
+        <v>129730674</v>
       </c>
       <c r="B196" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20966,21 +20971,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20990,10 +20995,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492210</v>
+        <v>492084</v>
       </c>
       <c r="R196" t="n">
-        <v>7135013</v>
+        <v>7135198</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21026,11 +21031,6 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21057,7 +21057,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129730613</v>
+        <v>129730553</v>
       </c>
       <c r="B197" t="n">
         <v>57736</v>
@@ -21092,10 +21092,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>492341</v>
+        <v>492008</v>
       </c>
       <c r="R197" t="n">
-        <v>7134968</v>
+        <v>7135137</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21159,7 +21159,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730560</v>
+        <v>129730596</v>
       </c>
       <c r="B198" t="n">
         <v>57736</v>
@@ -21194,10 +21194,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492037</v>
+        <v>492210</v>
       </c>
       <c r="R198" t="n">
-        <v>7135124</v>
+        <v>7135013</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21261,7 +21261,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730570</v>
+        <v>129730613</v>
       </c>
       <c r="B199" t="n">
         <v>57736</v>
@@ -21296,10 +21296,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492057</v>
+        <v>492341</v>
       </c>
       <c r="R199" t="n">
-        <v>7135109</v>
+        <v>7134968</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21363,7 +21363,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730641</v>
+        <v>129730570</v>
       </c>
       <c r="B200" t="n">
         <v>57736</v>
@@ -21398,10 +21398,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492462</v>
+        <v>492057</v>
       </c>
       <c r="R200" t="n">
-        <v>7134883</v>
+        <v>7135109</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21465,7 +21465,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730621</v>
+        <v>129730641</v>
       </c>
       <c r="B201" t="n">
         <v>57736</v>
@@ -21500,10 +21500,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492355</v>
+        <v>492462</v>
       </c>
       <c r="R201" t="n">
-        <v>7134935</v>
+        <v>7134883</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21567,7 +21567,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730651</v>
+        <v>129730621</v>
       </c>
       <c r="B202" t="n">
         <v>57736</v>
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492474</v>
+        <v>492355</v>
       </c>
       <c r="R202" t="n">
-        <v>7134863</v>
+        <v>7134935</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21642,7 +21642,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21769,6 +21769,115 @@
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>129811411</v>
+      </c>
+      <c r="B204" t="n">
+        <v>58369</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>492147</v>
+      </c>
+      <c r="R204" t="n">
+        <v>7135241</v>
+      </c>
+      <c r="S204" t="n">
+        <v>100</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726748</v>
+        <v>129728237</v>
       </c>
       <c r="B5" t="n">
-        <v>78094</v>
+        <v>80187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,34 +1037,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492403</v>
+        <v>492236</v>
       </c>
       <c r="R5" t="n">
-        <v>7135004</v>
+        <v>7135034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1101,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:04</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,25 +1117,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129728258</v>
+        <v>129726742</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1168,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492272</v>
+        <v>492287</v>
       </c>
       <c r="R6" t="n">
-        <v>7135018</v>
+        <v>7135066</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,14 +1229,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1256,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726742</v>
+        <v>129726749</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1279,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492287</v>
+        <v>492403</v>
       </c>
       <c r="R7" t="n">
-        <v>7135066</v>
+        <v>7135004</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1473,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728237</v>
+        <v>129728258</v>
       </c>
       <c r="B9" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,41 +1517,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492236</v>
+        <v>492272</v>
       </c>
       <c r="R9" t="n">
-        <v>7135034</v>
+        <v>7135018</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1581,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en klen levande sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,34 +1590,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726749</v>
+        <v>129726748</v>
       </c>
       <c r="B10" t="n">
-        <v>83050</v>
+        <v>78094</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1812,7 +1812,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129728251</v>
+        <v>129728261</v>
       </c>
       <c r="B12" t="n">
         <v>79081</v>
@@ -1841,19 +1841,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492530</v>
+        <v>492451</v>
       </c>
       <c r="R12" t="n">
-        <v>7135028</v>
+        <v>7134928</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1887,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,34 +1896,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1943,7 +1914,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129728261</v>
+        <v>129728251</v>
       </c>
       <c r="B13" t="n">
         <v>79081</v>
@@ -1972,16 +1943,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492451</v>
+        <v>492530</v>
       </c>
       <c r="R13" t="n">
-        <v>7134928</v>
+        <v>7135028</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +1992,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,8 +2001,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726741</v>
+        <v>129726738</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492282</v>
+        <v>492242</v>
       </c>
       <c r="R14" t="n">
-        <v>7135069</v>
+        <v>7135130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,7 +2152,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726752</v>
+        <v>129726741</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492482</v>
+        <v>492282</v>
       </c>
       <c r="R15" t="n">
-        <v>7134934</v>
+        <v>7135069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726738</v>
+        <v>129726752</v>
       </c>
       <c r="B16" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492242</v>
+        <v>492482</v>
       </c>
       <c r="R16" t="n">
-        <v>7135130</v>
+        <v>7134934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2943,45 +2943,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726716</v>
+        <v>129728246</v>
       </c>
       <c r="B22" t="n">
-        <v>97651</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492599</v>
+        <v>492341</v>
       </c>
       <c r="R22" t="n">
-        <v>7134962</v>
+        <v>7134976</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,19 +3031,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:13</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,83 +3047,69 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129728246</v>
+        <v>129726716</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>97651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492341</v>
+        <v>492599</v>
       </c>
       <c r="R23" t="n">
-        <v>7134976</v>
+        <v>7134962</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,14 +3139,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,89 +3160,63 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129728245</v>
+        <v>129728252</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492204</v>
+        <v>492377</v>
       </c>
       <c r="R24" t="n">
-        <v>7135099</v>
+        <v>7135110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3273,7 +3253,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3282,14 +3262,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3306,7 +3280,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129728242</v>
+        <v>129728245</v>
       </c>
       <c r="B25" t="n">
         <v>98774</v>
@@ -3336,7 +3310,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3361,10 +3335,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492205</v>
+        <v>492204</v>
       </c>
       <c r="R25" t="n">
-        <v>7135151</v>
+        <v>7135099</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3401,7 +3375,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3434,45 +3408,65 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129728252</v>
+        <v>129728242</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492377</v>
+        <v>492205</v>
       </c>
       <c r="R26" t="n">
-        <v>7135110</v>
+        <v>7135151</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3509,7 +3503,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3518,8 +3512,14 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3638,7 +3638,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129726719</v>
+        <v>129726754</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492458</v>
+        <v>492511</v>
       </c>
       <c r="R28" t="n">
-        <v>7135104</v>
+        <v>7134902</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3745,7 +3745,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129726732</v>
+        <v>129726719</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492176</v>
+        <v>492458</v>
       </c>
       <c r="R29" t="n">
-        <v>7135178</v>
+        <v>7135104</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3852,7 +3852,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726754</v>
+        <v>129726732</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492511</v>
+        <v>492176</v>
       </c>
       <c r="R30" t="n">
-        <v>7134902</v>
+        <v>7135178</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4066,10 +4066,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726722</v>
+        <v>129726726</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>91766</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,38 +4077,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492376</v>
+        <v>492285</v>
       </c>
       <c r="R32" t="n">
-        <v>7135128</v>
+        <v>7135248</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4140,7 +4136,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4146,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,10 +4173,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726726</v>
+        <v>129726722</v>
       </c>
       <c r="B33" t="n">
-        <v>91766</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,34 +4184,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492285</v>
+        <v>492376</v>
       </c>
       <c r="R33" t="n">
-        <v>7135248</v>
+        <v>7135128</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,7 +4284,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129728254</v>
+        <v>129726729</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492116</v>
+        <v>492180</v>
       </c>
       <c r="R34" t="n">
-        <v>7135129</v>
+        <v>7135242</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,14 +4352,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4374,19 +4379,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726729</v>
+        <v>129728256</v>
       </c>
       <c r="B35" t="n">
         <v>79081</v>
@@ -4421,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492180</v>
+        <v>492217</v>
       </c>
       <c r="R35" t="n">
-        <v>7135242</v>
+        <v>7135029</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4454,19 +4459,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4481,12 +4481,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4595,7 +4595,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129728256</v>
+        <v>129728254</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492217</v>
+        <v>492116</v>
       </c>
       <c r="R37" t="n">
-        <v>7135029</v>
+        <v>7135129</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4697,45 +4697,65 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726750</v>
+        <v>129728243</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492416</v>
+        <v>492168</v>
       </c>
       <c r="R38" t="n">
-        <v>7135000</v>
+        <v>7135133</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4765,19 +4785,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:01</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:01</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4786,83 +4801,69 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129728243</v>
+        <v>129726750</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492168</v>
+        <v>492416</v>
       </c>
       <c r="R39" t="n">
-        <v>7135133</v>
+        <v>7135000</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4892,14 +4893,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4908,24 +4914,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726740</v>
+        <v>129728253</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492268</v>
+        <v>492341</v>
       </c>
       <c r="R43" t="n">
-        <v>7135143</v>
+        <v>7135150</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5349,19 +5349,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:25</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5376,19 +5371,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129728253</v>
+        <v>129726740</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5423,10 +5418,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492341</v>
+        <v>492268</v>
       </c>
       <c r="R44" t="n">
-        <v>7135150</v>
+        <v>7135143</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5456,14 +5451,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5478,12 +5478,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5625,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129726733</v>
+        <v>129726751</v>
       </c>
       <c r="B46" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5636,21 +5636,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492186</v>
+        <v>492457</v>
       </c>
       <c r="R46" t="n">
-        <v>7135180</v>
+        <v>7134957</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5732,10 +5732,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129726751</v>
+        <v>129726733</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5743,21 +5743,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492457</v>
+        <v>492186</v>
       </c>
       <c r="R47" t="n">
-        <v>7134957</v>
+        <v>7135180</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5946,7 +5946,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129728262</v>
+        <v>129726721</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5975,19 +5975,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492479</v>
+        <v>492421</v>
       </c>
       <c r="R49" t="n">
-        <v>7134899</v>
+        <v>7135113</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6017,14 +6014,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran i gammal barrblandskog.</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6033,51 +6035,25 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129726721</v>
+        <v>129728262</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -6106,16 +6082,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492421</v>
+        <v>492479</v>
       </c>
       <c r="R50" t="n">
-        <v>7135113</v>
+        <v>7134899</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6145,19 +6124,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,18 +6140,44 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129726727</v>
+        <v>129726718</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492258</v>
+        <v>492543</v>
       </c>
       <c r="R52" t="n">
-        <v>7135232</v>
+        <v>7135091</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6388,7 +6388,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129726718</v>
+        <v>129726727</v>
       </c>
       <c r="B53" t="n">
         <v>79081</v>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492543</v>
+        <v>492258</v>
       </c>
       <c r="R53" t="n">
-        <v>7135091</v>
+        <v>7135232</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6602,10 +6602,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129726734</v>
+        <v>129728260</v>
       </c>
       <c r="B55" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6613,19 +6613,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6633,10 +6637,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492211</v>
+        <v>492378</v>
       </c>
       <c r="R55" t="n">
-        <v>7135170</v>
+        <v>7134955</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6666,19 +6670,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6687,64 +6686,83 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129728260</v>
+        <v>129728248</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492378</v>
+        <v>492492</v>
       </c>
       <c r="R56" t="n">
-        <v>7134955</v>
+        <v>7134909</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6781,7 +6799,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6790,8 +6808,14 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6915,65 +6939,41 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129728248</v>
+        <v>129726734</v>
       </c>
       <c r="B58" t="n">
-        <v>98774</v>
+        <v>91613</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492492</v>
+        <v>492211</v>
       </c>
       <c r="R58" t="n">
-        <v>7134909</v>
+        <v>7135170</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7003,14 +7003,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7023,30 +7028,25 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129726728</v>
+        <v>129728250</v>
       </c>
       <c r="B59" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7054,21 +7054,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492179</v>
+        <v>492572</v>
       </c>
       <c r="R59" t="n">
-        <v>7135241</v>
+        <v>7135009</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7111,19 +7111,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7138,22 +7133,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726753</v>
+        <v>129726725</v>
       </c>
       <c r="B60" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7161,21 +7156,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7185,10 +7180,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492496</v>
+        <v>492304</v>
       </c>
       <c r="R60" t="n">
-        <v>7134904</v>
+        <v>7135246</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7220,7 +7215,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7230,7 +7225,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7257,10 +7252,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129728250</v>
+        <v>129726728</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7268,21 +7263,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7292,10 +7287,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492572</v>
+        <v>492179</v>
       </c>
       <c r="R61" t="n">
-        <v>7135009</v>
+        <v>7135241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7325,14 +7320,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7347,22 +7347,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726725</v>
+        <v>129726753</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492304</v>
+        <v>492496</v>
       </c>
       <c r="R62" t="n">
-        <v>7135246</v>
+        <v>7134904</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730658</v>
+        <v>129730672</v>
       </c>
       <c r="B69" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492464</v>
+        <v>492334</v>
       </c>
       <c r="R69" t="n">
-        <v>7135049</v>
+        <v>7135092</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,11 +8173,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8204,7 +8199,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730615</v>
+        <v>129730573</v>
       </c>
       <c r="B70" t="n">
         <v>57736</v>
@@ -8239,10 +8234,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492345</v>
+        <v>492062</v>
       </c>
       <c r="R70" t="n">
-        <v>7134961</v>
+        <v>7135100</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8306,10 +8301,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730672</v>
+        <v>129730584</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8317,21 +8312,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8341,10 +8336,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492334</v>
+        <v>492107</v>
       </c>
       <c r="R71" t="n">
-        <v>7135092</v>
+        <v>7135052</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8377,6 +8372,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8403,7 +8403,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730573</v>
+        <v>129730598</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -8438,10 +8438,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492062</v>
+        <v>492220</v>
       </c>
       <c r="R72" t="n">
-        <v>7135100</v>
+        <v>7135003</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8505,7 +8505,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730584</v>
+        <v>129730615</v>
       </c>
       <c r="B73" t="n">
         <v>57736</v>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492107</v>
+        <v>492345</v>
       </c>
       <c r="R73" t="n">
-        <v>7135052</v>
+        <v>7134961</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8607,10 +8607,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730598</v>
+        <v>129730658</v>
       </c>
       <c r="B74" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492220</v>
+        <v>492464</v>
       </c>
       <c r="R74" t="n">
-        <v>7135003</v>
+        <v>7135049</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129730637</v>
+        <v>129730671</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>492431</v>
+        <v>492379</v>
       </c>
       <c r="R75" t="n">
-        <v>7134907</v>
+        <v>7135129</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8780,11 +8780,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8811,7 +8806,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129730551</v>
+        <v>129730645</v>
       </c>
       <c r="B76" t="n">
         <v>57736</v>
@@ -8846,10 +8841,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>491997</v>
+        <v>492464</v>
       </c>
       <c r="R76" t="n">
-        <v>7135143</v>
+        <v>7134870</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8913,10 +8908,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129730671</v>
+        <v>129730629</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8924,21 +8919,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8948,10 +8943,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>492379</v>
+        <v>492369</v>
       </c>
       <c r="R77" t="n">
-        <v>7135129</v>
+        <v>7134915</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8984,6 +8979,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9010,7 +9010,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129730629</v>
+        <v>129730637</v>
       </c>
       <c r="B78" t="n">
         <v>57736</v>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>492369</v>
+        <v>492431</v>
       </c>
       <c r="R78" t="n">
-        <v>7134915</v>
+        <v>7134907</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9112,7 +9112,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129730645</v>
+        <v>129730551</v>
       </c>
       <c r="B79" t="n">
         <v>57736</v>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>492464</v>
+        <v>491997</v>
       </c>
       <c r="R79" t="n">
-        <v>7134870</v>
+        <v>7135143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9214,32 +9214,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730594</v>
+        <v>129730665</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492205</v>
+        <v>492046</v>
       </c>
       <c r="R80" t="n">
-        <v>7135012</v>
+        <v>7135177</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730630</v>
+        <v>129730675</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9327,21 +9327,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492411</v>
+        <v>492075</v>
       </c>
       <c r="R81" t="n">
-        <v>7134926</v>
+        <v>7135214</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9387,11 +9387,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9418,7 +9413,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730635</v>
+        <v>129730603</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -9453,10 +9448,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492424</v>
+        <v>492265</v>
       </c>
       <c r="R82" t="n">
-        <v>7134911</v>
+        <v>7134987</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9520,7 +9515,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730639</v>
+        <v>129730594</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -9555,10 +9550,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492439</v>
+        <v>492205</v>
       </c>
       <c r="R83" t="n">
-        <v>7134899</v>
+        <v>7135012</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9622,7 +9617,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730562</v>
+        <v>129730599</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -9657,10 +9652,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492037</v>
+        <v>492216</v>
       </c>
       <c r="R84" t="n">
-        <v>7135120</v>
+        <v>7135002</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9697,7 +9692,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9724,7 +9719,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730575</v>
+        <v>129730635</v>
       </c>
       <c r="B85" t="n">
         <v>57736</v>
@@ -9759,10 +9754,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492063</v>
+        <v>492424</v>
       </c>
       <c r="R85" t="n">
-        <v>7135101</v>
+        <v>7134911</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9799,7 +9794,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9826,7 +9821,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129730603</v>
+        <v>129730639</v>
       </c>
       <c r="B86" t="n">
         <v>57736</v>
@@ -9861,10 +9856,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492265</v>
+        <v>492439</v>
       </c>
       <c r="R86" t="n">
-        <v>7134987</v>
+        <v>7134899</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9928,7 +9923,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129730599</v>
+        <v>129730562</v>
       </c>
       <c r="B87" t="n">
         <v>57736</v>
@@ -9963,10 +9958,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492216</v>
+        <v>492037</v>
       </c>
       <c r="R87" t="n">
-        <v>7135002</v>
+        <v>7135120</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10003,7 +9998,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10030,32 +10025,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730665</v>
+        <v>129730575</v>
       </c>
       <c r="B88" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10065,10 +10060,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492046</v>
+        <v>492063</v>
       </c>
       <c r="R88" t="n">
-        <v>7135177</v>
+        <v>7135101</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10105,7 +10100,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>8st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10132,10 +10127,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129730675</v>
+        <v>129730630</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10143,21 +10138,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10167,10 +10162,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492075</v>
+        <v>492411</v>
       </c>
       <c r="R89" t="n">
-        <v>7135214</v>
+        <v>7134926</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10203,6 +10198,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129730661</v>
+        <v>129730522</v>
       </c>
       <c r="B94" t="n">
-        <v>91613</v>
+        <v>97020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,19 +10648,23 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10668,10 +10672,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492069</v>
+        <v>492217</v>
       </c>
       <c r="R94" t="n">
-        <v>7135162</v>
+        <v>7135249</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10698,12 +10702,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10712,7 +10716,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10731,10 +10734,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730619</v>
+        <v>129730661</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10742,23 +10745,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10766,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492353</v>
+        <v>492069</v>
       </c>
       <c r="R95" t="n">
-        <v>7134945</v>
+        <v>7135162</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10796,17 +10795,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10815,6 +10809,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10833,7 +10828,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730604</v>
+        <v>129730619</v>
       </c>
       <c r="B96" t="n">
         <v>57736</v>
@@ -10868,10 +10863,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492297</v>
+        <v>492353</v>
       </c>
       <c r="R96" t="n">
-        <v>7134975</v>
+        <v>7134945</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10908,7 +10903,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10935,10 +10930,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730522</v>
+        <v>129730606</v>
       </c>
       <c r="B97" t="n">
-        <v>97020</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10946,21 +10941,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10970,10 +10965,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492217</v>
+        <v>492303</v>
       </c>
       <c r="R97" t="n">
-        <v>7135249</v>
+        <v>7134972</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11006,6 +11001,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11032,7 +11032,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129730606</v>
+        <v>129730569</v>
       </c>
       <c r="B98" t="n">
         <v>57736</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492303</v>
+        <v>492054</v>
       </c>
       <c r="R98" t="n">
-        <v>7134972</v>
+        <v>7135107</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11134,10 +11134,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730569</v>
+        <v>129730662</v>
       </c>
       <c r="B99" t="n">
-        <v>57736</v>
+        <v>78094</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11145,21 +11145,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11169,10 +11169,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492054</v>
+        <v>492166</v>
       </c>
       <c r="R99" t="n">
-        <v>7135107</v>
+        <v>7135239</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11205,11 +11205,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11338,10 +11333,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730662</v>
+        <v>129730604</v>
       </c>
       <c r="B101" t="n">
-        <v>78094</v>
+        <v>57736</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11349,21 +11344,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11373,10 +11368,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492166</v>
+        <v>492297</v>
       </c>
       <c r="R101" t="n">
-        <v>7135239</v>
+        <v>7134975</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11409,6 +11404,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11532,7 +11532,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730640</v>
+        <v>129730656</v>
       </c>
       <c r="B103" t="n">
         <v>57736</v>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492444</v>
+        <v>492466</v>
       </c>
       <c r="R103" t="n">
-        <v>7134887</v>
+        <v>7134851</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11634,7 +11634,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730656</v>
+        <v>129730602</v>
       </c>
       <c r="B104" t="n">
         <v>57736</v>
@@ -11669,10 +11669,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492466</v>
+        <v>492245</v>
       </c>
       <c r="R104" t="n">
-        <v>7134851</v>
+        <v>7134995</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11736,7 +11736,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730602</v>
+        <v>129730640</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>492245</v>
+        <v>492444</v>
       </c>
       <c r="R105" t="n">
-        <v>7134995</v>
+        <v>7134887</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11838,10 +11838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730521</v>
+        <v>129730529</v>
       </c>
       <c r="B106" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492100</v>
+        <v>492088</v>
       </c>
       <c r="R106" t="n">
-        <v>7135216</v>
+        <v>7135198</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11909,6 +11909,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11935,7 +11940,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730529</v>
+        <v>129730532</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11970,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492088</v>
+        <v>492082</v>
       </c>
       <c r="R107" t="n">
-        <v>7135198</v>
+        <v>7135294</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12010,7 +12015,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12139,7 +12144,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730532</v>
+        <v>129730576</v>
       </c>
       <c r="B109" t="n">
         <v>57736</v>
@@ -12174,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492082</v>
+        <v>492066</v>
       </c>
       <c r="R109" t="n">
-        <v>7135294</v>
+        <v>7135093</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12214,7 +12219,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,7 +12246,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730576</v>
+        <v>129730559</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12276,10 +12281,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492066</v>
+        <v>492032</v>
       </c>
       <c r="R110" t="n">
-        <v>7135093</v>
+        <v>7135120</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12343,10 +12348,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730559</v>
+        <v>129730521</v>
       </c>
       <c r="B111" t="n">
-        <v>57736</v>
+        <v>83050</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12354,21 +12359,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12378,10 +12383,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492032</v>
+        <v>492100</v>
       </c>
       <c r="R111" t="n">
-        <v>7135120</v>
+        <v>7135216</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12414,11 +12419,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12542,7 +12542,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730617</v>
+        <v>129730608</v>
       </c>
       <c r="B113" t="n">
         <v>57736</v>
@@ -12577,10 +12577,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492349</v>
+        <v>492316</v>
       </c>
       <c r="R113" t="n">
-        <v>7134943</v>
+        <v>7134971</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12617,7 +12617,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12644,7 +12644,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730579</v>
+        <v>129730617</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -12679,10 +12679,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492080</v>
+        <v>492349</v>
       </c>
       <c r="R114" t="n">
-        <v>7135064</v>
+        <v>7134943</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12746,7 +12746,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730528</v>
+        <v>129730624</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -12781,10 +12781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492476</v>
+        <v>492366</v>
       </c>
       <c r="R115" t="n">
-        <v>7135072</v>
+        <v>7134921</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730632</v>
+        <v>129730597</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -12883,10 +12883,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>492414</v>
+        <v>492213</v>
       </c>
       <c r="R116" t="n">
-        <v>7134915</v>
+        <v>7135010</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12950,7 +12950,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730608</v>
+        <v>129730528</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -12985,10 +12985,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492316</v>
+        <v>492476</v>
       </c>
       <c r="R117" t="n">
-        <v>7134971</v>
+        <v>7135072</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13052,7 +13052,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730624</v>
+        <v>129730632</v>
       </c>
       <c r="B118" t="n">
         <v>57736</v>
@@ -13087,10 +13087,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492366</v>
+        <v>492414</v>
       </c>
       <c r="R118" t="n">
-        <v>7134921</v>
+        <v>7134915</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13154,7 +13154,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730597</v>
+        <v>129730579</v>
       </c>
       <c r="B119" t="n">
         <v>57736</v>
@@ -13189,10 +13189,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492213</v>
+        <v>492080</v>
       </c>
       <c r="R119" t="n">
-        <v>7135010</v>
+        <v>7135064</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13455,7 +13455,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730614</v>
+        <v>129730585</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -13490,10 +13490,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492342</v>
+        <v>492123</v>
       </c>
       <c r="R122" t="n">
-        <v>7134966</v>
+        <v>7135047</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13557,7 +13557,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730618</v>
+        <v>129730657</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -13592,10 +13592,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492350</v>
+        <v>492468</v>
       </c>
       <c r="R123" t="n">
-        <v>7134947</v>
+        <v>7134848</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13659,7 +13659,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730568</v>
+        <v>129730614</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -13694,10 +13694,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492044</v>
+        <v>492342</v>
       </c>
       <c r="R124" t="n">
-        <v>7135114</v>
+        <v>7134966</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730582</v>
+        <v>129730618</v>
       </c>
       <c r="B125" t="n">
         <v>57736</v>
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492094</v>
+        <v>492350</v>
       </c>
       <c r="R125" t="n">
-        <v>7135060</v>
+        <v>7134947</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13863,7 +13863,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730585</v>
+        <v>129730568</v>
       </c>
       <c r="B126" t="n">
         <v>57736</v>
@@ -13898,10 +13898,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492123</v>
+        <v>492044</v>
       </c>
       <c r="R126" t="n">
-        <v>7135047</v>
+        <v>7135114</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13965,7 +13965,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730657</v>
+        <v>129730582</v>
       </c>
       <c r="B127" t="n">
         <v>57736</v>
@@ -14000,10 +14000,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>492468</v>
+        <v>492094</v>
       </c>
       <c r="R127" t="n">
-        <v>7134848</v>
+        <v>7135060</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14169,7 +14169,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730561</v>
+        <v>129730563</v>
       </c>
       <c r="B129" t="n">
         <v>57736</v>
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>492039</v>
+        <v>492037</v>
       </c>
       <c r="R129" t="n">
-        <v>7135123</v>
+        <v>7135119</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730539</v>
+        <v>129730561</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -14306,10 +14306,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>492011</v>
+        <v>492039</v>
       </c>
       <c r="R130" t="n">
-        <v>7135206</v>
+        <v>7135123</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14373,7 +14373,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730563</v>
+        <v>129730539</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -14408,10 +14408,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>492037</v>
+        <v>492011</v>
       </c>
       <c r="R131" t="n">
-        <v>7135119</v>
+        <v>7135206</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14776,7 +14776,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730574</v>
+        <v>129730580</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>492062</v>
+        <v>492077</v>
       </c>
       <c r="R135" t="n">
-        <v>7135103</v>
+        <v>7135066</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14878,7 +14878,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730580</v>
+        <v>129730574</v>
       </c>
       <c r="B136" t="n">
         <v>57736</v>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492077</v>
+        <v>492062</v>
       </c>
       <c r="R136" t="n">
-        <v>7135066</v>
+        <v>7135103</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15179,7 +15179,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730541</v>
+        <v>129730620</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -15214,10 +15214,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492004</v>
+        <v>492351</v>
       </c>
       <c r="R139" t="n">
-        <v>7135207</v>
+        <v>7134938</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15281,7 +15281,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730535</v>
+        <v>129730541</v>
       </c>
       <c r="B140" t="n">
         <v>57736</v>
@@ -15316,10 +15316,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492065</v>
+        <v>492004</v>
       </c>
       <c r="R140" t="n">
-        <v>7135257</v>
+        <v>7135207</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15383,7 +15383,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730620</v>
+        <v>129730535</v>
       </c>
       <c r="B141" t="n">
         <v>57736</v>
@@ -15418,10 +15418,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492351</v>
+        <v>492065</v>
       </c>
       <c r="R141" t="n">
-        <v>7134938</v>
+        <v>7135257</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15485,10 +15485,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730525</v>
+        <v>129730558</v>
       </c>
       <c r="B142" t="n">
-        <v>90625</v>
+        <v>57736</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15496,21 +15496,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492390</v>
+        <v>492028</v>
       </c>
       <c r="R142" t="n">
-        <v>7135053</v>
+        <v>7135126</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15556,6 +15556,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15582,32 +15587,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730524</v>
+        <v>129730525</v>
       </c>
       <c r="B143" t="n">
-        <v>91557</v>
+        <v>90625</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15617,10 +15622,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492271</v>
+        <v>492390</v>
       </c>
       <c r="R143" t="n">
-        <v>7135240</v>
+        <v>7135053</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15679,32 +15684,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730616</v>
+        <v>129730524</v>
       </c>
       <c r="B144" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15714,10 +15719,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>492343</v>
+        <v>492271</v>
       </c>
       <c r="R144" t="n">
-        <v>7134960</v>
+        <v>7135240</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15750,11 +15755,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15985,7 +15985,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730595</v>
+        <v>129730616</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -16020,10 +16020,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>492208</v>
+        <v>492343</v>
       </c>
       <c r="R147" t="n">
-        <v>7135012</v>
+        <v>7134960</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16060,7 +16060,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16087,7 +16087,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730549</v>
+        <v>129730595</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491986</v>
+        <v>492208</v>
       </c>
       <c r="R148" t="n">
-        <v>7135153</v>
+        <v>7135012</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16393,7 +16393,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730578</v>
+        <v>129730549</v>
       </c>
       <c r="B151" t="n">
         <v>57736</v>
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>492086</v>
+        <v>491986</v>
       </c>
       <c r="R151" t="n">
-        <v>7135087</v>
+        <v>7135153</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16495,7 +16495,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730558</v>
+        <v>129730578</v>
       </c>
       <c r="B152" t="n">
         <v>57736</v>
@@ -16530,10 +16530,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492028</v>
+        <v>492086</v>
       </c>
       <c r="R152" t="n">
-        <v>7135126</v>
+        <v>7135087</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16597,7 +16597,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730601</v>
+        <v>129730552</v>
       </c>
       <c r="B153" t="n">
         <v>57736</v>
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>492240</v>
+        <v>492001</v>
       </c>
       <c r="R153" t="n">
-        <v>7134998</v>
+        <v>7135144</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16672,7 +16672,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16699,7 +16699,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730552</v>
+        <v>129730571</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -16734,10 +16734,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>492001</v>
+        <v>492057</v>
       </c>
       <c r="R154" t="n">
-        <v>7135144</v>
+        <v>7135106</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16774,7 +16774,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16801,10 +16801,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730668</v>
+        <v>129730544</v>
       </c>
       <c r="B155" t="n">
-        <v>56917</v>
+        <v>57736</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16812,16 +16812,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -16836,10 +16836,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>492293</v>
+        <v>491998</v>
       </c>
       <c r="R155" t="n">
-        <v>7134991</v>
+        <v>7135201</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16872,6 +16872,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16898,10 +16903,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129730667</v>
+        <v>129730564</v>
       </c>
       <c r="B156" t="n">
-        <v>56917</v>
+        <v>57736</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16909,16 +16914,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -16933,10 +16938,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>492088</v>
+        <v>492039</v>
       </c>
       <c r="R156" t="n">
-        <v>7135189</v>
+        <v>7135120</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16969,6 +16974,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16995,7 +17005,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730571</v>
+        <v>129730634</v>
       </c>
       <c r="B157" t="n">
         <v>57736</v>
@@ -17030,10 +17040,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>492057</v>
+        <v>492423</v>
       </c>
       <c r="R157" t="n">
-        <v>7135106</v>
+        <v>7134915</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17070,7 +17080,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17097,7 +17107,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730544</v>
+        <v>129730601</v>
       </c>
       <c r="B158" t="n">
         <v>57736</v>
@@ -17132,10 +17142,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>491998</v>
+        <v>492240</v>
       </c>
       <c r="R158" t="n">
-        <v>7135201</v>
+        <v>7134998</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17172,7 +17182,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17199,7 +17209,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730564</v>
+        <v>129730590</v>
       </c>
       <c r="B159" t="n">
         <v>57736</v>
@@ -17234,10 +17244,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>492039</v>
+        <v>492184</v>
       </c>
       <c r="R159" t="n">
-        <v>7135120</v>
+        <v>7135029</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17301,10 +17311,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730590</v>
+        <v>129730668</v>
       </c>
       <c r="B160" t="n">
-        <v>57736</v>
+        <v>56917</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17312,16 +17322,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -17336,10 +17346,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>492184</v>
+        <v>492293</v>
       </c>
       <c r="R160" t="n">
-        <v>7135029</v>
+        <v>7134991</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17372,11 +17382,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17403,10 +17408,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129730634</v>
+        <v>129730667</v>
       </c>
       <c r="B161" t="n">
-        <v>57736</v>
+        <v>56917</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17414,16 +17419,16 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -17438,10 +17443,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>492423</v>
+        <v>492088</v>
       </c>
       <c r="R161" t="n">
-        <v>7134915</v>
+        <v>7135189</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17474,11 +17479,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17505,10 +17505,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730546</v>
+        <v>129730527</v>
       </c>
       <c r="B162" t="n">
-        <v>57736</v>
+        <v>90625</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17516,21 +17516,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17540,10 +17540,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>491985</v>
+        <v>492267</v>
       </c>
       <c r="R162" t="n">
-        <v>7135158</v>
+        <v>7135233</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17576,11 +17576,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17811,10 +17806,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730527</v>
+        <v>129730547</v>
       </c>
       <c r="B165" t="n">
-        <v>90625</v>
+        <v>57736</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17822,21 +17817,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17846,10 +17841,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>492267</v>
+        <v>491981</v>
       </c>
       <c r="R165" t="n">
-        <v>7135233</v>
+        <v>7135158</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17882,6 +17877,11 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17908,7 +17908,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730556</v>
+        <v>129730546</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -17943,10 +17943,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>492024</v>
+        <v>491985</v>
       </c>
       <c r="R166" t="n">
-        <v>7135131</v>
+        <v>7135158</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17983,7 +17983,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18010,7 +18010,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730547</v>
+        <v>129730556</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -18045,10 +18045,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>491981</v>
+        <v>492024</v>
       </c>
       <c r="R167" t="n">
-        <v>7135158</v>
+        <v>7135131</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18214,7 +18214,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129730605</v>
+        <v>129730588</v>
       </c>
       <c r="B169" t="n">
         <v>57736</v>
@@ -18249,10 +18249,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>492293</v>
+        <v>492176</v>
       </c>
       <c r="R169" t="n">
-        <v>7134975</v>
+        <v>7135032</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18316,7 +18316,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129730554</v>
+        <v>129730605</v>
       </c>
       <c r="B170" t="n">
         <v>57736</v>
@@ -18351,10 +18351,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>492027</v>
+        <v>492293</v>
       </c>
       <c r="R170" t="n">
-        <v>7135130</v>
+        <v>7134975</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18418,7 +18418,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129730588</v>
+        <v>129730554</v>
       </c>
       <c r="B171" t="n">
         <v>57736</v>
@@ -18453,10 +18453,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>492176</v>
+        <v>492027</v>
       </c>
       <c r="R171" t="n">
-        <v>7135032</v>
+        <v>7135130</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18493,7 +18493,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18520,7 +18520,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129730555</v>
+        <v>129730581</v>
       </c>
       <c r="B172" t="n">
         <v>57736</v>
@@ -18555,10 +18555,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>492031</v>
+        <v>492090</v>
       </c>
       <c r="R172" t="n">
-        <v>7135128</v>
+        <v>7135062</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18595,7 +18595,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18622,7 +18622,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129730567</v>
+        <v>129730649</v>
       </c>
       <c r="B173" t="n">
         <v>57736</v>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>492043</v>
+        <v>492466</v>
       </c>
       <c r="R173" t="n">
-        <v>7135115</v>
+        <v>7134866</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18724,7 +18724,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129730649</v>
+        <v>129730530</v>
       </c>
       <c r="B174" t="n">
         <v>57736</v>
@@ -18759,10 +18759,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>492466</v>
+        <v>492078</v>
       </c>
       <c r="R174" t="n">
-        <v>7134866</v>
+        <v>7135290</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18826,7 +18826,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129730581</v>
+        <v>129730567</v>
       </c>
       <c r="B175" t="n">
         <v>57736</v>
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>492090</v>
+        <v>492043</v>
       </c>
       <c r="R175" t="n">
-        <v>7135062</v>
+        <v>7135115</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18928,7 +18928,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129730530</v>
+        <v>129730555</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -18963,10 +18963,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>492078</v>
+        <v>492031</v>
       </c>
       <c r="R176" t="n">
-        <v>7135290</v>
+        <v>7135128</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19642,10 +19642,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129730660</v>
+        <v>129730653</v>
       </c>
       <c r="B183" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19653,19 +19653,23 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
@@ -19673,10 +19677,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>492059</v>
+        <v>492468</v>
       </c>
       <c r="R183" t="n">
-        <v>7135168</v>
+        <v>7134851</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19703,12 +19707,17 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19717,7 +19726,6 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19736,7 +19744,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129730653</v>
+        <v>129730654</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -19771,10 +19779,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>492468</v>
+        <v>492462</v>
       </c>
       <c r="R184" t="n">
-        <v>7134851</v>
+        <v>7134847</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19811,7 +19819,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19838,10 +19846,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129730537</v>
+        <v>129730660</v>
       </c>
       <c r="B185" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19849,23 +19857,19 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -19873,10 +19877,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>492037</v>
+        <v>492059</v>
       </c>
       <c r="R185" t="n">
-        <v>7135230</v>
+        <v>7135168</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19903,17 +19907,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19922,6 +19921,7 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -19940,7 +19940,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730572</v>
+        <v>129730557</v>
       </c>
       <c r="B186" t="n">
         <v>57736</v>
@@ -19975,10 +19975,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492060</v>
+        <v>492026</v>
       </c>
       <c r="R186" t="n">
-        <v>7135105</v>
+        <v>7135131</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20042,7 +20042,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730636</v>
+        <v>129730537</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -20077,10 +20077,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>492435</v>
+        <v>492037</v>
       </c>
       <c r="R187" t="n">
-        <v>7134917</v>
+        <v>7135230</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20117,7 +20117,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20144,7 +20144,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730577</v>
+        <v>129730572</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -20179,10 +20179,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>492066</v>
+        <v>492060</v>
       </c>
       <c r="R188" t="n">
-        <v>7135097</v>
+        <v>7135105</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20246,7 +20246,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129730654</v>
+        <v>129730636</v>
       </c>
       <c r="B189" t="n">
         <v>57736</v>
@@ -20281,10 +20281,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>492462</v>
+        <v>492435</v>
       </c>
       <c r="R189" t="n">
-        <v>7134847</v>
+        <v>7134917</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20348,7 +20348,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730557</v>
+        <v>129730550</v>
       </c>
       <c r="B190" t="n">
         <v>57736</v>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>492026</v>
+        <v>491991</v>
       </c>
       <c r="R190" t="n">
-        <v>7135131</v>
+        <v>7135149</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20450,7 +20450,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129730550</v>
+        <v>129730577</v>
       </c>
       <c r="B191" t="n">
         <v>57736</v>
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>491991</v>
+        <v>492066</v>
       </c>
       <c r="R191" t="n">
-        <v>7135149</v>
+        <v>7135097</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20552,10 +20552,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129730651</v>
+        <v>129730674</v>
       </c>
       <c r="B192" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20563,21 +20563,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20587,10 +20587,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>492474</v>
+        <v>492084</v>
       </c>
       <c r="R192" t="n">
-        <v>7134863</v>
+        <v>7135198</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20623,11 +20623,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20756,7 +20751,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730600</v>
+        <v>129730596</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -20791,10 +20786,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492239</v>
+        <v>492210</v>
       </c>
       <c r="R194" t="n">
-        <v>7134997</v>
+        <v>7135013</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20831,7 +20826,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20858,7 +20853,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730560</v>
+        <v>129730613</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -20893,10 +20888,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492037</v>
+        <v>492341</v>
       </c>
       <c r="R195" t="n">
-        <v>7135124</v>
+        <v>7134968</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20933,7 +20928,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20960,10 +20955,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730674</v>
+        <v>129730600</v>
       </c>
       <c r="B196" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20971,21 +20966,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20995,10 +20990,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492084</v>
+        <v>492239</v>
       </c>
       <c r="R196" t="n">
-        <v>7135198</v>
+        <v>7134997</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21031,6 +21026,11 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21057,7 +21057,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129730553</v>
+        <v>129730641</v>
       </c>
       <c r="B197" t="n">
         <v>57736</v>
@@ -21092,10 +21092,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>492008</v>
+        <v>492462</v>
       </c>
       <c r="R197" t="n">
-        <v>7135137</v>
+        <v>7134883</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21159,7 +21159,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730596</v>
+        <v>129730621</v>
       </c>
       <c r="B198" t="n">
         <v>57736</v>
@@ -21194,10 +21194,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492210</v>
+        <v>492355</v>
       </c>
       <c r="R198" t="n">
-        <v>7135013</v>
+        <v>7134935</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21261,7 +21261,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730613</v>
+        <v>129730651</v>
       </c>
       <c r="B199" t="n">
         <v>57736</v>
@@ -21296,10 +21296,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492341</v>
+        <v>492474</v>
       </c>
       <c r="R199" t="n">
-        <v>7134968</v>
+        <v>7134863</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21363,7 +21363,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730570</v>
+        <v>129730560</v>
       </c>
       <c r="B200" t="n">
         <v>57736</v>
@@ -21398,10 +21398,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492057</v>
+        <v>492037</v>
       </c>
       <c r="R200" t="n">
-        <v>7135109</v>
+        <v>7135124</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21465,7 +21465,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730641</v>
+        <v>129730570</v>
       </c>
       <c r="B201" t="n">
         <v>57736</v>
@@ -21500,10 +21500,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492462</v>
+        <v>492057</v>
       </c>
       <c r="R201" t="n">
-        <v>7134883</v>
+        <v>7135109</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21567,7 +21567,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730621</v>
+        <v>129730553</v>
       </c>
       <c r="B202" t="n">
         <v>57736</v>
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492355</v>
+        <v>492008</v>
       </c>
       <c r="R202" t="n">
-        <v>7134935</v>
+        <v>7135137</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728237</v>
+        <v>129728258</v>
       </c>
       <c r="B5" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,41 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492236</v>
+        <v>492272</v>
       </c>
       <c r="R5" t="n">
-        <v>7135034</v>
+        <v>7135018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1101,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en klen levande sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,34 +1110,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1161,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726742</v>
+        <v>129728249</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1190,16 +1157,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492287</v>
+        <v>492618</v>
       </c>
       <c r="R6" t="n">
-        <v>7135066</v>
+        <v>7134954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,19 +1199,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,18 +1215,44 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1375,48 +1366,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728249</v>
+        <v>129728238</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492618</v>
+        <v>492287</v>
       </c>
       <c r="R8" t="n">
-        <v>7134954</v>
+        <v>7135150</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,45 +1439,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1506,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728258</v>
+        <v>129728237</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,34 +1474,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492272</v>
+        <v>492236</v>
       </c>
       <c r="R9" t="n">
-        <v>7135018</v>
+        <v>7135034</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,7 +1545,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,8 +1554,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1608,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726748</v>
+        <v>129726742</v>
       </c>
       <c r="B10" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1609,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492403</v>
+        <v>492287</v>
       </c>
       <c r="R10" t="n">
-        <v>7135004</v>
+        <v>7135066</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,32 +1705,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129728238</v>
+        <v>129726748</v>
       </c>
       <c r="B11" t="n">
-        <v>80214</v>
+        <v>78094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492287</v>
+        <v>492403</v>
       </c>
       <c r="R11" t="n">
-        <v>7135150</v>
+        <v>7135004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,9 +1773,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,19 +1800,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129728261</v>
+        <v>129728251</v>
       </c>
       <c r="B12" t="n">
         <v>79081</v>
@@ -1841,16 +1841,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492451</v>
+        <v>492530</v>
       </c>
       <c r="R12" t="n">
-        <v>7134928</v>
+        <v>7135028</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,7 +1890,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,8 +1899,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1914,7 +1943,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129728251</v>
+        <v>129728261</v>
       </c>
       <c r="B13" t="n">
         <v>79081</v>
@@ -1943,19 +1972,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492530</v>
+        <v>492451</v>
       </c>
       <c r="R13" t="n">
-        <v>7135028</v>
+        <v>7134928</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,7 +2018,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,34 +2027,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2045,45 +2045,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726738</v>
+        <v>129728247</v>
       </c>
       <c r="B14" t="n">
-        <v>83050</v>
+        <v>98778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492242</v>
+        <v>492455</v>
       </c>
       <c r="R14" t="n">
-        <v>7135130</v>
+        <v>7134922</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,19 +2133,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:30</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,63 +2149,89 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726741</v>
+        <v>129728244</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492282</v>
+        <v>492133</v>
       </c>
       <c r="R15" t="n">
-        <v>7135069</v>
+        <v>7135159</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,19 +2261,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,25 +2277,31 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726752</v>
+        <v>129726741</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2294,10 +2336,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492482</v>
+        <v>492282</v>
       </c>
       <c r="R16" t="n">
-        <v>7134934</v>
+        <v>7135069</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,65 +2408,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129728247</v>
+        <v>129726738</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>83050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492455</v>
+        <v>492242</v>
       </c>
       <c r="R17" t="n">
-        <v>7134922</v>
+        <v>7135130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,14 +2476,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,89 +2497,63 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129728244</v>
+        <v>129726752</v>
       </c>
       <c r="B18" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492133</v>
+        <v>492482</v>
       </c>
       <c r="R18" t="n">
-        <v>7135159</v>
+        <v>7134934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2582,14 +2583,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,34 +2604,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726723</v>
+        <v>129726736</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492370</v>
+        <v>492194</v>
       </c>
       <c r="R19" t="n">
-        <v>7135127</v>
+        <v>7135150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,7 +2729,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726744</v>
+        <v>129726723</v>
       </c>
       <c r="B20" t="n">
         <v>79081</v>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492318</v>
+        <v>492370</v>
       </c>
       <c r="R20" t="n">
-        <v>7135032</v>
+        <v>7135127</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726736</v>
+        <v>129726744</v>
       </c>
       <c r="B21" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492194</v>
+        <v>492318</v>
       </c>
       <c r="R21" t="n">
-        <v>7135150</v>
+        <v>7135032</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2946,7 +2946,7 @@
         <v>129728246</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>129726716</v>
       </c>
       <c r="B23" t="n">
-        <v>97651</v>
+        <v>97655</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>129728245</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>129728242</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129726754</v>
+        <v>129726732</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492511</v>
+        <v>492176</v>
       </c>
       <c r="R28" t="n">
-        <v>7134902</v>
+        <v>7135178</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3745,7 +3745,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129726719</v>
+        <v>129726754</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492458</v>
+        <v>492511</v>
       </c>
       <c r="R29" t="n">
-        <v>7135104</v>
+        <v>7134902</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3852,7 +3852,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726732</v>
+        <v>129726719</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492176</v>
+        <v>492458</v>
       </c>
       <c r="R30" t="n">
-        <v>7135178</v>
+        <v>7135104</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3959,32 +3959,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726737</v>
+        <v>129726726</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>91770</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492228</v>
+        <v>492285</v>
       </c>
       <c r="R31" t="n">
-        <v>7135126</v>
+        <v>7135248</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,32 +4066,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726726</v>
+        <v>129726737</v>
       </c>
       <c r="B32" t="n">
-        <v>91766</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492285</v>
+        <v>492228</v>
       </c>
       <c r="R32" t="n">
-        <v>7135248</v>
+        <v>7135126</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4176,7 +4176,7 @@
         <v>129726722</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129726729</v>
+        <v>129728254</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492180</v>
+        <v>492116</v>
       </c>
       <c r="R34" t="n">
-        <v>7135242</v>
+        <v>7135129</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,19 +4352,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4379,19 +4374,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129728256</v>
+        <v>129726729</v>
       </c>
       <c r="B35" t="n">
         <v>79081</v>
@@ -4426,10 +4421,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492217</v>
+        <v>492180</v>
       </c>
       <c r="R35" t="n">
-        <v>7135029</v>
+        <v>7135242</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4459,14 +4454,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4481,19 +4481,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129728255</v>
+        <v>129726750</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492112</v>
+        <v>492416</v>
       </c>
       <c r="R36" t="n">
-        <v>7135077</v>
+        <v>7135000</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4561,14 +4561,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,19 +4588,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129728254</v>
+        <v>129728255</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4630,10 +4635,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492116</v>
+        <v>492112</v>
       </c>
       <c r="R37" t="n">
-        <v>7135129</v>
+        <v>7135077</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4697,65 +4702,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129728243</v>
+        <v>129728256</v>
       </c>
       <c r="B38" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492168</v>
+        <v>492217</v>
       </c>
       <c r="R38" t="n">
-        <v>7135133</v>
+        <v>7135029</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4792,7 +4777,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4801,14 +4786,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4825,45 +4804,65 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726750</v>
+        <v>129728243</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492416</v>
+        <v>492168</v>
       </c>
       <c r="R39" t="n">
-        <v>7135000</v>
+        <v>7135133</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4893,19 +4892,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:01</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:01</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4914,18 +4908,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5493,7 +5493,7 @@
         <v>129728234</v>
       </c>
       <c r="B45" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129726751</v>
+        <v>129726717</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492457</v>
+        <v>492583</v>
       </c>
       <c r="R46" t="n">
-        <v>7134957</v>
+        <v>7134977</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5732,10 +5732,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129726733</v>
+        <v>129726751</v>
       </c>
       <c r="B47" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5743,21 +5743,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492186</v>
+        <v>492457</v>
       </c>
       <c r="R47" t="n">
-        <v>7135180</v>
+        <v>7134957</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129726717</v>
+        <v>129726733</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>91597</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5850,21 +5850,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492583</v>
+        <v>492186</v>
       </c>
       <c r="R48" t="n">
-        <v>7134977</v>
+        <v>7135180</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6704,65 +6704,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129728248</v>
+        <v>129726731</v>
       </c>
       <c r="B56" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492492</v>
+        <v>492137</v>
       </c>
       <c r="R56" t="n">
-        <v>7134909</v>
+        <v>7135201</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6792,14 +6772,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6808,34 +6793,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129726731</v>
+        <v>129726734</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>91617</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6843,23 +6822,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6867,10 +6842,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492137</v>
+        <v>492211</v>
       </c>
       <c r="R57" t="n">
-        <v>7135201</v>
+        <v>7135170</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6902,7 +6877,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6912,7 +6887,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6921,6 +6896,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6939,41 +6915,65 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129726734</v>
+        <v>129728248</v>
       </c>
       <c r="B58" t="n">
-        <v>91613</v>
+        <v>98778</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492211</v>
+        <v>492492</v>
       </c>
       <c r="R58" t="n">
-        <v>7135170</v>
+        <v>7134909</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7003,19 +7003,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7028,22 +7023,27 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129728250</v>
+        <v>129726725</v>
       </c>
       <c r="B59" t="n">
         <v>79081</v>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492572</v>
+        <v>492304</v>
       </c>
       <c r="R59" t="n">
-        <v>7135009</v>
+        <v>7135246</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7111,14 +7111,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7133,22 +7138,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726725</v>
+        <v>129726728</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,21 +7161,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7180,10 +7185,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492304</v>
+        <v>492179</v>
       </c>
       <c r="R60" t="n">
-        <v>7135246</v>
+        <v>7135241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7215,7 +7220,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7225,7 +7230,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7252,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129726728</v>
+        <v>129726753</v>
       </c>
       <c r="B61" t="n">
-        <v>78094</v>
+        <v>78839</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7263,21 +7268,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7287,10 +7292,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492179</v>
+        <v>492496</v>
       </c>
       <c r="R61" t="n">
-        <v>7135241</v>
+        <v>7134904</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7322,7 +7327,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7332,7 +7337,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7359,10 +7364,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726753</v>
+        <v>129728250</v>
       </c>
       <c r="B62" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7375,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7399,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492496</v>
+        <v>492572</v>
       </c>
       <c r="R62" t="n">
-        <v>7134904</v>
+        <v>7135009</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7427,19 +7432,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>08:40</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7454,12 +7454,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7568,32 +7568,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726730</v>
+        <v>129728259</v>
       </c>
       <c r="B64" t="n">
-        <v>92311</v>
+        <v>79081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492124</v>
+        <v>492317</v>
       </c>
       <c r="R64" t="n">
-        <v>7135171</v>
+        <v>7134999</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7636,19 +7636,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:53</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7663,44 +7658,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129728240</v>
+        <v>129726745</v>
       </c>
       <c r="B65" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7710,10 +7705,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492405</v>
+        <v>492367</v>
       </c>
       <c r="R65" t="n">
-        <v>7134981</v>
+        <v>7135038</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7743,14 +7738,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7765,44 +7765,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129728259</v>
+        <v>129728240</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492317</v>
+        <v>492405</v>
       </c>
       <c r="R66" t="n">
-        <v>7134999</v>
+        <v>7134981</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7879,10 +7879,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129726745</v>
+        <v>129726724</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7890,34 +7890,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492367</v>
+        <v>492343</v>
       </c>
       <c r="R67" t="n">
-        <v>7135038</v>
+        <v>7135242</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7949,7 +7958,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7959,7 +7968,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7986,54 +7995,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726724</v>
+        <v>129726730</v>
       </c>
       <c r="B68" t="n">
-        <v>57896</v>
+        <v>92315</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492343</v>
+        <v>492124</v>
       </c>
       <c r="R68" t="n">
-        <v>7135242</v>
+        <v>7135171</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730672</v>
+        <v>129730598</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492334</v>
+        <v>492220</v>
       </c>
       <c r="R69" t="n">
-        <v>7135092</v>
+        <v>7135003</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,6 +8173,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8199,7 +8204,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730573</v>
+        <v>129730615</v>
       </c>
       <c r="B70" t="n">
         <v>57736</v>
@@ -8234,10 +8239,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492062</v>
+        <v>492345</v>
       </c>
       <c r="R70" t="n">
-        <v>7135100</v>
+        <v>7134961</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8403,10 +8408,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730598</v>
+        <v>129730658</v>
       </c>
       <c r="B72" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8414,21 +8419,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8438,10 +8443,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492220</v>
+        <v>492464</v>
       </c>
       <c r="R72" t="n">
-        <v>7135003</v>
+        <v>7135049</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8478,7 +8483,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8505,10 +8510,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730615</v>
+        <v>129730672</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8516,21 +8521,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8540,10 +8545,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492345</v>
+        <v>492334</v>
       </c>
       <c r="R73" t="n">
-        <v>7134961</v>
+        <v>7135092</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8576,11 +8581,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8607,10 +8607,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730658</v>
+        <v>129730573</v>
       </c>
       <c r="B74" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492464</v>
+        <v>492062</v>
       </c>
       <c r="R74" t="n">
-        <v>7135049</v>
+        <v>7135100</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8908,7 +8908,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129730629</v>
+        <v>129730637</v>
       </c>
       <c r="B77" t="n">
         <v>57736</v>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>492369</v>
+        <v>492431</v>
       </c>
       <c r="R77" t="n">
-        <v>7134915</v>
+        <v>7134907</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9010,7 +9010,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129730637</v>
+        <v>129730551</v>
       </c>
       <c r="B78" t="n">
         <v>57736</v>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>492431</v>
+        <v>491997</v>
       </c>
       <c r="R78" t="n">
-        <v>7134907</v>
+        <v>7135143</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9112,7 +9112,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129730551</v>
+        <v>129730629</v>
       </c>
       <c r="B79" t="n">
         <v>57736</v>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>491997</v>
+        <v>492369</v>
       </c>
       <c r="R79" t="n">
-        <v>7135143</v>
+        <v>7134915</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9214,32 +9214,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730665</v>
+        <v>129730603</v>
       </c>
       <c r="B80" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492046</v>
+        <v>492265</v>
       </c>
       <c r="R80" t="n">
-        <v>7135177</v>
+        <v>7134987</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>8st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730675</v>
+        <v>129730562</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9327,21 +9327,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492075</v>
+        <v>492037</v>
       </c>
       <c r="R81" t="n">
-        <v>7135214</v>
+        <v>7135120</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9387,6 +9387,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9413,7 +9418,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730603</v>
+        <v>129730594</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -9448,10 +9453,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492265</v>
+        <v>492205</v>
       </c>
       <c r="R82" t="n">
-        <v>7134987</v>
+        <v>7135012</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9515,7 +9520,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730594</v>
+        <v>129730599</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -9550,10 +9555,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492205</v>
+        <v>492216</v>
       </c>
       <c r="R83" t="n">
-        <v>7135012</v>
+        <v>7135002</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9590,7 +9595,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9617,7 +9622,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730599</v>
+        <v>129730639</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -9652,10 +9657,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492216</v>
+        <v>492439</v>
       </c>
       <c r="R84" t="n">
-        <v>7135002</v>
+        <v>7134899</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9692,7 +9697,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9821,7 +9826,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129730639</v>
+        <v>129730575</v>
       </c>
       <c r="B86" t="n">
         <v>57736</v>
@@ -9856,10 +9861,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492439</v>
+        <v>492063</v>
       </c>
       <c r="R86" t="n">
-        <v>7134899</v>
+        <v>7135101</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9896,7 +9901,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9923,7 +9928,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129730562</v>
+        <v>129730630</v>
       </c>
       <c r="B87" t="n">
         <v>57736</v>
@@ -9958,10 +9963,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492037</v>
+        <v>492411</v>
       </c>
       <c r="R87" t="n">
-        <v>7135120</v>
+        <v>7134926</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10025,32 +10030,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730575</v>
+        <v>129730665</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10060,10 +10065,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492063</v>
+        <v>492046</v>
       </c>
       <c r="R88" t="n">
-        <v>7135101</v>
+        <v>7135177</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10100,7 +10105,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10127,10 +10132,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129730630</v>
+        <v>129730675</v>
       </c>
       <c r="B89" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10138,21 +10143,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10162,10 +10167,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492411</v>
+        <v>492075</v>
       </c>
       <c r="R89" t="n">
-        <v>7134926</v>
+        <v>7135214</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10198,11 +10203,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10229,32 +10229,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129730625</v>
+        <v>129730663</v>
       </c>
       <c r="B90" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492367</v>
+        <v>492070</v>
       </c>
       <c r="R90" t="n">
-        <v>7134920</v>
+        <v>7135173</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>14st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10433,7 +10433,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129730565</v>
+        <v>129730625</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>492040</v>
+        <v>492367</v>
       </c>
       <c r="R92" t="n">
-        <v>7135117</v>
+        <v>7134920</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10535,32 +10535,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129730663</v>
+        <v>129730565</v>
       </c>
       <c r="B93" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>492070</v>
+        <v>492040</v>
       </c>
       <c r="R93" t="n">
-        <v>7135173</v>
+        <v>7135117</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>14st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10640,7 +10640,7 @@
         <v>129730522</v>
       </c>
       <c r="B94" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10734,10 +10734,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730661</v>
+        <v>129730650</v>
       </c>
       <c r="B95" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10745,19 +10745,23 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10765,10 +10769,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492069</v>
+        <v>492473</v>
       </c>
       <c r="R95" t="n">
-        <v>7135162</v>
+        <v>7134864</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10795,12 +10799,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10809,7 +10818,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11134,10 +11142,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730662</v>
+        <v>129730604</v>
       </c>
       <c r="B99" t="n">
-        <v>78094</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11145,21 +11153,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11169,10 +11177,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492166</v>
+        <v>492297</v>
       </c>
       <c r="R99" t="n">
-        <v>7135239</v>
+        <v>7134975</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11205,6 +11213,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11231,10 +11244,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730650</v>
+        <v>129730662</v>
       </c>
       <c r="B100" t="n">
-        <v>57736</v>
+        <v>78094</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11242,21 +11255,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11266,10 +11279,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492473</v>
+        <v>492166</v>
       </c>
       <c r="R100" t="n">
-        <v>7134864</v>
+        <v>7135239</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11302,11 +11315,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11333,10 +11341,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730604</v>
+        <v>129730661</v>
       </c>
       <c r="B101" t="n">
-        <v>57736</v>
+        <v>91617</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11344,23 +11352,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11368,10 +11372,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492297</v>
+        <v>492069</v>
       </c>
       <c r="R101" t="n">
-        <v>7134975</v>
+        <v>7135162</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11398,17 +11402,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11417,6 +11416,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v>129730523</v>
       </c>
       <c r="B102" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730656</v>
+        <v>129730640</v>
       </c>
       <c r="B103" t="n">
         <v>57736</v>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492466</v>
+        <v>492444</v>
       </c>
       <c r="R103" t="n">
-        <v>7134851</v>
+        <v>7134887</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11736,7 +11736,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730640</v>
+        <v>129730656</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>492444</v>
+        <v>492466</v>
       </c>
       <c r="R105" t="n">
-        <v>7134887</v>
+        <v>7134851</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11838,10 +11838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730529</v>
+        <v>129730521</v>
       </c>
       <c r="B106" t="n">
-        <v>57736</v>
+        <v>83050</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492088</v>
+        <v>492100</v>
       </c>
       <c r="R106" t="n">
-        <v>7135198</v>
+        <v>7135216</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11909,11 +11909,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11940,7 +11935,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730532</v>
+        <v>129730559</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11975,10 +11970,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492082</v>
+        <v>492032</v>
       </c>
       <c r="R107" t="n">
-        <v>7135294</v>
+        <v>7135120</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12015,7 +12010,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12042,7 +12037,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730631</v>
+        <v>129730529</v>
       </c>
       <c r="B108" t="n">
         <v>57736</v>
@@ -12077,10 +12072,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492409</v>
+        <v>492088</v>
       </c>
       <c r="R108" t="n">
-        <v>7134918</v>
+        <v>7135198</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12117,7 +12112,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12144,7 +12139,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730576</v>
+        <v>129730532</v>
       </c>
       <c r="B109" t="n">
         <v>57736</v>
@@ -12179,10 +12174,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492066</v>
+        <v>492082</v>
       </c>
       <c r="R109" t="n">
-        <v>7135093</v>
+        <v>7135294</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12219,7 +12214,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12246,7 +12241,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730559</v>
+        <v>129730631</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12281,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492032</v>
+        <v>492409</v>
       </c>
       <c r="R110" t="n">
-        <v>7135120</v>
+        <v>7134918</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12321,7 +12316,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12348,10 +12343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730521</v>
+        <v>129730576</v>
       </c>
       <c r="B111" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12359,21 +12354,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12383,10 +12378,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492100</v>
+        <v>492066</v>
       </c>
       <c r="R111" t="n">
-        <v>7135216</v>
+        <v>7135093</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12419,6 +12414,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12448,7 +12448,7 @@
         <v>129730526</v>
       </c>
       <c r="B112" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730608</v>
+        <v>129730617</v>
       </c>
       <c r="B113" t="n">
         <v>57736</v>
@@ -12577,10 +12577,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492316</v>
+        <v>492349</v>
       </c>
       <c r="R113" t="n">
-        <v>7134971</v>
+        <v>7134943</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12617,7 +12617,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12644,7 +12644,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730617</v>
+        <v>129730624</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -12679,10 +12679,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492349</v>
+        <v>492366</v>
       </c>
       <c r="R114" t="n">
-        <v>7134943</v>
+        <v>7134921</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12746,7 +12746,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730624</v>
+        <v>129730528</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -12781,10 +12781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492366</v>
+        <v>492476</v>
       </c>
       <c r="R115" t="n">
-        <v>7134921</v>
+        <v>7135072</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12950,7 +12950,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730528</v>
+        <v>129730579</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -12985,10 +12985,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492476</v>
+        <v>492080</v>
       </c>
       <c r="R117" t="n">
-        <v>7135072</v>
+        <v>7135064</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13154,7 +13154,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730579</v>
+        <v>129730608</v>
       </c>
       <c r="B119" t="n">
         <v>57736</v>
@@ -13189,10 +13189,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492080</v>
+        <v>492316</v>
       </c>
       <c r="R119" t="n">
-        <v>7135064</v>
+        <v>7134971</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13353,7 +13353,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730587</v>
+        <v>129730585</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>492125</v>
+        <v>492123</v>
       </c>
       <c r="R121" t="n">
         <v>7135047</v>
@@ -13455,7 +13455,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730585</v>
+        <v>129730582</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -13490,10 +13490,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492123</v>
+        <v>492094</v>
       </c>
       <c r="R122" t="n">
-        <v>7135047</v>
+        <v>7135060</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13659,7 +13659,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730614</v>
+        <v>129730587</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -13694,10 +13694,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492342</v>
+        <v>492125</v>
       </c>
       <c r="R124" t="n">
-        <v>7134966</v>
+        <v>7135047</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730618</v>
+        <v>129730568</v>
       </c>
       <c r="B125" t="n">
         <v>57736</v>
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492350</v>
+        <v>492044</v>
       </c>
       <c r="R125" t="n">
-        <v>7134947</v>
+        <v>7135114</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13863,7 +13863,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730568</v>
+        <v>129730618</v>
       </c>
       <c r="B126" t="n">
         <v>57736</v>
@@ -13898,10 +13898,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492044</v>
+        <v>492350</v>
       </c>
       <c r="R126" t="n">
-        <v>7135114</v>
+        <v>7134947</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13965,7 +13965,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730582</v>
+        <v>129730614</v>
       </c>
       <c r="B127" t="n">
         <v>57736</v>
@@ -14000,10 +14000,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>492094</v>
+        <v>492342</v>
       </c>
       <c r="R127" t="n">
-        <v>7135060</v>
+        <v>7134966</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14067,7 +14067,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730643</v>
+        <v>129730539</v>
       </c>
       <c r="B128" t="n">
         <v>57736</v>
@@ -14102,10 +14102,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>492464</v>
+        <v>492011</v>
       </c>
       <c r="R128" t="n">
-        <v>7134867</v>
+        <v>7135206</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14142,7 +14142,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14271,7 +14271,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730561</v>
+        <v>129730643</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -14306,10 +14306,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>492039</v>
+        <v>492464</v>
       </c>
       <c r="R130" t="n">
-        <v>7135123</v>
+        <v>7134867</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14373,7 +14373,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730539</v>
+        <v>129730561</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -14408,10 +14408,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>492011</v>
+        <v>492039</v>
       </c>
       <c r="R131" t="n">
-        <v>7135206</v>
+        <v>7135123</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14478,7 +14478,7 @@
         <v>129730670</v>
       </c>
       <c r="B132" t="n">
-        <v>91766</v>
+        <v>91770</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730545</v>
+        <v>129730531</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491983</v>
+        <v>492083</v>
       </c>
       <c r="R133" t="n">
-        <v>7135171</v>
+        <v>7135291</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14674,7 +14674,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730531</v>
+        <v>129730574</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>492083</v>
+        <v>492062</v>
       </c>
       <c r="R134" t="n">
-        <v>7135291</v>
+        <v>7135103</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14776,7 +14776,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730580</v>
+        <v>129730545</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>492077</v>
+        <v>491983</v>
       </c>
       <c r="R135" t="n">
-        <v>7135066</v>
+        <v>7135171</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14878,7 +14878,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730574</v>
+        <v>129730580</v>
       </c>
       <c r="B136" t="n">
         <v>57736</v>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492062</v>
+        <v>492077</v>
       </c>
       <c r="R136" t="n">
-        <v>7135103</v>
+        <v>7135066</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14980,32 +14980,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129730669</v>
+        <v>129730620</v>
       </c>
       <c r="B137" t="n">
-        <v>91766</v>
+        <v>57736</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15015,10 +15015,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>492248</v>
+        <v>492351</v>
       </c>
       <c r="R137" t="n">
-        <v>7135292</v>
+        <v>7134938</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15051,6 +15051,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15077,7 +15082,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730646</v>
+        <v>129730535</v>
       </c>
       <c r="B138" t="n">
         <v>57736</v>
@@ -15112,10 +15117,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>492465</v>
+        <v>492065</v>
       </c>
       <c r="R138" t="n">
-        <v>7134871</v>
+        <v>7135257</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15179,7 +15184,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730620</v>
+        <v>129730541</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -15214,10 +15219,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492351</v>
+        <v>492004</v>
       </c>
       <c r="R139" t="n">
-        <v>7134938</v>
+        <v>7135207</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15281,7 +15286,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730541</v>
+        <v>129730646</v>
       </c>
       <c r="B140" t="n">
         <v>57736</v>
@@ -15316,10 +15321,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492004</v>
+        <v>492465</v>
       </c>
       <c r="R140" t="n">
-        <v>7135207</v>
+        <v>7134871</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15383,32 +15388,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730535</v>
+        <v>129730669</v>
       </c>
       <c r="B141" t="n">
-        <v>57736</v>
+        <v>91770</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15418,10 +15423,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492065</v>
+        <v>492248</v>
       </c>
       <c r="R141" t="n">
-        <v>7135257</v>
+        <v>7135292</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15454,11 +15459,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15485,32 +15485,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730558</v>
+        <v>129730524</v>
       </c>
       <c r="B142" t="n">
-        <v>57736</v>
+        <v>91561</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492028</v>
+        <v>492271</v>
       </c>
       <c r="R142" t="n">
-        <v>7135126</v>
+        <v>7135240</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15556,11 +15556,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15590,7 +15585,7 @@
         <v>129730525</v>
       </c>
       <c r="B143" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15684,32 +15679,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730524</v>
+        <v>129730648</v>
       </c>
       <c r="B144" t="n">
-        <v>91557</v>
+        <v>57736</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15719,10 +15714,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>492271</v>
+        <v>492457</v>
       </c>
       <c r="R144" t="n">
-        <v>7135240</v>
+        <v>7134863</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15755,6 +15750,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15781,7 +15781,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730655</v>
+        <v>129730616</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>492460</v>
+        <v>492343</v>
       </c>
       <c r="R145" t="n">
-        <v>7134849</v>
+        <v>7134960</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15883,7 +15883,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730609</v>
+        <v>129730593</v>
       </c>
       <c r="B146" t="n">
         <v>57736</v>
@@ -15918,10 +15918,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>492330</v>
+        <v>492199</v>
       </c>
       <c r="R146" t="n">
-        <v>7134971</v>
+        <v>7135015</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15985,7 +15985,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730616</v>
+        <v>129730578</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -16020,10 +16020,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>492343</v>
+        <v>492086</v>
       </c>
       <c r="R147" t="n">
-        <v>7134960</v>
+        <v>7135087</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16087,7 +16087,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730595</v>
+        <v>129730609</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>492208</v>
+        <v>492330</v>
       </c>
       <c r="R148" t="n">
-        <v>7135012</v>
+        <v>7134971</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16189,7 +16189,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730648</v>
+        <v>129730549</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -16224,10 +16224,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>492457</v>
+        <v>491986</v>
       </c>
       <c r="R149" t="n">
-        <v>7134863</v>
+        <v>7135153</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16291,7 +16291,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730593</v>
+        <v>129730655</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -16326,10 +16326,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>492199</v>
+        <v>492460</v>
       </c>
       <c r="R150" t="n">
-        <v>7135015</v>
+        <v>7134849</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16393,7 +16393,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730549</v>
+        <v>129730595</v>
       </c>
       <c r="B151" t="n">
         <v>57736</v>
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>491986</v>
+        <v>492208</v>
       </c>
       <c r="R151" t="n">
-        <v>7135153</v>
+        <v>7135012</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16495,7 +16495,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730578</v>
+        <v>129730558</v>
       </c>
       <c r="B152" t="n">
         <v>57736</v>
@@ -16530,10 +16530,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492086</v>
+        <v>492028</v>
       </c>
       <c r="R152" t="n">
-        <v>7135087</v>
+        <v>7135126</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16597,7 +16597,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730552</v>
+        <v>129730544</v>
       </c>
       <c r="B153" t="n">
         <v>57736</v>
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>492001</v>
+        <v>491998</v>
       </c>
       <c r="R153" t="n">
-        <v>7135144</v>
+        <v>7135201</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16699,7 +16699,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730571</v>
+        <v>129730590</v>
       </c>
       <c r="B154" t="n">
         <v>57736</v>
@@ -16734,10 +16734,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>492057</v>
+        <v>492184</v>
       </c>
       <c r="R154" t="n">
-        <v>7135106</v>
+        <v>7135029</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16774,7 +16774,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16801,7 +16801,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730544</v>
+        <v>129730601</v>
       </c>
       <c r="B155" t="n">
         <v>57736</v>
@@ -16836,10 +16836,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>491998</v>
+        <v>492240</v>
       </c>
       <c r="R155" t="n">
-        <v>7135201</v>
+        <v>7134998</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16903,7 +16903,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129730564</v>
+        <v>129730552</v>
       </c>
       <c r="B156" t="n">
         <v>57736</v>
@@ -16938,10 +16938,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>492039</v>
+        <v>492001</v>
       </c>
       <c r="R156" t="n">
-        <v>7135120</v>
+        <v>7135144</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17005,7 +17005,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730634</v>
+        <v>129730564</v>
       </c>
       <c r="B157" t="n">
         <v>57736</v>
@@ -17040,10 +17040,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>492423</v>
+        <v>492039</v>
       </c>
       <c r="R157" t="n">
-        <v>7134915</v>
+        <v>7135120</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17107,7 +17107,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730601</v>
+        <v>129730571</v>
       </c>
       <c r="B158" t="n">
         <v>57736</v>
@@ -17142,10 +17142,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>492240</v>
+        <v>492057</v>
       </c>
       <c r="R158" t="n">
-        <v>7134998</v>
+        <v>7135106</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17209,7 +17209,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730590</v>
+        <v>129730634</v>
       </c>
       <c r="B159" t="n">
         <v>57736</v>
@@ -17244,10 +17244,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>492184</v>
+        <v>492423</v>
       </c>
       <c r="R159" t="n">
-        <v>7135029</v>
+        <v>7134915</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17508,7 +17508,7 @@
         <v>129730527</v>
       </c>
       <c r="B162" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730592</v>
+        <v>129730547</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -17637,10 +17637,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>492195</v>
+        <v>491981</v>
       </c>
       <c r="R163" t="n">
-        <v>7135016</v>
+        <v>7135158</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17677,7 +17677,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17704,7 +17704,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730591</v>
+        <v>129730556</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -17739,10 +17739,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>492194</v>
+        <v>492024</v>
       </c>
       <c r="R164" t="n">
-        <v>7135016</v>
+        <v>7135131</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17806,7 +17806,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730547</v>
+        <v>129730591</v>
       </c>
       <c r="B165" t="n">
         <v>57736</v>
@@ -17841,10 +17841,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>491981</v>
+        <v>492194</v>
       </c>
       <c r="R165" t="n">
-        <v>7135158</v>
+        <v>7135016</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18010,7 +18010,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730556</v>
+        <v>129730592</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -18045,10 +18045,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492024</v>
+        <v>492195</v>
       </c>
       <c r="R167" t="n">
-        <v>7135131</v>
+        <v>7135016</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18112,7 +18112,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129730652</v>
+        <v>129730554</v>
       </c>
       <c r="B168" t="n">
         <v>57736</v>
@@ -18147,10 +18147,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>492473</v>
+        <v>492027</v>
       </c>
       <c r="R168" t="n">
-        <v>7134862</v>
+        <v>7135130</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18214,7 +18214,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129730588</v>
+        <v>129730605</v>
       </c>
       <c r="B169" t="n">
         <v>57736</v>
@@ -18249,10 +18249,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>492176</v>
+        <v>492293</v>
       </c>
       <c r="R169" t="n">
-        <v>7135032</v>
+        <v>7134975</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18316,7 +18316,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129730605</v>
+        <v>129730652</v>
       </c>
       <c r="B170" t="n">
         <v>57736</v>
@@ -18351,10 +18351,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>492293</v>
+        <v>492473</v>
       </c>
       <c r="R170" t="n">
-        <v>7134975</v>
+        <v>7134862</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18418,7 +18418,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129730554</v>
+        <v>129730588</v>
       </c>
       <c r="B171" t="n">
         <v>57736</v>
@@ -18453,10 +18453,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>492027</v>
+        <v>492176</v>
       </c>
       <c r="R171" t="n">
-        <v>7135130</v>
+        <v>7135032</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18493,7 +18493,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18520,7 +18520,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129730581</v>
+        <v>129730530</v>
       </c>
       <c r="B172" t="n">
         <v>57736</v>
@@ -18555,10 +18555,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>492090</v>
+        <v>492078</v>
       </c>
       <c r="R172" t="n">
-        <v>7135062</v>
+        <v>7135290</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18595,7 +18595,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18622,7 +18622,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129730649</v>
+        <v>129730567</v>
       </c>
       <c r="B173" t="n">
         <v>57736</v>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>492466</v>
+        <v>492043</v>
       </c>
       <c r="R173" t="n">
-        <v>7134866</v>
+        <v>7135115</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18724,7 +18724,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129730530</v>
+        <v>129730555</v>
       </c>
       <c r="B174" t="n">
         <v>57736</v>
@@ -18759,10 +18759,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>492078</v>
+        <v>492031</v>
       </c>
       <c r="R174" t="n">
-        <v>7135290</v>
+        <v>7135128</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18826,7 +18826,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129730567</v>
+        <v>129730649</v>
       </c>
       <c r="B175" t="n">
         <v>57736</v>
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>492043</v>
+        <v>492466</v>
       </c>
       <c r="R175" t="n">
-        <v>7135115</v>
+        <v>7134866</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18928,7 +18928,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129730555</v>
+        <v>129730581</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -18963,10 +18963,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>492031</v>
+        <v>492090</v>
       </c>
       <c r="R176" t="n">
-        <v>7135128</v>
+        <v>7135062</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19030,7 +19030,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129730586</v>
+        <v>129730607</v>
       </c>
       <c r="B177" t="n">
         <v>57736</v>
@@ -19065,10 +19065,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>492124</v>
+        <v>492312</v>
       </c>
       <c r="R177" t="n">
-        <v>7135046</v>
+        <v>7134971</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19132,7 +19132,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129730612</v>
+        <v>129730644</v>
       </c>
       <c r="B178" t="n">
         <v>57736</v>
@@ -19167,10 +19167,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>492333</v>
+        <v>492462</v>
       </c>
       <c r="R178" t="n">
-        <v>7134969</v>
+        <v>7134869</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19234,7 +19234,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129730623</v>
+        <v>129730612</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -19269,10 +19269,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>492353</v>
+        <v>492333</v>
       </c>
       <c r="R179" t="n">
-        <v>7134936</v>
+        <v>7134969</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19336,7 +19336,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129730607</v>
+        <v>129730586</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -19371,10 +19371,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>492312</v>
+        <v>492124</v>
       </c>
       <c r="R180" t="n">
-        <v>7134971</v>
+        <v>7135046</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19438,7 +19438,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129730610</v>
+        <v>129730623</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>492330</v>
+        <v>492353</v>
       </c>
       <c r="R181" t="n">
-        <v>7134972</v>
+        <v>7134936</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19540,7 +19540,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129730644</v>
+        <v>129730610</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>492462</v>
+        <v>492330</v>
       </c>
       <c r="R182" t="n">
-        <v>7134869</v>
+        <v>7134972</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19642,10 +19642,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129730653</v>
+        <v>129730660</v>
       </c>
       <c r="B183" t="n">
-        <v>57736</v>
+        <v>91617</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19653,23 +19653,19 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
@@ -19677,10 +19673,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>492468</v>
+        <v>492059</v>
       </c>
       <c r="R183" t="n">
-        <v>7134851</v>
+        <v>7135168</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19707,17 +19703,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19726,6 +19717,7 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19744,7 +19736,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129730654</v>
+        <v>129730550</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -19779,10 +19771,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>492462</v>
+        <v>491991</v>
       </c>
       <c r="R184" t="n">
-        <v>7134847</v>
+        <v>7135149</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19846,10 +19838,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129730660</v>
+        <v>129730653</v>
       </c>
       <c r="B185" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19857,19 +19849,23 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -19877,10 +19873,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>492059</v>
+        <v>492468</v>
       </c>
       <c r="R185" t="n">
-        <v>7135168</v>
+        <v>7134851</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19907,12 +19903,17 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19921,7 +19922,6 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -19940,7 +19940,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730557</v>
+        <v>129730577</v>
       </c>
       <c r="B186" t="n">
         <v>57736</v>
@@ -19975,10 +19975,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492026</v>
+        <v>492066</v>
       </c>
       <c r="R186" t="n">
-        <v>7135131</v>
+        <v>7135097</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20042,7 +20042,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730537</v>
+        <v>129730636</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -20077,10 +20077,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>492037</v>
+        <v>492435</v>
       </c>
       <c r="R187" t="n">
-        <v>7135230</v>
+        <v>7134917</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20117,7 +20117,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20144,7 +20144,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730572</v>
+        <v>129730557</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -20179,10 +20179,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>492060</v>
+        <v>492026</v>
       </c>
       <c r="R188" t="n">
-        <v>7135105</v>
+        <v>7135131</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20246,7 +20246,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129730636</v>
+        <v>129730537</v>
       </c>
       <c r="B189" t="n">
         <v>57736</v>
@@ -20281,10 +20281,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>492435</v>
+        <v>492037</v>
       </c>
       <c r="R189" t="n">
-        <v>7134917</v>
+        <v>7135230</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20348,7 +20348,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730550</v>
+        <v>129730654</v>
       </c>
       <c r="B190" t="n">
         <v>57736</v>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>491991</v>
+        <v>492462</v>
       </c>
       <c r="R190" t="n">
-        <v>7135149</v>
+        <v>7134847</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20450,7 +20450,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129730577</v>
+        <v>129730572</v>
       </c>
       <c r="B191" t="n">
         <v>57736</v>
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>492066</v>
+        <v>492060</v>
       </c>
       <c r="R191" t="n">
-        <v>7135097</v>
+        <v>7135105</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20552,10 +20552,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129730674</v>
+        <v>129730641</v>
       </c>
       <c r="B192" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20563,21 +20563,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20587,10 +20587,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>492084</v>
+        <v>492462</v>
       </c>
       <c r="R192" t="n">
-        <v>7135198</v>
+        <v>7134883</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20623,6 +20623,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20649,7 +20654,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730642</v>
+        <v>129730621</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -20684,10 +20689,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492466</v>
+        <v>492355</v>
       </c>
       <c r="R193" t="n">
-        <v>7134877</v>
+        <v>7134935</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20751,7 +20756,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730596</v>
+        <v>129730613</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -20786,10 +20791,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492210</v>
+        <v>492341</v>
       </c>
       <c r="R194" t="n">
-        <v>7135013</v>
+        <v>7134968</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20826,7 +20831,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20853,7 +20858,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730613</v>
+        <v>129730570</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -20888,10 +20893,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492341</v>
+        <v>492057</v>
       </c>
       <c r="R195" t="n">
-        <v>7134968</v>
+        <v>7135109</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20955,7 +20960,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730600</v>
+        <v>129730642</v>
       </c>
       <c r="B196" t="n">
         <v>57736</v>
@@ -20990,10 +20995,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492239</v>
+        <v>492466</v>
       </c>
       <c r="R196" t="n">
-        <v>7134997</v>
+        <v>7134877</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21057,7 +21062,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129730641</v>
+        <v>129730560</v>
       </c>
       <c r="B197" t="n">
         <v>57736</v>
@@ -21092,10 +21097,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>492462</v>
+        <v>492037</v>
       </c>
       <c r="R197" t="n">
-        <v>7134883</v>
+        <v>7135124</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21159,7 +21164,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730621</v>
+        <v>129730651</v>
       </c>
       <c r="B198" t="n">
         <v>57736</v>
@@ -21194,10 +21199,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492355</v>
+        <v>492474</v>
       </c>
       <c r="R198" t="n">
-        <v>7134935</v>
+        <v>7134863</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21234,7 +21239,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21261,7 +21266,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730651</v>
+        <v>129730553</v>
       </c>
       <c r="B199" t="n">
         <v>57736</v>
@@ -21296,10 +21301,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492474</v>
+        <v>492008</v>
       </c>
       <c r="R199" t="n">
-        <v>7134863</v>
+        <v>7135137</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21336,7 +21341,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21363,7 +21368,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730560</v>
+        <v>129730600</v>
       </c>
       <c r="B200" t="n">
         <v>57736</v>
@@ -21398,10 +21403,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492037</v>
+        <v>492239</v>
       </c>
       <c r="R200" t="n">
-        <v>7135124</v>
+        <v>7134997</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21438,7 +21443,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21465,7 +21470,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730570</v>
+        <v>129730596</v>
       </c>
       <c r="B201" t="n">
         <v>57736</v>
@@ -21500,10 +21505,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492057</v>
+        <v>492210</v>
       </c>
       <c r="R201" t="n">
-        <v>7135109</v>
+        <v>7135013</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21540,7 +21545,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21567,10 +21572,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730553</v>
+        <v>129730674</v>
       </c>
       <c r="B202" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21578,21 +21583,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21602,10 +21607,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492008</v>
+        <v>492084</v>
       </c>
       <c r="R202" t="n">
-        <v>7135137</v>
+        <v>7135198</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21638,11 +21643,6 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21672,7 +21672,7 @@
         <v>129730666</v>
       </c>
       <c r="B203" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728258</v>
+        <v>129726748</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492272</v>
+        <v>492403</v>
       </c>
       <c r="R5" t="n">
-        <v>7135018</v>
+        <v>7135004</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,14 +1094,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,19 +1121,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129728249</v>
+        <v>129728258</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1157,19 +1162,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492618</v>
+        <v>492272</v>
       </c>
       <c r="R6" t="n">
-        <v>7134954</v>
+        <v>7135018</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1208,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,34 +1217,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1259,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726749</v>
+        <v>129726742</v>
       </c>
       <c r="B7" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492403</v>
+        <v>492287</v>
       </c>
       <c r="R7" t="n">
-        <v>7135004</v>
+        <v>7135066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,45 +1342,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728238</v>
+        <v>129728249</v>
       </c>
       <c r="B8" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492287</v>
+        <v>492618</v>
       </c>
       <c r="R8" t="n">
-        <v>7135150</v>
+        <v>7134954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,14 +1418,45 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1463,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728237</v>
+        <v>129726749</v>
       </c>
       <c r="B9" t="n">
-        <v>80187</v>
+        <v>83052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,41 +1484,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492236</v>
+        <v>492403</v>
       </c>
       <c r="R9" t="n">
-        <v>7135034</v>
+        <v>7135004</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,14 +1541,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På en klen levande sälg.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,76 +1562,50 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726742</v>
+        <v>129728238</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,7 +1618,7 @@
         <v>492287</v>
       </c>
       <c r="R10" t="n">
-        <v>7135066</v>
+        <v>7135150</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,19 +1648,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,22 +1665,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726748</v>
+        <v>129728237</v>
       </c>
       <c r="B11" t="n">
-        <v>78094</v>
+        <v>80187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,34 +1688,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492403</v>
+        <v>492236</v>
       </c>
       <c r="R11" t="n">
-        <v>7135004</v>
+        <v>7135034</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,19 +1752,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:04</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,18 +1768,44 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2045,65 +2045,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129728247</v>
+        <v>129726752</v>
       </c>
       <c r="B14" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492455</v>
+        <v>492482</v>
       </c>
       <c r="R14" t="n">
-        <v>7134922</v>
+        <v>7134934</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,14 +2113,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,89 +2134,63 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129728244</v>
+        <v>129726741</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492133</v>
+        <v>492282</v>
       </c>
       <c r="R15" t="n">
-        <v>7135159</v>
+        <v>7135069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,14 +2220,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,34 +2241,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726741</v>
+        <v>129726738</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,21 +2270,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2336,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492282</v>
+        <v>492242</v>
       </c>
       <c r="R16" t="n">
-        <v>7135069</v>
+        <v>7135130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,45 +2366,65 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726738</v>
+        <v>129728247</v>
       </c>
       <c r="B17" t="n">
-        <v>83050</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492242</v>
+        <v>492455</v>
       </c>
       <c r="R17" t="n">
-        <v>7135130</v>
+        <v>7134922</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,19 +2454,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:30</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,63 +2470,89 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726752</v>
+        <v>129728244</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492482</v>
+        <v>492133</v>
       </c>
       <c r="R18" t="n">
-        <v>7134934</v>
+        <v>7135159</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,19 +2582,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>08:50</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,28 +2598,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726736</v>
+        <v>129726723</v>
       </c>
       <c r="B19" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492194</v>
+        <v>492370</v>
       </c>
       <c r="R19" t="n">
-        <v>7135150</v>
+        <v>7135127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726723</v>
+        <v>129726736</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492370</v>
+        <v>492194</v>
       </c>
       <c r="R20" t="n">
-        <v>7135127</v>
+        <v>7135150</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2946,7 +2946,7 @@
         <v>129728246</v>
       </c>
       <c r="B22" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>129726716</v>
       </c>
       <c r="B23" t="n">
-        <v>97655</v>
+        <v>97657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3178,45 +3178,65 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129728252</v>
+        <v>129728242</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492377</v>
+        <v>492205</v>
       </c>
       <c r="R24" t="n">
-        <v>7135110</v>
+        <v>7135151</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3253,7 +3273,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,8 +3282,14 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3280,65 +3306,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129728245</v>
+        <v>129728252</v>
       </c>
       <c r="B25" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492204</v>
+        <v>492377</v>
       </c>
       <c r="R25" t="n">
-        <v>7135099</v>
+        <v>7135110</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,7 +3381,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3384,14 +3390,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3408,10 +3408,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129728242</v>
+        <v>129728245</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492205</v>
+        <v>492204</v>
       </c>
       <c r="R26" t="n">
-        <v>7135151</v>
+        <v>7135099</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3536,7 +3536,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129728257</v>
+        <v>129726732</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492250</v>
+        <v>492176</v>
       </c>
       <c r="R27" t="n">
-        <v>7135035</v>
+        <v>7135178</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3604,14 +3604,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,19 +3631,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129726732</v>
+        <v>129728257</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3673,10 +3678,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492176</v>
+        <v>492250</v>
       </c>
       <c r="R28" t="n">
-        <v>7135178</v>
+        <v>7135035</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3706,19 +3711,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3733,12 +3733,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3959,32 +3959,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726726</v>
+        <v>129726737</v>
       </c>
       <c r="B31" t="n">
-        <v>91770</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492285</v>
+        <v>492228</v>
       </c>
       <c r="R31" t="n">
-        <v>7135248</v>
+        <v>7135126</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,32 +4066,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726737</v>
+        <v>129726726</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>91772</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492228</v>
+        <v>492285</v>
       </c>
       <c r="R32" t="n">
-        <v>7135126</v>
+        <v>7135248</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4176,7 +4176,7 @@
         <v>129726722</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129728254</v>
+        <v>129726729</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492116</v>
+        <v>492180</v>
       </c>
       <c r="R34" t="n">
-        <v>7135129</v>
+        <v>7135242</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,14 +4352,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4374,22 +4379,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726729</v>
+        <v>129726720</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,21 +4402,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4421,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492180</v>
+        <v>492458</v>
       </c>
       <c r="R35" t="n">
-        <v>7135242</v>
+        <v>7135104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4466,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,7 +4498,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726750</v>
+        <v>129728254</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4528,10 +4533,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492416</v>
+        <v>492116</v>
       </c>
       <c r="R36" t="n">
-        <v>7135000</v>
+        <v>7135129</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4561,19 +4566,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:01</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:01</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,12 +4588,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4804,65 +4804,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129728243</v>
+        <v>129726750</v>
       </c>
       <c r="B39" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492168</v>
+        <v>492416</v>
       </c>
       <c r="R39" t="n">
-        <v>7135133</v>
+        <v>7135000</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4892,14 +4872,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4908,69 +4893,83 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129726720</v>
+        <v>129728243</v>
       </c>
       <c r="B40" t="n">
-        <v>78094</v>
+        <v>98780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492458</v>
+        <v>492168</v>
       </c>
       <c r="R40" t="n">
-        <v>7135104</v>
+        <v>7135133</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5000,19 +4999,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:55</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5021,18 +5015,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5042,7 +5042,7 @@
         <v>129726735</v>
       </c>
       <c r="B41" t="n">
-        <v>83045</v>
+        <v>83047</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>129728234</v>
       </c>
       <c r="B45" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5625,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129726717</v>
+        <v>129726733</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5636,21 +5636,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492583</v>
+        <v>492186</v>
       </c>
       <c r="R46" t="n">
-        <v>7134977</v>
+        <v>7135180</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5732,7 +5732,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129726751</v>
+        <v>129726717</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492457</v>
+        <v>492583</v>
       </c>
       <c r="R47" t="n">
-        <v>7134957</v>
+        <v>7134977</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129726733</v>
+        <v>129726751</v>
       </c>
       <c r="B48" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5850,21 +5850,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492186</v>
+        <v>492457</v>
       </c>
       <c r="R48" t="n">
-        <v>7135180</v>
+        <v>7134957</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5946,7 +5946,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129726721</v>
+        <v>129728262</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5975,16 +5975,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492421</v>
+        <v>492479</v>
       </c>
       <c r="R49" t="n">
-        <v>7135113</v>
+        <v>7134899</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6014,19 +6017,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6035,25 +6033,51 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129728262</v>
+        <v>129726721</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -6082,19 +6106,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492479</v>
+        <v>492421</v>
       </c>
       <c r="R50" t="n">
-        <v>7134899</v>
+        <v>7135113</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6124,14 +6145,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran i gammal barrblandskog.</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6140,44 +6166,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6814,7 +6814,7 @@
         <v>129726734</v>
       </c>
       <c r="B57" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>129728248</v>
       </c>
       <c r="B58" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129726725</v>
+        <v>129728250</v>
       </c>
       <c r="B59" t="n">
         <v>79081</v>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492304</v>
+        <v>492572</v>
       </c>
       <c r="R59" t="n">
-        <v>7135246</v>
+        <v>7135009</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7111,19 +7111,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7138,22 +7133,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726728</v>
+        <v>129726725</v>
       </c>
       <c r="B60" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7161,21 +7156,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7185,10 +7180,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492179</v>
+        <v>492304</v>
       </c>
       <c r="R60" t="n">
-        <v>7135241</v>
+        <v>7135246</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7220,7 +7215,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7230,7 +7225,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7257,10 +7252,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129726753</v>
+        <v>129726728</v>
       </c>
       <c r="B61" t="n">
-        <v>78839</v>
+        <v>78094</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7268,21 +7263,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7292,10 +7287,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492496</v>
+        <v>492179</v>
       </c>
       <c r="R61" t="n">
-        <v>7134904</v>
+        <v>7135241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7327,7 +7322,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7337,7 +7332,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7364,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129728250</v>
+        <v>129726753</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7375,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7399,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492572</v>
+        <v>492496</v>
       </c>
       <c r="R62" t="n">
-        <v>7135009</v>
+        <v>7134904</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7432,14 +7427,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7454,12 +7454,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7568,32 +7568,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129728259</v>
+        <v>129726730</v>
       </c>
       <c r="B64" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492317</v>
+        <v>492124</v>
       </c>
       <c r="R64" t="n">
-        <v>7134999</v>
+        <v>7135171</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7636,14 +7636,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7658,19 +7663,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129726745</v>
+        <v>129728259</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7705,10 +7710,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492367</v>
+        <v>492317</v>
       </c>
       <c r="R65" t="n">
-        <v>7135038</v>
+        <v>7134999</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7738,19 +7743,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:12</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7765,44 +7765,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129728240</v>
+        <v>129726745</v>
       </c>
       <c r="B66" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492405</v>
+        <v>492367</v>
       </c>
       <c r="R66" t="n">
-        <v>7134981</v>
+        <v>7135038</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7845,14 +7845,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7867,66 +7872,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129726724</v>
+        <v>129728240</v>
       </c>
       <c r="B67" t="n">
-        <v>57896</v>
+        <v>80214</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492343</v>
+        <v>492405</v>
       </c>
       <c r="R67" t="n">
-        <v>7135242</v>
+        <v>7134981</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7956,19 +7952,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:28</t>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7983,57 +7974,66 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726730</v>
+        <v>129726724</v>
       </c>
       <c r="B68" t="n">
-        <v>92315</v>
+        <v>57896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492124</v>
+        <v>492343</v>
       </c>
       <c r="R68" t="n">
-        <v>7135171</v>
+        <v>7135242</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730598</v>
+        <v>129730672</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492220</v>
+        <v>492334</v>
       </c>
       <c r="R69" t="n">
-        <v>7135003</v>
+        <v>7135092</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,11 +8173,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8204,10 +8199,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730615</v>
+        <v>129730658</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8215,21 +8210,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8239,10 +8234,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492345</v>
+        <v>492464</v>
       </c>
       <c r="R70" t="n">
-        <v>7134961</v>
+        <v>7135049</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8279,7 +8274,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8306,7 +8301,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730584</v>
+        <v>129730573</v>
       </c>
       <c r="B71" t="n">
         <v>57736</v>
@@ -8341,10 +8336,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492107</v>
+        <v>492062</v>
       </c>
       <c r="R71" t="n">
-        <v>7135052</v>
+        <v>7135100</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8381,7 +8376,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8408,10 +8403,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730658</v>
+        <v>129730584</v>
       </c>
       <c r="B72" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8419,21 +8414,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8443,10 +8438,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492464</v>
+        <v>492107</v>
       </c>
       <c r="R72" t="n">
-        <v>7135049</v>
+        <v>7135052</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8483,7 +8478,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8510,10 +8505,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730672</v>
+        <v>129730598</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8521,21 +8516,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8545,10 +8540,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492334</v>
+        <v>492220</v>
       </c>
       <c r="R73" t="n">
-        <v>7135092</v>
+        <v>7135003</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8581,6 +8576,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8607,7 +8607,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730573</v>
+        <v>129730615</v>
       </c>
       <c r="B74" t="n">
         <v>57736</v>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492062</v>
+        <v>492345</v>
       </c>
       <c r="R74" t="n">
-        <v>7135100</v>
+        <v>7134961</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8806,7 +8806,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129730645</v>
+        <v>129730629</v>
       </c>
       <c r="B76" t="n">
         <v>57736</v>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>492464</v>
+        <v>492369</v>
       </c>
       <c r="R76" t="n">
-        <v>7134870</v>
+        <v>7134915</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9112,7 +9112,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129730629</v>
+        <v>129730645</v>
       </c>
       <c r="B79" t="n">
         <v>57736</v>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>492369</v>
+        <v>492464</v>
       </c>
       <c r="R79" t="n">
-        <v>7134915</v>
+        <v>7134870</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9214,7 +9214,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730603</v>
+        <v>129730594</v>
       </c>
       <c r="B80" t="n">
         <v>57736</v>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492265</v>
+        <v>492205</v>
       </c>
       <c r="R80" t="n">
-        <v>7134987</v>
+        <v>7135012</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9316,7 +9316,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730562</v>
+        <v>129730599</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492037</v>
+        <v>492216</v>
       </c>
       <c r="R81" t="n">
-        <v>7135120</v>
+        <v>7135002</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9418,7 +9418,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730594</v>
+        <v>129730635</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492205</v>
+        <v>492424</v>
       </c>
       <c r="R82" t="n">
-        <v>7135012</v>
+        <v>7134911</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9520,7 +9520,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730599</v>
+        <v>129730639</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492216</v>
+        <v>492439</v>
       </c>
       <c r="R83" t="n">
-        <v>7135002</v>
+        <v>7134899</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9622,7 +9622,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730639</v>
+        <v>129730562</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492439</v>
+        <v>492037</v>
       </c>
       <c r="R84" t="n">
-        <v>7134899</v>
+        <v>7135120</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9724,7 +9724,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730635</v>
+        <v>129730575</v>
       </c>
       <c r="B85" t="n">
         <v>57736</v>
@@ -9759,10 +9759,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492424</v>
+        <v>492063</v>
       </c>
       <c r="R85" t="n">
-        <v>7134911</v>
+        <v>7135101</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9826,7 +9826,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129730575</v>
+        <v>129730603</v>
       </c>
       <c r="B86" t="n">
         <v>57736</v>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492063</v>
+        <v>492265</v>
       </c>
       <c r="R86" t="n">
-        <v>7135101</v>
+        <v>7134987</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10033,7 +10033,7 @@
         <v>129730665</v>
       </c>
       <c r="B88" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>129730663</v>
       </c>
       <c r="B90" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129730522</v>
+        <v>129730606</v>
       </c>
       <c r="B94" t="n">
-        <v>97024</v>
+        <v>57736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10672,10 +10672,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492217</v>
+        <v>492303</v>
       </c>
       <c r="R94" t="n">
-        <v>7135249</v>
+        <v>7134972</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10708,6 +10708,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10734,7 +10739,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730650</v>
+        <v>129730619</v>
       </c>
       <c r="B95" t="n">
         <v>57736</v>
@@ -10769,10 +10774,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492473</v>
+        <v>492353</v>
       </c>
       <c r="R95" t="n">
-        <v>7134864</v>
+        <v>7134945</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10809,7 +10814,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10836,7 +10841,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730619</v>
+        <v>129730650</v>
       </c>
       <c r="B96" t="n">
         <v>57736</v>
@@ -10871,10 +10876,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492353</v>
+        <v>492473</v>
       </c>
       <c r="R96" t="n">
-        <v>7134945</v>
+        <v>7134864</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10911,7 +10916,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10938,7 +10943,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730606</v>
+        <v>129730604</v>
       </c>
       <c r="B97" t="n">
         <v>57736</v>
@@ -10973,10 +10978,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492303</v>
+        <v>492297</v>
       </c>
       <c r="R97" t="n">
-        <v>7134972</v>
+        <v>7134975</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11142,10 +11147,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730604</v>
+        <v>129730522</v>
       </c>
       <c r="B99" t="n">
-        <v>57736</v>
+        <v>97026</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11153,21 +11158,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11177,10 +11182,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492297</v>
+        <v>492217</v>
       </c>
       <c r="R99" t="n">
-        <v>7134975</v>
+        <v>7135249</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11213,11 +11218,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11244,10 +11244,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730662</v>
+        <v>129730661</v>
       </c>
       <c r="B100" t="n">
-        <v>78094</v>
+        <v>91619</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11255,23 +11255,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11279,10 +11275,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492166</v>
+        <v>492069</v>
       </c>
       <c r="R100" t="n">
-        <v>7135239</v>
+        <v>7135162</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11309,12 +11305,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11323,6 +11319,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11341,10 +11338,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730661</v>
+        <v>129730662</v>
       </c>
       <c r="B101" t="n">
-        <v>91617</v>
+        <v>78094</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11352,19 +11349,23 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11372,10 +11373,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492069</v>
+        <v>492166</v>
       </c>
       <c r="R101" t="n">
-        <v>7135162</v>
+        <v>7135239</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11402,12 +11403,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11416,7 +11417,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730523</v>
+        <v>129730656</v>
       </c>
       <c r="B102" t="n">
-        <v>97024</v>
+        <v>57736</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11446,21 +11446,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492316</v>
+        <v>492466</v>
       </c>
       <c r="R102" t="n">
-        <v>7135071</v>
+        <v>7134851</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11506,6 +11506,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11532,7 +11537,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730640</v>
+        <v>129730602</v>
       </c>
       <c r="B103" t="n">
         <v>57736</v>
@@ -11567,10 +11572,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492444</v>
+        <v>492245</v>
       </c>
       <c r="R103" t="n">
-        <v>7134887</v>
+        <v>7134995</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,10 +11639,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730602</v>
+        <v>129730523</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>97026</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11645,21 +11650,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11669,10 +11674,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492245</v>
+        <v>492316</v>
       </c>
       <c r="R104" t="n">
-        <v>7134995</v>
+        <v>7135071</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11705,11 +11710,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11736,7 +11736,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730656</v>
+        <v>129730640</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>492466</v>
+        <v>492444</v>
       </c>
       <c r="R105" t="n">
-        <v>7134851</v>
+        <v>7134887</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11838,10 +11838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730521</v>
+        <v>129730529</v>
       </c>
       <c r="B106" t="n">
-        <v>83050</v>
+        <v>57736</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492100</v>
+        <v>492088</v>
       </c>
       <c r="R106" t="n">
-        <v>7135216</v>
+        <v>7135198</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11909,6 +11909,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11935,7 +11940,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730559</v>
+        <v>129730631</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11970,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492032</v>
+        <v>492409</v>
       </c>
       <c r="R107" t="n">
-        <v>7135120</v>
+        <v>7134918</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12010,7 +12015,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12037,10 +12042,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730529</v>
+        <v>129730521</v>
       </c>
       <c r="B108" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12048,21 +12053,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12072,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492088</v>
+        <v>492100</v>
       </c>
       <c r="R108" t="n">
-        <v>7135198</v>
+        <v>7135216</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12108,11 +12113,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12241,7 +12241,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730631</v>
+        <v>129730576</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492409</v>
+        <v>492066</v>
       </c>
       <c r="R110" t="n">
-        <v>7134918</v>
+        <v>7135093</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12343,7 +12343,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730576</v>
+        <v>129730559</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492066</v>
+        <v>492032</v>
       </c>
       <c r="R111" t="n">
-        <v>7135093</v>
+        <v>7135120</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129730526</v>
+        <v>129730528</v>
       </c>
       <c r="B112" t="n">
-        <v>90629</v>
+        <v>57736</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12456,21 +12456,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>492395</v>
+        <v>492476</v>
       </c>
       <c r="R112" t="n">
-        <v>7135064</v>
+        <v>7135072</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12516,6 +12516,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12542,7 +12547,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730617</v>
+        <v>129730632</v>
       </c>
       <c r="B113" t="n">
         <v>57736</v>
@@ -12577,10 +12582,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492349</v>
+        <v>492414</v>
       </c>
       <c r="R113" t="n">
-        <v>7134943</v>
+        <v>7134915</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12617,7 +12622,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12644,7 +12649,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730624</v>
+        <v>129730608</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -12679,10 +12684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492366</v>
+        <v>492316</v>
       </c>
       <c r="R114" t="n">
-        <v>7134921</v>
+        <v>7134971</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12746,7 +12751,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730528</v>
+        <v>129730617</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -12781,10 +12786,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492476</v>
+        <v>492349</v>
       </c>
       <c r="R115" t="n">
-        <v>7135072</v>
+        <v>7134943</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12821,7 +12826,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12848,7 +12853,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730597</v>
+        <v>129730579</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -12883,10 +12888,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>492213</v>
+        <v>492080</v>
       </c>
       <c r="R116" t="n">
-        <v>7135010</v>
+        <v>7135064</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12950,7 +12955,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730579</v>
+        <v>129730624</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -12985,10 +12990,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492080</v>
+        <v>492366</v>
       </c>
       <c r="R117" t="n">
-        <v>7135064</v>
+        <v>7134921</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13052,7 +13057,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730632</v>
+        <v>129730597</v>
       </c>
       <c r="B118" t="n">
         <v>57736</v>
@@ -13087,10 +13092,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492414</v>
+        <v>492213</v>
       </c>
       <c r="R118" t="n">
-        <v>7134915</v>
+        <v>7135010</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13154,10 +13159,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730608</v>
+        <v>129730526</v>
       </c>
       <c r="B119" t="n">
-        <v>57736</v>
+        <v>90631</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13165,21 +13170,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13189,10 +13194,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492316</v>
+        <v>492395</v>
       </c>
       <c r="R119" t="n">
-        <v>7134971</v>
+        <v>7135064</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13225,11 +13230,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13353,7 +13353,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730585</v>
+        <v>129730587</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>492123</v>
+        <v>492125</v>
       </c>
       <c r="R121" t="n">
         <v>7135047</v>
@@ -13455,7 +13455,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730582</v>
+        <v>129730568</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -13490,10 +13490,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492094</v>
+        <v>492044</v>
       </c>
       <c r="R122" t="n">
-        <v>7135060</v>
+        <v>7135114</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13557,7 +13557,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730657</v>
+        <v>129730582</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -13592,10 +13592,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492468</v>
+        <v>492094</v>
       </c>
       <c r="R123" t="n">
-        <v>7134848</v>
+        <v>7135060</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13659,7 +13659,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730587</v>
+        <v>129730585</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492125</v>
+        <v>492123</v>
       </c>
       <c r="R124" t="n">
         <v>7135047</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730568</v>
+        <v>129730657</v>
       </c>
       <c r="B125" t="n">
         <v>57736</v>
@@ -13796,10 +13796,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492044</v>
+        <v>492468</v>
       </c>
       <c r="R125" t="n">
-        <v>7135114</v>
+        <v>7134848</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13863,7 +13863,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730618</v>
+        <v>129730614</v>
       </c>
       <c r="B126" t="n">
         <v>57736</v>
@@ -13898,10 +13898,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492350</v>
+        <v>492342</v>
       </c>
       <c r="R126" t="n">
-        <v>7134947</v>
+        <v>7134966</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13965,7 +13965,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730614</v>
+        <v>129730618</v>
       </c>
       <c r="B127" t="n">
         <v>57736</v>
@@ -14000,10 +14000,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>492342</v>
+        <v>492350</v>
       </c>
       <c r="R127" t="n">
-        <v>7134966</v>
+        <v>7134947</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14067,7 +14067,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730539</v>
+        <v>129730563</v>
       </c>
       <c r="B128" t="n">
         <v>57736</v>
@@ -14102,10 +14102,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>492011</v>
+        <v>492037</v>
       </c>
       <c r="R128" t="n">
-        <v>7135206</v>
+        <v>7135119</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14169,7 +14169,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730563</v>
+        <v>129730561</v>
       </c>
       <c r="B129" t="n">
         <v>57736</v>
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>492037</v>
+        <v>492039</v>
       </c>
       <c r="R129" t="n">
-        <v>7135119</v>
+        <v>7135123</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730643</v>
+        <v>129730539</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -14306,10 +14306,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>492464</v>
+        <v>492011</v>
       </c>
       <c r="R130" t="n">
-        <v>7134867</v>
+        <v>7135206</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14373,7 +14373,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730561</v>
+        <v>129730643</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -14408,10 +14408,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>492039</v>
+        <v>492464</v>
       </c>
       <c r="R131" t="n">
-        <v>7135123</v>
+        <v>7134867</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14478,7 +14478,7 @@
         <v>129730670</v>
       </c>
       <c r="B132" t="n">
-        <v>91770</v>
+        <v>91772</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730531</v>
+        <v>129730545</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>492083</v>
+        <v>491983</v>
       </c>
       <c r="R133" t="n">
-        <v>7135291</v>
+        <v>7135171</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14674,7 +14674,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730574</v>
+        <v>129730531</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>492062</v>
+        <v>492083</v>
       </c>
       <c r="R134" t="n">
-        <v>7135103</v>
+        <v>7135291</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14776,7 +14776,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730545</v>
+        <v>129730580</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491983</v>
+        <v>492077</v>
       </c>
       <c r="R135" t="n">
-        <v>7135171</v>
+        <v>7135066</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14878,7 +14878,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730580</v>
+        <v>129730574</v>
       </c>
       <c r="B136" t="n">
         <v>57736</v>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492077</v>
+        <v>492062</v>
       </c>
       <c r="R136" t="n">
-        <v>7135066</v>
+        <v>7135103</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14980,7 +14980,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129730620</v>
+        <v>129730541</v>
       </c>
       <c r="B137" t="n">
         <v>57736</v>
@@ -15015,10 +15015,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>492351</v>
+        <v>492004</v>
       </c>
       <c r="R137" t="n">
-        <v>7134938</v>
+        <v>7135207</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15184,7 +15184,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730541</v>
+        <v>129730620</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -15219,10 +15219,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492004</v>
+        <v>492351</v>
       </c>
       <c r="R139" t="n">
-        <v>7135207</v>
+        <v>7134938</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15286,32 +15286,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730646</v>
+        <v>129730669</v>
       </c>
       <c r="B140" t="n">
-        <v>57736</v>
+        <v>91772</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15321,10 +15321,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492465</v>
+        <v>492248</v>
       </c>
       <c r="R140" t="n">
-        <v>7134871</v>
+        <v>7135292</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15357,11 +15357,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15388,32 +15383,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730669</v>
+        <v>129730646</v>
       </c>
       <c r="B141" t="n">
-        <v>91770</v>
+        <v>57736</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15423,10 +15418,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492248</v>
+        <v>492465</v>
       </c>
       <c r="R141" t="n">
-        <v>7135292</v>
+        <v>7134871</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15459,6 +15454,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15485,32 +15485,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730524</v>
+        <v>129730525</v>
       </c>
       <c r="B142" t="n">
-        <v>91561</v>
+        <v>90631</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492271</v>
+        <v>492390</v>
       </c>
       <c r="R142" t="n">
-        <v>7135240</v>
+        <v>7135053</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15582,10 +15582,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730525</v>
+        <v>129730655</v>
       </c>
       <c r="B143" t="n">
-        <v>90629</v>
+        <v>57736</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15593,21 +15593,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15617,10 +15617,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492390</v>
+        <v>492460</v>
       </c>
       <c r="R143" t="n">
-        <v>7135053</v>
+        <v>7134849</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15653,6 +15653,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15679,7 +15684,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730648</v>
+        <v>129730558</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -15714,10 +15719,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>492457</v>
+        <v>492028</v>
       </c>
       <c r="R144" t="n">
-        <v>7134863</v>
+        <v>7135126</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15781,7 +15786,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730616</v>
+        <v>129730609</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -15816,10 +15821,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>492343</v>
+        <v>492330</v>
       </c>
       <c r="R145" t="n">
-        <v>7134960</v>
+        <v>7134971</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15856,7 +15861,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15883,7 +15888,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730593</v>
+        <v>129730616</v>
       </c>
       <c r="B146" t="n">
         <v>57736</v>
@@ -15918,10 +15923,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>492199</v>
+        <v>492343</v>
       </c>
       <c r="R146" t="n">
-        <v>7135015</v>
+        <v>7134960</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15985,7 +15990,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730578</v>
+        <v>129730595</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -16020,10 +16025,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>492086</v>
+        <v>492208</v>
       </c>
       <c r="R147" t="n">
-        <v>7135087</v>
+        <v>7135012</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16060,7 +16065,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16087,7 +16092,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730609</v>
+        <v>129730549</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -16122,10 +16127,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>492330</v>
+        <v>491986</v>
       </c>
       <c r="R148" t="n">
-        <v>7134971</v>
+        <v>7135153</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16162,7 +16167,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16189,7 +16194,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730549</v>
+        <v>129730648</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -16224,10 +16229,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491986</v>
+        <v>492457</v>
       </c>
       <c r="R149" t="n">
-        <v>7135153</v>
+        <v>7134863</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16264,7 +16269,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16291,7 +16296,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730655</v>
+        <v>129730593</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -16326,10 +16331,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>492460</v>
+        <v>492199</v>
       </c>
       <c r="R150" t="n">
-        <v>7134849</v>
+        <v>7135015</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16393,7 +16398,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730595</v>
+        <v>129730578</v>
       </c>
       <c r="B151" t="n">
         <v>57736</v>
@@ -16428,10 +16433,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>492208</v>
+        <v>492086</v>
       </c>
       <c r="R151" t="n">
-        <v>7135012</v>
+        <v>7135087</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16468,7 +16473,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16495,32 +16500,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730558</v>
+        <v>129730524</v>
       </c>
       <c r="B152" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16530,10 +16535,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492028</v>
+        <v>492271</v>
       </c>
       <c r="R152" t="n">
-        <v>7135126</v>
+        <v>7135240</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16566,11 +16571,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16597,10 +16597,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730544</v>
+        <v>129730668</v>
       </c>
       <c r="B153" t="n">
-        <v>57736</v>
+        <v>56917</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16608,16 +16608,16 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>491998</v>
+        <v>492293</v>
       </c>
       <c r="R153" t="n">
-        <v>7135201</v>
+        <v>7134991</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16668,11 +16668,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16699,10 +16694,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730590</v>
+        <v>129730667</v>
       </c>
       <c r="B154" t="n">
-        <v>57736</v>
+        <v>56917</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16710,16 +16705,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -16734,10 +16729,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>492184</v>
+        <v>492088</v>
       </c>
       <c r="R154" t="n">
-        <v>7135029</v>
+        <v>7135189</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16770,11 +16765,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17005,7 +16995,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730564</v>
+        <v>129730571</v>
       </c>
       <c r="B157" t="n">
         <v>57736</v>
@@ -17040,10 +17030,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>492039</v>
+        <v>492057</v>
       </c>
       <c r="R157" t="n">
-        <v>7135120</v>
+        <v>7135106</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17080,7 +17070,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17107,7 +17097,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730571</v>
+        <v>129730544</v>
       </c>
       <c r="B158" t="n">
         <v>57736</v>
@@ -17142,10 +17132,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>492057</v>
+        <v>491998</v>
       </c>
       <c r="R158" t="n">
-        <v>7135106</v>
+        <v>7135201</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17182,7 +17172,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17209,7 +17199,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730634</v>
+        <v>129730564</v>
       </c>
       <c r="B159" t="n">
         <v>57736</v>
@@ -17244,10 +17234,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>492423</v>
+        <v>492039</v>
       </c>
       <c r="R159" t="n">
-        <v>7134915</v>
+        <v>7135120</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17311,10 +17301,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730668</v>
+        <v>129730590</v>
       </c>
       <c r="B160" t="n">
-        <v>56917</v>
+        <v>57736</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17322,16 +17312,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -17346,10 +17336,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>492293</v>
+        <v>492184</v>
       </c>
       <c r="R160" t="n">
-        <v>7134991</v>
+        <v>7135029</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17382,6 +17372,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17408,10 +17403,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129730667</v>
+        <v>129730634</v>
       </c>
       <c r="B161" t="n">
-        <v>56917</v>
+        <v>57736</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17419,16 +17414,16 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -17443,10 +17438,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>492088</v>
+        <v>492423</v>
       </c>
       <c r="R161" t="n">
-        <v>7135189</v>
+        <v>7134915</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17479,6 +17474,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17505,10 +17505,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730527</v>
+        <v>129730547</v>
       </c>
       <c r="B162" t="n">
-        <v>90629</v>
+        <v>57736</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17516,21 +17516,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17540,10 +17540,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>492267</v>
+        <v>491981</v>
       </c>
       <c r="R162" t="n">
-        <v>7135233</v>
+        <v>7135158</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17576,6 +17576,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17602,7 +17607,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730547</v>
+        <v>129730592</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -17637,10 +17642,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>491981</v>
+        <v>492195</v>
       </c>
       <c r="R163" t="n">
-        <v>7135158</v>
+        <v>7135016</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17677,7 +17682,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17704,7 +17709,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730556</v>
+        <v>129730591</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -17739,10 +17744,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>492024</v>
+        <v>492194</v>
       </c>
       <c r="R164" t="n">
-        <v>7135131</v>
+        <v>7135016</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17806,10 +17811,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730591</v>
+        <v>129730527</v>
       </c>
       <c r="B165" t="n">
-        <v>57736</v>
+        <v>90631</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17817,21 +17822,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17841,10 +17846,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>492194</v>
+        <v>492267</v>
       </c>
       <c r="R165" t="n">
-        <v>7135016</v>
+        <v>7135233</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17877,11 +17882,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18010,7 +18010,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730592</v>
+        <v>129730556</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -18045,10 +18045,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492195</v>
+        <v>492024</v>
       </c>
       <c r="R167" t="n">
-        <v>7135016</v>
+        <v>7135131</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18112,7 +18112,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129730554</v>
+        <v>129730652</v>
       </c>
       <c r="B168" t="n">
         <v>57736</v>
@@ -18147,10 +18147,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>492027</v>
+        <v>492473</v>
       </c>
       <c r="R168" t="n">
-        <v>7135130</v>
+        <v>7134862</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18316,7 +18316,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129730652</v>
+        <v>129730554</v>
       </c>
       <c r="B170" t="n">
         <v>57736</v>
@@ -18351,10 +18351,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>492473</v>
+        <v>492027</v>
       </c>
       <c r="R170" t="n">
-        <v>7134862</v>
+        <v>7135130</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18520,7 +18520,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129730530</v>
+        <v>129730567</v>
       </c>
       <c r="B172" t="n">
         <v>57736</v>
@@ -18555,10 +18555,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>492078</v>
+        <v>492043</v>
       </c>
       <c r="R172" t="n">
-        <v>7135290</v>
+        <v>7135115</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18622,7 +18622,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129730567</v>
+        <v>129730649</v>
       </c>
       <c r="B173" t="n">
         <v>57736</v>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>492043</v>
+        <v>492466</v>
       </c>
       <c r="R173" t="n">
-        <v>7135115</v>
+        <v>7134866</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18826,7 +18826,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129730649</v>
+        <v>129730581</v>
       </c>
       <c r="B175" t="n">
         <v>57736</v>
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>492466</v>
+        <v>492090</v>
       </c>
       <c r="R175" t="n">
-        <v>7134866</v>
+        <v>7135062</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18928,7 +18928,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129730581</v>
+        <v>129730530</v>
       </c>
       <c r="B176" t="n">
         <v>57736</v>
@@ -18963,10 +18963,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>492090</v>
+        <v>492078</v>
       </c>
       <c r="R176" t="n">
-        <v>7135062</v>
+        <v>7135290</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19030,7 +19030,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129730607</v>
+        <v>129730623</v>
       </c>
       <c r="B177" t="n">
         <v>57736</v>
@@ -19065,10 +19065,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>492312</v>
+        <v>492353</v>
       </c>
       <c r="R177" t="n">
-        <v>7134971</v>
+        <v>7134936</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19234,7 +19234,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129730612</v>
+        <v>129730611</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -19309,7 +19309,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19438,7 +19438,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129730623</v>
+        <v>129730607</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>492353</v>
+        <v>492312</v>
       </c>
       <c r="R181" t="n">
-        <v>7134936</v>
+        <v>7134971</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19513,7 +19513,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19645,7 +19645,7 @@
         <v>129730660</v>
       </c>
       <c r="B183" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129730550</v>
+        <v>129730572</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -19771,10 +19771,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>491991</v>
+        <v>492060</v>
       </c>
       <c r="R184" t="n">
-        <v>7135149</v>
+        <v>7135105</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19940,7 +19940,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730577</v>
+        <v>129730636</v>
       </c>
       <c r="B186" t="n">
         <v>57736</v>
@@ -19975,10 +19975,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492066</v>
+        <v>492435</v>
       </c>
       <c r="R186" t="n">
-        <v>7135097</v>
+        <v>7134917</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20042,7 +20042,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730636</v>
+        <v>129730550</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -20077,10 +20077,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>492435</v>
+        <v>491991</v>
       </c>
       <c r="R187" t="n">
-        <v>7134917</v>
+        <v>7135149</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20144,7 +20144,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730557</v>
+        <v>129730577</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -20179,10 +20179,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>492026</v>
+        <v>492066</v>
       </c>
       <c r="R188" t="n">
-        <v>7135131</v>
+        <v>7135097</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20246,7 +20246,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129730537</v>
+        <v>129730654</v>
       </c>
       <c r="B189" t="n">
         <v>57736</v>
@@ -20281,10 +20281,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>492037</v>
+        <v>492462</v>
       </c>
       <c r="R189" t="n">
-        <v>7135230</v>
+        <v>7134847</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20348,7 +20348,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730654</v>
+        <v>129730557</v>
       </c>
       <c r="B190" t="n">
         <v>57736</v>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>492462</v>
+        <v>492026</v>
       </c>
       <c r="R190" t="n">
-        <v>7134847</v>
+        <v>7135131</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20450,7 +20450,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129730572</v>
+        <v>129730537</v>
       </c>
       <c r="B191" t="n">
         <v>57736</v>
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>492060</v>
+        <v>492037</v>
       </c>
       <c r="R191" t="n">
-        <v>7135105</v>
+        <v>7135230</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20552,7 +20552,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129730641</v>
+        <v>129730553</v>
       </c>
       <c r="B192" t="n">
         <v>57736</v>
@@ -20587,10 +20587,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>492462</v>
+        <v>492008</v>
       </c>
       <c r="R192" t="n">
-        <v>7134883</v>
+        <v>7135137</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20627,7 +20627,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20654,7 +20654,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730621</v>
+        <v>129730642</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -20689,10 +20689,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492355</v>
+        <v>492466</v>
       </c>
       <c r="R193" t="n">
-        <v>7134935</v>
+        <v>7134877</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20756,7 +20756,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730613</v>
+        <v>129730596</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -20791,10 +20791,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492341</v>
+        <v>492210</v>
       </c>
       <c r="R194" t="n">
-        <v>7134968</v>
+        <v>7135013</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20831,7 +20831,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20858,7 +20858,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730570</v>
+        <v>129730613</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -20893,10 +20893,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492057</v>
+        <v>492341</v>
       </c>
       <c r="R195" t="n">
-        <v>7135109</v>
+        <v>7134968</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20960,7 +20960,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730642</v>
+        <v>129730600</v>
       </c>
       <c r="B196" t="n">
         <v>57736</v>
@@ -20995,10 +20995,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492466</v>
+        <v>492239</v>
       </c>
       <c r="R196" t="n">
-        <v>7134877</v>
+        <v>7134997</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21164,7 +21164,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730651</v>
+        <v>129730570</v>
       </c>
       <c r="B198" t="n">
         <v>57736</v>
@@ -21199,10 +21199,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492474</v>
+        <v>492057</v>
       </c>
       <c r="R198" t="n">
-        <v>7134863</v>
+        <v>7135109</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21239,7 +21239,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21266,7 +21266,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730553</v>
+        <v>129730621</v>
       </c>
       <c r="B199" t="n">
         <v>57736</v>
@@ -21301,10 +21301,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492008</v>
+        <v>492355</v>
       </c>
       <c r="R199" t="n">
-        <v>7135137</v>
+        <v>7134935</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21368,7 +21368,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730600</v>
+        <v>129730651</v>
       </c>
       <c r="B200" t="n">
         <v>57736</v>
@@ -21403,10 +21403,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492239</v>
+        <v>492474</v>
       </c>
       <c r="R200" t="n">
-        <v>7134997</v>
+        <v>7134863</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21443,7 +21443,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21470,32 +21470,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730596</v>
+        <v>129730666</v>
       </c>
       <c r="B201" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21505,10 +21505,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492210</v>
+        <v>492253</v>
       </c>
       <c r="R201" t="n">
-        <v>7135013</v>
+        <v>7135293</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>7st</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21669,32 +21669,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129730666</v>
+        <v>129730641</v>
       </c>
       <c r="B203" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21704,10 +21704,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>492253</v>
+        <v>492462</v>
       </c>
       <c r="R203" t="n">
-        <v>7135293</v>
+        <v>7134883</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21744,7 +21744,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>7st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD203" t="b">

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726748</v>
+        <v>129728237</v>
       </c>
       <c r="B5" t="n">
-        <v>78094</v>
+        <v>80187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,34 +1037,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492403</v>
+        <v>492236</v>
       </c>
       <c r="R5" t="n">
-        <v>7135004</v>
+        <v>7135034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1101,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:04</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,18 +1117,44 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1677,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129728237</v>
+        <v>129726748</v>
       </c>
       <c r="B11" t="n">
-        <v>80187</v>
+        <v>78094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,41 +1716,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492236</v>
+        <v>492403</v>
       </c>
       <c r="R11" t="n">
-        <v>7135034</v>
+        <v>7135004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,14 +1773,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en klen levande sälg.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,44 +1794,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726723</v>
+        <v>129726744</v>
       </c>
       <c r="B19" t="n">
         <v>79081</v>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492370</v>
+        <v>492318</v>
       </c>
       <c r="R19" t="n">
-        <v>7135127</v>
+        <v>7135032</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726736</v>
+        <v>129726723</v>
       </c>
       <c r="B20" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492194</v>
+        <v>492370</v>
       </c>
       <c r="R20" t="n">
-        <v>7135150</v>
+        <v>7135127</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726744</v>
+        <v>129726736</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492318</v>
+        <v>492194</v>
       </c>
       <c r="R21" t="n">
-        <v>7135032</v>
+        <v>7135150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,65 +3178,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129728242</v>
+        <v>129728252</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492205</v>
+        <v>492377</v>
       </c>
       <c r="R24" t="n">
-        <v>7135151</v>
+        <v>7135110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3273,7 +3253,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3282,14 +3262,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3306,45 +3280,65 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129728252</v>
+        <v>129728245</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492377</v>
+        <v>492204</v>
       </c>
       <c r="R25" t="n">
-        <v>7135110</v>
+        <v>7135099</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3381,7 +3375,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3390,8 +3384,14 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3408,7 +3408,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129728245</v>
+        <v>129728242</v>
       </c>
       <c r="B26" t="n">
         <v>98780</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492204</v>
+        <v>492205</v>
       </c>
       <c r="R26" t="n">
-        <v>7135099</v>
+        <v>7135151</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
+          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -7568,45 +7568,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726730</v>
+        <v>129726724</v>
       </c>
       <c r="B64" t="n">
-        <v>92317</v>
+        <v>57896</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492124</v>
+        <v>492343</v>
       </c>
       <c r="R64" t="n">
-        <v>7135171</v>
+        <v>7135242</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7638,7 +7647,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7648,7 +7657,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7884,10 +7893,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129728240</v>
+        <v>129726730</v>
       </c>
       <c r="B67" t="n">
-        <v>80214</v>
+        <v>92317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7895,21 +7904,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7919,10 +7928,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492405</v>
+        <v>492124</v>
       </c>
       <c r="R67" t="n">
-        <v>7134981</v>
+        <v>7135171</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7952,14 +7961,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7974,66 +7988,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726724</v>
+        <v>129728240</v>
       </c>
       <c r="B68" t="n">
-        <v>57896</v>
+        <v>80214</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492343</v>
+        <v>492405</v>
       </c>
       <c r="R68" t="n">
-        <v>7135242</v>
+        <v>7134981</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8063,19 +8068,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:28</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8090,22 +8090,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730672</v>
+        <v>129730573</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492334</v>
+        <v>492062</v>
       </c>
       <c r="R69" t="n">
-        <v>7135092</v>
+        <v>7135100</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,6 +8173,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8199,10 +8204,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730658</v>
+        <v>129730584</v>
       </c>
       <c r="B70" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8210,21 +8215,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8234,10 +8239,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492464</v>
+        <v>492107</v>
       </c>
       <c r="R70" t="n">
-        <v>7135049</v>
+        <v>7135052</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8274,7 +8279,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8301,7 +8306,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730573</v>
+        <v>129730598</v>
       </c>
       <c r="B71" t="n">
         <v>57736</v>
@@ -8336,10 +8341,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492062</v>
+        <v>492220</v>
       </c>
       <c r="R71" t="n">
-        <v>7135100</v>
+        <v>7135003</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8376,7 +8381,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8403,7 +8408,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730584</v>
+        <v>129730615</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -8438,10 +8443,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492107</v>
+        <v>492345</v>
       </c>
       <c r="R72" t="n">
-        <v>7135052</v>
+        <v>7134961</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8478,7 +8483,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8505,10 +8510,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730598</v>
+        <v>129730658</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8516,21 +8521,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8540,10 +8545,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492220</v>
+        <v>492464</v>
       </c>
       <c r="R73" t="n">
-        <v>7135003</v>
+        <v>7135049</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8580,7 +8585,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8607,10 +8612,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730615</v>
+        <v>129730672</v>
       </c>
       <c r="B74" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8618,21 +8623,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8642,10 +8647,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492345</v>
+        <v>492334</v>
       </c>
       <c r="R74" t="n">
-        <v>7134961</v>
+        <v>7135092</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8678,11 +8683,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9214,10 +9214,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730594</v>
+        <v>129730675</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9225,21 +9225,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492205</v>
+        <v>492075</v>
       </c>
       <c r="R80" t="n">
-        <v>7135012</v>
+        <v>7135214</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9285,11 +9285,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,7 +9311,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730599</v>
+        <v>129730635</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -9351,10 +9346,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492216</v>
+        <v>492424</v>
       </c>
       <c r="R81" t="n">
-        <v>7135002</v>
+        <v>7134911</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9391,7 +9386,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9418,7 +9413,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730635</v>
+        <v>129730639</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -9453,10 +9448,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492424</v>
+        <v>492439</v>
       </c>
       <c r="R82" t="n">
-        <v>7134911</v>
+        <v>7134899</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9520,7 +9515,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730639</v>
+        <v>129730562</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -9555,10 +9550,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492439</v>
+        <v>492037</v>
       </c>
       <c r="R83" t="n">
-        <v>7134899</v>
+        <v>7135120</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9622,7 +9617,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730562</v>
+        <v>129730575</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -9657,10 +9652,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492037</v>
+        <v>492063</v>
       </c>
       <c r="R84" t="n">
-        <v>7135120</v>
+        <v>7135101</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9697,7 +9692,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9724,7 +9719,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730575</v>
+        <v>129730603</v>
       </c>
       <c r="B85" t="n">
         <v>57736</v>
@@ -9759,10 +9754,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492063</v>
+        <v>492265</v>
       </c>
       <c r="R85" t="n">
-        <v>7135101</v>
+        <v>7134987</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9799,7 +9794,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9826,7 +9821,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129730603</v>
+        <v>129730594</v>
       </c>
       <c r="B86" t="n">
         <v>57736</v>
@@ -9861,10 +9856,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492265</v>
+        <v>492205</v>
       </c>
       <c r="R86" t="n">
-        <v>7134987</v>
+        <v>7135012</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9928,7 +9923,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129730630</v>
+        <v>129730599</v>
       </c>
       <c r="B87" t="n">
         <v>57736</v>
@@ -9963,10 +9958,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492411</v>
+        <v>492216</v>
       </c>
       <c r="R87" t="n">
-        <v>7134926</v>
+        <v>7135002</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10003,7 +9998,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10030,32 +10025,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730665</v>
+        <v>129730630</v>
       </c>
       <c r="B88" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10065,10 +10060,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492046</v>
+        <v>492411</v>
       </c>
       <c r="R88" t="n">
-        <v>7135177</v>
+        <v>7134926</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10105,7 +10100,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>8st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10132,32 +10127,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129730675</v>
+        <v>129730665</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10167,10 +10162,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492075</v>
+        <v>492046</v>
       </c>
       <c r="R89" t="n">
-        <v>7135214</v>
+        <v>7135177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10203,6 +10198,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10229,32 +10229,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129730663</v>
+        <v>129730583</v>
       </c>
       <c r="B90" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492070</v>
+        <v>492105</v>
       </c>
       <c r="R90" t="n">
-        <v>7135173</v>
+        <v>7135051</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>14st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,7 +10331,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129730583</v>
+        <v>129730625</v>
       </c>
       <c r="B91" t="n">
         <v>57736</v>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492105</v>
+        <v>492367</v>
       </c>
       <c r="R91" t="n">
-        <v>7135051</v>
+        <v>7134920</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10433,7 +10433,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129730625</v>
+        <v>129730565</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>492367</v>
+        <v>492040</v>
       </c>
       <c r="R92" t="n">
-        <v>7134920</v>
+        <v>7135117</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10535,32 +10535,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129730565</v>
+        <v>129730663</v>
       </c>
       <c r="B93" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>492040</v>
+        <v>492070</v>
       </c>
       <c r="R93" t="n">
-        <v>7135117</v>
+        <v>7135173</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>14st</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11838,7 +11838,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730529</v>
+        <v>129730532</v>
       </c>
       <c r="B106" t="n">
         <v>57736</v>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492088</v>
+        <v>492082</v>
       </c>
       <c r="R106" t="n">
-        <v>7135198</v>
+        <v>7135294</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11940,7 +11940,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730631</v>
+        <v>129730576</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492409</v>
+        <v>492066</v>
       </c>
       <c r="R107" t="n">
-        <v>7134918</v>
+        <v>7135093</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12042,10 +12042,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730521</v>
+        <v>129730559</v>
       </c>
       <c r="B108" t="n">
-        <v>83052</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12053,21 +12053,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12077,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492100</v>
+        <v>492032</v>
       </c>
       <c r="R108" t="n">
-        <v>7135216</v>
+        <v>7135120</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12113,6 +12113,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12139,10 +12144,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730532</v>
+        <v>129730521</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12150,21 +12155,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12174,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492082</v>
+        <v>492100</v>
       </c>
       <c r="R109" t="n">
-        <v>7135294</v>
+        <v>7135216</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12210,11 +12215,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,7 +12241,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730576</v>
+        <v>129730529</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492066</v>
+        <v>492088</v>
       </c>
       <c r="R110" t="n">
-        <v>7135093</v>
+        <v>7135198</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12343,7 +12343,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730559</v>
+        <v>129730631</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492032</v>
+        <v>492409</v>
       </c>
       <c r="R111" t="n">
-        <v>7135120</v>
+        <v>7134918</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12445,7 +12445,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129730528</v>
+        <v>129730579</v>
       </c>
       <c r="B112" t="n">
         <v>57736</v>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>492476</v>
+        <v>492080</v>
       </c>
       <c r="R112" t="n">
-        <v>7135072</v>
+        <v>7135064</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12547,7 +12547,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730632</v>
+        <v>129730624</v>
       </c>
       <c r="B113" t="n">
         <v>57736</v>
@@ -12582,10 +12582,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492414</v>
+        <v>492366</v>
       </c>
       <c r="R113" t="n">
-        <v>7134915</v>
+        <v>7134921</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12649,7 +12649,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730608</v>
+        <v>129730597</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -12684,10 +12684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492316</v>
+        <v>492213</v>
       </c>
       <c r="R114" t="n">
-        <v>7134971</v>
+        <v>7135010</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12751,10 +12751,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730617</v>
+        <v>129730526</v>
       </c>
       <c r="B115" t="n">
-        <v>57736</v>
+        <v>90631</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12762,21 +12762,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12786,10 +12786,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492349</v>
+        <v>492395</v>
       </c>
       <c r="R115" t="n">
-        <v>7134943</v>
+        <v>7135064</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12822,11 +12822,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12853,7 +12848,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730579</v>
+        <v>129730528</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -12888,10 +12883,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>492080</v>
+        <v>492476</v>
       </c>
       <c r="R116" t="n">
-        <v>7135064</v>
+        <v>7135072</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12955,7 +12950,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730624</v>
+        <v>129730632</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -12990,10 +12985,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492366</v>
+        <v>492414</v>
       </c>
       <c r="R117" t="n">
-        <v>7134921</v>
+        <v>7134915</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13057,7 +13052,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730597</v>
+        <v>129730608</v>
       </c>
       <c r="B118" t="n">
         <v>57736</v>
@@ -13092,10 +13087,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492213</v>
+        <v>492316</v>
       </c>
       <c r="R118" t="n">
-        <v>7135010</v>
+        <v>7134971</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13159,10 +13154,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730526</v>
+        <v>129730617</v>
       </c>
       <c r="B119" t="n">
-        <v>90631</v>
+        <v>57736</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13170,21 +13165,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13194,10 +13189,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492395</v>
+        <v>492349</v>
       </c>
       <c r="R119" t="n">
-        <v>7135064</v>
+        <v>7134943</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13230,6 +13225,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14169,7 +14169,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730561</v>
+        <v>129730643</v>
       </c>
       <c r="B129" t="n">
         <v>57736</v>
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>492039</v>
+        <v>492464</v>
       </c>
       <c r="R129" t="n">
-        <v>7135123</v>
+        <v>7134867</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14271,7 +14271,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730539</v>
+        <v>129730561</v>
       </c>
       <c r="B130" t="n">
         <v>57736</v>
@@ -14306,10 +14306,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>492011</v>
+        <v>492039</v>
       </c>
       <c r="R130" t="n">
-        <v>7135206</v>
+        <v>7135123</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14373,7 +14373,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730643</v>
+        <v>129730539</v>
       </c>
       <c r="B131" t="n">
         <v>57736</v>
@@ -14408,10 +14408,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>492464</v>
+        <v>492011</v>
       </c>
       <c r="R131" t="n">
-        <v>7134867</v>
+        <v>7135206</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14475,32 +14475,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730670</v>
+        <v>129730545</v>
       </c>
       <c r="B132" t="n">
-        <v>91772</v>
+        <v>57736</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>492219</v>
+        <v>491983</v>
       </c>
       <c r="R132" t="n">
-        <v>7135247</v>
+        <v>7135171</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14546,6 +14546,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14572,7 +14577,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730545</v>
+        <v>129730531</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -14607,10 +14612,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491983</v>
+        <v>492083</v>
       </c>
       <c r="R133" t="n">
-        <v>7135171</v>
+        <v>7135291</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14674,7 +14679,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730531</v>
+        <v>129730580</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -14709,10 +14714,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>492083</v>
+        <v>492077</v>
       </c>
       <c r="R134" t="n">
-        <v>7135291</v>
+        <v>7135066</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14776,7 +14781,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730580</v>
+        <v>129730574</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -14811,10 +14816,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>492077</v>
+        <v>492062</v>
       </c>
       <c r="R135" t="n">
-        <v>7135066</v>
+        <v>7135103</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14878,32 +14883,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730574</v>
+        <v>129730670</v>
       </c>
       <c r="B136" t="n">
-        <v>57736</v>
+        <v>91772</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14913,10 +14918,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492062</v>
+        <v>492219</v>
       </c>
       <c r="R136" t="n">
-        <v>7135103</v>
+        <v>7135247</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14949,11 +14954,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -19736,7 +19736,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129730572</v>
+        <v>129730557</v>
       </c>
       <c r="B184" t="n">
         <v>57736</v>
@@ -19771,10 +19771,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>492060</v>
+        <v>492026</v>
       </c>
       <c r="R184" t="n">
-        <v>7135105</v>
+        <v>7135131</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19838,7 +19838,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129730653</v>
+        <v>129730537</v>
       </c>
       <c r="B185" t="n">
         <v>57736</v>
@@ -19873,10 +19873,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>492468</v>
+        <v>492037</v>
       </c>
       <c r="R185" t="n">
-        <v>7134851</v>
+        <v>7135230</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19940,7 +19940,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730636</v>
+        <v>129730572</v>
       </c>
       <c r="B186" t="n">
         <v>57736</v>
@@ -19975,10 +19975,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492435</v>
+        <v>492060</v>
       </c>
       <c r="R186" t="n">
-        <v>7134917</v>
+        <v>7135105</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20042,7 +20042,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730550</v>
+        <v>129730653</v>
       </c>
       <c r="B187" t="n">
         <v>57736</v>
@@ -20077,10 +20077,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>491991</v>
+        <v>492468</v>
       </c>
       <c r="R187" t="n">
-        <v>7135149</v>
+        <v>7134851</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20117,7 +20117,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20144,7 +20144,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730577</v>
+        <v>129730636</v>
       </c>
       <c r="B188" t="n">
         <v>57736</v>
@@ -20179,10 +20179,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>492066</v>
+        <v>492435</v>
       </c>
       <c r="R188" t="n">
-        <v>7135097</v>
+        <v>7134917</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20246,7 +20246,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129730654</v>
+        <v>129730550</v>
       </c>
       <c r="B189" t="n">
         <v>57736</v>
@@ -20281,10 +20281,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>492462</v>
+        <v>491991</v>
       </c>
       <c r="R189" t="n">
-        <v>7134847</v>
+        <v>7135149</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20348,7 +20348,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730557</v>
+        <v>129730577</v>
       </c>
       <c r="B190" t="n">
         <v>57736</v>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>492026</v>
+        <v>492066</v>
       </c>
       <c r="R190" t="n">
-        <v>7135131</v>
+        <v>7135097</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20450,7 +20450,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129730537</v>
+        <v>129730654</v>
       </c>
       <c r="B191" t="n">
         <v>57736</v>
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>492037</v>
+        <v>492462</v>
       </c>
       <c r="R191" t="n">
-        <v>7135230</v>
+        <v>7134847</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD191" t="b">

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728237</v>
+        <v>129728258</v>
       </c>
       <c r="B5" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,41 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492236</v>
+        <v>492272</v>
       </c>
       <c r="R5" t="n">
-        <v>7135034</v>
+        <v>7135018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1101,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en klen levande sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,34 +1110,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1161,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129728258</v>
+        <v>129726742</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1196,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492272</v>
+        <v>492287</v>
       </c>
       <c r="R6" t="n">
-        <v>7135018</v>
+        <v>7135066</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,14 +1196,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,19 +1223,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726742</v>
+        <v>129728249</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1292,16 +1264,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492287</v>
+        <v>492618</v>
       </c>
       <c r="R7" t="n">
-        <v>7135066</v>
+        <v>7134954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,19 +1306,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,28 +1322,54 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728249</v>
+        <v>129726749</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,37 +1377,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492618</v>
+        <v>492403</v>
       </c>
       <c r="R8" t="n">
-        <v>7134954</v>
+        <v>7135004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,14 +1434,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,76 +1455,50 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726749</v>
+        <v>129728238</v>
       </c>
       <c r="B9" t="n">
-        <v>83052</v>
+        <v>80214</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1536,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492403</v>
+        <v>492287</v>
       </c>
       <c r="R9" t="n">
-        <v>7135004</v>
+        <v>7135150</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,19 +1541,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,44 +1558,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129728238</v>
+        <v>129726748</v>
       </c>
       <c r="B10" t="n">
-        <v>80214</v>
+        <v>78094</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1605,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492287</v>
+        <v>492403</v>
       </c>
       <c r="R10" t="n">
-        <v>7135150</v>
+        <v>7135004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,9 +1638,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,22 +1665,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726748</v>
+        <v>129728237</v>
       </c>
       <c r="B11" t="n">
-        <v>78094</v>
+        <v>80187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,34 +1688,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492403</v>
+        <v>492236</v>
       </c>
       <c r="R11" t="n">
-        <v>7135004</v>
+        <v>7135034</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,19 +1752,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:04</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,18 +1768,44 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726744</v>
+        <v>129726723</v>
       </c>
       <c r="B19" t="n">
         <v>79081</v>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492318</v>
+        <v>492370</v>
       </c>
       <c r="R19" t="n">
-        <v>7135032</v>
+        <v>7135127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726723</v>
+        <v>129726736</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492370</v>
+        <v>492194</v>
       </c>
       <c r="R20" t="n">
-        <v>7135127</v>
+        <v>7135150</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726736</v>
+        <v>129726744</v>
       </c>
       <c r="B21" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492194</v>
+        <v>492318</v>
       </c>
       <c r="R21" t="n">
-        <v>7135150</v>
+        <v>7135032</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3959,32 +3959,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726737</v>
+        <v>129726726</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>91772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492228</v>
+        <v>492285</v>
       </c>
       <c r="R31" t="n">
-        <v>7135126</v>
+        <v>7135248</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,10 +4066,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726726</v>
+        <v>129726722</v>
       </c>
       <c r="B32" t="n">
-        <v>91772</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,34 +4077,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492285</v>
+        <v>492376</v>
       </c>
       <c r="R32" t="n">
-        <v>7135248</v>
+        <v>7135128</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4146,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4173,49 +4177,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726722</v>
+        <v>129726737</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492376</v>
+        <v>492228</v>
       </c>
       <c r="R33" t="n">
-        <v>7135128</v>
+        <v>7135126</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -7043,10 +7043,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129728250</v>
+        <v>129726728</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7054,21 +7054,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492572</v>
+        <v>492179</v>
       </c>
       <c r="R59" t="n">
-        <v>7135009</v>
+        <v>7135241</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7111,14 +7111,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7133,22 +7138,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726725</v>
+        <v>129726753</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,21 +7161,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7180,10 +7185,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492304</v>
+        <v>492496</v>
       </c>
       <c r="R60" t="n">
-        <v>7135246</v>
+        <v>7134904</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7215,7 +7220,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7225,7 +7230,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7252,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129726728</v>
+        <v>129728250</v>
       </c>
       <c r="B61" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7263,21 +7268,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7287,10 +7292,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492179</v>
+        <v>492572</v>
       </c>
       <c r="R61" t="n">
-        <v>7135241</v>
+        <v>7135009</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7320,19 +7325,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7347,22 +7347,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726753</v>
+        <v>129726725</v>
       </c>
       <c r="B62" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492496</v>
+        <v>492304</v>
       </c>
       <c r="R62" t="n">
-        <v>7134904</v>
+        <v>7135246</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9214,10 +9214,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730675</v>
+        <v>129730594</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9225,21 +9225,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492075</v>
+        <v>492205</v>
       </c>
       <c r="R80" t="n">
-        <v>7135214</v>
+        <v>7135012</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9285,6 +9285,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9311,7 +9316,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730635</v>
+        <v>129730599</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -9346,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492424</v>
+        <v>492216</v>
       </c>
       <c r="R81" t="n">
-        <v>7134911</v>
+        <v>7135002</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9386,7 +9391,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9413,7 +9418,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730639</v>
+        <v>129730635</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -9448,10 +9453,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492439</v>
+        <v>492424</v>
       </c>
       <c r="R82" t="n">
-        <v>7134899</v>
+        <v>7134911</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9515,7 +9520,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730562</v>
+        <v>129730639</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -9550,10 +9555,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492037</v>
+        <v>492439</v>
       </c>
       <c r="R83" t="n">
-        <v>7135120</v>
+        <v>7134899</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9617,7 +9622,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730575</v>
+        <v>129730562</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -9652,10 +9657,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492063</v>
+        <v>492037</v>
       </c>
       <c r="R84" t="n">
-        <v>7135101</v>
+        <v>7135120</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9692,7 +9697,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9719,7 +9724,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730603</v>
+        <v>129730575</v>
       </c>
       <c r="B85" t="n">
         <v>57736</v>
@@ -9754,10 +9759,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492265</v>
+        <v>492063</v>
       </c>
       <c r="R85" t="n">
-        <v>7134987</v>
+        <v>7135101</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9794,7 +9799,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9821,7 +9826,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129730594</v>
+        <v>129730603</v>
       </c>
       <c r="B86" t="n">
         <v>57736</v>
@@ -9856,10 +9861,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492205</v>
+        <v>492265</v>
       </c>
       <c r="R86" t="n">
-        <v>7135012</v>
+        <v>7134987</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9923,7 +9928,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129730599</v>
+        <v>129730630</v>
       </c>
       <c r="B87" t="n">
         <v>57736</v>
@@ -9958,10 +9963,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492216</v>
+        <v>492411</v>
       </c>
       <c r="R87" t="n">
-        <v>7135002</v>
+        <v>7134926</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9998,7 +10003,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10025,32 +10030,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730630</v>
+        <v>129730665</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10060,10 +10065,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492411</v>
+        <v>492046</v>
       </c>
       <c r="R88" t="n">
-        <v>7134926</v>
+        <v>7135177</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10100,7 +10105,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10127,32 +10132,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129730665</v>
+        <v>129730675</v>
       </c>
       <c r="B89" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10162,10 +10167,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492046</v>
+        <v>492075</v>
       </c>
       <c r="R89" t="n">
-        <v>7135177</v>
+        <v>7135214</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10198,11 +10203,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>8st</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11838,7 +11838,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730532</v>
+        <v>129730529</v>
       </c>
       <c r="B106" t="n">
         <v>57736</v>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492082</v>
+        <v>492088</v>
       </c>
       <c r="R106" t="n">
-        <v>7135294</v>
+        <v>7135198</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11940,7 +11940,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730576</v>
+        <v>129730631</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492066</v>
+        <v>492409</v>
       </c>
       <c r="R107" t="n">
-        <v>7135093</v>
+        <v>7134918</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12042,10 +12042,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730559</v>
+        <v>129730521</v>
       </c>
       <c r="B108" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12053,21 +12053,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12077,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492032</v>
+        <v>492100</v>
       </c>
       <c r="R108" t="n">
-        <v>7135120</v>
+        <v>7135216</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12113,11 +12113,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12144,10 +12139,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730521</v>
+        <v>129730532</v>
       </c>
       <c r="B109" t="n">
-        <v>83052</v>
+        <v>57736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12155,21 +12150,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12179,10 +12174,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492100</v>
+        <v>492082</v>
       </c>
       <c r="R109" t="n">
-        <v>7135216</v>
+        <v>7135294</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12215,6 +12210,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,7 +12241,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730529</v>
+        <v>129730576</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492088</v>
+        <v>492066</v>
       </c>
       <c r="R110" t="n">
-        <v>7135198</v>
+        <v>7135093</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12343,7 +12343,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730631</v>
+        <v>129730559</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492409</v>
+        <v>492032</v>
       </c>
       <c r="R111" t="n">
-        <v>7134918</v>
+        <v>7135120</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129730579</v>
+        <v>129730526</v>
       </c>
       <c r="B112" t="n">
-        <v>57736</v>
+        <v>90631</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12456,21 +12456,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12480,7 +12480,7 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>492080</v>
+        <v>492395</v>
       </c>
       <c r="R112" t="n">
         <v>7135064</v>
@@ -12516,11 +12516,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12547,7 +12542,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730624</v>
+        <v>129730528</v>
       </c>
       <c r="B113" t="n">
         <v>57736</v>
@@ -12582,10 +12577,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492366</v>
+        <v>492476</v>
       </c>
       <c r="R113" t="n">
-        <v>7134921</v>
+        <v>7135072</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12649,7 +12644,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730597</v>
+        <v>129730632</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -12684,10 +12679,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492213</v>
+        <v>492414</v>
       </c>
       <c r="R114" t="n">
-        <v>7135010</v>
+        <v>7134915</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12751,10 +12746,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730526</v>
+        <v>129730608</v>
       </c>
       <c r="B115" t="n">
-        <v>90631</v>
+        <v>57736</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12762,21 +12757,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12786,10 +12781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492395</v>
+        <v>492316</v>
       </c>
       <c r="R115" t="n">
-        <v>7135064</v>
+        <v>7134971</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12822,6 +12817,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12848,7 +12848,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730528</v>
+        <v>129730617</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -12883,10 +12883,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>492476</v>
+        <v>492349</v>
       </c>
       <c r="R116" t="n">
-        <v>7135072</v>
+        <v>7134943</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12950,7 +12950,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730632</v>
+        <v>129730579</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -12985,10 +12985,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492414</v>
+        <v>492080</v>
       </c>
       <c r="R117" t="n">
-        <v>7134915</v>
+        <v>7135064</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13052,7 +13052,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730608</v>
+        <v>129730624</v>
       </c>
       <c r="B118" t="n">
         <v>57736</v>
@@ -13087,10 +13087,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492316</v>
+        <v>492366</v>
       </c>
       <c r="R118" t="n">
-        <v>7134971</v>
+        <v>7134921</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13154,7 +13154,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730617</v>
+        <v>129730597</v>
       </c>
       <c r="B119" t="n">
         <v>57736</v>
@@ -13189,10 +13189,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492349</v>
+        <v>492213</v>
       </c>
       <c r="R119" t="n">
-        <v>7134943</v>
+        <v>7135010</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14475,32 +14475,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730545</v>
+        <v>129730670</v>
       </c>
       <c r="B132" t="n">
-        <v>57736</v>
+        <v>91772</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>491983</v>
+        <v>492219</v>
       </c>
       <c r="R132" t="n">
-        <v>7135171</v>
+        <v>7135247</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14546,11 +14546,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14577,7 +14572,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730531</v>
+        <v>129730545</v>
       </c>
       <c r="B133" t="n">
         <v>57736</v>
@@ -14612,10 +14607,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>492083</v>
+        <v>491983</v>
       </c>
       <c r="R133" t="n">
-        <v>7135291</v>
+        <v>7135171</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14679,7 +14674,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730580</v>
+        <v>129730531</v>
       </c>
       <c r="B134" t="n">
         <v>57736</v>
@@ -14714,10 +14709,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>492077</v>
+        <v>492083</v>
       </c>
       <c r="R134" t="n">
-        <v>7135066</v>
+        <v>7135291</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14781,7 +14776,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730574</v>
+        <v>129730580</v>
       </c>
       <c r="B135" t="n">
         <v>57736</v>
@@ -14816,10 +14811,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>492062</v>
+        <v>492077</v>
       </c>
       <c r="R135" t="n">
-        <v>7135103</v>
+        <v>7135066</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14883,32 +14878,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730670</v>
+        <v>129730574</v>
       </c>
       <c r="B136" t="n">
-        <v>91772</v>
+        <v>57736</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14918,10 +14913,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492219</v>
+        <v>492062</v>
       </c>
       <c r="R136" t="n">
-        <v>7135247</v>
+        <v>7135103</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14954,6 +14949,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -19030,7 +19030,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129730623</v>
+        <v>129730586</v>
       </c>
       <c r="B177" t="n">
         <v>57736</v>
@@ -19065,10 +19065,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>492353</v>
+        <v>492124</v>
       </c>
       <c r="R177" t="n">
-        <v>7134936</v>
+        <v>7135046</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19132,7 +19132,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129730644</v>
+        <v>129730612</v>
       </c>
       <c r="B178" t="n">
         <v>57736</v>
@@ -19167,10 +19167,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>492462</v>
+        <v>492333</v>
       </c>
       <c r="R178" t="n">
-        <v>7134869</v>
+        <v>7134969</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19234,7 +19234,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129730611</v>
+        <v>129730607</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -19269,10 +19269,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>492333</v>
+        <v>492312</v>
       </c>
       <c r="R179" t="n">
-        <v>7134969</v>
+        <v>7134971</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19336,7 +19336,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129730586</v>
+        <v>129730610</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -19371,10 +19371,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>492124</v>
+        <v>492330</v>
       </c>
       <c r="R180" t="n">
-        <v>7135046</v>
+        <v>7134972</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19438,7 +19438,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129730607</v>
+        <v>129730623</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>492312</v>
+        <v>492353</v>
       </c>
       <c r="R181" t="n">
-        <v>7134971</v>
+        <v>7134936</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19513,7 +19513,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19540,7 +19540,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129730610</v>
+        <v>129730644</v>
       </c>
       <c r="B182" t="n">
         <v>57736</v>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>492330</v>
+        <v>492462</v>
       </c>
       <c r="R182" t="n">
-        <v>7134972</v>
+        <v>7134869</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20552,10 +20552,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129730553</v>
+        <v>129730674</v>
       </c>
       <c r="B192" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20563,21 +20563,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20587,10 +20587,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>492008</v>
+        <v>492084</v>
       </c>
       <c r="R192" t="n">
-        <v>7135137</v>
+        <v>7135198</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20623,11 +20623,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20654,7 +20649,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730642</v>
+        <v>129730596</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -20689,10 +20684,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492466</v>
+        <v>492210</v>
       </c>
       <c r="R193" t="n">
-        <v>7134877</v>
+        <v>7135013</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20729,7 +20724,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20756,7 +20751,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730596</v>
+        <v>129730613</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -20791,10 +20786,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492210</v>
+        <v>492341</v>
       </c>
       <c r="R194" t="n">
-        <v>7135013</v>
+        <v>7134968</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20831,7 +20826,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20858,7 +20853,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730613</v>
+        <v>129730600</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -20893,10 +20888,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492341</v>
+        <v>492239</v>
       </c>
       <c r="R195" t="n">
-        <v>7134968</v>
+        <v>7134997</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20960,32 +20955,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730600</v>
+        <v>129730666</v>
       </c>
       <c r="B196" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20995,10 +20990,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492239</v>
+        <v>492253</v>
       </c>
       <c r="R196" t="n">
-        <v>7134997</v>
+        <v>7135293</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21035,7 +21030,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>7st</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21062,7 +21057,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129730560</v>
+        <v>129730553</v>
       </c>
       <c r="B197" t="n">
         <v>57736</v>
@@ -21097,10 +21092,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>492037</v>
+        <v>492008</v>
       </c>
       <c r="R197" t="n">
-        <v>7135124</v>
+        <v>7135137</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21137,7 +21132,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21164,7 +21159,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730570</v>
+        <v>129730642</v>
       </c>
       <c r="B198" t="n">
         <v>57736</v>
@@ -21199,10 +21194,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492057</v>
+        <v>492466</v>
       </c>
       <c r="R198" t="n">
-        <v>7135109</v>
+        <v>7134877</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21266,7 +21261,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730621</v>
+        <v>129730560</v>
       </c>
       <c r="B199" t="n">
         <v>57736</v>
@@ -21301,10 +21296,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492355</v>
+        <v>492037</v>
       </c>
       <c r="R199" t="n">
-        <v>7134935</v>
+        <v>7135124</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21341,7 +21336,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21368,7 +21363,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730651</v>
+        <v>129730570</v>
       </c>
       <c r="B200" t="n">
         <v>57736</v>
@@ -21403,10 +21398,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492474</v>
+        <v>492057</v>
       </c>
       <c r="R200" t="n">
-        <v>7134863</v>
+        <v>7135109</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21443,7 +21438,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21470,32 +21465,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730666</v>
+        <v>129730641</v>
       </c>
       <c r="B201" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21505,10 +21500,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492253</v>
+        <v>492462</v>
       </c>
       <c r="R201" t="n">
-        <v>7135293</v>
+        <v>7134883</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21545,7 +21540,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>7st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21572,10 +21567,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730674</v>
+        <v>129730621</v>
       </c>
       <c r="B202" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21583,21 +21578,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21607,10 +21602,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492084</v>
+        <v>492355</v>
       </c>
       <c r="R202" t="n">
-        <v>7135198</v>
+        <v>7134935</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21643,6 +21638,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21669,7 +21669,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129730641</v>
+        <v>129730651</v>
       </c>
       <c r="B203" t="n">
         <v>57736</v>
@@ -21704,10 +21704,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>492462</v>
+        <v>492474</v>
       </c>
       <c r="R203" t="n">
-        <v>7134883</v>
+        <v>7134863</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -3959,32 +3959,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726726</v>
+        <v>129726737</v>
       </c>
       <c r="B31" t="n">
-        <v>91772</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492285</v>
+        <v>492228</v>
       </c>
       <c r="R31" t="n">
-        <v>7135248</v>
+        <v>7135126</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,10 +4066,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726722</v>
+        <v>129726726</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>91772</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,38 +4077,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492376</v>
+        <v>492285</v>
       </c>
       <c r="R32" t="n">
-        <v>7135128</v>
+        <v>7135248</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4140,7 +4136,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4146,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,45 +4173,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726737</v>
+        <v>129726722</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492228</v>
+        <v>492376</v>
       </c>
       <c r="R33" t="n">
-        <v>7135126</v>
+        <v>7135128</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -7568,54 +7568,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726724</v>
+        <v>129726730</v>
       </c>
       <c r="B64" t="n">
-        <v>57896</v>
+        <v>92317</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492343</v>
+        <v>492124</v>
       </c>
       <c r="R64" t="n">
-        <v>7135242</v>
+        <v>7135171</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7647,7 +7638,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7657,7 +7648,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7893,10 +7884,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129726730</v>
+        <v>129728240</v>
       </c>
       <c r="B67" t="n">
-        <v>92317</v>
+        <v>80214</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7904,21 +7895,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7928,10 +7919,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492124</v>
+        <v>492405</v>
       </c>
       <c r="R67" t="n">
-        <v>7135171</v>
+        <v>7134981</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7961,19 +7952,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:53</t>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7988,57 +7974,66 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129728240</v>
+        <v>129726724</v>
       </c>
       <c r="B68" t="n">
-        <v>80214</v>
+        <v>57896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492405</v>
+        <v>492343</v>
       </c>
       <c r="R68" t="n">
-        <v>7134981</v>
+        <v>7135242</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8068,14 +8063,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8090,12 +8090,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -20552,10 +20552,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129730674</v>
+        <v>129730553</v>
       </c>
       <c r="B192" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20563,21 +20563,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20587,10 +20587,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>492084</v>
+        <v>492008</v>
       </c>
       <c r="R192" t="n">
-        <v>7135198</v>
+        <v>7135137</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20623,6 +20623,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20649,7 +20654,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730596</v>
+        <v>129730642</v>
       </c>
       <c r="B193" t="n">
         <v>57736</v>
@@ -20684,10 +20689,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492210</v>
+        <v>492466</v>
       </c>
       <c r="R193" t="n">
-        <v>7135013</v>
+        <v>7134877</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20724,7 +20729,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20751,7 +20756,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730613</v>
+        <v>129730596</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -20786,10 +20791,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492341</v>
+        <v>492210</v>
       </c>
       <c r="R194" t="n">
-        <v>7134968</v>
+        <v>7135013</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20826,7 +20831,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20853,7 +20858,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730600</v>
+        <v>129730613</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -20888,10 +20893,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492239</v>
+        <v>492341</v>
       </c>
       <c r="R195" t="n">
-        <v>7134997</v>
+        <v>7134968</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20955,32 +20960,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730666</v>
+        <v>129730600</v>
       </c>
       <c r="B196" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20990,10 +20995,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492253</v>
+        <v>492239</v>
       </c>
       <c r="R196" t="n">
-        <v>7135293</v>
+        <v>7134997</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21030,7 +21035,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>7st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21057,7 +21062,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129730553</v>
+        <v>129730560</v>
       </c>
       <c r="B197" t="n">
         <v>57736</v>
@@ -21092,10 +21097,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>492008</v>
+        <v>492037</v>
       </c>
       <c r="R197" t="n">
-        <v>7135137</v>
+        <v>7135124</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21132,7 +21137,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21159,7 +21164,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730642</v>
+        <v>129730570</v>
       </c>
       <c r="B198" t="n">
         <v>57736</v>
@@ -21194,10 +21199,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492466</v>
+        <v>492057</v>
       </c>
       <c r="R198" t="n">
-        <v>7134877</v>
+        <v>7135109</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21261,7 +21266,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730560</v>
+        <v>129730621</v>
       </c>
       <c r="B199" t="n">
         <v>57736</v>
@@ -21296,10 +21301,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492037</v>
+        <v>492355</v>
       </c>
       <c r="R199" t="n">
-        <v>7135124</v>
+        <v>7134935</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21336,7 +21341,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21363,7 +21368,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730570</v>
+        <v>129730651</v>
       </c>
       <c r="B200" t="n">
         <v>57736</v>
@@ -21398,10 +21403,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492057</v>
+        <v>492474</v>
       </c>
       <c r="R200" t="n">
-        <v>7135109</v>
+        <v>7134863</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21438,7 +21443,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21465,32 +21470,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730641</v>
+        <v>129730666</v>
       </c>
       <c r="B201" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21500,10 +21505,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492462</v>
+        <v>492253</v>
       </c>
       <c r="R201" t="n">
-        <v>7134883</v>
+        <v>7135293</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21540,7 +21545,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>7st</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21567,10 +21572,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730621</v>
+        <v>129730674</v>
       </c>
       <c r="B202" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21578,21 +21583,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21602,10 +21607,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492355</v>
+        <v>492084</v>
       </c>
       <c r="R202" t="n">
-        <v>7134935</v>
+        <v>7135198</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21638,11 +21643,6 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21669,7 +21669,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129730651</v>
+        <v>129730641</v>
       </c>
       <c r="B203" t="n">
         <v>57736</v>
@@ -21704,10 +21704,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>492474</v>
+        <v>492462</v>
       </c>
       <c r="R203" t="n">
-        <v>7134863</v>
+        <v>7134883</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728258</v>
+        <v>129728237</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,34 +1037,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492272</v>
+        <v>492236</v>
       </c>
       <c r="R5" t="n">
-        <v>7135018</v>
+        <v>7135034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1108,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,8 +1117,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,32 +1161,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726742</v>
+        <v>129728238</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,7 +1199,7 @@
         <v>492287</v>
       </c>
       <c r="R6" t="n">
-        <v>7135066</v>
+        <v>7135150</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1229,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1246,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728249</v>
+        <v>129726749</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,37 +1269,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492618</v>
+        <v>492403</v>
       </c>
       <c r="R7" t="n">
-        <v>7134954</v>
+        <v>7135004</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,14 +1326,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,54 +1347,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726749</v>
+        <v>129728258</v>
       </c>
       <c r="B8" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492403</v>
+        <v>492272</v>
       </c>
       <c r="R8" t="n">
-        <v>7135004</v>
+        <v>7135018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,19 +1433,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:03</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,44 +1455,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728238</v>
+        <v>129726742</v>
       </c>
       <c r="B9" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,7 +1505,7 @@
         <v>492287</v>
       </c>
       <c r="R9" t="n">
-        <v>7135150</v>
+        <v>7135066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,9 +1535,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,22 +1562,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726748</v>
+        <v>129728249</v>
       </c>
       <c r="B10" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,34 +1585,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492403</v>
+        <v>492618</v>
       </c>
       <c r="R10" t="n">
-        <v>7135004</v>
+        <v>7134954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,19 +1645,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:04</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,28 +1661,54 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129728237</v>
+        <v>129726748</v>
       </c>
       <c r="B11" t="n">
-        <v>80187</v>
+        <v>78094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,41 +1716,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492236</v>
+        <v>492403</v>
       </c>
       <c r="R11" t="n">
-        <v>7135034</v>
+        <v>7135004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,14 +1773,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en klen levande sälg.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,44 +1794,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2045,45 +2045,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726752</v>
+        <v>129728247</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492482</v>
+        <v>492455</v>
       </c>
       <c r="R14" t="n">
-        <v>7134934</v>
+        <v>7134922</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,19 +2133,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>08:50</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,63 +2149,89 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726741</v>
+        <v>129728244</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492282</v>
+        <v>492133</v>
       </c>
       <c r="R15" t="n">
-        <v>7135069</v>
+        <v>7135159</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,19 +2261,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,28 +2277,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726738</v>
+        <v>129726752</v>
       </c>
       <c r="B16" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,21 +2312,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,10 +2336,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492242</v>
+        <v>492482</v>
       </c>
       <c r="R16" t="n">
-        <v>7135130</v>
+        <v>7134934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,65 +2408,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129728247</v>
+        <v>129726741</v>
       </c>
       <c r="B17" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492455</v>
+        <v>492282</v>
       </c>
       <c r="R17" t="n">
-        <v>7134922</v>
+        <v>7135069</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,14 +2476,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,89 +2497,63 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129728244</v>
+        <v>129726738</v>
       </c>
       <c r="B18" t="n">
-        <v>98780</v>
+        <v>83052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492133</v>
+        <v>492242</v>
       </c>
       <c r="R18" t="n">
-        <v>7135159</v>
+        <v>7135130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2582,14 +2583,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,24 +2604,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726736</v>
+        <v>129726744</v>
       </c>
       <c r="B20" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492194</v>
+        <v>492318</v>
       </c>
       <c r="R20" t="n">
-        <v>7135150</v>
+        <v>7135032</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726744</v>
+        <v>129726736</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492318</v>
+        <v>492194</v>
       </c>
       <c r="R21" t="n">
-        <v>7135032</v>
+        <v>7135150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2946,7 +2946,7 @@
         <v>129728246</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>129726716</v>
       </c>
       <c r="B23" t="n">
-        <v>97657</v>
+        <v>97667</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3178,45 +3178,65 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129728252</v>
+        <v>129728245</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492377</v>
+        <v>492204</v>
       </c>
       <c r="R24" t="n">
-        <v>7135110</v>
+        <v>7135099</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3253,7 +3273,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,8 +3282,14 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3280,10 +3306,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129728245</v>
+        <v>129728242</v>
       </c>
       <c r="B25" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3336,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3335,10 +3361,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492204</v>
+        <v>492205</v>
       </c>
       <c r="R25" t="n">
-        <v>7135099</v>
+        <v>7135151</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,7 +3401,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
+          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,65 +3434,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129728242</v>
+        <v>129728252</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492205</v>
+        <v>492377</v>
       </c>
       <c r="R26" t="n">
-        <v>7135151</v>
+        <v>7135110</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3503,7 +3509,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3512,14 +3518,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3959,32 +3959,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726737</v>
+        <v>129726726</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>91772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492228</v>
+        <v>492285</v>
       </c>
       <c r="R31" t="n">
-        <v>7135126</v>
+        <v>7135248</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,32 +4066,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726726</v>
+        <v>129726737</v>
       </c>
       <c r="B32" t="n">
-        <v>91772</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492285</v>
+        <v>492228</v>
       </c>
       <c r="R32" t="n">
-        <v>7135248</v>
+        <v>7135126</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4176,7 +4176,7 @@
         <v>129726722</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129726729</v>
+        <v>129728254</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492180</v>
+        <v>492116</v>
       </c>
       <c r="R34" t="n">
-        <v>7135242</v>
+        <v>7135129</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,19 +4352,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4379,22 +4374,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726720</v>
+        <v>129728255</v>
       </c>
       <c r="B35" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4402,21 +4397,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4421,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492458</v>
+        <v>492112</v>
       </c>
       <c r="R35" t="n">
-        <v>7135104</v>
+        <v>7135077</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4459,19 +4454,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:55</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4486,19 +4476,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129728254</v>
+        <v>129728256</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4533,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492116</v>
+        <v>492217</v>
       </c>
       <c r="R36" t="n">
-        <v>7135129</v>
+        <v>7135029</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4600,7 +4590,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129728255</v>
+        <v>129726729</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4635,10 +4625,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492112</v>
+        <v>492180</v>
       </c>
       <c r="R37" t="n">
-        <v>7135077</v>
+        <v>7135242</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4668,14 +4658,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,19 +4685,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129728256</v>
+        <v>129726750</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4737,10 +4732,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492217</v>
+        <v>492416</v>
       </c>
       <c r="R38" t="n">
-        <v>7135029</v>
+        <v>7135000</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4770,14 +4765,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4792,57 +4792,77 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726750</v>
+        <v>129728243</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492416</v>
+        <v>492168</v>
       </c>
       <c r="R39" t="n">
-        <v>7135000</v>
+        <v>7135133</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4872,19 +4892,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:01</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:01</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4893,83 +4908,69 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129728243</v>
+        <v>129726720</v>
       </c>
       <c r="B40" t="n">
-        <v>98780</v>
+        <v>78094</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492168</v>
+        <v>492458</v>
       </c>
       <c r="R40" t="n">
-        <v>7135133</v>
+        <v>7135104</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4999,14 +5000,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5015,24 +5021,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6388,7 +6388,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129726727</v>
+        <v>129726747</v>
       </c>
       <c r="B53" t="n">
         <v>79081</v>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492258</v>
+        <v>492381</v>
       </c>
       <c r="R53" t="n">
-        <v>7135232</v>
+        <v>7135002</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6495,7 +6495,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129726747</v>
+        <v>129726727</v>
       </c>
       <c r="B54" t="n">
         <v>79081</v>
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492381</v>
+        <v>492258</v>
       </c>
       <c r="R54" t="n">
-        <v>7135002</v>
+        <v>7135232</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6918,7 +6918,7 @@
         <v>129728248</v>
       </c>
       <c r="B58" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7043,10 +7043,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129726728</v>
+        <v>129728250</v>
       </c>
       <c r="B59" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7054,21 +7054,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492179</v>
+        <v>492572</v>
       </c>
       <c r="R59" t="n">
-        <v>7135241</v>
+        <v>7135009</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7111,19 +7111,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7138,22 +7133,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726753</v>
+        <v>129726725</v>
       </c>
       <c r="B60" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7161,21 +7156,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7185,10 +7180,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492496</v>
+        <v>492304</v>
       </c>
       <c r="R60" t="n">
-        <v>7134904</v>
+        <v>7135246</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7220,7 +7215,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7230,7 +7225,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7257,10 +7252,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129728250</v>
+        <v>129726728</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7268,21 +7263,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7292,10 +7287,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492572</v>
+        <v>492179</v>
       </c>
       <c r="R61" t="n">
-        <v>7135009</v>
+        <v>7135241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7325,14 +7320,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7347,22 +7347,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726725</v>
+        <v>129726753</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492304</v>
+        <v>492496</v>
       </c>
       <c r="R62" t="n">
-        <v>7135246</v>
+        <v>7134904</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7675,32 +7675,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129728259</v>
+        <v>129728240</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492317</v>
+        <v>492405</v>
       </c>
       <c r="R65" t="n">
-        <v>7134999</v>
+        <v>7134981</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7777,7 +7777,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129726745</v>
+        <v>129728259</v>
       </c>
       <c r="B66" t="n">
         <v>79081</v>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492367</v>
+        <v>492317</v>
       </c>
       <c r="R66" t="n">
-        <v>7135038</v>
+        <v>7134999</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7845,19 +7845,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:12</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7872,44 +7867,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129728240</v>
+        <v>129726745</v>
       </c>
       <c r="B67" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7919,10 +7914,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492405</v>
+        <v>492367</v>
       </c>
       <c r="R67" t="n">
-        <v>7134981</v>
+        <v>7135038</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7952,14 +7947,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8102,10 +8102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730573</v>
+        <v>129730672</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492062</v>
+        <v>492334</v>
       </c>
       <c r="R69" t="n">
-        <v>7135100</v>
+        <v>7135092</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,11 +8173,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8204,7 +8199,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730584</v>
+        <v>129730573</v>
       </c>
       <c r="B70" t="n">
         <v>57736</v>
@@ -8239,10 +8234,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492107</v>
+        <v>492062</v>
       </c>
       <c r="R70" t="n">
-        <v>7135052</v>
+        <v>7135100</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8279,7 +8274,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8306,7 +8301,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730598</v>
+        <v>129730584</v>
       </c>
       <c r="B71" t="n">
         <v>57736</v>
@@ -8341,10 +8336,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492220</v>
+        <v>492107</v>
       </c>
       <c r="R71" t="n">
-        <v>7135003</v>
+        <v>7135052</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8408,7 +8403,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730615</v>
+        <v>129730598</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -8443,10 +8438,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492345</v>
+        <v>492220</v>
       </c>
       <c r="R72" t="n">
-        <v>7134961</v>
+        <v>7135003</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8483,7 +8478,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8510,10 +8505,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730658</v>
+        <v>129730615</v>
       </c>
       <c r="B73" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8521,21 +8516,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8545,10 +8540,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492464</v>
+        <v>492345</v>
       </c>
       <c r="R73" t="n">
-        <v>7135049</v>
+        <v>7134961</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8585,7 +8580,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8612,10 +8607,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730672</v>
+        <v>129730658</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8623,21 +8618,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8647,10 +8642,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492334</v>
+        <v>492464</v>
       </c>
       <c r="R74" t="n">
-        <v>7135092</v>
+        <v>7135049</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8683,6 +8678,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9214,32 +9214,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730594</v>
+        <v>129730665</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492205</v>
+        <v>492046</v>
       </c>
       <c r="R80" t="n">
-        <v>7135012</v>
+        <v>7135177</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730599</v>
+        <v>129730675</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9327,21 +9327,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492216</v>
+        <v>492075</v>
       </c>
       <c r="R81" t="n">
-        <v>7135002</v>
+        <v>7135214</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9387,11 +9387,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9928,7 +9923,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129730630</v>
+        <v>129730594</v>
       </c>
       <c r="B87" t="n">
         <v>57736</v>
@@ -9963,10 +9958,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492411</v>
+        <v>492205</v>
       </c>
       <c r="R87" t="n">
-        <v>7134926</v>
+        <v>7135012</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10030,32 +10025,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730665</v>
+        <v>129730599</v>
       </c>
       <c r="B88" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10065,10 +10060,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492046</v>
+        <v>492216</v>
       </c>
       <c r="R88" t="n">
-        <v>7135177</v>
+        <v>7135002</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10105,7 +10100,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>8st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10132,10 +10127,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129730675</v>
+        <v>129730630</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10143,21 +10138,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10167,10 +10162,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492075</v>
+        <v>492411</v>
       </c>
       <c r="R89" t="n">
-        <v>7135214</v>
+        <v>7134926</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10203,6 +10198,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10229,32 +10229,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129730583</v>
+        <v>129730663</v>
       </c>
       <c r="B90" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492105</v>
+        <v>492070</v>
       </c>
       <c r="R90" t="n">
-        <v>7135051</v>
+        <v>7135173</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>14st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,7 +10331,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129730625</v>
+        <v>129730583</v>
       </c>
       <c r="B91" t="n">
         <v>57736</v>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492367</v>
+        <v>492105</v>
       </c>
       <c r="R91" t="n">
-        <v>7134920</v>
+        <v>7135051</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10433,7 +10433,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129730565</v>
+        <v>129730625</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>492040</v>
+        <v>492367</v>
       </c>
       <c r="R92" t="n">
-        <v>7135117</v>
+        <v>7134920</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10535,32 +10535,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129730663</v>
+        <v>129730565</v>
       </c>
       <c r="B93" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>492070</v>
+        <v>492040</v>
       </c>
       <c r="R93" t="n">
-        <v>7135173</v>
+        <v>7135117</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>14st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129730606</v>
+        <v>129730661</v>
       </c>
       <c r="B94" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,23 +10648,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10672,10 +10668,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492303</v>
+        <v>492069</v>
       </c>
       <c r="R94" t="n">
-        <v>7134972</v>
+        <v>7135162</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10702,17 +10698,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10721,6 +10712,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10739,10 +10731,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730619</v>
+        <v>129730522</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>97036</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10750,21 +10742,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10774,10 +10766,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492353</v>
+        <v>492217</v>
       </c>
       <c r="R95" t="n">
-        <v>7134945</v>
+        <v>7135249</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10810,11 +10802,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10841,7 +10828,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730650</v>
+        <v>129730606</v>
       </c>
       <c r="B96" t="n">
         <v>57736</v>
@@ -10876,10 +10863,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492473</v>
+        <v>492303</v>
       </c>
       <c r="R96" t="n">
-        <v>7134864</v>
+        <v>7134972</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10943,7 +10930,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730604</v>
+        <v>129730619</v>
       </c>
       <c r="B97" t="n">
         <v>57736</v>
@@ -10978,10 +10965,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492297</v>
+        <v>492353</v>
       </c>
       <c r="R97" t="n">
-        <v>7134975</v>
+        <v>7134945</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11018,7 +11005,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11045,7 +11032,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129730569</v>
+        <v>129730650</v>
       </c>
       <c r="B98" t="n">
         <v>57736</v>
@@ -11080,10 +11067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492054</v>
+        <v>492473</v>
       </c>
       <c r="R98" t="n">
-        <v>7135107</v>
+        <v>7134864</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11120,7 +11107,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11147,10 +11134,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730522</v>
+        <v>129730604</v>
       </c>
       <c r="B99" t="n">
-        <v>97026</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11158,21 +11145,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11182,10 +11169,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492217</v>
+        <v>492297</v>
       </c>
       <c r="R99" t="n">
-        <v>7135249</v>
+        <v>7134975</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11218,6 +11205,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11244,10 +11236,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730661</v>
+        <v>129730569</v>
       </c>
       <c r="B100" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11255,19 +11247,23 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11275,10 +11271,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492069</v>
+        <v>492054</v>
       </c>
       <c r="R100" t="n">
-        <v>7135162</v>
+        <v>7135107</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11305,12 +11301,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11319,7 +11320,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11639,10 +11639,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730523</v>
+        <v>129730640</v>
       </c>
       <c r="B104" t="n">
-        <v>97026</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11650,21 +11650,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11674,10 +11674,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492316</v>
+        <v>492444</v>
       </c>
       <c r="R104" t="n">
-        <v>7135071</v>
+        <v>7134887</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11710,6 +11710,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11736,10 +11741,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730640</v>
+        <v>129730523</v>
       </c>
       <c r="B105" t="n">
-        <v>57736</v>
+        <v>97036</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11747,21 +11752,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11771,10 +11776,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>492444</v>
+        <v>492316</v>
       </c>
       <c r="R105" t="n">
-        <v>7134887</v>
+        <v>7135071</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11807,11 +11812,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12042,10 +12042,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730521</v>
+        <v>129730532</v>
       </c>
       <c r="B108" t="n">
-        <v>83052</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12053,21 +12053,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12077,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492100</v>
+        <v>492082</v>
       </c>
       <c r="R108" t="n">
-        <v>7135216</v>
+        <v>7135294</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12113,6 +12113,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12139,7 +12144,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730532</v>
+        <v>129730576</v>
       </c>
       <c r="B109" t="n">
         <v>57736</v>
@@ -12174,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492082</v>
+        <v>492066</v>
       </c>
       <c r="R109" t="n">
-        <v>7135294</v>
+        <v>7135093</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12214,7 +12219,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,7 +12246,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730576</v>
+        <v>129730559</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -12276,10 +12281,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492066</v>
+        <v>492032</v>
       </c>
       <c r="R110" t="n">
-        <v>7135093</v>
+        <v>7135120</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12343,10 +12348,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730559</v>
+        <v>129730521</v>
       </c>
       <c r="B111" t="n">
-        <v>57736</v>
+        <v>83052</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12354,21 +12359,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12378,10 +12383,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492032</v>
+        <v>492100</v>
       </c>
       <c r="R111" t="n">
-        <v>7135120</v>
+        <v>7135216</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12414,11 +12419,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14980,7 +14980,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129730541</v>
+        <v>129730646</v>
       </c>
       <c r="B137" t="n">
         <v>57736</v>
@@ -15015,10 +15015,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>492004</v>
+        <v>492465</v>
       </c>
       <c r="R137" t="n">
-        <v>7135207</v>
+        <v>7134871</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15082,7 +15082,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730535</v>
+        <v>129730541</v>
       </c>
       <c r="B138" t="n">
         <v>57736</v>
@@ -15117,10 +15117,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>492065</v>
+        <v>492004</v>
       </c>
       <c r="R138" t="n">
-        <v>7135257</v>
+        <v>7135207</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15184,7 +15184,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730620</v>
+        <v>129730535</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -15219,10 +15219,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492351</v>
+        <v>492065</v>
       </c>
       <c r="R139" t="n">
-        <v>7134938</v>
+        <v>7135257</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15286,32 +15286,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730669</v>
+        <v>129730620</v>
       </c>
       <c r="B140" t="n">
-        <v>91772</v>
+        <v>57736</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15321,10 +15321,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492248</v>
+        <v>492351</v>
       </c>
       <c r="R140" t="n">
-        <v>7135292</v>
+        <v>7134938</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15357,6 +15357,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15383,32 +15388,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730646</v>
+        <v>129730669</v>
       </c>
       <c r="B141" t="n">
-        <v>57736</v>
+        <v>91772</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15418,10 +15423,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492465</v>
+        <v>492248</v>
       </c>
       <c r="R141" t="n">
-        <v>7134871</v>
+        <v>7135292</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15454,11 +15459,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15485,10 +15485,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730525</v>
+        <v>129730655</v>
       </c>
       <c r="B142" t="n">
-        <v>90631</v>
+        <v>57736</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15496,21 +15496,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492390</v>
+        <v>492460</v>
       </c>
       <c r="R142" t="n">
-        <v>7135053</v>
+        <v>7134849</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15556,6 +15556,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15582,7 +15587,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730655</v>
+        <v>129730558</v>
       </c>
       <c r="B143" t="n">
         <v>57736</v>
@@ -15617,10 +15622,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492460</v>
+        <v>492028</v>
       </c>
       <c r="R143" t="n">
-        <v>7134849</v>
+        <v>7135126</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15657,7 +15662,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15684,7 +15689,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730558</v>
+        <v>129730609</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -15719,10 +15724,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>492028</v>
+        <v>492330</v>
       </c>
       <c r="R144" t="n">
-        <v>7135126</v>
+        <v>7134971</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15786,7 +15791,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730609</v>
+        <v>129730616</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -15821,10 +15826,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>492330</v>
+        <v>492343</v>
       </c>
       <c r="R145" t="n">
-        <v>7134971</v>
+        <v>7134960</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15861,7 +15866,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15888,7 +15893,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730616</v>
+        <v>129730595</v>
       </c>
       <c r="B146" t="n">
         <v>57736</v>
@@ -15923,10 +15928,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>492343</v>
+        <v>492208</v>
       </c>
       <c r="R146" t="n">
-        <v>7134960</v>
+        <v>7135012</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15963,7 +15968,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15990,7 +15995,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730595</v>
+        <v>129730549</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -16025,10 +16030,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>492208</v>
+        <v>491986</v>
       </c>
       <c r="R147" t="n">
-        <v>7135012</v>
+        <v>7135153</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16065,7 +16070,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16092,7 +16097,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730549</v>
+        <v>129730648</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -16127,10 +16132,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>491986</v>
+        <v>492457</v>
       </c>
       <c r="R148" t="n">
-        <v>7135153</v>
+        <v>7134863</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16167,7 +16172,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16194,7 +16199,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730648</v>
+        <v>129730593</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -16229,10 +16234,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>492457</v>
+        <v>492199</v>
       </c>
       <c r="R149" t="n">
-        <v>7134863</v>
+        <v>7135015</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16269,7 +16274,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16296,7 +16301,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730593</v>
+        <v>129730578</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -16331,10 +16336,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>492199</v>
+        <v>492086</v>
       </c>
       <c r="R150" t="n">
-        <v>7135015</v>
+        <v>7135087</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16398,32 +16403,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730578</v>
+        <v>129730524</v>
       </c>
       <c r="B151" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16433,10 +16438,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>492086</v>
+        <v>492271</v>
       </c>
       <c r="R151" t="n">
-        <v>7135087</v>
+        <v>7135240</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16469,11 +16474,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16500,32 +16500,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730524</v>
+        <v>129730525</v>
       </c>
       <c r="B152" t="n">
-        <v>91563</v>
+        <v>90631</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16535,10 +16535,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492271</v>
+        <v>492390</v>
       </c>
       <c r="R152" t="n">
-        <v>7135240</v>
+        <v>7135053</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17505,10 +17505,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730547</v>
+        <v>129730527</v>
       </c>
       <c r="B162" t="n">
-        <v>57736</v>
+        <v>90631</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17516,21 +17516,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17540,10 +17540,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>491981</v>
+        <v>492267</v>
       </c>
       <c r="R162" t="n">
-        <v>7135158</v>
+        <v>7135233</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17576,11 +17576,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17607,7 +17602,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730592</v>
+        <v>129730547</v>
       </c>
       <c r="B163" t="n">
         <v>57736</v>
@@ -17642,10 +17637,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>492195</v>
+        <v>491981</v>
       </c>
       <c r="R163" t="n">
-        <v>7135016</v>
+        <v>7135158</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17682,7 +17677,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17709,7 +17704,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730591</v>
+        <v>129730546</v>
       </c>
       <c r="B164" t="n">
         <v>57736</v>
@@ -17744,10 +17739,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>492194</v>
+        <v>491985</v>
       </c>
       <c r="R164" t="n">
-        <v>7135016</v>
+        <v>7135158</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17784,7 +17779,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17811,10 +17806,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730527</v>
+        <v>129730556</v>
       </c>
       <c r="B165" t="n">
-        <v>90631</v>
+        <v>57736</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17822,21 +17817,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17846,10 +17841,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>492267</v>
+        <v>492024</v>
       </c>
       <c r="R165" t="n">
-        <v>7135233</v>
+        <v>7135131</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17882,6 +17877,11 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17908,7 +17908,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730546</v>
+        <v>129730592</v>
       </c>
       <c r="B166" t="n">
         <v>57736</v>
@@ -17943,10 +17943,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>491985</v>
+        <v>492195</v>
       </c>
       <c r="R166" t="n">
-        <v>7135158</v>
+        <v>7135016</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18010,7 +18010,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730556</v>
+        <v>129730591</v>
       </c>
       <c r="B167" t="n">
         <v>57736</v>
@@ -18045,10 +18045,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492024</v>
+        <v>492194</v>
       </c>
       <c r="R167" t="n">
-        <v>7135131</v>
+        <v>7135016</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19234,7 +19234,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129730607</v>
+        <v>129730623</v>
       </c>
       <c r="B179" t="n">
         <v>57736</v>
@@ -19269,10 +19269,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>492312</v>
+        <v>492353</v>
       </c>
       <c r="R179" t="n">
-        <v>7134971</v>
+        <v>7134936</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19309,7 +19309,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19336,7 +19336,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129730610</v>
+        <v>129730607</v>
       </c>
       <c r="B180" t="n">
         <v>57736</v>
@@ -19371,10 +19371,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>492330</v>
+        <v>492312</v>
       </c>
       <c r="R180" t="n">
-        <v>7134972</v>
+        <v>7134971</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19438,7 +19438,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129730623</v>
+        <v>129730610</v>
       </c>
       <c r="B181" t="n">
         <v>57736</v>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>492353</v>
+        <v>492330</v>
       </c>
       <c r="R181" t="n">
-        <v>7134936</v>
+        <v>7134972</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20552,10 +20552,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129730553</v>
+        <v>129730674</v>
       </c>
       <c r="B192" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20563,21 +20563,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20587,10 +20587,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>492008</v>
+        <v>492084</v>
       </c>
       <c r="R192" t="n">
-        <v>7135137</v>
+        <v>7135198</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20623,11 +20623,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20654,32 +20649,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730642</v>
+        <v>129730666</v>
       </c>
       <c r="B193" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20689,10 +20684,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492466</v>
+        <v>492253</v>
       </c>
       <c r="R193" t="n">
-        <v>7134877</v>
+        <v>7135293</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20729,7 +20724,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>7st</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20756,7 +20751,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730596</v>
+        <v>129730553</v>
       </c>
       <c r="B194" t="n">
         <v>57736</v>
@@ -20791,10 +20786,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492210</v>
+        <v>492008</v>
       </c>
       <c r="R194" t="n">
-        <v>7135013</v>
+        <v>7135137</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20831,7 +20826,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20858,7 +20853,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730613</v>
+        <v>129730642</v>
       </c>
       <c r="B195" t="n">
         <v>57736</v>
@@ -20893,10 +20888,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492341</v>
+        <v>492466</v>
       </c>
       <c r="R195" t="n">
-        <v>7134968</v>
+        <v>7134877</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20960,7 +20955,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730600</v>
+        <v>129730596</v>
       </c>
       <c r="B196" t="n">
         <v>57736</v>
@@ -20995,10 +20990,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492239</v>
+        <v>492210</v>
       </c>
       <c r="R196" t="n">
-        <v>7134997</v>
+        <v>7135013</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21035,7 +21030,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21062,7 +21057,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129730560</v>
+        <v>129730613</v>
       </c>
       <c r="B197" t="n">
         <v>57736</v>
@@ -21097,10 +21092,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>492037</v>
+        <v>492341</v>
       </c>
       <c r="R197" t="n">
-        <v>7135124</v>
+        <v>7134968</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21137,7 +21132,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21164,7 +21159,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730570</v>
+        <v>129730600</v>
       </c>
       <c r="B198" t="n">
         <v>57736</v>
@@ -21199,10 +21194,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492057</v>
+        <v>492239</v>
       </c>
       <c r="R198" t="n">
-        <v>7135109</v>
+        <v>7134997</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21266,7 +21261,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730621</v>
+        <v>129730560</v>
       </c>
       <c r="B199" t="n">
         <v>57736</v>
@@ -21301,10 +21296,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492355</v>
+        <v>492037</v>
       </c>
       <c r="R199" t="n">
-        <v>7134935</v>
+        <v>7135124</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21341,7 +21336,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21368,7 +21363,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730651</v>
+        <v>129730570</v>
       </c>
       <c r="B200" t="n">
         <v>57736</v>
@@ -21403,10 +21398,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492474</v>
+        <v>492057</v>
       </c>
       <c r="R200" t="n">
-        <v>7134863</v>
+        <v>7135109</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21443,7 +21438,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21470,32 +21465,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730666</v>
+        <v>129730641</v>
       </c>
       <c r="B201" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21505,10 +21500,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492253</v>
+        <v>492462</v>
       </c>
       <c r="R201" t="n">
-        <v>7135293</v>
+        <v>7134883</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21545,7 +21540,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>7st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21572,10 +21567,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730674</v>
+        <v>129730621</v>
       </c>
       <c r="B202" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21583,21 +21578,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21607,10 +21602,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492084</v>
+        <v>492355</v>
       </c>
       <c r="R202" t="n">
-        <v>7135198</v>
+        <v>7134935</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21643,6 +21638,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21669,7 +21669,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129730641</v>
+        <v>129730651</v>
       </c>
       <c r="B203" t="n">
         <v>57736</v>
@@ -21704,10 +21704,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>492462</v>
+        <v>492474</v>
       </c>
       <c r="R203" t="n">
-        <v>7134883</v>
+        <v>7134863</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -2836,45 +2836,65 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726736</v>
+        <v>129728246</v>
       </c>
       <c r="B21" t="n">
-        <v>83052</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492194</v>
+        <v>492341</v>
       </c>
       <c r="R21" t="n">
-        <v>7135150</v>
+        <v>7134976</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2904,19 +2924,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,83 +2940,69 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129728246</v>
+        <v>129726716</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>97667</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492341</v>
+        <v>492599</v>
       </c>
       <c r="R22" t="n">
-        <v>7134976</v>
+        <v>7134962</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,14 +3032,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,56 +3053,50 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726716</v>
+        <v>129726736</v>
       </c>
       <c r="B23" t="n">
-        <v>97667</v>
+        <v>83052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492599</v>
+        <v>492194</v>
       </c>
       <c r="R23" t="n">
-        <v>7134962</v>
+        <v>7135150</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3178,65 +3178,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129728245</v>
+        <v>129728252</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492204</v>
+        <v>492377</v>
       </c>
       <c r="R24" t="n">
-        <v>7135099</v>
+        <v>7135110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3273,7 +3253,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3282,14 +3262,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3306,7 +3280,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129728242</v>
+        <v>129728245</v>
       </c>
       <c r="B25" t="n">
         <v>98790</v>
@@ -3336,7 +3310,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3361,10 +3335,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492205</v>
+        <v>492204</v>
       </c>
       <c r="R25" t="n">
-        <v>7135151</v>
+        <v>7135099</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3401,7 +3375,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3434,45 +3408,65 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129728252</v>
+        <v>129728242</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492377</v>
+        <v>492205</v>
       </c>
       <c r="R26" t="n">
-        <v>7135110</v>
+        <v>7135151</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3509,7 +3503,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3518,8 +3512,14 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -5946,48 +5946,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129728262</v>
+        <v>129728241</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492479</v>
+        <v>492451</v>
       </c>
       <c r="R49" t="n">
-        <v>7134899</v>
+        <v>7134904</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6022,45 +6019,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran i gammal barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6077,7 +6043,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129726721</v>
+        <v>129728262</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -6106,16 +6072,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492421</v>
+        <v>492479</v>
       </c>
       <c r="R50" t="n">
-        <v>7135113</v>
+        <v>7134899</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6145,19 +6114,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,50 +6130,76 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129728241</v>
+        <v>129726721</v>
       </c>
       <c r="B51" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6219,10 +6209,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492451</v>
+        <v>492421</v>
       </c>
       <c r="R51" t="n">
-        <v>7134904</v>
+        <v>7135113</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6252,9 +6242,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6269,12 +6269,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6602,45 +6602,65 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129728260</v>
+        <v>129728248</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492378</v>
+        <v>492492</v>
       </c>
       <c r="R55" t="n">
-        <v>7134955</v>
+        <v>7134909</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6677,7 +6697,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6686,8 +6706,14 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6704,10 +6730,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129726731</v>
+        <v>129726734</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6715,23 +6741,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6739,10 +6761,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492137</v>
+        <v>492211</v>
       </c>
       <c r="R56" t="n">
-        <v>7135201</v>
+        <v>7135170</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6774,7 +6796,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6784,7 +6806,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6793,6 +6815,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6811,10 +6834,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129726734</v>
+        <v>129728260</v>
       </c>
       <c r="B57" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6822,19 +6845,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6842,10 +6869,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492211</v>
+        <v>492378</v>
       </c>
       <c r="R57" t="n">
-        <v>7135170</v>
+        <v>7134955</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6875,19 +6902,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6896,84 +6918,63 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129728248</v>
+        <v>129726731</v>
       </c>
       <c r="B58" t="n">
-        <v>98790</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492492</v>
+        <v>492137</v>
       </c>
       <c r="R58" t="n">
-        <v>7134909</v>
+        <v>7135201</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7003,14 +7004,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7019,24 +7025,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7568,45 +7568,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726730</v>
+        <v>129726724</v>
       </c>
       <c r="B64" t="n">
-        <v>92317</v>
+        <v>57896</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492124</v>
+        <v>492343</v>
       </c>
       <c r="R64" t="n">
-        <v>7135171</v>
+        <v>7135242</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7638,7 +7647,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7648,7 +7657,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7675,10 +7684,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129728240</v>
+        <v>129726730</v>
       </c>
       <c r="B65" t="n">
-        <v>80214</v>
+        <v>92317</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7686,21 +7695,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>3298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7710,10 +7719,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492405</v>
+        <v>492124</v>
       </c>
       <c r="R65" t="n">
-        <v>7134981</v>
+        <v>7135171</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7743,14 +7752,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7765,44 +7779,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129728259</v>
+        <v>129728240</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7812,10 +7826,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492317</v>
+        <v>492405</v>
       </c>
       <c r="R66" t="n">
-        <v>7134999</v>
+        <v>7134981</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7852,7 +7866,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7879,7 +7893,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129726745</v>
+        <v>129728259</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7914,10 +7928,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492367</v>
+        <v>492317</v>
       </c>
       <c r="R67" t="n">
-        <v>7135038</v>
+        <v>7134999</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7947,19 +7961,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:12</t>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7974,22 +7983,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726724</v>
+        <v>129726745</v>
       </c>
       <c r="B68" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7997,43 +8006,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492343</v>
+        <v>492367</v>
       </c>
       <c r="R68" t="n">
-        <v>7135242</v>
+        <v>7135038</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730672</v>
+        <v>129730573</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492334</v>
+        <v>492062</v>
       </c>
       <c r="R69" t="n">
-        <v>7135092</v>
+        <v>7135100</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,6 +8173,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8199,7 +8204,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730573</v>
+        <v>129730584</v>
       </c>
       <c r="B70" t="n">
         <v>57736</v>
@@ -8234,10 +8239,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492062</v>
+        <v>492107</v>
       </c>
       <c r="R70" t="n">
-        <v>7135100</v>
+        <v>7135052</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8274,7 +8279,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8301,7 +8306,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730584</v>
+        <v>129730598</v>
       </c>
       <c r="B71" t="n">
         <v>57736</v>
@@ -8336,10 +8341,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492107</v>
+        <v>492220</v>
       </c>
       <c r="R71" t="n">
-        <v>7135052</v>
+        <v>7135003</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8403,7 +8408,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730598</v>
+        <v>129730615</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -8438,10 +8443,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492220</v>
+        <v>492345</v>
       </c>
       <c r="R72" t="n">
-        <v>7135003</v>
+        <v>7134961</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8478,7 +8483,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8505,10 +8510,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730615</v>
+        <v>129730658</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8516,21 +8521,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8540,10 +8545,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492345</v>
+        <v>492464</v>
       </c>
       <c r="R73" t="n">
-        <v>7134961</v>
+        <v>7135049</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8580,7 +8585,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8607,10 +8612,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730658</v>
+        <v>129730672</v>
       </c>
       <c r="B74" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8618,21 +8623,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8642,10 +8647,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492464</v>
+        <v>492334</v>
       </c>
       <c r="R74" t="n">
-        <v>7135049</v>
+        <v>7135092</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8678,11 +8683,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9214,32 +9214,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730665</v>
+        <v>129730675</v>
       </c>
       <c r="B80" t="n">
-        <v>98790</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492046</v>
+        <v>492075</v>
       </c>
       <c r="R80" t="n">
-        <v>7135177</v>
+        <v>7135214</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9285,11 +9285,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>8st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,32 +9311,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730675</v>
+        <v>129730665</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9346,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492075</v>
+        <v>492046</v>
       </c>
       <c r="R81" t="n">
-        <v>7135214</v>
+        <v>7135177</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9387,6 +9382,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129730661</v>
+        <v>129730606</v>
       </c>
       <c r="B94" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,19 +10648,23 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10668,10 +10672,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492069</v>
+        <v>492303</v>
       </c>
       <c r="R94" t="n">
-        <v>7135162</v>
+        <v>7134972</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10698,12 +10702,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10712,7 +10721,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10731,10 +10739,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730522</v>
+        <v>129730619</v>
       </c>
       <c r="B95" t="n">
-        <v>97036</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10742,21 +10750,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10766,10 +10774,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492217</v>
+        <v>492353</v>
       </c>
       <c r="R95" t="n">
-        <v>7135249</v>
+        <v>7134945</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10802,6 +10810,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10828,7 +10841,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730606</v>
+        <v>129730650</v>
       </c>
       <c r="B96" t="n">
         <v>57736</v>
@@ -10863,10 +10876,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492303</v>
+        <v>492473</v>
       </c>
       <c r="R96" t="n">
-        <v>7134972</v>
+        <v>7134864</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10930,7 +10943,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730619</v>
+        <v>129730604</v>
       </c>
       <c r="B97" t="n">
         <v>57736</v>
@@ -10965,10 +10978,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492353</v>
+        <v>492297</v>
       </c>
       <c r="R97" t="n">
-        <v>7134945</v>
+        <v>7134975</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11005,7 +11018,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11032,7 +11045,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129730650</v>
+        <v>129730569</v>
       </c>
       <c r="B98" t="n">
         <v>57736</v>
@@ -11067,10 +11080,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492473</v>
+        <v>492054</v>
       </c>
       <c r="R98" t="n">
-        <v>7134864</v>
+        <v>7135107</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11107,7 +11120,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11134,10 +11147,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730604</v>
+        <v>129730662</v>
       </c>
       <c r="B99" t="n">
-        <v>57736</v>
+        <v>78094</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11145,21 +11158,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11169,10 +11182,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492297</v>
+        <v>492166</v>
       </c>
       <c r="R99" t="n">
-        <v>7134975</v>
+        <v>7135239</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11205,11 +11218,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11236,10 +11244,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730569</v>
+        <v>129730661</v>
       </c>
       <c r="B100" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11247,23 +11255,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11271,10 +11275,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492054</v>
+        <v>492069</v>
       </c>
       <c r="R100" t="n">
-        <v>7135107</v>
+        <v>7135162</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11301,17 +11305,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11320,6 +11319,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11338,10 +11338,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730662</v>
+        <v>129730522</v>
       </c>
       <c r="B101" t="n">
-        <v>78094</v>
+        <v>97036</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11349,21 +11349,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228579</v>
+        <v>53</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11373,10 +11373,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492166</v>
+        <v>492217</v>
       </c>
       <c r="R101" t="n">
-        <v>7135239</v>
+        <v>7135249</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129730526</v>
+        <v>129730528</v>
       </c>
       <c r="B112" t="n">
-        <v>90631</v>
+        <v>57736</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12456,21 +12456,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>492395</v>
+        <v>492476</v>
       </c>
       <c r="R112" t="n">
-        <v>7135064</v>
+        <v>7135072</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12516,6 +12516,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12542,7 +12547,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730528</v>
+        <v>129730632</v>
       </c>
       <c r="B113" t="n">
         <v>57736</v>
@@ -12577,10 +12582,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492476</v>
+        <v>492414</v>
       </c>
       <c r="R113" t="n">
-        <v>7135072</v>
+        <v>7134915</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12644,7 +12649,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730632</v>
+        <v>129730608</v>
       </c>
       <c r="B114" t="n">
         <v>57736</v>
@@ -12679,10 +12684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492414</v>
+        <v>492316</v>
       </c>
       <c r="R114" t="n">
-        <v>7134915</v>
+        <v>7134971</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12746,7 +12751,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730608</v>
+        <v>129730617</v>
       </c>
       <c r="B115" t="n">
         <v>57736</v>
@@ -12781,10 +12786,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492316</v>
+        <v>492349</v>
       </c>
       <c r="R115" t="n">
-        <v>7134971</v>
+        <v>7134943</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12821,7 +12826,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12848,7 +12853,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730617</v>
+        <v>129730579</v>
       </c>
       <c r="B116" t="n">
         <v>57736</v>
@@ -12883,10 +12888,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>492349</v>
+        <v>492080</v>
       </c>
       <c r="R116" t="n">
-        <v>7134943</v>
+        <v>7135064</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12923,7 +12928,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12950,7 +12955,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730579</v>
+        <v>129730624</v>
       </c>
       <c r="B117" t="n">
         <v>57736</v>
@@ -12985,10 +12990,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492080</v>
+        <v>492366</v>
       </c>
       <c r="R117" t="n">
-        <v>7135064</v>
+        <v>7134921</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13052,7 +13057,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730624</v>
+        <v>129730597</v>
       </c>
       <c r="B118" t="n">
         <v>57736</v>
@@ -13087,10 +13092,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492366</v>
+        <v>492213</v>
       </c>
       <c r="R118" t="n">
-        <v>7134921</v>
+        <v>7135010</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13154,10 +13159,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730597</v>
+        <v>129730526</v>
       </c>
       <c r="B119" t="n">
-        <v>57736</v>
+        <v>90631</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13165,21 +13170,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13189,10 +13194,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492213</v>
+        <v>492395</v>
       </c>
       <c r="R119" t="n">
-        <v>7135010</v>
+        <v>7135064</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13225,11 +13230,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13256,10 +13256,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129730673</v>
+        <v>129730587</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13267,21 +13267,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>492342</v>
+        <v>492125</v>
       </c>
       <c r="R120" t="n">
-        <v>7135223</v>
+        <v>7135047</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13327,6 +13327,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13353,7 +13358,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730587</v>
+        <v>129730568</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -13388,10 +13393,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>492125</v>
+        <v>492044</v>
       </c>
       <c r="R121" t="n">
-        <v>7135047</v>
+        <v>7135114</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13455,7 +13460,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730568</v>
+        <v>129730582</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -13490,10 +13495,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492044</v>
+        <v>492094</v>
       </c>
       <c r="R122" t="n">
-        <v>7135114</v>
+        <v>7135060</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13530,7 +13535,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13557,7 +13562,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730582</v>
+        <v>129730585</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -13592,10 +13597,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492094</v>
+        <v>492123</v>
       </c>
       <c r="R123" t="n">
-        <v>7135060</v>
+        <v>7135047</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13632,7 +13637,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13659,7 +13664,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730585</v>
+        <v>129730657</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -13694,10 +13699,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492123</v>
+        <v>492468</v>
       </c>
       <c r="R124" t="n">
-        <v>7135047</v>
+        <v>7134848</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13761,7 +13766,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730657</v>
+        <v>129730614</v>
       </c>
       <c r="B125" t="n">
         <v>57736</v>
@@ -13796,10 +13801,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492468</v>
+        <v>492342</v>
       </c>
       <c r="R125" t="n">
-        <v>7134848</v>
+        <v>7134966</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13863,7 +13868,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730614</v>
+        <v>129730618</v>
       </c>
       <c r="B126" t="n">
         <v>57736</v>
@@ -13898,10 +13903,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492342</v>
+        <v>492350</v>
       </c>
       <c r="R126" t="n">
-        <v>7134966</v>
+        <v>7134947</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13938,7 +13943,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13965,10 +13970,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730618</v>
+        <v>129730673</v>
       </c>
       <c r="B127" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13976,21 +13981,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14000,10 +14005,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>492350</v>
+        <v>492342</v>
       </c>
       <c r="R127" t="n">
-        <v>7134947</v>
+        <v>7135223</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14036,11 +14041,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14980,32 +14980,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129730646</v>
+        <v>129730669</v>
       </c>
       <c r="B137" t="n">
-        <v>57736</v>
+        <v>91772</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15015,10 +15015,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>492465</v>
+        <v>492248</v>
       </c>
       <c r="R137" t="n">
-        <v>7134871</v>
+        <v>7135292</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15051,11 +15051,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15082,7 +15077,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730541</v>
+        <v>129730646</v>
       </c>
       <c r="B138" t="n">
         <v>57736</v>
@@ -15117,10 +15112,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>492004</v>
+        <v>492465</v>
       </c>
       <c r="R138" t="n">
-        <v>7135207</v>
+        <v>7134871</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15184,7 +15179,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730535</v>
+        <v>129730541</v>
       </c>
       <c r="B139" t="n">
         <v>57736</v>
@@ -15219,10 +15214,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492065</v>
+        <v>492004</v>
       </c>
       <c r="R139" t="n">
-        <v>7135257</v>
+        <v>7135207</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15286,7 +15281,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730620</v>
+        <v>129730535</v>
       </c>
       <c r="B140" t="n">
         <v>57736</v>
@@ -15321,10 +15316,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492351</v>
+        <v>492065</v>
       </c>
       <c r="R140" t="n">
-        <v>7134938</v>
+        <v>7135257</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15388,32 +15383,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730669</v>
+        <v>129730620</v>
       </c>
       <c r="B141" t="n">
-        <v>91772</v>
+        <v>57736</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15423,10 +15418,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492248</v>
+        <v>492351</v>
       </c>
       <c r="R141" t="n">
-        <v>7135292</v>
+        <v>7134938</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15459,6 +15454,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15485,32 +15485,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730655</v>
+        <v>129730524</v>
       </c>
       <c r="B142" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492460</v>
+        <v>492271</v>
       </c>
       <c r="R142" t="n">
-        <v>7134849</v>
+        <v>7135240</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15556,11 +15556,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15587,10 +15582,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730558</v>
+        <v>129730525</v>
       </c>
       <c r="B143" t="n">
-        <v>57736</v>
+        <v>90631</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15598,21 +15593,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15622,10 +15617,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492028</v>
+        <v>492390</v>
       </c>
       <c r="R143" t="n">
-        <v>7135126</v>
+        <v>7135053</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15658,11 +15653,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15689,7 +15679,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730609</v>
+        <v>129730655</v>
       </c>
       <c r="B144" t="n">
         <v>57736</v>
@@ -15724,10 +15714,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>492330</v>
+        <v>492460</v>
       </c>
       <c r="R144" t="n">
-        <v>7134971</v>
+        <v>7134849</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15764,7 +15754,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15791,7 +15781,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730616</v>
+        <v>129730558</v>
       </c>
       <c r="B145" t="n">
         <v>57736</v>
@@ -15826,10 +15816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>492343</v>
+        <v>492028</v>
       </c>
       <c r="R145" t="n">
-        <v>7134960</v>
+        <v>7135126</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15866,7 +15856,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15893,7 +15883,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730595</v>
+        <v>129730609</v>
       </c>
       <c r="B146" t="n">
         <v>57736</v>
@@ -15928,10 +15918,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>492208</v>
+        <v>492330</v>
       </c>
       <c r="R146" t="n">
-        <v>7135012</v>
+        <v>7134971</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15995,7 +15985,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730549</v>
+        <v>129730616</v>
       </c>
       <c r="B147" t="n">
         <v>57736</v>
@@ -16030,10 +16020,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>491986</v>
+        <v>492343</v>
       </c>
       <c r="R147" t="n">
-        <v>7135153</v>
+        <v>7134960</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16097,7 +16087,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730648</v>
+        <v>129730595</v>
       </c>
       <c r="B148" t="n">
         <v>57736</v>
@@ -16132,10 +16122,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>492457</v>
+        <v>492208</v>
       </c>
       <c r="R148" t="n">
-        <v>7134863</v>
+        <v>7135012</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16199,7 +16189,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730593</v>
+        <v>129730549</v>
       </c>
       <c r="B149" t="n">
         <v>57736</v>
@@ -16234,10 +16224,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>492199</v>
+        <v>491986</v>
       </c>
       <c r="R149" t="n">
-        <v>7135015</v>
+        <v>7135153</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16301,7 +16291,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730578</v>
+        <v>129730648</v>
       </c>
       <c r="B150" t="n">
         <v>57736</v>
@@ -16336,10 +16326,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>492086</v>
+        <v>492457</v>
       </c>
       <c r="R150" t="n">
-        <v>7135087</v>
+        <v>7134863</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16376,7 +16366,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16403,32 +16393,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730524</v>
+        <v>129730593</v>
       </c>
       <c r="B151" t="n">
-        <v>91563</v>
+        <v>57736</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16438,10 +16428,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>492271</v>
+        <v>492199</v>
       </c>
       <c r="R151" t="n">
-        <v>7135240</v>
+        <v>7135015</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16474,6 +16464,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16500,10 +16495,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730525</v>
+        <v>129730578</v>
       </c>
       <c r="B152" t="n">
-        <v>90631</v>
+        <v>57736</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16511,21 +16506,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16535,10 +16530,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492390</v>
+        <v>492086</v>
       </c>
       <c r="R152" t="n">
-        <v>7135053</v>
+        <v>7135087</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16571,6 +16566,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -2301,10 +2301,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726752</v>
+        <v>129726738</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492482</v>
+        <v>492242</v>
       </c>
       <c r="R16" t="n">
-        <v>7134934</v>
+        <v>7135130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,7 +2408,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726741</v>
+        <v>129726752</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492282</v>
+        <v>492482</v>
       </c>
       <c r="R17" t="n">
-        <v>7135069</v>
+        <v>7134934</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726738</v>
+        <v>129726741</v>
       </c>
       <c r="B18" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,21 +2526,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492242</v>
+        <v>492282</v>
       </c>
       <c r="R18" t="n">
-        <v>7135130</v>
+        <v>7135069</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2836,65 +2836,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129728246</v>
+        <v>129726736</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>83052</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492341</v>
+        <v>492194</v>
       </c>
       <c r="R21" t="n">
-        <v>7134976</v>
+        <v>7135150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,14 +2904,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,69 +2925,83 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726716</v>
+        <v>129728246</v>
       </c>
       <c r="B22" t="n">
-        <v>97667</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492599</v>
+        <v>492341</v>
       </c>
       <c r="R22" t="n">
-        <v>7134962</v>
+        <v>7134976</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3032,19 +3031,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:13</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3053,50 +3047,56 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726736</v>
+        <v>129726716</v>
       </c>
       <c r="B23" t="n">
-        <v>83052</v>
+        <v>97667</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492194</v>
+        <v>492599</v>
       </c>
       <c r="R23" t="n">
-        <v>7135150</v>
+        <v>7134962</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5946,45 +5946,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129728241</v>
+        <v>129728262</v>
       </c>
       <c r="B49" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492451</v>
+        <v>492479</v>
       </c>
       <c r="R49" t="n">
-        <v>7134904</v>
+        <v>7134899</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6019,14 +6022,45 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6043,7 +6077,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129728262</v>
+        <v>129726721</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -6072,19 +6106,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492479</v>
+        <v>492421</v>
       </c>
       <c r="R50" t="n">
-        <v>7134899</v>
+        <v>7135113</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6114,14 +6145,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran i gammal barrblandskog.</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6130,76 +6166,50 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129726721</v>
+        <v>129728241</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6209,10 +6219,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492421</v>
+        <v>492451</v>
       </c>
       <c r="R51" t="n">
-        <v>7135113</v>
+        <v>7134904</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6242,19 +6252,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6269,12 +6269,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6730,10 +6730,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129726734</v>
+        <v>129728260</v>
       </c>
       <c r="B56" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6741,19 +6741,23 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6761,10 +6765,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492211</v>
+        <v>492378</v>
       </c>
       <c r="R56" t="n">
-        <v>7135170</v>
+        <v>7134955</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6794,19 +6798,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6815,26 +6814,25 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129728260</v>
+        <v>129726731</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6869,10 +6867,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492378</v>
+        <v>492137</v>
       </c>
       <c r="R57" t="n">
-        <v>7134955</v>
+        <v>7135201</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6902,14 +6900,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6924,22 +6927,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129726731</v>
+        <v>129726734</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6947,23 +6950,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6971,10 +6970,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492137</v>
+        <v>492211</v>
       </c>
       <c r="R58" t="n">
-        <v>7135201</v>
+        <v>7135170</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7006,7 +7005,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7016,7 +7015,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7025,6 +7024,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7568,54 +7568,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726724</v>
+        <v>129726730</v>
       </c>
       <c r="B64" t="n">
-        <v>57896</v>
+        <v>92317</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492343</v>
+        <v>492124</v>
       </c>
       <c r="R64" t="n">
-        <v>7135242</v>
+        <v>7135171</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7647,7 +7638,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7657,7 +7648,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7684,10 +7675,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129726730</v>
+        <v>129728240</v>
       </c>
       <c r="B65" t="n">
-        <v>92317</v>
+        <v>80214</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7695,21 +7686,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7719,10 +7710,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492124</v>
+        <v>492405</v>
       </c>
       <c r="R65" t="n">
-        <v>7135171</v>
+        <v>7134981</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7752,19 +7743,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:53</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7779,44 +7765,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129728240</v>
+        <v>129728259</v>
       </c>
       <c r="B66" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7826,10 +7812,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492405</v>
+        <v>492317</v>
       </c>
       <c r="R66" t="n">
-        <v>7134981</v>
+        <v>7134999</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7866,7 +7852,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På ett mossöverväxt block.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7893,7 +7879,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129728259</v>
+        <v>129726745</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7928,10 +7914,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492317</v>
+        <v>492367</v>
       </c>
       <c r="R67" t="n">
-        <v>7134999</v>
+        <v>7135038</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7961,14 +7947,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7983,22 +7974,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726745</v>
+        <v>129726724</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8006,34 +7997,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492367</v>
+        <v>492343</v>
       </c>
       <c r="R68" t="n">
-        <v>7135038</v>
+        <v>7135242</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730573</v>
+        <v>129730672</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492062</v>
+        <v>492334</v>
       </c>
       <c r="R69" t="n">
-        <v>7135100</v>
+        <v>7135092</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,11 +8173,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8204,10 +8199,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730584</v>
+        <v>129730658</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>57895</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8215,21 +8210,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8239,10 +8234,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492107</v>
+        <v>492464</v>
       </c>
       <c r="R70" t="n">
-        <v>7135052</v>
+        <v>7135049</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8279,7 +8274,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8306,10 +8301,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730598</v>
+        <v>129730573</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8341,10 +8336,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492220</v>
+        <v>492062</v>
       </c>
       <c r="R71" t="n">
-        <v>7135003</v>
+        <v>7135100</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8381,7 +8376,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8408,10 +8403,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730615</v>
+        <v>129730598</v>
       </c>
       <c r="B72" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8443,10 +8438,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492345</v>
+        <v>492220</v>
       </c>
       <c r="R72" t="n">
-        <v>7134961</v>
+        <v>7135003</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8483,7 +8478,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8510,10 +8505,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730658</v>
+        <v>129730615</v>
       </c>
       <c r="B73" t="n">
-        <v>57896</v>
+        <v>57737</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8521,21 +8516,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8545,10 +8540,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492464</v>
+        <v>492345</v>
       </c>
       <c r="R73" t="n">
-        <v>7135049</v>
+        <v>7134961</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8585,7 +8580,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8612,10 +8607,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730672</v>
+        <v>129730584</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8623,21 +8618,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8647,10 +8642,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492334</v>
+        <v>492107</v>
       </c>
       <c r="R74" t="n">
-        <v>7135092</v>
+        <v>7135052</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8683,6 +8678,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8712,7 +8712,7 @@
         <v>129730671</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8806,10 +8806,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129730629</v>
+        <v>129730645</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>492369</v>
+        <v>492464</v>
       </c>
       <c r="R76" t="n">
-        <v>7134915</v>
+        <v>7134870</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8911,7 +8911,7 @@
         <v>129730637</v>
       </c>
       <c r="B77" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>129730551</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129730645</v>
+        <v>129730629</v>
       </c>
       <c r="B79" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>492464</v>
+        <v>492369</v>
       </c>
       <c r="R79" t="n">
-        <v>7134870</v>
+        <v>7134915</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9214,10 +9214,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730675</v>
+        <v>129730603</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9225,21 +9225,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492075</v>
+        <v>492265</v>
       </c>
       <c r="R80" t="n">
-        <v>7135214</v>
+        <v>7134987</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9285,6 +9285,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9311,32 +9316,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730665</v>
+        <v>129730562</v>
       </c>
       <c r="B81" t="n">
-        <v>98790</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9346,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492046</v>
+        <v>492037</v>
       </c>
       <c r="R81" t="n">
-        <v>7135177</v>
+        <v>7135120</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9386,7 +9391,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>8st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9413,10 +9418,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730635</v>
+        <v>129730594</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9448,10 +9453,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492424</v>
+        <v>492205</v>
       </c>
       <c r="R82" t="n">
-        <v>7134911</v>
+        <v>7135012</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9515,10 +9520,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730639</v>
+        <v>129730599</v>
       </c>
       <c r="B83" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9550,10 +9555,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492439</v>
+        <v>492216</v>
       </c>
       <c r="R83" t="n">
-        <v>7134899</v>
+        <v>7135002</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9590,7 +9595,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9617,32 +9622,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730562</v>
+        <v>129730665</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>98794</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9652,10 +9657,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492037</v>
+        <v>492046</v>
       </c>
       <c r="R84" t="n">
-        <v>7135120</v>
+        <v>7135177</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9692,7 +9697,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9719,10 +9724,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730575</v>
+        <v>129730675</v>
       </c>
       <c r="B85" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9730,21 +9735,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9754,10 +9759,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492063</v>
+        <v>492075</v>
       </c>
       <c r="R85" t="n">
-        <v>7135101</v>
+        <v>7135214</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9790,11 +9795,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9821,10 +9821,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129730603</v>
+        <v>129730639</v>
       </c>
       <c r="B86" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492265</v>
+        <v>492439</v>
       </c>
       <c r="R86" t="n">
-        <v>7134987</v>
+        <v>7134899</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9923,10 +9923,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129730594</v>
+        <v>129730635</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9958,10 +9958,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492205</v>
+        <v>492424</v>
       </c>
       <c r="R87" t="n">
-        <v>7135012</v>
+        <v>7134911</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10025,10 +10025,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129730599</v>
+        <v>129730575</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>492216</v>
+        <v>492063</v>
       </c>
       <c r="R88" t="n">
-        <v>7135002</v>
+        <v>7135101</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10130,7 +10130,7 @@
         <v>129730630</v>
       </c>
       <c r="B89" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10229,32 +10229,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129730663</v>
+        <v>129730583</v>
       </c>
       <c r="B90" t="n">
-        <v>98790</v>
+        <v>57737</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492070</v>
+        <v>492105</v>
       </c>
       <c r="R90" t="n">
-        <v>7135173</v>
+        <v>7135051</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>14st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,10 +10331,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129730583</v>
+        <v>129730625</v>
       </c>
       <c r="B91" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492105</v>
+        <v>492367</v>
       </c>
       <c r="R91" t="n">
-        <v>7135051</v>
+        <v>7134920</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10433,10 +10433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129730625</v>
+        <v>129730565</v>
       </c>
       <c r="B92" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>492367</v>
+        <v>492040</v>
       </c>
       <c r="R92" t="n">
-        <v>7134920</v>
+        <v>7135117</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10535,32 +10535,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129730565</v>
+        <v>129730663</v>
       </c>
       <c r="B93" t="n">
-        <v>57736</v>
+        <v>98794</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>492040</v>
+        <v>492070</v>
       </c>
       <c r="R93" t="n">
-        <v>7135117</v>
+        <v>7135173</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>14st</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129730606</v>
+        <v>129730522</v>
       </c>
       <c r="B94" t="n">
-        <v>57736</v>
+        <v>97040</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10672,10 +10672,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492303</v>
+        <v>492217</v>
       </c>
       <c r="R94" t="n">
-        <v>7134972</v>
+        <v>7135249</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10708,11 +10708,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10739,10 +10734,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730619</v>
+        <v>129730650</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10774,10 +10769,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492353</v>
+        <v>492473</v>
       </c>
       <c r="R95" t="n">
-        <v>7134945</v>
+        <v>7134864</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10814,7 +10809,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10841,10 +10836,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730650</v>
+        <v>129730619</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10876,10 +10871,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492473</v>
+        <v>492353</v>
       </c>
       <c r="R96" t="n">
-        <v>7134864</v>
+        <v>7134945</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10916,7 +10911,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10943,10 +10938,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730604</v>
+        <v>129730606</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10978,10 +10973,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492297</v>
+        <v>492303</v>
       </c>
       <c r="R97" t="n">
-        <v>7134975</v>
+        <v>7134972</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11048,7 +11043,7 @@
         <v>129730569</v>
       </c>
       <c r="B98" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11147,10 +11142,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730662</v>
+        <v>129730604</v>
       </c>
       <c r="B99" t="n">
-        <v>78094</v>
+        <v>57737</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11158,21 +11153,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11182,10 +11177,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492166</v>
+        <v>492297</v>
       </c>
       <c r="R99" t="n">
-        <v>7135239</v>
+        <v>7134975</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11218,6 +11213,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11244,10 +11244,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730661</v>
+        <v>129730662</v>
       </c>
       <c r="B100" t="n">
-        <v>91619</v>
+        <v>78097</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11255,19 +11255,23 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11275,10 +11279,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492069</v>
+        <v>492166</v>
       </c>
       <c r="R100" t="n">
-        <v>7135162</v>
+        <v>7135239</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11305,12 +11309,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11319,7 +11323,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11338,10 +11341,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730522</v>
+        <v>129730661</v>
       </c>
       <c r="B101" t="n">
-        <v>97036</v>
+        <v>91622</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11349,23 +11352,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11373,10 +11372,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492217</v>
+        <v>492069</v>
       </c>
       <c r="R101" t="n">
-        <v>7135249</v>
+        <v>7135162</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,12 +11402,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11417,6 +11416,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730656</v>
+        <v>129730523</v>
       </c>
       <c r="B102" t="n">
-        <v>57736</v>
+        <v>97040</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11446,21 +11446,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492466</v>
+        <v>492316</v>
       </c>
       <c r="R102" t="n">
-        <v>7134851</v>
+        <v>7135071</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11506,11 +11506,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11537,10 +11532,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730602</v>
+        <v>129730640</v>
       </c>
       <c r="B103" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11572,10 +11567,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492245</v>
+        <v>492444</v>
       </c>
       <c r="R103" t="n">
-        <v>7134995</v>
+        <v>7134887</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11639,10 +11634,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730640</v>
+        <v>129730602</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11674,10 +11669,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492444</v>
+        <v>492245</v>
       </c>
       <c r="R104" t="n">
-        <v>7134887</v>
+        <v>7134995</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11741,10 +11736,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730523</v>
+        <v>129730656</v>
       </c>
       <c r="B105" t="n">
-        <v>97036</v>
+        <v>57737</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11752,21 +11747,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11776,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>492316</v>
+        <v>492466</v>
       </c>
       <c r="R105" t="n">
-        <v>7135071</v>
+        <v>7134851</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11812,6 +11807,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11838,10 +11838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730529</v>
+        <v>129730521</v>
       </c>
       <c r="B106" t="n">
-        <v>57736</v>
+        <v>83055</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492088</v>
+        <v>492100</v>
       </c>
       <c r="R106" t="n">
-        <v>7135198</v>
+        <v>7135216</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11909,11 +11909,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11940,10 +11935,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730631</v>
+        <v>129730559</v>
       </c>
       <c r="B107" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11975,10 +11970,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492409</v>
+        <v>492032</v>
       </c>
       <c r="R107" t="n">
-        <v>7134918</v>
+        <v>7135120</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12015,7 +12010,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12042,10 +12037,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730532</v>
+        <v>129730529</v>
       </c>
       <c r="B108" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12077,10 +12072,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492082</v>
+        <v>492088</v>
       </c>
       <c r="R108" t="n">
-        <v>7135294</v>
+        <v>7135198</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12117,7 +12112,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12144,10 +12139,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730576</v>
+        <v>129730532</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12179,10 +12174,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492066</v>
+        <v>492082</v>
       </c>
       <c r="R109" t="n">
-        <v>7135093</v>
+        <v>7135294</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12219,7 +12214,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12246,10 +12241,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730559</v>
+        <v>129730631</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12281,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492032</v>
+        <v>492409</v>
       </c>
       <c r="R110" t="n">
-        <v>7135120</v>
+        <v>7134918</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12321,7 +12316,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12348,10 +12343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730521</v>
+        <v>129730576</v>
       </c>
       <c r="B111" t="n">
-        <v>83052</v>
+        <v>57737</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12359,21 +12354,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12383,10 +12378,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492100</v>
+        <v>492066</v>
       </c>
       <c r="R111" t="n">
-        <v>7135216</v>
+        <v>7135093</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12419,6 +12414,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129730528</v>
+        <v>129730617</v>
       </c>
       <c r="B112" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>492476</v>
+        <v>492349</v>
       </c>
       <c r="R112" t="n">
-        <v>7135072</v>
+        <v>7134943</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12520,7 +12520,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12547,10 +12547,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730632</v>
+        <v>129730624</v>
       </c>
       <c r="B113" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12582,10 +12582,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492414</v>
+        <v>492366</v>
       </c>
       <c r="R113" t="n">
-        <v>7134915</v>
+        <v>7134921</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12649,10 +12649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730608</v>
+        <v>129730528</v>
       </c>
       <c r="B114" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12684,10 +12684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492316</v>
+        <v>492476</v>
       </c>
       <c r="R114" t="n">
-        <v>7134971</v>
+        <v>7135072</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12751,10 +12751,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730617</v>
+        <v>129730597</v>
       </c>
       <c r="B115" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12786,10 +12786,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492349</v>
+        <v>492213</v>
       </c>
       <c r="R115" t="n">
-        <v>7134943</v>
+        <v>7135010</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12856,7 +12856,7 @@
         <v>129730579</v>
       </c>
       <c r="B116" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12955,10 +12955,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730624</v>
+        <v>129730632</v>
       </c>
       <c r="B117" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12990,10 +12990,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492366</v>
+        <v>492414</v>
       </c>
       <c r="R117" t="n">
-        <v>7134921</v>
+        <v>7134915</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13057,10 +13057,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730597</v>
+        <v>129730608</v>
       </c>
       <c r="B118" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13092,10 +13092,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492213</v>
+        <v>492316</v>
       </c>
       <c r="R118" t="n">
-        <v>7135010</v>
+        <v>7134971</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13162,7 +13162,7 @@
         <v>129730526</v>
       </c>
       <c r="B119" t="n">
-        <v>90631</v>
+        <v>90634</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129730587</v>
+        <v>129730585</v>
       </c>
       <c r="B120" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>492125</v>
+        <v>492123</v>
       </c>
       <c r="R120" t="n">
         <v>7135047</v>
@@ -13358,10 +13358,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730568</v>
+        <v>129730582</v>
       </c>
       <c r="B121" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13393,10 +13393,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>492044</v>
+        <v>492094</v>
       </c>
       <c r="R121" t="n">
-        <v>7135114</v>
+        <v>7135060</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13433,7 +13433,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13460,10 +13460,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730582</v>
+        <v>129730657</v>
       </c>
       <c r="B122" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13495,10 +13495,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492094</v>
+        <v>492468</v>
       </c>
       <c r="R122" t="n">
-        <v>7135060</v>
+        <v>7134848</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13562,10 +13562,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730585</v>
+        <v>129730587</v>
       </c>
       <c r="B123" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492123</v>
+        <v>492125</v>
       </c>
       <c r="R123" t="n">
         <v>7135047</v>
@@ -13664,10 +13664,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730657</v>
+        <v>129730568</v>
       </c>
       <c r="B124" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13699,10 +13699,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492468</v>
+        <v>492044</v>
       </c>
       <c r="R124" t="n">
-        <v>7134848</v>
+        <v>7135114</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13766,10 +13766,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730614</v>
+        <v>129730618</v>
       </c>
       <c r="B125" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492342</v>
+        <v>492350</v>
       </c>
       <c r="R125" t="n">
-        <v>7134966</v>
+        <v>7134947</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13841,7 +13841,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13868,10 +13868,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730618</v>
+        <v>129730614</v>
       </c>
       <c r="B126" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13903,10 +13903,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492350</v>
+        <v>492342</v>
       </c>
       <c r="R126" t="n">
-        <v>7134947</v>
+        <v>7134966</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13973,7 +13973,7 @@
         <v>129730673</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14067,10 +14067,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730563</v>
+        <v>129730539</v>
       </c>
       <c r="B128" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14102,10 +14102,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>492037</v>
+        <v>492011</v>
       </c>
       <c r="R128" t="n">
-        <v>7135119</v>
+        <v>7135206</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14169,10 +14169,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730643</v>
+        <v>129730563</v>
       </c>
       <c r="B129" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>492464</v>
+        <v>492037</v>
       </c>
       <c r="R129" t="n">
-        <v>7134867</v>
+        <v>7135119</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14271,10 +14271,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730561</v>
+        <v>129730643</v>
       </c>
       <c r="B130" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14306,10 +14306,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>492039</v>
+        <v>492464</v>
       </c>
       <c r="R130" t="n">
-        <v>7135123</v>
+        <v>7134867</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14373,10 +14373,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730539</v>
+        <v>129730561</v>
       </c>
       <c r="B131" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14408,10 +14408,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>492011</v>
+        <v>492039</v>
       </c>
       <c r="R131" t="n">
-        <v>7135206</v>
+        <v>7135123</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14478,7 +14478,7 @@
         <v>129730670</v>
       </c>
       <c r="B132" t="n">
-        <v>91772</v>
+        <v>91775</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14572,10 +14572,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730545</v>
+        <v>129730531</v>
       </c>
       <c r="B133" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491983</v>
+        <v>492083</v>
       </c>
       <c r="R133" t="n">
-        <v>7135171</v>
+        <v>7135291</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14674,10 +14674,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730531</v>
+        <v>129730574</v>
       </c>
       <c r="B134" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>492083</v>
+        <v>492062</v>
       </c>
       <c r="R134" t="n">
-        <v>7135291</v>
+        <v>7135103</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14776,10 +14776,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730580</v>
+        <v>129730545</v>
       </c>
       <c r="B135" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>492077</v>
+        <v>491983</v>
       </c>
       <c r="R135" t="n">
-        <v>7135066</v>
+        <v>7135171</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14878,10 +14878,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730574</v>
+        <v>129730580</v>
       </c>
       <c r="B136" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492062</v>
+        <v>492077</v>
       </c>
       <c r="R136" t="n">
-        <v>7135103</v>
+        <v>7135066</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14983,7 +14983,7 @@
         <v>129730669</v>
       </c>
       <c r="B137" t="n">
-        <v>91772</v>
+        <v>91775</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15077,10 +15077,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730646</v>
+        <v>129730620</v>
       </c>
       <c r="B138" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15112,10 +15112,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>492465</v>
+        <v>492351</v>
       </c>
       <c r="R138" t="n">
-        <v>7134871</v>
+        <v>7134938</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15179,10 +15179,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730541</v>
+        <v>129730535</v>
       </c>
       <c r="B139" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15214,10 +15214,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492004</v>
+        <v>492065</v>
       </c>
       <c r="R139" t="n">
-        <v>7135207</v>
+        <v>7135257</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15281,10 +15281,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730535</v>
+        <v>129730541</v>
       </c>
       <c r="B140" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15316,10 +15316,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492065</v>
+        <v>492004</v>
       </c>
       <c r="R140" t="n">
-        <v>7135257</v>
+        <v>7135207</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15383,10 +15383,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730620</v>
+        <v>129730646</v>
       </c>
       <c r="B141" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15418,10 +15418,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492351</v>
+        <v>492465</v>
       </c>
       <c r="R141" t="n">
-        <v>7134938</v>
+        <v>7134871</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15485,32 +15485,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730524</v>
+        <v>129730525</v>
       </c>
       <c r="B142" t="n">
-        <v>91563</v>
+        <v>90634</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492271</v>
+        <v>492390</v>
       </c>
       <c r="R142" t="n">
-        <v>7135240</v>
+        <v>7135053</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15582,32 +15582,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730525</v>
+        <v>129730524</v>
       </c>
       <c r="B143" t="n">
-        <v>90631</v>
+        <v>91566</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15617,10 +15617,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492390</v>
+        <v>492271</v>
       </c>
       <c r="R143" t="n">
-        <v>7135053</v>
+        <v>7135240</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15679,10 +15679,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730655</v>
+        <v>129730648</v>
       </c>
       <c r="B144" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15714,10 +15714,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>492460</v>
+        <v>492457</v>
       </c>
       <c r="R144" t="n">
-        <v>7134849</v>
+        <v>7134863</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15781,10 +15781,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730558</v>
+        <v>129730616</v>
       </c>
       <c r="B145" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>492028</v>
+        <v>492343</v>
       </c>
       <c r="R145" t="n">
-        <v>7135126</v>
+        <v>7134960</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15856,7 +15856,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15883,10 +15883,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730609</v>
+        <v>129730593</v>
       </c>
       <c r="B146" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15918,10 +15918,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>492330</v>
+        <v>492199</v>
       </c>
       <c r="R146" t="n">
-        <v>7134971</v>
+        <v>7135015</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15985,10 +15985,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730616</v>
+        <v>129730578</v>
       </c>
       <c r="B147" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16020,10 +16020,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>492343</v>
+        <v>492086</v>
       </c>
       <c r="R147" t="n">
-        <v>7134960</v>
+        <v>7135087</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16087,10 +16087,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730595</v>
+        <v>129730609</v>
       </c>
       <c r="B148" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>492208</v>
+        <v>492330</v>
       </c>
       <c r="R148" t="n">
-        <v>7135012</v>
+        <v>7134971</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16192,7 +16192,7 @@
         <v>129730549</v>
       </c>
       <c r="B149" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16291,10 +16291,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730648</v>
+        <v>129730655</v>
       </c>
       <c r="B150" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16326,10 +16326,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>492457</v>
+        <v>492460</v>
       </c>
       <c r="R150" t="n">
-        <v>7134863</v>
+        <v>7134849</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16393,10 +16393,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730593</v>
+        <v>129730595</v>
       </c>
       <c r="B151" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>492199</v>
+        <v>492208</v>
       </c>
       <c r="R151" t="n">
-        <v>7135015</v>
+        <v>7135012</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16495,10 +16495,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730578</v>
+        <v>129730558</v>
       </c>
       <c r="B152" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16530,10 +16530,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492086</v>
+        <v>492028</v>
       </c>
       <c r="R152" t="n">
-        <v>7135087</v>
+        <v>7135126</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16597,10 +16597,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129730668</v>
+        <v>129730544</v>
       </c>
       <c r="B153" t="n">
-        <v>56917</v>
+        <v>57737</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16608,16 +16608,16 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>492293</v>
+        <v>491998</v>
       </c>
       <c r="R153" t="n">
-        <v>7134991</v>
+        <v>7135201</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16668,6 +16668,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16694,10 +16699,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730667</v>
+        <v>129730590</v>
       </c>
       <c r="B154" t="n">
-        <v>56917</v>
+        <v>57737</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16705,16 +16710,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -16729,10 +16734,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>492088</v>
+        <v>492184</v>
       </c>
       <c r="R154" t="n">
-        <v>7135189</v>
+        <v>7135029</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16765,6 +16770,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16794,7 +16804,7 @@
         <v>129730601</v>
       </c>
       <c r="B155" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16896,7 +16906,7 @@
         <v>129730552</v>
       </c>
       <c r="B156" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16995,10 +17005,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730571</v>
+        <v>129730564</v>
       </c>
       <c r="B157" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17030,10 +17040,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>492057</v>
+        <v>492039</v>
       </c>
       <c r="R157" t="n">
-        <v>7135106</v>
+        <v>7135120</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17070,7 +17080,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17097,10 +17107,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730544</v>
+        <v>129730571</v>
       </c>
       <c r="B158" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17132,10 +17142,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>491998</v>
+        <v>492057</v>
       </c>
       <c r="R158" t="n">
-        <v>7135201</v>
+        <v>7135106</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17172,7 +17182,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17199,10 +17209,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730564</v>
+        <v>129730634</v>
       </c>
       <c r="B159" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17234,10 +17244,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>492039</v>
+        <v>492423</v>
       </c>
       <c r="R159" t="n">
-        <v>7135120</v>
+        <v>7134915</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17301,10 +17311,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730590</v>
+        <v>129730668</v>
       </c>
       <c r="B160" t="n">
-        <v>57736</v>
+        <v>56918</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17312,16 +17322,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -17336,10 +17346,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>492184</v>
+        <v>492293</v>
       </c>
       <c r="R160" t="n">
-        <v>7135029</v>
+        <v>7134991</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17372,11 +17382,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17403,10 +17408,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129730634</v>
+        <v>129730667</v>
       </c>
       <c r="B161" t="n">
-        <v>57736</v>
+        <v>56918</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17414,16 +17419,16 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -17438,10 +17443,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>492423</v>
+        <v>492088</v>
       </c>
       <c r="R161" t="n">
-        <v>7134915</v>
+        <v>7135189</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17474,11 +17479,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17505,10 +17505,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730527</v>
+        <v>129730547</v>
       </c>
       <c r="B162" t="n">
-        <v>90631</v>
+        <v>57737</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17516,21 +17516,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17540,10 +17540,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>492267</v>
+        <v>491981</v>
       </c>
       <c r="R162" t="n">
-        <v>7135233</v>
+        <v>7135158</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17576,6 +17576,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17602,10 +17607,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730547</v>
+        <v>129730556</v>
       </c>
       <c r="B163" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17637,10 +17642,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>491981</v>
+        <v>492024</v>
       </c>
       <c r="R163" t="n">
-        <v>7135158</v>
+        <v>7135131</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17704,10 +17709,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730546</v>
+        <v>129730591</v>
       </c>
       <c r="B164" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17739,10 +17744,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>491985</v>
+        <v>492194</v>
       </c>
       <c r="R164" t="n">
-        <v>7135158</v>
+        <v>7135016</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17779,7 +17784,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17806,10 +17811,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730556</v>
+        <v>129730546</v>
       </c>
       <c r="B165" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17841,10 +17846,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>492024</v>
+        <v>491985</v>
       </c>
       <c r="R165" t="n">
-        <v>7135131</v>
+        <v>7135158</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17881,7 +17886,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17911,7 +17916,7 @@
         <v>129730592</v>
       </c>
       <c r="B166" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18010,10 +18015,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730591</v>
+        <v>129730527</v>
       </c>
       <c r="B167" t="n">
-        <v>57736</v>
+        <v>90634</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18021,21 +18026,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18045,10 +18050,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492194</v>
+        <v>492267</v>
       </c>
       <c r="R167" t="n">
-        <v>7135016</v>
+        <v>7135233</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18081,11 +18086,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18112,10 +18112,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129730652</v>
+        <v>129730554</v>
       </c>
       <c r="B168" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18147,10 +18147,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>492473</v>
+        <v>492027</v>
       </c>
       <c r="R168" t="n">
-        <v>7134862</v>
+        <v>7135130</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18217,7 +18217,7 @@
         <v>129730605</v>
       </c>
       <c r="B169" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18316,10 +18316,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129730554</v>
+        <v>129730652</v>
       </c>
       <c r="B170" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18351,10 +18351,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>492027</v>
+        <v>492473</v>
       </c>
       <c r="R170" t="n">
-        <v>7135130</v>
+        <v>7134862</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18421,7 +18421,7 @@
         <v>129730588</v>
       </c>
       <c r="B171" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18520,10 +18520,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129730567</v>
+        <v>129730530</v>
       </c>
       <c r="B172" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18555,10 +18555,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>492043</v>
+        <v>492078</v>
       </c>
       <c r="R172" t="n">
-        <v>7135115</v>
+        <v>7135290</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18622,10 +18622,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129730649</v>
+        <v>129730567</v>
       </c>
       <c r="B173" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>492466</v>
+        <v>492043</v>
       </c>
       <c r="R173" t="n">
-        <v>7134866</v>
+        <v>7135115</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18727,7 +18727,7 @@
         <v>129730555</v>
       </c>
       <c r="B174" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18826,10 +18826,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129730581</v>
+        <v>129730649</v>
       </c>
       <c r="B175" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>492090</v>
+        <v>492466</v>
       </c>
       <c r="R175" t="n">
-        <v>7135062</v>
+        <v>7134866</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18928,10 +18928,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129730530</v>
+        <v>129730581</v>
       </c>
       <c r="B176" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18963,10 +18963,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>492078</v>
+        <v>492090</v>
       </c>
       <c r="R176" t="n">
-        <v>7135290</v>
+        <v>7135062</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19030,10 +19030,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129730586</v>
+        <v>129730607</v>
       </c>
       <c r="B177" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19065,10 +19065,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>492124</v>
+        <v>492312</v>
       </c>
       <c r="R177" t="n">
-        <v>7135046</v>
+        <v>7134971</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19132,10 +19132,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129730612</v>
+        <v>129730644</v>
       </c>
       <c r="B178" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19167,10 +19167,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>492333</v>
+        <v>492462</v>
       </c>
       <c r="R178" t="n">
-        <v>7134969</v>
+        <v>7134869</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19234,10 +19234,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129730623</v>
+        <v>129730612</v>
       </c>
       <c r="B179" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19269,10 +19269,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>492353</v>
+        <v>492333</v>
       </c>
       <c r="R179" t="n">
-        <v>7134936</v>
+        <v>7134969</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19336,10 +19336,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129730607</v>
+        <v>129730586</v>
       </c>
       <c r="B180" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19371,10 +19371,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>492312</v>
+        <v>492124</v>
       </c>
       <c r="R180" t="n">
-        <v>7134971</v>
+        <v>7135046</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19438,10 +19438,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129730610</v>
+        <v>129730623</v>
       </c>
       <c r="B181" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>492330</v>
+        <v>492353</v>
       </c>
       <c r="R181" t="n">
-        <v>7134972</v>
+        <v>7134936</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19540,10 +19540,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129730644</v>
+        <v>129730610</v>
       </c>
       <c r="B182" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>492462</v>
+        <v>492330</v>
       </c>
       <c r="R182" t="n">
-        <v>7134869</v>
+        <v>7134972</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19645,7 +19645,7 @@
         <v>129730660</v>
       </c>
       <c r="B183" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19736,10 +19736,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129730557</v>
+        <v>129730550</v>
       </c>
       <c r="B184" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19771,10 +19771,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>492026</v>
+        <v>491991</v>
       </c>
       <c r="R184" t="n">
-        <v>7135131</v>
+        <v>7135149</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19838,10 +19838,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129730537</v>
+        <v>129730653</v>
       </c>
       <c r="B185" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19873,10 +19873,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>492037</v>
+        <v>492468</v>
       </c>
       <c r="R185" t="n">
-        <v>7135230</v>
+        <v>7134851</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19940,10 +19940,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730572</v>
+        <v>129730577</v>
       </c>
       <c r="B186" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19975,10 +19975,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492060</v>
+        <v>492066</v>
       </c>
       <c r="R186" t="n">
-        <v>7135105</v>
+        <v>7135097</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20042,10 +20042,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730653</v>
+        <v>129730636</v>
       </c>
       <c r="B187" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20077,10 +20077,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>492468</v>
+        <v>492435</v>
       </c>
       <c r="R187" t="n">
-        <v>7134851</v>
+        <v>7134917</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20117,7 +20117,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20144,10 +20144,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730636</v>
+        <v>129730557</v>
       </c>
       <c r="B188" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20179,10 +20179,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>492435</v>
+        <v>492026</v>
       </c>
       <c r="R188" t="n">
-        <v>7134917</v>
+        <v>7135131</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20246,10 +20246,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129730550</v>
+        <v>129730537</v>
       </c>
       <c r="B189" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20281,10 +20281,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>491991</v>
+        <v>492037</v>
       </c>
       <c r="R189" t="n">
-        <v>7135149</v>
+        <v>7135230</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20348,10 +20348,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730577</v>
+        <v>129730654</v>
       </c>
       <c r="B190" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>492066</v>
+        <v>492462</v>
       </c>
       <c r="R190" t="n">
-        <v>7135097</v>
+        <v>7134847</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20450,10 +20450,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129730654</v>
+        <v>129730572</v>
       </c>
       <c r="B191" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>492462</v>
+        <v>492060</v>
       </c>
       <c r="R191" t="n">
-        <v>7134847</v>
+        <v>7135105</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20555,7 +20555,7 @@
         <v>129730674</v>
       </c>
       <c r="B192" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20649,32 +20649,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730666</v>
+        <v>129730641</v>
       </c>
       <c r="B193" t="n">
-        <v>98790</v>
+        <v>57737</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492253</v>
+        <v>492462</v>
       </c>
       <c r="R193" t="n">
-        <v>7135293</v>
+        <v>7134883</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>7st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20751,10 +20751,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730553</v>
+        <v>129730621</v>
       </c>
       <c r="B194" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20786,10 +20786,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492008</v>
+        <v>492355</v>
       </c>
       <c r="R194" t="n">
-        <v>7135137</v>
+        <v>7134935</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20853,10 +20853,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730642</v>
+        <v>129730613</v>
       </c>
       <c r="B195" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20888,10 +20888,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492466</v>
+        <v>492341</v>
       </c>
       <c r="R195" t="n">
-        <v>7134877</v>
+        <v>7134968</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20955,10 +20955,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730596</v>
+        <v>129730570</v>
       </c>
       <c r="B196" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20990,10 +20990,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492210</v>
+        <v>492057</v>
       </c>
       <c r="R196" t="n">
-        <v>7135013</v>
+        <v>7135109</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21030,7 +21030,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21057,10 +21057,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129730613</v>
+        <v>129730642</v>
       </c>
       <c r="B197" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21092,10 +21092,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>492341</v>
+        <v>492466</v>
       </c>
       <c r="R197" t="n">
-        <v>7134968</v>
+        <v>7134877</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21159,10 +21159,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730600</v>
+        <v>129730560</v>
       </c>
       <c r="B198" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21194,10 +21194,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492239</v>
+        <v>492037</v>
       </c>
       <c r="R198" t="n">
-        <v>7134997</v>
+        <v>7135124</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21261,10 +21261,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730560</v>
+        <v>129730651</v>
       </c>
       <c r="B199" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21296,10 +21296,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492037</v>
+        <v>492474</v>
       </c>
       <c r="R199" t="n">
-        <v>7135124</v>
+        <v>7134863</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21363,10 +21363,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730570</v>
+        <v>129730553</v>
       </c>
       <c r="B200" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21398,10 +21398,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492057</v>
+        <v>492008</v>
       </c>
       <c r="R200" t="n">
-        <v>7135109</v>
+        <v>7135137</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21465,10 +21465,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730641</v>
+        <v>129730600</v>
       </c>
       <c r="B201" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21500,10 +21500,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492462</v>
+        <v>492239</v>
       </c>
       <c r="R201" t="n">
-        <v>7134883</v>
+        <v>7134997</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21567,10 +21567,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730621</v>
+        <v>129730596</v>
       </c>
       <c r="B202" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492355</v>
+        <v>492210</v>
       </c>
       <c r="R202" t="n">
-        <v>7134935</v>
+        <v>7135013</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21642,7 +21642,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21669,32 +21669,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129730651</v>
+        <v>129730666</v>
       </c>
       <c r="B203" t="n">
-        <v>57736</v>
+        <v>98794</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21704,10 +21704,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>492474</v>
+        <v>492253</v>
       </c>
       <c r="R203" t="n">
-        <v>7134863</v>
+        <v>7135293</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21744,7 +21744,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>7st</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21774,7 +21774,7 @@
         <v>129811411</v>
       </c>
       <c r="B204" t="n">
-        <v>58369</v>
+        <v>58372</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728237</v>
+        <v>129728258</v>
       </c>
       <c r="B5" t="n">
-        <v>80187</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,41 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492236</v>
+        <v>492272</v>
       </c>
       <c r="R5" t="n">
-        <v>7135034</v>
+        <v>7135018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1101,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en klen levande sälg.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,34 +1110,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1164,7 +1131,7 @@
         <v>129728238</v>
       </c>
       <c r="B6" t="n">
-        <v>80214</v>
+        <v>80217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726749</v>
+        <v>129726742</v>
       </c>
       <c r="B7" t="n">
-        <v>83052</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492403</v>
+        <v>492287</v>
       </c>
       <c r="R7" t="n">
-        <v>7135004</v>
+        <v>7135066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728258</v>
+        <v>129726749</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492272</v>
+        <v>492403</v>
       </c>
       <c r="R8" t="n">
-        <v>7135018</v>
+        <v>7135004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,14 +1400,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,22 +1427,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726742</v>
+        <v>129728249</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,16 +1468,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492287</v>
+        <v>492618</v>
       </c>
       <c r="R9" t="n">
-        <v>7135066</v>
+        <v>7134954</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,19 +1510,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,28 +1526,54 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129728249</v>
+        <v>129726748</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>78097</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,37 +1581,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492618</v>
+        <v>492403</v>
       </c>
       <c r="R10" t="n">
-        <v>7134954</v>
+        <v>7135004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,14 +1638,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,54 +1659,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726748</v>
+        <v>129728237</v>
       </c>
       <c r="B11" t="n">
-        <v>78094</v>
+        <v>80190</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,34 +1688,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492403</v>
+        <v>492236</v>
       </c>
       <c r="R11" t="n">
-        <v>7135004</v>
+        <v>7135034</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,19 +1752,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:04</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,18 +1768,44 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
         <v>129728251</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>129728261</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,65 +2045,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129728247</v>
+        <v>129726752</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492455</v>
+        <v>492482</v>
       </c>
       <c r="R14" t="n">
-        <v>7134922</v>
+        <v>7134934</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,14 +2113,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,89 +2134,63 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129728244</v>
+        <v>129726741</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492133</v>
+        <v>492282</v>
       </c>
       <c r="R15" t="n">
-        <v>7135159</v>
+        <v>7135069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,14 +2220,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,24 +2241,18 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2304,7 +2262,7 @@
         <v>129726738</v>
       </c>
       <c r="B16" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,45 +2366,65 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726752</v>
+        <v>129728247</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492482</v>
+        <v>492455</v>
       </c>
       <c r="R17" t="n">
-        <v>7134934</v>
+        <v>7134922</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,19 +2454,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>08:50</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,63 +2470,89 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726741</v>
+        <v>129728244</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492282</v>
+        <v>492133</v>
       </c>
       <c r="R18" t="n">
-        <v>7135069</v>
+        <v>7135159</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,19 +2582,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,28 +2598,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726723</v>
+        <v>129726744</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492370</v>
+        <v>492318</v>
       </c>
       <c r="R19" t="n">
-        <v>7135127</v>
+        <v>7135032</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726744</v>
+        <v>129726723</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492318</v>
+        <v>492370</v>
       </c>
       <c r="R20" t="n">
-        <v>7135032</v>
+        <v>7135127</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,7 +2839,7 @@
         <v>129726736</v>
       </c>
       <c r="B21" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>129728246</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>129726716</v>
       </c>
       <c r="B23" t="n">
-        <v>97667</v>
+        <v>97671</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>129728252</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>129728245</v>
       </c>
       <c r="B25" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>129728242</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129726732</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>129728257</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>129726754</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>129726719</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726726</v>
+        <v>129726722</v>
       </c>
       <c r="B31" t="n">
-        <v>91772</v>
+        <v>98794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,34 +3970,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492285</v>
+        <v>492376</v>
       </c>
       <c r="R31" t="n">
-        <v>7135248</v>
+        <v>7135128</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4069,7 +4073,7 @@
         <v>129726737</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726722</v>
+        <v>129726726</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>91775</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4184,38 +4188,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492376</v>
+        <v>492285</v>
       </c>
       <c r="R33" t="n">
-        <v>7135128</v>
+        <v>7135248</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4287,7 +4287,7 @@
         <v>129728254</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>129728255</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>129728256</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>129726729</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>129726750</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>129728243</v>
       </c>
       <c r="B39" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>129726720</v>
       </c>
       <c r="B40" t="n">
-        <v>78094</v>
+        <v>78097</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>129726735</v>
       </c>
       <c r="B41" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>129728236</v>
       </c>
       <c r="B42" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5281,10 +5281,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129728253</v>
+        <v>129726740</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492341</v>
+        <v>492268</v>
       </c>
       <c r="R43" t="n">
-        <v>7135150</v>
+        <v>7135143</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5349,14 +5349,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5371,22 +5376,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726740</v>
+        <v>129728253</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5418,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492268</v>
+        <v>492341</v>
       </c>
       <c r="R44" t="n">
-        <v>7135143</v>
+        <v>7135150</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5451,19 +5456,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:25</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5478,12 +5478,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5493,7 +5493,7 @@
         <v>129728234</v>
       </c>
       <c r="B45" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>129726733</v>
       </c>
       <c r="B46" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>129726717</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>129726751</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>129728262</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>129726721</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>129728241</v>
       </c>
       <c r="B51" t="n">
-        <v>80214</v>
+        <v>80217</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6281,10 +6281,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129726718</v>
+        <v>129726727</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492543</v>
+        <v>492258</v>
       </c>
       <c r="R52" t="n">
-        <v>7135091</v>
+        <v>7135232</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6388,10 +6388,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129726747</v>
+        <v>129726718</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492381</v>
+        <v>492543</v>
       </c>
       <c r="R53" t="n">
-        <v>7135002</v>
+        <v>7135091</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6495,10 +6495,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129726727</v>
+        <v>129726747</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492258</v>
+        <v>492381</v>
       </c>
       <c r="R54" t="n">
-        <v>7135232</v>
+        <v>7135002</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6602,65 +6602,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129728248</v>
+        <v>129728260</v>
       </c>
       <c r="B55" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492492</v>
+        <v>492378</v>
       </c>
       <c r="R55" t="n">
-        <v>7134909</v>
+        <v>7134955</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6697,7 +6677,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6706,14 +6686,8 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6730,10 +6704,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129728260</v>
+        <v>129726734</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>91622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6741,23 +6715,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6765,10 +6735,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492378</v>
+        <v>492211</v>
       </c>
       <c r="R56" t="n">
-        <v>7134955</v>
+        <v>7135170</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6798,14 +6768,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6814,18 +6789,19 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6835,7 +6811,7 @@
         <v>129726731</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6939,41 +6915,65 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129726734</v>
+        <v>129728248</v>
       </c>
       <c r="B58" t="n">
-        <v>91619</v>
+        <v>98794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492211</v>
+        <v>492492</v>
       </c>
       <c r="R58" t="n">
-        <v>7135170</v>
+        <v>7134909</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7003,19 +7003,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst 32 plantor inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7028,25 +7023,30 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129728250</v>
+        <v>129726728</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>78097</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7054,21 +7054,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492572</v>
+        <v>492179</v>
       </c>
       <c r="R59" t="n">
-        <v>7135009</v>
+        <v>7135241</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7111,14 +7111,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7133,22 +7138,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726725</v>
+        <v>129726753</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7156,21 +7161,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7180,10 +7185,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492304</v>
+        <v>492496</v>
       </c>
       <c r="R60" t="n">
-        <v>7135246</v>
+        <v>7134904</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7215,7 +7220,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7225,7 +7230,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7252,10 +7257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129726728</v>
+        <v>129728250</v>
       </c>
       <c r="B61" t="n">
-        <v>78094</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7263,21 +7268,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7287,10 +7292,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492179</v>
+        <v>492572</v>
       </c>
       <c r="R61" t="n">
-        <v>7135241</v>
+        <v>7135009</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7320,19 +7325,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7347,22 +7347,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726753</v>
+        <v>129726725</v>
       </c>
       <c r="B62" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492496</v>
+        <v>492304</v>
       </c>
       <c r="R62" t="n">
-        <v>7134904</v>
+        <v>7135246</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7469,7 +7469,7 @@
         <v>129728239</v>
       </c>
       <c r="B63" t="n">
-        <v>80214</v>
+        <v>80217</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>129726730</v>
       </c>
       <c r="B64" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129728240</v>
+        <v>129728259</v>
       </c>
       <c r="B65" t="n">
-        <v>80214</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492405</v>
+        <v>492317</v>
       </c>
       <c r="R65" t="n">
-        <v>7134981</v>
+        <v>7134999</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På ett mossöverväxt block.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7777,10 +7777,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129728259</v>
+        <v>129726745</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492317</v>
+        <v>492367</v>
       </c>
       <c r="R66" t="n">
-        <v>7134999</v>
+        <v>7135038</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7845,14 +7845,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7867,44 +7872,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129726745</v>
+        <v>129728240</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>80217</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7914,10 +7919,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492367</v>
+        <v>492405</v>
       </c>
       <c r="R67" t="n">
-        <v>7135038</v>
+        <v>7134981</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7947,19 +7952,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:12</t>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
         <v>129726724</v>
       </c>
       <c r="B68" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8102,10 +8102,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129730672</v>
+        <v>129730573</v>
       </c>
       <c r="B69" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492334</v>
+        <v>492062</v>
       </c>
       <c r="R69" t="n">
-        <v>7135092</v>
+        <v>7135100</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,6 +8173,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8199,10 +8204,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730658</v>
+        <v>129730598</v>
       </c>
       <c r="B70" t="n">
-        <v>57895</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8210,21 +8215,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8234,10 +8239,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492464</v>
+        <v>492220</v>
       </c>
       <c r="R70" t="n">
-        <v>7135049</v>
+        <v>7135003</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8274,7 +8279,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8301,7 +8306,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730573</v>
+        <v>129730615</v>
       </c>
       <c r="B71" t="n">
         <v>57737</v>
@@ -8336,10 +8341,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492062</v>
+        <v>492345</v>
       </c>
       <c r="R71" t="n">
-        <v>7135100</v>
+        <v>7134961</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8403,7 +8408,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730598</v>
+        <v>129730584</v>
       </c>
       <c r="B72" t="n">
         <v>57737</v>
@@ -8438,10 +8443,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492220</v>
+        <v>492107</v>
       </c>
       <c r="R72" t="n">
-        <v>7135003</v>
+        <v>7135052</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8505,10 +8510,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730615</v>
+        <v>129730658</v>
       </c>
       <c r="B73" t="n">
-        <v>57737</v>
+        <v>57895</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8516,21 +8521,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8540,10 +8545,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492345</v>
+        <v>492464</v>
       </c>
       <c r="R73" t="n">
-        <v>7134961</v>
+        <v>7135049</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8580,7 +8585,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8607,10 +8612,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730584</v>
+        <v>129730672</v>
       </c>
       <c r="B74" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8618,21 +8623,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8642,10 +8647,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492107</v>
+        <v>492334</v>
       </c>
       <c r="R74" t="n">
-        <v>7135052</v>
+        <v>7135092</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8678,11 +8683,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9214,32 +9214,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730603</v>
+        <v>129730665</v>
       </c>
       <c r="B80" t="n">
-        <v>57737</v>
+        <v>98794</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492265</v>
+        <v>492046</v>
       </c>
       <c r="R80" t="n">
-        <v>7134987</v>
+        <v>7135177</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730562</v>
+        <v>129730675</v>
       </c>
       <c r="B81" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9327,21 +9327,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492037</v>
+        <v>492075</v>
       </c>
       <c r="R81" t="n">
-        <v>7135120</v>
+        <v>7135214</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9387,11 +9387,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9418,7 +9413,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730594</v>
+        <v>129730603</v>
       </c>
       <c r="B82" t="n">
         <v>57737</v>
@@ -9453,10 +9448,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492205</v>
+        <v>492265</v>
       </c>
       <c r="R82" t="n">
-        <v>7135012</v>
+        <v>7134987</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9520,7 +9515,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730599</v>
+        <v>129730562</v>
       </c>
       <c r="B83" t="n">
         <v>57737</v>
@@ -9555,10 +9550,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492216</v>
+        <v>492037</v>
       </c>
       <c r="R83" t="n">
-        <v>7135002</v>
+        <v>7135120</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9595,7 +9590,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9622,32 +9617,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730665</v>
+        <v>129730594</v>
       </c>
       <c r="B84" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9657,10 +9652,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492046</v>
+        <v>492205</v>
       </c>
       <c r="R84" t="n">
-        <v>7135177</v>
+        <v>7135012</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9697,7 +9692,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>8st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9724,10 +9719,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730675</v>
+        <v>129730599</v>
       </c>
       <c r="B85" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9735,21 +9730,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9759,10 +9754,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492075</v>
+        <v>492216</v>
       </c>
       <c r="R85" t="n">
-        <v>7135214</v>
+        <v>7135002</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9795,6 +9790,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10229,7 +10229,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129730583</v>
+        <v>129730565</v>
       </c>
       <c r="B90" t="n">
         <v>57737</v>
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492105</v>
+        <v>492040</v>
       </c>
       <c r="R90" t="n">
-        <v>7135051</v>
+        <v>7135117</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,7 +10331,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129730625</v>
+        <v>129730583</v>
       </c>
       <c r="B91" t="n">
         <v>57737</v>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492367</v>
+        <v>492105</v>
       </c>
       <c r="R91" t="n">
-        <v>7134920</v>
+        <v>7135051</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10433,7 +10433,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129730565</v>
+        <v>129730625</v>
       </c>
       <c r="B92" t="n">
         <v>57737</v>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>492040</v>
+        <v>492367</v>
       </c>
       <c r="R92" t="n">
-        <v>7135117</v>
+        <v>7134920</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10734,7 +10734,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730650</v>
+        <v>129730604</v>
       </c>
       <c r="B95" t="n">
         <v>57737</v>
@@ -10769,10 +10769,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492473</v>
+        <v>492297</v>
       </c>
       <c r="R95" t="n">
-        <v>7134864</v>
+        <v>7134975</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10836,10 +10836,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730619</v>
+        <v>129730661</v>
       </c>
       <c r="B96" t="n">
-        <v>57737</v>
+        <v>91622</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10847,23 +10847,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10871,10 +10867,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492353</v>
+        <v>492069</v>
       </c>
       <c r="R96" t="n">
-        <v>7134945</v>
+        <v>7135162</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10901,17 +10897,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10920,6 +10911,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10938,7 +10930,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730606</v>
+        <v>129730650</v>
       </c>
       <c r="B97" t="n">
         <v>57737</v>
@@ -10973,10 +10965,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492303</v>
+        <v>492473</v>
       </c>
       <c r="R97" t="n">
-        <v>7134972</v>
+        <v>7134864</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11040,7 +11032,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129730569</v>
+        <v>129730619</v>
       </c>
       <c r="B98" t="n">
         <v>57737</v>
@@ -11075,10 +11067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492054</v>
+        <v>492353</v>
       </c>
       <c r="R98" t="n">
-        <v>7135107</v>
+        <v>7134945</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11142,7 +11134,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730604</v>
+        <v>129730606</v>
       </c>
       <c r="B99" t="n">
         <v>57737</v>
@@ -11177,10 +11169,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492297</v>
+        <v>492303</v>
       </c>
       <c r="R99" t="n">
-        <v>7134975</v>
+        <v>7134972</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11244,10 +11236,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730662</v>
+        <v>129730569</v>
       </c>
       <c r="B100" t="n">
-        <v>78097</v>
+        <v>57737</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11255,21 +11247,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11279,10 +11271,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492166</v>
+        <v>492054</v>
       </c>
       <c r="R100" t="n">
-        <v>7135239</v>
+        <v>7135107</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11315,6 +11307,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11341,10 +11338,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730661</v>
+        <v>129730662</v>
       </c>
       <c r="B101" t="n">
-        <v>91622</v>
+        <v>78097</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11352,19 +11349,23 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11372,10 +11373,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492069</v>
+        <v>492166</v>
       </c>
       <c r="R101" t="n">
-        <v>7135162</v>
+        <v>7135239</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11402,12 +11403,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11416,7 +11417,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11935,7 +11935,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730559</v>
+        <v>129730529</v>
       </c>
       <c r="B107" t="n">
         <v>57737</v>
@@ -11970,10 +11970,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492032</v>
+        <v>492088</v>
       </c>
       <c r="R107" t="n">
-        <v>7135120</v>
+        <v>7135198</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12037,7 +12037,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730529</v>
+        <v>129730631</v>
       </c>
       <c r="B108" t="n">
         <v>57737</v>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492088</v>
+        <v>492409</v>
       </c>
       <c r="R108" t="n">
-        <v>7135198</v>
+        <v>7134918</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12139,7 +12139,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730532</v>
+        <v>129730576</v>
       </c>
       <c r="B109" t="n">
         <v>57737</v>
@@ -12174,10 +12174,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492082</v>
+        <v>492066</v>
       </c>
       <c r="R109" t="n">
-        <v>7135294</v>
+        <v>7135093</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,7 +12241,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730631</v>
+        <v>129730559</v>
       </c>
       <c r="B110" t="n">
         <v>57737</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492409</v>
+        <v>492032</v>
       </c>
       <c r="R110" t="n">
-        <v>7134918</v>
+        <v>7135120</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12343,7 +12343,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730576</v>
+        <v>129730532</v>
       </c>
       <c r="B111" t="n">
         <v>57737</v>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492066</v>
+        <v>492082</v>
       </c>
       <c r="R111" t="n">
-        <v>7135093</v>
+        <v>7135294</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129730617</v>
+        <v>129730526</v>
       </c>
       <c r="B112" t="n">
-        <v>57737</v>
+        <v>90634</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12456,21 +12456,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>492349</v>
+        <v>492395</v>
       </c>
       <c r="R112" t="n">
-        <v>7134943</v>
+        <v>7135064</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12516,11 +12516,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12547,7 +12542,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730624</v>
+        <v>129730617</v>
       </c>
       <c r="B113" t="n">
         <v>57737</v>
@@ -12582,10 +12577,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492366</v>
+        <v>492349</v>
       </c>
       <c r="R113" t="n">
-        <v>7134921</v>
+        <v>7134943</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12622,7 +12617,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12649,7 +12644,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730528</v>
+        <v>129730624</v>
       </c>
       <c r="B114" t="n">
         <v>57737</v>
@@ -12684,10 +12679,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492476</v>
+        <v>492366</v>
       </c>
       <c r="R114" t="n">
-        <v>7135072</v>
+        <v>7134921</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12751,7 +12746,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730597</v>
+        <v>129730528</v>
       </c>
       <c r="B115" t="n">
         <v>57737</v>
@@ -12786,10 +12781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492213</v>
+        <v>492476</v>
       </c>
       <c r="R115" t="n">
-        <v>7135010</v>
+        <v>7135072</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12853,7 +12848,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730579</v>
+        <v>129730597</v>
       </c>
       <c r="B116" t="n">
         <v>57737</v>
@@ -12888,10 +12883,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>492080</v>
+        <v>492213</v>
       </c>
       <c r="R116" t="n">
-        <v>7135064</v>
+        <v>7135010</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12955,7 +12950,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730632</v>
+        <v>129730579</v>
       </c>
       <c r="B117" t="n">
         <v>57737</v>
@@ -12990,10 +12985,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492414</v>
+        <v>492080</v>
       </c>
       <c r="R117" t="n">
-        <v>7134915</v>
+        <v>7135064</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13057,7 +13052,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730608</v>
+        <v>129730632</v>
       </c>
       <c r="B118" t="n">
         <v>57737</v>
@@ -13092,10 +13087,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492316</v>
+        <v>492414</v>
       </c>
       <c r="R118" t="n">
-        <v>7134971</v>
+        <v>7134915</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13159,10 +13154,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730526</v>
+        <v>129730608</v>
       </c>
       <c r="B119" t="n">
-        <v>90634</v>
+        <v>57737</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13170,21 +13165,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13194,10 +13189,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492395</v>
+        <v>492316</v>
       </c>
       <c r="R119" t="n">
-        <v>7135064</v>
+        <v>7134971</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13230,6 +13225,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13256,10 +13256,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129730585</v>
+        <v>129730673</v>
       </c>
       <c r="B120" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13267,21 +13267,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>492123</v>
+        <v>492342</v>
       </c>
       <c r="R120" t="n">
-        <v>7135047</v>
+        <v>7135223</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13327,11 +13327,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13358,7 +13353,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730582</v>
+        <v>129730585</v>
       </c>
       <c r="B121" t="n">
         <v>57737</v>
@@ -13393,10 +13388,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>492094</v>
+        <v>492123</v>
       </c>
       <c r="R121" t="n">
-        <v>7135060</v>
+        <v>7135047</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13433,7 +13428,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13460,7 +13455,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730657</v>
+        <v>129730582</v>
       </c>
       <c r="B122" t="n">
         <v>57737</v>
@@ -13495,10 +13490,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492468</v>
+        <v>492094</v>
       </c>
       <c r="R122" t="n">
-        <v>7134848</v>
+        <v>7135060</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13535,7 +13530,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13562,7 +13557,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730587</v>
+        <v>129730657</v>
       </c>
       <c r="B123" t="n">
         <v>57737</v>
@@ -13597,10 +13592,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492125</v>
+        <v>492468</v>
       </c>
       <c r="R123" t="n">
-        <v>7135047</v>
+        <v>7134848</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13664,7 +13659,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730568</v>
+        <v>129730587</v>
       </c>
       <c r="B124" t="n">
         <v>57737</v>
@@ -13699,10 +13694,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492044</v>
+        <v>492125</v>
       </c>
       <c r="R124" t="n">
-        <v>7135114</v>
+        <v>7135047</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13766,7 +13761,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730618</v>
+        <v>129730568</v>
       </c>
       <c r="B125" t="n">
         <v>57737</v>
@@ -13801,10 +13796,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492350</v>
+        <v>492044</v>
       </c>
       <c r="R125" t="n">
-        <v>7134947</v>
+        <v>7135114</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13841,7 +13836,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13868,7 +13863,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730614</v>
+        <v>129730618</v>
       </c>
       <c r="B126" t="n">
         <v>57737</v>
@@ -13903,10 +13898,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492342</v>
+        <v>492350</v>
       </c>
       <c r="R126" t="n">
-        <v>7134966</v>
+        <v>7134947</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13943,7 +13938,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13970,10 +13965,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730673</v>
+        <v>129730614</v>
       </c>
       <c r="B127" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13981,21 +13976,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14008,7 +14003,7 @@
         <v>492342</v>
       </c>
       <c r="R127" t="n">
-        <v>7135223</v>
+        <v>7134966</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14041,6 +14036,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14067,7 +14067,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730539</v>
+        <v>129730643</v>
       </c>
       <c r="B128" t="n">
         <v>57737</v>
@@ -14102,10 +14102,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>492011</v>
+        <v>492464</v>
       </c>
       <c r="R128" t="n">
-        <v>7135206</v>
+        <v>7134867</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14142,7 +14142,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14169,7 +14169,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730563</v>
+        <v>129730539</v>
       </c>
       <c r="B129" t="n">
         <v>57737</v>
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>492037</v>
+        <v>492011</v>
       </c>
       <c r="R129" t="n">
-        <v>7135119</v>
+        <v>7135206</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730643</v>
+        <v>129730563</v>
       </c>
       <c r="B130" t="n">
         <v>57737</v>
@@ -14306,10 +14306,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>492464</v>
+        <v>492037</v>
       </c>
       <c r="R130" t="n">
-        <v>7134867</v>
+        <v>7135119</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15485,32 +15485,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730525</v>
+        <v>129730524</v>
       </c>
       <c r="B142" t="n">
-        <v>90634</v>
+        <v>91566</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492390</v>
+        <v>492271</v>
       </c>
       <c r="R142" t="n">
-        <v>7135053</v>
+        <v>7135240</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15582,32 +15582,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730524</v>
+        <v>129730525</v>
       </c>
       <c r="B143" t="n">
-        <v>91566</v>
+        <v>90634</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15617,10 +15617,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492271</v>
+        <v>492390</v>
       </c>
       <c r="R143" t="n">
-        <v>7135240</v>
+        <v>7135053</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17107,10 +17107,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730571</v>
+        <v>129730668</v>
       </c>
       <c r="B158" t="n">
-        <v>57737</v>
+        <v>56918</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17118,16 +17118,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -17142,10 +17142,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>492057</v>
+        <v>492293</v>
       </c>
       <c r="R158" t="n">
-        <v>7135106</v>
+        <v>7134991</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17178,11 +17178,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17209,10 +17204,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730634</v>
+        <v>129730667</v>
       </c>
       <c r="B159" t="n">
-        <v>57737</v>
+        <v>56918</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17220,16 +17215,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -17244,10 +17239,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>492423</v>
+        <v>492088</v>
       </c>
       <c r="R159" t="n">
-        <v>7134915</v>
+        <v>7135189</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17280,11 +17275,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17311,10 +17301,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730668</v>
+        <v>129730571</v>
       </c>
       <c r="B160" t="n">
-        <v>56918</v>
+        <v>57737</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17322,16 +17312,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -17346,10 +17336,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>492293</v>
+        <v>492057</v>
       </c>
       <c r="R160" t="n">
-        <v>7134991</v>
+        <v>7135106</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17382,6 +17372,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17408,10 +17403,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129730667</v>
+        <v>129730634</v>
       </c>
       <c r="B161" t="n">
-        <v>56918</v>
+        <v>57737</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17419,16 +17414,16 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -17443,10 +17438,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>492088</v>
+        <v>492423</v>
       </c>
       <c r="R161" t="n">
-        <v>7135189</v>
+        <v>7134915</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17479,6 +17474,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17505,7 +17505,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730547</v>
+        <v>129730546</v>
       </c>
       <c r="B162" t="n">
         <v>57737</v>
@@ -17540,7 +17540,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>491981</v>
+        <v>491985</v>
       </c>
       <c r="R162" t="n">
         <v>7135158</v>
@@ -17580,7 +17580,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17607,7 +17607,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730556</v>
+        <v>129730592</v>
       </c>
       <c r="B163" t="n">
         <v>57737</v>
@@ -17642,10 +17642,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>492024</v>
+        <v>492195</v>
       </c>
       <c r="R163" t="n">
-        <v>7135131</v>
+        <v>7135016</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17682,7 +17682,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17709,10 +17709,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730591</v>
+        <v>129730527</v>
       </c>
       <c r="B164" t="n">
-        <v>57737</v>
+        <v>90634</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17720,21 +17720,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17744,10 +17744,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>492194</v>
+        <v>492267</v>
       </c>
       <c r="R164" t="n">
-        <v>7135016</v>
+        <v>7135233</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17780,11 +17780,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17811,7 +17806,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730546</v>
+        <v>129730547</v>
       </c>
       <c r="B165" t="n">
         <v>57737</v>
@@ -17846,7 +17841,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>491985</v>
+        <v>491981</v>
       </c>
       <c r="R165" t="n">
         <v>7135158</v>
@@ -17886,7 +17881,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17913,7 +17908,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730592</v>
+        <v>129730556</v>
       </c>
       <c r="B166" t="n">
         <v>57737</v>
@@ -17948,10 +17943,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>492195</v>
+        <v>492024</v>
       </c>
       <c r="R166" t="n">
-        <v>7135016</v>
+        <v>7135131</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17988,7 +17983,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18015,10 +18010,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730527</v>
+        <v>129730591</v>
       </c>
       <c r="B167" t="n">
-        <v>90634</v>
+        <v>57737</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18026,21 +18021,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18050,10 +18045,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492267</v>
+        <v>492194</v>
       </c>
       <c r="R167" t="n">
-        <v>7135233</v>
+        <v>7135016</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18086,6 +18081,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18112,7 +18112,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129730554</v>
+        <v>129730652</v>
       </c>
       <c r="B168" t="n">
         <v>57737</v>
@@ -18147,10 +18147,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>492027</v>
+        <v>492473</v>
       </c>
       <c r="R168" t="n">
-        <v>7135130</v>
+        <v>7134862</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18214,7 +18214,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129730605</v>
+        <v>129730554</v>
       </c>
       <c r="B169" t="n">
         <v>57737</v>
@@ -18249,10 +18249,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>492293</v>
+        <v>492027</v>
       </c>
       <c r="R169" t="n">
-        <v>7134975</v>
+        <v>7135130</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18289,7 +18289,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18316,7 +18316,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129730652</v>
+        <v>129730605</v>
       </c>
       <c r="B170" t="n">
         <v>57737</v>
@@ -18351,10 +18351,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>492473</v>
+        <v>492293</v>
       </c>
       <c r="R170" t="n">
-        <v>7134862</v>
+        <v>7134975</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19030,7 +19030,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129730607</v>
+        <v>129730644</v>
       </c>
       <c r="B177" t="n">
         <v>57737</v>
@@ -19065,10 +19065,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>492312</v>
+        <v>492462</v>
       </c>
       <c r="R177" t="n">
-        <v>7134971</v>
+        <v>7134869</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19132,7 +19132,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129730644</v>
+        <v>129730610</v>
       </c>
       <c r="B178" t="n">
         <v>57737</v>
@@ -19167,10 +19167,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>492462</v>
+        <v>492330</v>
       </c>
       <c r="R178" t="n">
-        <v>7134869</v>
+        <v>7134972</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19234,7 +19234,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129730612</v>
+        <v>129730607</v>
       </c>
       <c r="B179" t="n">
         <v>57737</v>
@@ -19269,10 +19269,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>492333</v>
+        <v>492312</v>
       </c>
       <c r="R179" t="n">
-        <v>7134969</v>
+        <v>7134971</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19309,7 +19309,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19336,7 +19336,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129730586</v>
+        <v>129730612</v>
       </c>
       <c r="B180" t="n">
         <v>57737</v>
@@ -19371,10 +19371,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>492124</v>
+        <v>492333</v>
       </c>
       <c r="R180" t="n">
-        <v>7135046</v>
+        <v>7134969</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19438,7 +19438,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129730623</v>
+        <v>129730586</v>
       </c>
       <c r="B181" t="n">
         <v>57737</v>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>492353</v>
+        <v>492124</v>
       </c>
       <c r="R181" t="n">
-        <v>7134936</v>
+        <v>7135046</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19540,7 +19540,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129730610</v>
+        <v>129730623</v>
       </c>
       <c r="B182" t="n">
         <v>57737</v>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>492330</v>
+        <v>492353</v>
       </c>
       <c r="R182" t="n">
-        <v>7134972</v>
+        <v>7134936</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19642,10 +19642,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129730660</v>
+        <v>129730550</v>
       </c>
       <c r="B183" t="n">
-        <v>91622</v>
+        <v>57737</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19653,19 +19653,23 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
@@ -19673,10 +19677,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>492059</v>
+        <v>491991</v>
       </c>
       <c r="R183" t="n">
-        <v>7135168</v>
+        <v>7135149</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19703,12 +19707,17 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19717,7 +19726,6 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19736,7 +19744,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129730550</v>
+        <v>129730653</v>
       </c>
       <c r="B184" t="n">
         <v>57737</v>
@@ -19771,10 +19779,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>491991</v>
+        <v>492468</v>
       </c>
       <c r="R184" t="n">
-        <v>7135149</v>
+        <v>7134851</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19811,7 +19819,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19838,7 +19846,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129730653</v>
+        <v>129730577</v>
       </c>
       <c r="B185" t="n">
         <v>57737</v>
@@ -19873,10 +19881,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>492468</v>
+        <v>492066</v>
       </c>
       <c r="R185" t="n">
-        <v>7134851</v>
+        <v>7135097</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19940,7 +19948,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730577</v>
+        <v>129730636</v>
       </c>
       <c r="B186" t="n">
         <v>57737</v>
@@ -19975,10 +19983,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492066</v>
+        <v>492435</v>
       </c>
       <c r="R186" t="n">
-        <v>7135097</v>
+        <v>7134917</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20015,7 +20023,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20042,7 +20050,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730636</v>
+        <v>129730557</v>
       </c>
       <c r="B187" t="n">
         <v>57737</v>
@@ -20077,10 +20085,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>492435</v>
+        <v>492026</v>
       </c>
       <c r="R187" t="n">
-        <v>7134917</v>
+        <v>7135131</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20117,7 +20125,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20144,7 +20152,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730557</v>
+        <v>129730537</v>
       </c>
       <c r="B188" t="n">
         <v>57737</v>
@@ -20179,10 +20187,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>492026</v>
+        <v>492037</v>
       </c>
       <c r="R188" t="n">
-        <v>7135131</v>
+        <v>7135230</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20246,7 +20254,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129730537</v>
+        <v>129730654</v>
       </c>
       <c r="B189" t="n">
         <v>57737</v>
@@ -20281,10 +20289,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>492037</v>
+        <v>492462</v>
       </c>
       <c r="R189" t="n">
-        <v>7135230</v>
+        <v>7134847</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20321,7 +20329,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20348,7 +20356,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730654</v>
+        <v>129730572</v>
       </c>
       <c r="B190" t="n">
         <v>57737</v>
@@ -20383,10 +20391,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>492462</v>
+        <v>492060</v>
       </c>
       <c r="R190" t="n">
-        <v>7134847</v>
+        <v>7135105</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20450,10 +20458,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129730572</v>
+        <v>129730660</v>
       </c>
       <c r="B191" t="n">
-        <v>57737</v>
+        <v>91622</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20461,23 +20469,19 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
@@ -20485,10 +20489,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>492060</v>
+        <v>492059</v>
       </c>
       <c r="R191" t="n">
-        <v>7135105</v>
+        <v>7135168</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20515,17 +20519,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20534,6 +20533,7 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -20649,7 +20649,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730641</v>
+        <v>129730651</v>
       </c>
       <c r="B193" t="n">
         <v>57737</v>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492462</v>
+        <v>492474</v>
       </c>
       <c r="R193" t="n">
-        <v>7134883</v>
+        <v>7134863</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20751,7 +20751,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730621</v>
+        <v>129730600</v>
       </c>
       <c r="B194" t="n">
         <v>57737</v>
@@ -20786,10 +20786,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492355</v>
+        <v>492239</v>
       </c>
       <c r="R194" t="n">
-        <v>7134935</v>
+        <v>7134997</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20853,7 +20853,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730613</v>
+        <v>129730596</v>
       </c>
       <c r="B195" t="n">
         <v>57737</v>
@@ -20888,10 +20888,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492341</v>
+        <v>492210</v>
       </c>
       <c r="R195" t="n">
-        <v>7134968</v>
+        <v>7135013</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20928,7 +20928,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20955,7 +20955,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129730570</v>
+        <v>129730641</v>
       </c>
       <c r="B196" t="n">
         <v>57737</v>
@@ -20990,10 +20990,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>492057</v>
+        <v>492462</v>
       </c>
       <c r="R196" t="n">
-        <v>7135109</v>
+        <v>7134883</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21030,7 +21030,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21057,7 +21057,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129730642</v>
+        <v>129730621</v>
       </c>
       <c r="B197" t="n">
         <v>57737</v>
@@ -21092,10 +21092,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>492466</v>
+        <v>492355</v>
       </c>
       <c r="R197" t="n">
-        <v>7134877</v>
+        <v>7134935</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21159,7 +21159,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730560</v>
+        <v>129730613</v>
       </c>
       <c r="B198" t="n">
         <v>57737</v>
@@ -21194,10 +21194,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492037</v>
+        <v>492341</v>
       </c>
       <c r="R198" t="n">
-        <v>7135124</v>
+        <v>7134968</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21261,7 +21261,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730651</v>
+        <v>129730570</v>
       </c>
       <c r="B199" t="n">
         <v>57737</v>
@@ -21296,10 +21296,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492474</v>
+        <v>492057</v>
       </c>
       <c r="R199" t="n">
-        <v>7134863</v>
+        <v>7135109</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21363,7 +21363,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730553</v>
+        <v>129730642</v>
       </c>
       <c r="B200" t="n">
         <v>57737</v>
@@ -21398,10 +21398,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492008</v>
+        <v>492466</v>
       </c>
       <c r="R200" t="n">
-        <v>7135137</v>
+        <v>7134877</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21465,7 +21465,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730600</v>
+        <v>129730560</v>
       </c>
       <c r="B201" t="n">
         <v>57737</v>
@@ -21500,10 +21500,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492239</v>
+        <v>492037</v>
       </c>
       <c r="R201" t="n">
-        <v>7134997</v>
+        <v>7135124</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21567,7 +21567,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730596</v>
+        <v>129730553</v>
       </c>
       <c r="B202" t="n">
         <v>57737</v>
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492210</v>
+        <v>492008</v>
       </c>
       <c r="R202" t="n">
-        <v>7135013</v>
+        <v>7135137</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21642,7 +21642,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD202" t="b">

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -3959,10 +3959,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726722</v>
+        <v>129726726</v>
       </c>
       <c r="B31" t="n">
-        <v>98794</v>
+        <v>91775</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,38 +3970,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492376</v>
+        <v>492285</v>
       </c>
       <c r="R31" t="n">
-        <v>7135128</v>
+        <v>7135248</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4033,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,45 +4066,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726737</v>
+        <v>129726722</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492228</v>
+        <v>492376</v>
       </c>
       <c r="R32" t="n">
-        <v>7135126</v>
+        <v>7135128</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,32 +4177,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726726</v>
+        <v>129726737</v>
       </c>
       <c r="B33" t="n">
-        <v>91775</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492285</v>
+        <v>492228</v>
       </c>
       <c r="R33" t="n">
-        <v>7135248</v>
+        <v>7135126</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726740</v>
+        <v>129728253</v>
       </c>
       <c r="B43" t="n">
         <v>79084</v>
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492268</v>
+        <v>492341</v>
       </c>
       <c r="R43" t="n">
-        <v>7135143</v>
+        <v>7135150</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5349,19 +5349,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:25</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5376,19 +5371,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129728253</v>
+        <v>129726740</v>
       </c>
       <c r="B44" t="n">
         <v>79084</v>
@@ -5423,10 +5418,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492341</v>
+        <v>492268</v>
       </c>
       <c r="R44" t="n">
-        <v>7135150</v>
+        <v>7135143</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5456,14 +5451,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5478,12 +5478,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -7043,10 +7043,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129726728</v>
+        <v>129726753</v>
       </c>
       <c r="B59" t="n">
-        <v>78097</v>
+        <v>78842</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7054,21 +7054,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492179</v>
+        <v>492496</v>
       </c>
       <c r="R59" t="n">
-        <v>7135241</v>
+        <v>7134904</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7150,10 +7150,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129726753</v>
+        <v>129728250</v>
       </c>
       <c r="B60" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7161,21 +7161,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492496</v>
+        <v>492572</v>
       </c>
       <c r="R60" t="n">
-        <v>7134904</v>
+        <v>7135009</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7218,19 +7218,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>08:40</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7245,19 +7240,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129728250</v>
+        <v>129726725</v>
       </c>
       <c r="B61" t="n">
         <v>79084</v>
@@ -7292,10 +7287,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492572</v>
+        <v>492304</v>
       </c>
       <c r="R61" t="n">
-        <v>7135009</v>
+        <v>7135246</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7325,14 +7320,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7347,22 +7347,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726725</v>
+        <v>129726728</v>
       </c>
       <c r="B62" t="n">
-        <v>79084</v>
+        <v>78097</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492304</v>
+        <v>492179</v>
       </c>
       <c r="R62" t="n">
-        <v>7135246</v>
+        <v>7135241</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -10229,7 +10229,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129730565</v>
+        <v>129730583</v>
       </c>
       <c r="B90" t="n">
         <v>57737</v>
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492040</v>
+        <v>492105</v>
       </c>
       <c r="R90" t="n">
-        <v>7135117</v>
+        <v>7135051</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,7 +10331,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129730583</v>
+        <v>129730625</v>
       </c>
       <c r="B91" t="n">
         <v>57737</v>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492105</v>
+        <v>492367</v>
       </c>
       <c r="R91" t="n">
-        <v>7135051</v>
+        <v>7134920</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10433,7 +10433,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129730625</v>
+        <v>129730565</v>
       </c>
       <c r="B92" t="n">
         <v>57737</v>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>492367</v>
+        <v>492040</v>
       </c>
       <c r="R92" t="n">
-        <v>7134920</v>
+        <v>7135117</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13256,10 +13256,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129730673</v>
+        <v>129730585</v>
       </c>
       <c r="B120" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13267,21 +13267,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>492342</v>
+        <v>492123</v>
       </c>
       <c r="R120" t="n">
-        <v>7135223</v>
+        <v>7135047</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13327,6 +13327,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13353,7 +13358,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730585</v>
+        <v>129730582</v>
       </c>
       <c r="B121" t="n">
         <v>57737</v>
@@ -13388,10 +13393,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>492123</v>
+        <v>492094</v>
       </c>
       <c r="R121" t="n">
-        <v>7135047</v>
+        <v>7135060</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13428,7 +13433,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13455,7 +13460,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730582</v>
+        <v>129730657</v>
       </c>
       <c r="B122" t="n">
         <v>57737</v>
@@ -13490,10 +13495,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492094</v>
+        <v>492468</v>
       </c>
       <c r="R122" t="n">
-        <v>7135060</v>
+        <v>7134848</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13530,7 +13535,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13557,7 +13562,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730657</v>
+        <v>129730587</v>
       </c>
       <c r="B123" t="n">
         <v>57737</v>
@@ -13592,10 +13597,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492468</v>
+        <v>492125</v>
       </c>
       <c r="R123" t="n">
-        <v>7134848</v>
+        <v>7135047</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13659,7 +13664,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730587</v>
+        <v>129730568</v>
       </c>
       <c r="B124" t="n">
         <v>57737</v>
@@ -13694,10 +13699,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492125</v>
+        <v>492044</v>
       </c>
       <c r="R124" t="n">
-        <v>7135047</v>
+        <v>7135114</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13761,7 +13766,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730568</v>
+        <v>129730618</v>
       </c>
       <c r="B125" t="n">
         <v>57737</v>
@@ -13796,10 +13801,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492044</v>
+        <v>492350</v>
       </c>
       <c r="R125" t="n">
-        <v>7135114</v>
+        <v>7134947</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13836,7 +13841,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13863,7 +13868,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730618</v>
+        <v>129730614</v>
       </c>
       <c r="B126" t="n">
         <v>57737</v>
@@ -13898,10 +13903,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492350</v>
+        <v>492342</v>
       </c>
       <c r="R126" t="n">
-        <v>7134947</v>
+        <v>7134966</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13938,7 +13943,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13965,10 +13970,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730614</v>
+        <v>129730673</v>
       </c>
       <c r="B127" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13976,21 +13981,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14003,7 +14008,7 @@
         <v>492342</v>
       </c>
       <c r="R127" t="n">
-        <v>7134966</v>
+        <v>7135223</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14036,11 +14041,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14475,32 +14475,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730670</v>
+        <v>129730531</v>
       </c>
       <c r="B132" t="n">
-        <v>91775</v>
+        <v>57737</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>492219</v>
+        <v>492083</v>
       </c>
       <c r="R132" t="n">
-        <v>7135247</v>
+        <v>7135291</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14546,6 +14546,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14572,7 +14577,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730531</v>
+        <v>129730574</v>
       </c>
       <c r="B133" t="n">
         <v>57737</v>
@@ -14607,10 +14612,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>492083</v>
+        <v>492062</v>
       </c>
       <c r="R133" t="n">
-        <v>7135291</v>
+        <v>7135103</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14674,7 +14679,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730574</v>
+        <v>129730545</v>
       </c>
       <c r="B134" t="n">
         <v>57737</v>
@@ -14709,10 +14714,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>492062</v>
+        <v>491983</v>
       </c>
       <c r="R134" t="n">
-        <v>7135103</v>
+        <v>7135171</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14776,7 +14781,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730545</v>
+        <v>129730580</v>
       </c>
       <c r="B135" t="n">
         <v>57737</v>
@@ -14811,10 +14816,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491983</v>
+        <v>492077</v>
       </c>
       <c r="R135" t="n">
-        <v>7135171</v>
+        <v>7135066</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14878,32 +14883,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730580</v>
+        <v>129730670</v>
       </c>
       <c r="B136" t="n">
-        <v>57737</v>
+        <v>91775</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14913,10 +14918,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492077</v>
+        <v>492219</v>
       </c>
       <c r="R136" t="n">
-        <v>7135066</v>
+        <v>7135247</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14949,11 +14954,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17505,10 +17505,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730546</v>
+        <v>129730527</v>
       </c>
       <c r="B162" t="n">
-        <v>57737</v>
+        <v>90634</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17516,21 +17516,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17540,10 +17540,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>491985</v>
+        <v>492267</v>
       </c>
       <c r="R162" t="n">
-        <v>7135158</v>
+        <v>7135233</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17576,11 +17576,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17607,7 +17602,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129730592</v>
+        <v>129730547</v>
       </c>
       <c r="B163" t="n">
         <v>57737</v>
@@ -17642,10 +17637,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>492195</v>
+        <v>491981</v>
       </c>
       <c r="R163" t="n">
-        <v>7135016</v>
+        <v>7135158</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17682,7 +17677,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17709,10 +17704,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730527</v>
+        <v>129730556</v>
       </c>
       <c r="B164" t="n">
-        <v>90634</v>
+        <v>57737</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17720,21 +17715,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17744,10 +17739,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>492267</v>
+        <v>492024</v>
       </c>
       <c r="R164" t="n">
-        <v>7135233</v>
+        <v>7135131</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17780,6 +17775,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17806,7 +17806,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129730547</v>
+        <v>129730591</v>
       </c>
       <c r="B165" t="n">
         <v>57737</v>
@@ -17841,10 +17841,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>491981</v>
+        <v>492194</v>
       </c>
       <c r="R165" t="n">
-        <v>7135158</v>
+        <v>7135016</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17908,7 +17908,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730556</v>
+        <v>129730546</v>
       </c>
       <c r="B166" t="n">
         <v>57737</v>
@@ -17943,10 +17943,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>492024</v>
+        <v>491985</v>
       </c>
       <c r="R166" t="n">
-        <v>7135131</v>
+        <v>7135158</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17983,7 +17983,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18010,7 +18010,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730591</v>
+        <v>129730592</v>
       </c>
       <c r="B167" t="n">
         <v>57737</v>
@@ -18045,7 +18045,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492194</v>
+        <v>492195</v>
       </c>
       <c r="R167" t="n">
         <v>7135016</v>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728258</v>
+        <v>129728237</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>80193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,34 +1037,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492272</v>
+        <v>492236</v>
       </c>
       <c r="R5" t="n">
-        <v>7135018</v>
+        <v>7135034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1108,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gran.</t>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,8 +1117,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,32 +1161,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129728238</v>
+        <v>129728258</v>
       </c>
       <c r="B6" t="n">
-        <v>80217</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492287</v>
+        <v>492272</v>
       </c>
       <c r="R6" t="n">
-        <v>7135150</v>
+        <v>7135018</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,6 +1232,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1266,7 @@
         <v>129726742</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726749</v>
+        <v>129728249</v>
       </c>
       <c r="B8" t="n">
-        <v>83055</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,34 +1381,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492403</v>
+        <v>492618</v>
       </c>
       <c r="R8" t="n">
-        <v>7135004</v>
+        <v>7134954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,19 +1441,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:03</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,28 +1457,54 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728249</v>
+        <v>129726749</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>83058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,37 +1512,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492618</v>
+        <v>492403</v>
       </c>
       <c r="R9" t="n">
-        <v>7134954</v>
+        <v>7135004</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,14 +1569,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,76 +1590,50 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726748</v>
+        <v>129728238</v>
       </c>
       <c r="B10" t="n">
-        <v>78097</v>
+        <v>80220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1605,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492403</v>
+        <v>492287</v>
       </c>
       <c r="R10" t="n">
-        <v>7135004</v>
+        <v>7135150</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,19 +1676,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129728237</v>
+        <v>129726748</v>
       </c>
       <c r="B11" t="n">
-        <v>80190</v>
+        <v>78100</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,41 +1716,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492236</v>
+        <v>492403</v>
       </c>
       <c r="R11" t="n">
-        <v>7135034</v>
+        <v>7135004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,14 +1773,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en klen levande sälg.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,44 +1794,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
         <v>129728251</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>129728261</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>129726752</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>129726741</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129726738</v>
       </c>
       <c r="B16" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129728247</v>
+        <v>129728244</v>
       </c>
       <c r="B17" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492455</v>
+        <v>492133</v>
       </c>
       <c r="R17" t="n">
-        <v>7134922</v>
+        <v>7135159</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
+          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129728244</v>
+        <v>129728247</v>
       </c>
       <c r="B18" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492133</v>
+        <v>492455</v>
       </c>
       <c r="R18" t="n">
-        <v>7135159</v>
+        <v>7134922</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 1 vinterståndare inom ca 0,5 m2 yta på sluttande frisk mark i gammal granskog. Fyndplatsen finns utanför planerad naturhänsyn inom en avverkningsanmälan.</t>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726744</v>
+        <v>129726723</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492318</v>
+        <v>492370</v>
       </c>
       <c r="R19" t="n">
-        <v>7135032</v>
+        <v>7135127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726723</v>
+        <v>129726744</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492370</v>
+        <v>492318</v>
       </c>
       <c r="R20" t="n">
-        <v>7135127</v>
+        <v>7135032</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,7 +2839,7 @@
         <v>129726736</v>
       </c>
       <c r="B21" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>129728246</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>129726716</v>
       </c>
       <c r="B23" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3178,45 +3178,65 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129728252</v>
+        <v>129728245</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>98797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492377</v>
+        <v>492204</v>
       </c>
       <c r="R24" t="n">
-        <v>7135110</v>
+        <v>7135099</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3253,7 +3273,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,8 +3282,14 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3280,10 +3306,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129728245</v>
+        <v>129728242</v>
       </c>
       <c r="B25" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3336,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3335,10 +3361,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492204</v>
+        <v>492205</v>
       </c>
       <c r="R25" t="n">
-        <v>7135099</v>
+        <v>7135151</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,7 +3401,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta i gammal barrblandskog utanför en hänsynsyta inom en avverkningsanmälan.</t>
+          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,65 +3434,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129728242</v>
+        <v>129728252</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492205</v>
+        <v>492377</v>
       </c>
       <c r="R26" t="n">
-        <v>7135151</v>
+        <v>7135110</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3503,7 +3509,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3512,14 +3518,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3539,7 +3539,7 @@
         <v>129726732</v>
       </c>
       <c r="B27" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>129728257</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>129726754</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>129726719</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726726</v>
+        <v>129726722</v>
       </c>
       <c r="B31" t="n">
-        <v>91775</v>
+        <v>98797</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,34 +3970,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492285</v>
+        <v>492376</v>
       </c>
       <c r="R31" t="n">
-        <v>7135248</v>
+        <v>7135128</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4039,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726722</v>
+        <v>129726726</v>
       </c>
       <c r="B32" t="n">
-        <v>98794</v>
+        <v>91778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,38 +4081,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492376</v>
+        <v>492285</v>
       </c>
       <c r="R32" t="n">
-        <v>7135128</v>
+        <v>7135248</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,7 +4180,7 @@
         <v>129726737</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>129728254</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>129728255</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>129728256</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>129726729</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>129726750</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4804,65 +4804,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129728243</v>
+        <v>129726720</v>
       </c>
       <c r="B39" t="n">
-        <v>98794</v>
+        <v>78100</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492168</v>
+        <v>492458</v>
       </c>
       <c r="R39" t="n">
-        <v>7135133</v>
+        <v>7135104</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4892,14 +4872,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4908,69 +4893,83 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129726720</v>
+        <v>129728243</v>
       </c>
       <c r="B40" t="n">
-        <v>78097</v>
+        <v>98797</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492458</v>
+        <v>492168</v>
       </c>
       <c r="R40" t="n">
-        <v>7135104</v>
+        <v>7135133</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5000,19 +4999,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:55</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5021,18 +5015,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5042,7 +5042,7 @@
         <v>129726735</v>
       </c>
       <c r="B41" t="n">
-        <v>83050</v>
+        <v>83053</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>129728236</v>
       </c>
       <c r="B42" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>129728253</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>129726740</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>129728234</v>
       </c>
       <c r="B45" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>129726733</v>
       </c>
       <c r="B46" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>129726717</v>
       </c>
       <c r="B47" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>129726751</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5946,48 +5946,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129728262</v>
+        <v>129728241</v>
       </c>
       <c r="B49" t="n">
-        <v>79084</v>
+        <v>80220</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492479</v>
+        <v>492451</v>
       </c>
       <c r="R49" t="n">
-        <v>7134899</v>
+        <v>7134904</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6022,45 +6019,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran i gammal barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6077,10 +6043,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129726721</v>
+        <v>129728262</v>
       </c>
       <c r="B50" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6106,16 +6072,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492421</v>
+        <v>492479</v>
       </c>
       <c r="R50" t="n">
-        <v>7135113</v>
+        <v>7134899</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6145,19 +6114,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,50 +6130,76 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129728241</v>
+        <v>129726721</v>
       </c>
       <c r="B51" t="n">
-        <v>80217</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6219,10 +6209,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492451</v>
+        <v>492421</v>
       </c>
       <c r="R51" t="n">
-        <v>7134904</v>
+        <v>7135113</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6252,9 +6242,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6269,22 +6269,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129726727</v>
+        <v>129726718</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492258</v>
+        <v>492543</v>
       </c>
       <c r="R52" t="n">
-        <v>7135232</v>
+        <v>7135091</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6388,10 +6388,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129726718</v>
+        <v>129726727</v>
       </c>
       <c r="B53" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492543</v>
+        <v>492258</v>
       </c>
       <c r="R53" t="n">
-        <v>7135091</v>
+        <v>7135232</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6498,7 +6498,7 @@
         <v>129726747</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>129728260</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129726734</v>
+        <v>129726731</v>
       </c>
       <c r="B56" t="n">
-        <v>91622</v>
+        <v>79087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6715,19 +6715,23 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6735,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492211</v>
+        <v>492137</v>
       </c>
       <c r="R56" t="n">
-        <v>7135170</v>
+        <v>7135201</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6770,7 +6774,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6780,7 +6784,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6789,7 +6793,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6808,10 +6811,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129726731</v>
+        <v>129726734</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>91625</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6819,23 +6822,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6843,10 +6842,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492137</v>
+        <v>492211</v>
       </c>
       <c r="R57" t="n">
-        <v>7135201</v>
+        <v>7135170</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6878,7 +6877,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6888,7 +6887,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6897,6 +6896,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>129728248</v>
       </c>
       <c r="B58" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7043,10 +7043,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129726753</v>
+        <v>129728250</v>
       </c>
       <c r="B59" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7054,21 +7054,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492496</v>
+        <v>492572</v>
       </c>
       <c r="R59" t="n">
-        <v>7134904</v>
+        <v>7135009</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7111,19 +7111,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>08:40</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7138,22 +7133,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129728250</v>
+        <v>129726725</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7185,10 +7180,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492572</v>
+        <v>492304</v>
       </c>
       <c r="R60" t="n">
-        <v>7135009</v>
+        <v>7135246</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7218,14 +7213,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7240,22 +7240,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129726725</v>
+        <v>129726728</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>78100</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7263,21 +7263,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492304</v>
+        <v>492179</v>
       </c>
       <c r="R61" t="n">
-        <v>7135246</v>
+        <v>7135241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7359,10 +7359,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129726728</v>
+        <v>129726753</v>
       </c>
       <c r="B62" t="n">
-        <v>78097</v>
+        <v>78845</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492179</v>
+        <v>492496</v>
       </c>
       <c r="R62" t="n">
-        <v>7135241</v>
+        <v>7134904</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7469,7 +7469,7 @@
         <v>129728239</v>
       </c>
       <c r="B63" t="n">
-        <v>80217</v>
+        <v>80220</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,32 +7568,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726730</v>
+        <v>129728259</v>
       </c>
       <c r="B64" t="n">
-        <v>92320</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492124</v>
+        <v>492317</v>
       </c>
       <c r="R64" t="n">
-        <v>7135171</v>
+        <v>7134999</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7636,19 +7636,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:53</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7663,22 +7658,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129728259</v>
+        <v>129726745</v>
       </c>
       <c r="B65" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7710,10 +7705,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492317</v>
+        <v>492367</v>
       </c>
       <c r="R65" t="n">
-        <v>7134999</v>
+        <v>7135038</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7743,14 +7738,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7765,22 +7765,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129726745</v>
+        <v>129726724</v>
       </c>
       <c r="B66" t="n">
-        <v>79084</v>
+        <v>57898</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7788,34 +7788,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492367</v>
+        <v>492343</v>
       </c>
       <c r="R66" t="n">
-        <v>7135038</v>
+        <v>7135242</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7847,7 +7856,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7857,7 +7866,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7884,10 +7893,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129728240</v>
+        <v>129726730</v>
       </c>
       <c r="B67" t="n">
-        <v>80217</v>
+        <v>92323</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7895,21 +7904,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7919,10 +7928,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492405</v>
+        <v>492124</v>
       </c>
       <c r="R67" t="n">
-        <v>7134981</v>
+        <v>7135171</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7952,14 +7961,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På ett mossöverväxt block.</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7974,66 +7988,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129726724</v>
+        <v>129728240</v>
       </c>
       <c r="B68" t="n">
-        <v>57895</v>
+        <v>80220</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492343</v>
+        <v>492405</v>
       </c>
       <c r="R68" t="n">
-        <v>7135242</v>
+        <v>7134981</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8063,19 +8068,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:28</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På ett mossöverväxt block.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8090,12 +8090,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8105,7 +8105,7 @@
         <v>129730573</v>
       </c>
       <c r="B69" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8204,10 +8204,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129730598</v>
+        <v>129730658</v>
       </c>
       <c r="B70" t="n">
-        <v>57737</v>
+        <v>57898</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8215,21 +8215,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8239,10 +8239,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492220</v>
+        <v>492464</v>
       </c>
       <c r="R70" t="n">
-        <v>7135003</v>
+        <v>7135049</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8306,10 +8306,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129730615</v>
+        <v>129730598</v>
       </c>
       <c r="B71" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8341,10 +8341,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492345</v>
+        <v>492220</v>
       </c>
       <c r="R71" t="n">
-        <v>7134961</v>
+        <v>7135003</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8408,10 +8408,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129730584</v>
+        <v>129730672</v>
       </c>
       <c r="B72" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8419,21 +8419,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8443,10 +8443,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>492107</v>
+        <v>492334</v>
       </c>
       <c r="R72" t="n">
-        <v>7135052</v>
+        <v>7135092</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8479,11 +8479,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8510,10 +8505,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129730658</v>
+        <v>129730615</v>
       </c>
       <c r="B73" t="n">
-        <v>57895</v>
+        <v>57740</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8521,21 +8516,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8545,10 +8540,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>492464</v>
+        <v>492345</v>
       </c>
       <c r="R73" t="n">
-        <v>7135049</v>
+        <v>7134961</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8585,7 +8580,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8612,10 +8607,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129730672</v>
+        <v>129730584</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8623,21 +8618,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8647,10 +8642,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492334</v>
+        <v>492107</v>
       </c>
       <c r="R74" t="n">
-        <v>7135092</v>
+        <v>7135052</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8683,6 +8678,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129730671</v>
+        <v>129730645</v>
       </c>
       <c r="B75" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>492379</v>
+        <v>492464</v>
       </c>
       <c r="R75" t="n">
-        <v>7135129</v>
+        <v>7134870</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8780,6 +8780,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8806,10 +8811,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129730645</v>
+        <v>129730637</v>
       </c>
       <c r="B76" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8841,10 +8846,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>492464</v>
+        <v>492431</v>
       </c>
       <c r="R76" t="n">
-        <v>7134870</v>
+        <v>7134907</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8881,7 +8886,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8908,10 +8913,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129730637</v>
+        <v>129730671</v>
       </c>
       <c r="B77" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8919,21 +8924,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>492431</v>
+        <v>492379</v>
       </c>
       <c r="R77" t="n">
-        <v>7134907</v>
+        <v>7135129</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8979,11 +8984,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9013,7 +9013,7 @@
         <v>129730551</v>
       </c>
       <c r="B78" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>129730629</v>
       </c>
       <c r="B79" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9214,32 +9214,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129730665</v>
+        <v>129730562</v>
       </c>
       <c r="B80" t="n">
-        <v>98794</v>
+        <v>57740</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492046</v>
+        <v>492037</v>
       </c>
       <c r="R80" t="n">
-        <v>7135177</v>
+        <v>7135120</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>8st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129730675</v>
+        <v>129730594</v>
       </c>
       <c r="B81" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9327,21 +9327,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492075</v>
+        <v>492205</v>
       </c>
       <c r="R81" t="n">
-        <v>7135214</v>
+        <v>7135012</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9387,6 +9387,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9413,10 +9418,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129730603</v>
+        <v>129730599</v>
       </c>
       <c r="B82" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9448,10 +9453,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492265</v>
+        <v>492216</v>
       </c>
       <c r="R82" t="n">
-        <v>7134987</v>
+        <v>7135002</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9488,7 +9493,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9515,10 +9520,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129730562</v>
+        <v>129730675</v>
       </c>
       <c r="B83" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9526,21 +9531,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9550,10 +9555,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492037</v>
+        <v>492075</v>
       </c>
       <c r="R83" t="n">
-        <v>7135120</v>
+        <v>7135214</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9586,11 +9591,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9617,10 +9617,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129730594</v>
+        <v>129730630</v>
       </c>
       <c r="B84" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492205</v>
+        <v>492411</v>
       </c>
       <c r="R84" t="n">
-        <v>7135012</v>
+        <v>7134926</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9719,10 +9719,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129730599</v>
+        <v>129730603</v>
       </c>
       <c r="B85" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492216</v>
+        <v>492265</v>
       </c>
       <c r="R85" t="n">
-        <v>7135002</v>
+        <v>7134987</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9824,7 +9824,7 @@
         <v>129730639</v>
       </c>
       <c r="B86" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>129730635</v>
       </c>
       <c r="B87" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>129730575</v>
       </c>
       <c r="B88" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10127,32 +10127,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129730630</v>
+        <v>129730665</v>
       </c>
       <c r="B89" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10162,10 +10162,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492411</v>
+        <v>492046</v>
       </c>
       <c r="R89" t="n">
-        <v>7134926</v>
+        <v>7135177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>8st</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10232,7 +10232,7 @@
         <v>129730583</v>
       </c>
       <c r="B90" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>129730625</v>
       </c>
       <c r="B91" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>129730565</v>
       </c>
       <c r="B92" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>129730663</v>
       </c>
       <c r="B93" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129730522</v>
+        <v>129730661</v>
       </c>
       <c r="B94" t="n">
-        <v>97040</v>
+        <v>91625</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,23 +10648,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10672,10 +10668,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492217</v>
+        <v>492069</v>
       </c>
       <c r="R94" t="n">
-        <v>7135249</v>
+        <v>7135162</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10702,12 +10698,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10716,6 +10712,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10734,10 +10731,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730604</v>
+        <v>129730522</v>
       </c>
       <c r="B95" t="n">
-        <v>57737</v>
+        <v>97043</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10745,21 +10742,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10769,10 +10766,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492297</v>
+        <v>492217</v>
       </c>
       <c r="R95" t="n">
-        <v>7134975</v>
+        <v>7135249</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10805,11 +10802,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10836,10 +10828,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730661</v>
+        <v>129730604</v>
       </c>
       <c r="B96" t="n">
-        <v>91622</v>
+        <v>57740</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10847,19 +10839,23 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10867,10 +10863,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492069</v>
+        <v>492297</v>
       </c>
       <c r="R96" t="n">
-        <v>7135162</v>
+        <v>7134975</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10897,12 +10893,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10911,7 +10912,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10930,10 +10930,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730650</v>
+        <v>129730606</v>
       </c>
       <c r="B97" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10965,10 +10965,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492473</v>
+        <v>492303</v>
       </c>
       <c r="R97" t="n">
-        <v>7134864</v>
+        <v>7134972</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11032,10 +11032,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129730619</v>
+        <v>129730650</v>
       </c>
       <c r="B98" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492353</v>
+        <v>492473</v>
       </c>
       <c r="R98" t="n">
-        <v>7134945</v>
+        <v>7134864</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11134,10 +11134,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129730606</v>
+        <v>129730619</v>
       </c>
       <c r="B99" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11169,10 +11169,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492303</v>
+        <v>492353</v>
       </c>
       <c r="R99" t="n">
-        <v>7134972</v>
+        <v>7134945</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11239,7 +11239,7 @@
         <v>129730569</v>
       </c>
       <c r="B100" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>129730662</v>
       </c>
       <c r="B101" t="n">
-        <v>78097</v>
+        <v>78100</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730523</v>
+        <v>129730640</v>
       </c>
       <c r="B102" t="n">
-        <v>97040</v>
+        <v>57740</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11446,21 +11446,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492316</v>
+        <v>492444</v>
       </c>
       <c r="R102" t="n">
-        <v>7135071</v>
+        <v>7134887</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11506,6 +11506,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11532,10 +11537,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730640</v>
+        <v>129730602</v>
       </c>
       <c r="B103" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11567,10 +11572,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492444</v>
+        <v>492245</v>
       </c>
       <c r="R103" t="n">
-        <v>7134887</v>
+        <v>7134995</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,10 +11639,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730602</v>
+        <v>129730656</v>
       </c>
       <c r="B104" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11669,10 +11674,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492245</v>
+        <v>492466</v>
       </c>
       <c r="R104" t="n">
-        <v>7134995</v>
+        <v>7134851</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11709,7 +11714,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11736,10 +11741,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730656</v>
+        <v>129730523</v>
       </c>
       <c r="B105" t="n">
-        <v>57737</v>
+        <v>97043</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11747,21 +11752,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11771,10 +11776,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>492466</v>
+        <v>492316</v>
       </c>
       <c r="R105" t="n">
-        <v>7134851</v>
+        <v>7135071</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11807,11 +11812,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11838,10 +11838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730521</v>
+        <v>129730631</v>
       </c>
       <c r="B106" t="n">
-        <v>83055</v>
+        <v>57740</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492100</v>
+        <v>492409</v>
       </c>
       <c r="R106" t="n">
-        <v>7135216</v>
+        <v>7134918</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11909,6 +11909,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11935,10 +11940,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730529</v>
+        <v>129730532</v>
       </c>
       <c r="B107" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11970,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>492088</v>
+        <v>492082</v>
       </c>
       <c r="R107" t="n">
-        <v>7135198</v>
+        <v>7135294</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12010,7 +12015,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12037,10 +12042,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730631</v>
+        <v>129730529</v>
       </c>
       <c r="B108" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12072,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492409</v>
+        <v>492088</v>
       </c>
       <c r="R108" t="n">
-        <v>7134918</v>
+        <v>7135198</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12112,7 +12117,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12139,10 +12144,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730576</v>
+        <v>129730521</v>
       </c>
       <c r="B109" t="n">
-        <v>57737</v>
+        <v>83058</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12150,21 +12155,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12174,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492066</v>
+        <v>492100</v>
       </c>
       <c r="R109" t="n">
-        <v>7135093</v>
+        <v>7135216</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12210,11 +12215,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,10 +12241,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730559</v>
+        <v>129730576</v>
       </c>
       <c r="B110" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492032</v>
+        <v>492066</v>
       </c>
       <c r="R110" t="n">
-        <v>7135120</v>
+        <v>7135093</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12343,10 +12343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129730532</v>
+        <v>129730559</v>
       </c>
       <c r="B111" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492082</v>
+        <v>492032</v>
       </c>
       <c r="R111" t="n">
-        <v>7135294</v>
+        <v>7135120</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12448,7 +12448,7 @@
         <v>129730526</v>
       </c>
       <c r="B112" t="n">
-        <v>90634</v>
+        <v>90637</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12542,10 +12542,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730617</v>
+        <v>129730579</v>
       </c>
       <c r="B113" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12577,10 +12577,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492349</v>
+        <v>492080</v>
       </c>
       <c r="R113" t="n">
-        <v>7134943</v>
+        <v>7135064</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12617,7 +12617,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12644,10 +12644,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730624</v>
+        <v>129730632</v>
       </c>
       <c r="B114" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12679,10 +12679,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>492366</v>
+        <v>492414</v>
       </c>
       <c r="R114" t="n">
-        <v>7134921</v>
+        <v>7134915</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12746,10 +12746,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129730528</v>
+        <v>129730617</v>
       </c>
       <c r="B115" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12781,10 +12781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492476</v>
+        <v>492349</v>
       </c>
       <c r="R115" t="n">
-        <v>7135072</v>
+        <v>7134943</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12821,7 +12821,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12851,7 +12851,7 @@
         <v>129730597</v>
       </c>
       <c r="B116" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12950,10 +12950,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730579</v>
+        <v>129730528</v>
       </c>
       <c r="B117" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12985,10 +12985,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492080</v>
+        <v>492476</v>
       </c>
       <c r="R117" t="n">
-        <v>7135064</v>
+        <v>7135072</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13052,10 +13052,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730632</v>
+        <v>129730608</v>
       </c>
       <c r="B118" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13087,10 +13087,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492414</v>
+        <v>492316</v>
       </c>
       <c r="R118" t="n">
-        <v>7134915</v>
+        <v>7134971</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13154,10 +13154,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730608</v>
+        <v>129730624</v>
       </c>
       <c r="B119" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13189,10 +13189,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492316</v>
+        <v>492366</v>
       </c>
       <c r="R119" t="n">
-        <v>7134971</v>
+        <v>7134921</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13256,10 +13256,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129730585</v>
+        <v>129730673</v>
       </c>
       <c r="B120" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13267,21 +13267,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>492123</v>
+        <v>492342</v>
       </c>
       <c r="R120" t="n">
-        <v>7135047</v>
+        <v>7135223</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13327,11 +13327,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13361,7 +13356,7 @@
         <v>129730582</v>
       </c>
       <c r="B121" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13460,10 +13455,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730657</v>
+        <v>129730618</v>
       </c>
       <c r="B122" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13495,10 +13490,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492468</v>
+        <v>492350</v>
       </c>
       <c r="R122" t="n">
-        <v>7134848</v>
+        <v>7134947</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13535,7 +13530,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13562,10 +13557,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730587</v>
+        <v>129730614</v>
       </c>
       <c r="B123" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13597,10 +13592,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492125</v>
+        <v>492342</v>
       </c>
       <c r="R123" t="n">
-        <v>7135047</v>
+        <v>7134966</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13664,10 +13659,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730568</v>
+        <v>129730657</v>
       </c>
       <c r="B124" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13699,10 +13694,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492044</v>
+        <v>492468</v>
       </c>
       <c r="R124" t="n">
-        <v>7135114</v>
+        <v>7134848</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13766,10 +13761,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730618</v>
+        <v>129730587</v>
       </c>
       <c r="B125" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13801,10 +13796,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>492350</v>
+        <v>492125</v>
       </c>
       <c r="R125" t="n">
-        <v>7134947</v>
+        <v>7135047</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13841,7 +13836,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13868,10 +13863,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129730614</v>
+        <v>129730568</v>
       </c>
       <c r="B126" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13903,10 +13898,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492342</v>
+        <v>492044</v>
       </c>
       <c r="R126" t="n">
-        <v>7134966</v>
+        <v>7135114</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13970,10 +13965,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730673</v>
+        <v>129730585</v>
       </c>
       <c r="B127" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13981,21 +13976,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14005,10 +14000,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>492342</v>
+        <v>492123</v>
       </c>
       <c r="R127" t="n">
-        <v>7135223</v>
+        <v>7135047</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14041,6 +14036,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14067,10 +14067,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730643</v>
+        <v>129730539</v>
       </c>
       <c r="B128" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14102,10 +14102,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>492464</v>
+        <v>492011</v>
       </c>
       <c r="R128" t="n">
-        <v>7134867</v>
+        <v>7135206</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14142,7 +14142,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14169,10 +14169,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730539</v>
+        <v>129730561</v>
       </c>
       <c r="B129" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>492011</v>
+        <v>492039</v>
       </c>
       <c r="R129" t="n">
-        <v>7135206</v>
+        <v>7135123</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14274,7 +14274,7 @@
         <v>129730563</v>
       </c>
       <c r="B130" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14373,10 +14373,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730561</v>
+        <v>129730643</v>
       </c>
       <c r="B131" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14408,10 +14408,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>492039</v>
+        <v>492464</v>
       </c>
       <c r="R131" t="n">
-        <v>7135123</v>
+        <v>7134867</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14475,32 +14475,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129730531</v>
+        <v>129730670</v>
       </c>
       <c r="B132" t="n">
-        <v>57737</v>
+        <v>91778</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>492083</v>
+        <v>492219</v>
       </c>
       <c r="R132" t="n">
-        <v>7135291</v>
+        <v>7135247</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14546,11 +14546,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14577,10 +14572,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129730574</v>
+        <v>129730545</v>
       </c>
       <c r="B133" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14612,10 +14607,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>492062</v>
+        <v>491983</v>
       </c>
       <c r="R133" t="n">
-        <v>7135103</v>
+        <v>7135171</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14679,10 +14674,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129730545</v>
+        <v>129730580</v>
       </c>
       <c r="B134" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14714,10 +14709,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>491983</v>
+        <v>492077</v>
       </c>
       <c r="R134" t="n">
-        <v>7135171</v>
+        <v>7135066</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14781,10 +14776,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129730580</v>
+        <v>129730531</v>
       </c>
       <c r="B135" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14816,10 +14811,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>492077</v>
+        <v>492083</v>
       </c>
       <c r="R135" t="n">
-        <v>7135066</v>
+        <v>7135291</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14883,32 +14878,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129730670</v>
+        <v>129730574</v>
       </c>
       <c r="B136" t="n">
-        <v>91775</v>
+        <v>57740</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14918,10 +14913,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>492219</v>
+        <v>492062</v>
       </c>
       <c r="R136" t="n">
-        <v>7135247</v>
+        <v>7135103</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14954,6 +14949,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14980,32 +14980,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129730669</v>
+        <v>129730541</v>
       </c>
       <c r="B137" t="n">
-        <v>91775</v>
+        <v>57740</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15015,10 +15015,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>492248</v>
+        <v>492004</v>
       </c>
       <c r="R137" t="n">
-        <v>7135292</v>
+        <v>7135207</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15051,6 +15051,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15077,10 +15082,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129730620</v>
+        <v>129730646</v>
       </c>
       <c r="B138" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15112,10 +15117,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>492351</v>
+        <v>492465</v>
       </c>
       <c r="R138" t="n">
-        <v>7134938</v>
+        <v>7134871</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15179,32 +15184,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129730535</v>
+        <v>129730669</v>
       </c>
       <c r="B139" t="n">
-        <v>57737</v>
+        <v>91778</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15214,10 +15219,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492065</v>
+        <v>492248</v>
       </c>
       <c r="R139" t="n">
-        <v>7135257</v>
+        <v>7135292</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15250,11 +15255,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15281,10 +15281,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129730541</v>
+        <v>129730535</v>
       </c>
       <c r="B140" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15316,10 +15316,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492004</v>
+        <v>492065</v>
       </c>
       <c r="R140" t="n">
-        <v>7135207</v>
+        <v>7135257</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15383,10 +15383,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129730646</v>
+        <v>129730620</v>
       </c>
       <c r="B141" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15418,10 +15418,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492465</v>
+        <v>492351</v>
       </c>
       <c r="R141" t="n">
-        <v>7134871</v>
+        <v>7134938</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15485,32 +15485,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129730524</v>
+        <v>129730525</v>
       </c>
       <c r="B142" t="n">
-        <v>91566</v>
+        <v>90637</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15520,10 +15520,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492271</v>
+        <v>492390</v>
       </c>
       <c r="R142" t="n">
-        <v>7135240</v>
+        <v>7135053</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15582,32 +15582,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129730525</v>
+        <v>129730524</v>
       </c>
       <c r="B143" t="n">
-        <v>90634</v>
+        <v>91569</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15617,10 +15617,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>492390</v>
+        <v>492271</v>
       </c>
       <c r="R143" t="n">
-        <v>7135053</v>
+        <v>7135240</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15679,10 +15679,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129730648</v>
+        <v>129730578</v>
       </c>
       <c r="B144" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15714,10 +15714,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>492457</v>
+        <v>492086</v>
       </c>
       <c r="R144" t="n">
-        <v>7134863</v>
+        <v>7135087</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15781,10 +15781,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129730616</v>
+        <v>129730558</v>
       </c>
       <c r="B145" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>492343</v>
+        <v>492028</v>
       </c>
       <c r="R145" t="n">
-        <v>7134960</v>
+        <v>7135126</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15856,7 +15856,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15883,10 +15883,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129730593</v>
+        <v>129730616</v>
       </c>
       <c r="B146" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15918,10 +15918,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>492199</v>
+        <v>492343</v>
       </c>
       <c r="R146" t="n">
-        <v>7135015</v>
+        <v>7134960</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15985,10 +15985,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129730578</v>
+        <v>129730648</v>
       </c>
       <c r="B147" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16020,10 +16020,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>492086</v>
+        <v>492457</v>
       </c>
       <c r="R147" t="n">
-        <v>7135087</v>
+        <v>7134863</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16060,7 +16060,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16087,10 +16087,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129730609</v>
+        <v>129730655</v>
       </c>
       <c r="B148" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>492330</v>
+        <v>492460</v>
       </c>
       <c r="R148" t="n">
-        <v>7134971</v>
+        <v>7134849</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16189,10 +16189,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129730549</v>
+        <v>129730609</v>
       </c>
       <c r="B149" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16224,10 +16224,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>491986</v>
+        <v>492330</v>
       </c>
       <c r="R149" t="n">
-        <v>7135153</v>
+        <v>7134971</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16291,10 +16291,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129730655</v>
+        <v>129730595</v>
       </c>
       <c r="B150" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16326,10 +16326,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>492460</v>
+        <v>492208</v>
       </c>
       <c r="R150" t="n">
-        <v>7134849</v>
+        <v>7135012</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16393,10 +16393,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129730595</v>
+        <v>129730549</v>
       </c>
       <c r="B151" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>492208</v>
+        <v>491986</v>
       </c>
       <c r="R151" t="n">
-        <v>7135012</v>
+        <v>7135153</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16495,10 +16495,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129730558</v>
+        <v>129730593</v>
       </c>
       <c r="B152" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16530,10 +16530,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>492028</v>
+        <v>492199</v>
       </c>
       <c r="R152" t="n">
-        <v>7135126</v>
+        <v>7135015</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16600,7 +16600,7 @@
         <v>129730544</v>
       </c>
       <c r="B153" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16699,10 +16699,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129730590</v>
+        <v>129730552</v>
       </c>
       <c r="B154" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16734,10 +16734,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>492184</v>
+        <v>492001</v>
       </c>
       <c r="R154" t="n">
-        <v>7135029</v>
+        <v>7135144</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16801,10 +16801,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129730601</v>
+        <v>129730668</v>
       </c>
       <c r="B155" t="n">
-        <v>57737</v>
+        <v>56921</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16812,16 +16812,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -16836,10 +16836,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>492240</v>
+        <v>492293</v>
       </c>
       <c r="R155" t="n">
-        <v>7134998</v>
+        <v>7134991</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16872,11 +16872,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16903,10 +16898,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129730552</v>
+        <v>129730667</v>
       </c>
       <c r="B156" t="n">
-        <v>57737</v>
+        <v>56921</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16914,16 +16909,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -16938,10 +16933,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>492001</v>
+        <v>492088</v>
       </c>
       <c r="R156" t="n">
-        <v>7135144</v>
+        <v>7135189</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16974,11 +16969,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17005,10 +16995,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129730564</v>
+        <v>129730571</v>
       </c>
       <c r="B157" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17040,10 +17030,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>492039</v>
+        <v>492057</v>
       </c>
       <c r="R157" t="n">
-        <v>7135120</v>
+        <v>7135106</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17080,7 +17070,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17107,10 +17097,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129730668</v>
+        <v>129730564</v>
       </c>
       <c r="B158" t="n">
-        <v>56918</v>
+        <v>57740</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17118,16 +17108,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -17142,10 +17132,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>492293</v>
+        <v>492039</v>
       </c>
       <c r="R158" t="n">
-        <v>7134991</v>
+        <v>7135120</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17178,6 +17168,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17204,10 +17199,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129730667</v>
+        <v>129730590</v>
       </c>
       <c r="B159" t="n">
-        <v>56918</v>
+        <v>57740</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17215,16 +17210,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -17239,10 +17234,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>492088</v>
+        <v>492184</v>
       </c>
       <c r="R159" t="n">
-        <v>7135189</v>
+        <v>7135029</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17275,6 +17270,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17301,10 +17301,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129730571</v>
+        <v>129730634</v>
       </c>
       <c r="B160" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>492057</v>
+        <v>492423</v>
       </c>
       <c r="R160" t="n">
-        <v>7135106</v>
+        <v>7134915</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17376,7 +17376,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17403,10 +17403,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129730634</v>
+        <v>129730601</v>
       </c>
       <c r="B161" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17438,10 +17438,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>492423</v>
+        <v>492240</v>
       </c>
       <c r="R161" t="n">
-        <v>7134915</v>
+        <v>7134998</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17505,10 +17505,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129730527</v>
+        <v>129730556</v>
       </c>
       <c r="B162" t="n">
-        <v>90634</v>
+        <v>57740</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17516,21 +17516,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17540,10 +17540,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>492267</v>
+        <v>492024</v>
       </c>
       <c r="R162" t="n">
-        <v>7135233</v>
+        <v>7135131</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17576,6 +17576,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17605,7 +17610,7 @@
         <v>129730547</v>
       </c>
       <c r="B163" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17704,10 +17709,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129730556</v>
+        <v>129730592</v>
       </c>
       <c r="B164" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17739,10 +17744,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>492024</v>
+        <v>492195</v>
       </c>
       <c r="R164" t="n">
-        <v>7135131</v>
+        <v>7135016</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17779,7 +17784,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17809,7 +17814,7 @@
         <v>129730591</v>
       </c>
       <c r="B165" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17908,10 +17913,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129730546</v>
+        <v>129730527</v>
       </c>
       <c r="B166" t="n">
-        <v>57737</v>
+        <v>90637</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17919,21 +17924,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17943,10 +17948,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>491985</v>
+        <v>492267</v>
       </c>
       <c r="R166" t="n">
-        <v>7135158</v>
+        <v>7135233</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17979,11 +17984,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18010,10 +18010,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129730592</v>
+        <v>129730546</v>
       </c>
       <c r="B167" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18045,10 +18045,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>492195</v>
+        <v>491985</v>
       </c>
       <c r="R167" t="n">
-        <v>7135016</v>
+        <v>7135158</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18112,10 +18112,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129730652</v>
+        <v>129730588</v>
       </c>
       <c r="B168" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18147,10 +18147,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>492473</v>
+        <v>492176</v>
       </c>
       <c r="R168" t="n">
-        <v>7134862</v>
+        <v>7135032</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18187,7 +18187,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18214,10 +18214,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129730554</v>
+        <v>129730605</v>
       </c>
       <c r="B169" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18249,10 +18249,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>492027</v>
+        <v>492293</v>
       </c>
       <c r="R169" t="n">
-        <v>7135130</v>
+        <v>7134975</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18289,7 +18289,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18316,10 +18316,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129730605</v>
+        <v>129730652</v>
       </c>
       <c r="B170" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18351,10 +18351,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>492293</v>
+        <v>492473</v>
       </c>
       <c r="R170" t="n">
-        <v>7134975</v>
+        <v>7134862</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18418,10 +18418,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129730588</v>
+        <v>129730554</v>
       </c>
       <c r="B171" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18453,10 +18453,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>492176</v>
+        <v>492027</v>
       </c>
       <c r="R171" t="n">
-        <v>7135032</v>
+        <v>7135130</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18493,7 +18493,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18520,10 +18520,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129730530</v>
+        <v>129730581</v>
       </c>
       <c r="B172" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18555,10 +18555,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>492078</v>
+        <v>492090</v>
       </c>
       <c r="R172" t="n">
-        <v>7135290</v>
+        <v>7135062</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18595,7 +18595,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18622,10 +18622,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129730567</v>
+        <v>129730649</v>
       </c>
       <c r="B173" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>492043</v>
+        <v>492466</v>
       </c>
       <c r="R173" t="n">
-        <v>7135115</v>
+        <v>7134866</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18724,10 +18724,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129730555</v>
+        <v>129730530</v>
       </c>
       <c r="B174" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18759,10 +18759,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>492031</v>
+        <v>492078</v>
       </c>
       <c r="R174" t="n">
-        <v>7135128</v>
+        <v>7135290</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18826,10 +18826,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129730649</v>
+        <v>129730555</v>
       </c>
       <c r="B175" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>492466</v>
+        <v>492031</v>
       </c>
       <c r="R175" t="n">
-        <v>7134866</v>
+        <v>7135128</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18928,10 +18928,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129730581</v>
+        <v>129730567</v>
       </c>
       <c r="B176" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18963,10 +18963,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>492090</v>
+        <v>492043</v>
       </c>
       <c r="R176" t="n">
-        <v>7135062</v>
+        <v>7135115</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19030,10 +19030,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129730644</v>
+        <v>129730586</v>
       </c>
       <c r="B177" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19065,10 +19065,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>492462</v>
+        <v>492124</v>
       </c>
       <c r="R177" t="n">
-        <v>7134869</v>
+        <v>7135046</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19132,10 +19132,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129730610</v>
+        <v>129730612</v>
       </c>
       <c r="B178" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19167,10 +19167,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>492330</v>
+        <v>492333</v>
       </c>
       <c r="R178" t="n">
-        <v>7134972</v>
+        <v>7134969</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19234,10 +19234,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129730607</v>
+        <v>129730623</v>
       </c>
       <c r="B179" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19269,10 +19269,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>492312</v>
+        <v>492353</v>
       </c>
       <c r="R179" t="n">
-        <v>7134971</v>
+        <v>7134936</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19309,7 +19309,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19336,10 +19336,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129730612</v>
+        <v>129730607</v>
       </c>
       <c r="B180" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19371,10 +19371,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>492333</v>
+        <v>492312</v>
       </c>
       <c r="R180" t="n">
-        <v>7134969</v>
+        <v>7134971</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19438,10 +19438,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129730586</v>
+        <v>129730610</v>
       </c>
       <c r="B181" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>492124</v>
+        <v>492330</v>
       </c>
       <c r="R181" t="n">
-        <v>7135046</v>
+        <v>7134972</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19540,10 +19540,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129730623</v>
+        <v>129730644</v>
       </c>
       <c r="B182" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>492353</v>
+        <v>492462</v>
       </c>
       <c r="R182" t="n">
-        <v>7134936</v>
+        <v>7134869</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19642,10 +19642,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129730550</v>
+        <v>129730636</v>
       </c>
       <c r="B183" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19677,10 +19677,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>491991</v>
+        <v>492435</v>
       </c>
       <c r="R183" t="n">
-        <v>7135149</v>
+        <v>7134917</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19747,7 +19747,7 @@
         <v>129730653</v>
       </c>
       <c r="B184" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19846,10 +19846,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129730577</v>
+        <v>129730537</v>
       </c>
       <c r="B185" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>492066</v>
+        <v>492037</v>
       </c>
       <c r="R185" t="n">
-        <v>7135097</v>
+        <v>7135230</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19948,10 +19948,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129730636</v>
+        <v>129730557</v>
       </c>
       <c r="B186" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19983,10 +19983,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>492435</v>
+        <v>492026</v>
       </c>
       <c r="R186" t="n">
-        <v>7134917</v>
+        <v>7135131</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20023,7 +20023,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20050,10 +20050,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129730557</v>
+        <v>129730572</v>
       </c>
       <c r="B187" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20085,10 +20085,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>492026</v>
+        <v>492060</v>
       </c>
       <c r="R187" t="n">
-        <v>7135131</v>
+        <v>7135105</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20152,10 +20152,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129730537</v>
+        <v>129730550</v>
       </c>
       <c r="B188" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20187,10 +20187,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>492037</v>
+        <v>491991</v>
       </c>
       <c r="R188" t="n">
-        <v>7135230</v>
+        <v>7135149</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20257,7 +20257,7 @@
         <v>129730654</v>
       </c>
       <c r="B189" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20356,10 +20356,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129730572</v>
+        <v>129730577</v>
       </c>
       <c r="B190" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20391,10 +20391,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>492060</v>
+        <v>492066</v>
       </c>
       <c r="R190" t="n">
-        <v>7135105</v>
+        <v>7135097</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20461,7 +20461,7 @@
         <v>129730660</v>
       </c>
       <c r="B191" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>129730674</v>
       </c>
       <c r="B192" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20649,10 +20649,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129730651</v>
+        <v>129730553</v>
       </c>
       <c r="B193" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>492474</v>
+        <v>492008</v>
       </c>
       <c r="R193" t="n">
-        <v>7134863</v>
+        <v>7135137</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20751,10 +20751,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129730600</v>
+        <v>129730596</v>
       </c>
       <c r="B194" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20786,10 +20786,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>492239</v>
+        <v>492210</v>
       </c>
       <c r="R194" t="n">
-        <v>7134997</v>
+        <v>7135013</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20826,7 +20826,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20853,10 +20853,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129730596</v>
+        <v>129730600</v>
       </c>
       <c r="B195" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20888,10 +20888,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>492210</v>
+        <v>492239</v>
       </c>
       <c r="R195" t="n">
-        <v>7135013</v>
+        <v>7134997</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20928,7 +20928,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20958,7 +20958,7 @@
         <v>129730641</v>
       </c>
       <c r="B196" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21057,10 +21057,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129730621</v>
+        <v>129730560</v>
       </c>
       <c r="B197" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21092,10 +21092,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>492355</v>
+        <v>492037</v>
       </c>
       <c r="R197" t="n">
-        <v>7134935</v>
+        <v>7135124</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21159,10 +21159,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129730613</v>
+        <v>129730642</v>
       </c>
       <c r="B198" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21194,10 +21194,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>492341</v>
+        <v>492466</v>
       </c>
       <c r="R198" t="n">
-        <v>7134968</v>
+        <v>7134877</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21261,10 +21261,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129730570</v>
+        <v>129730613</v>
       </c>
       <c r="B199" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21296,10 +21296,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>492057</v>
+        <v>492341</v>
       </c>
       <c r="R199" t="n">
-        <v>7135109</v>
+        <v>7134968</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21363,10 +21363,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129730642</v>
+        <v>129730570</v>
       </c>
       <c r="B200" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21398,10 +21398,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>492466</v>
+        <v>492057</v>
       </c>
       <c r="R200" t="n">
-        <v>7134877</v>
+        <v>7135109</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21465,10 +21465,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129730560</v>
+        <v>129730621</v>
       </c>
       <c r="B201" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21500,10 +21500,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>492037</v>
+        <v>492355</v>
       </c>
       <c r="R201" t="n">
-        <v>7135124</v>
+        <v>7134935</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21567,10 +21567,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129730553</v>
+        <v>129730651</v>
       </c>
       <c r="B202" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21602,10 +21602,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>492008</v>
+        <v>492474</v>
       </c>
       <c r="R202" t="n">
-        <v>7135137</v>
+        <v>7134863</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21642,7 +21642,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21672,7 +21672,7 @@
         <v>129730666</v>
       </c>
       <c r="B203" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         <v>129811411</v>
       </c>
       <c r="B204" t="n">
-        <v>58372</v>
+        <v>58375</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>

--- a/artfynd/A 56149-2025 artfynd.xlsx
+++ b/artfynd/A 56149-2025 artfynd.xlsx
@@ -2622,45 +2622,65 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726723</v>
+        <v>129728246</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>98797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492370</v>
+        <v>492341</v>
       </c>
       <c r="R19" t="n">
-        <v>7135127</v>
+        <v>7134976</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,19 +2710,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:42</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,50 +2726,56 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726744</v>
+        <v>129726716</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>97674</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2785,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492318</v>
+        <v>492599</v>
       </c>
       <c r="R20" t="n">
-        <v>7135032</v>
+        <v>7134962</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726736</v>
+        <v>129726723</v>
       </c>
       <c r="B21" t="n">
-        <v>83058</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,21 +2868,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2871,10 +2892,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492194</v>
+        <v>492370</v>
       </c>
       <c r="R21" t="n">
-        <v>7135150</v>
+        <v>7135127</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2906,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2916,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2943,65 +2964,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129728246</v>
+        <v>129726744</v>
       </c>
       <c r="B22" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492341</v>
+        <v>492318</v>
       </c>
       <c r="R22" t="n">
-        <v>7134976</v>
+        <v>7135032</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,14 +3032,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 85 plantor och 1 vinterståndare inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,56 +3053,50 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726716</v>
+        <v>129726736</v>
       </c>
       <c r="B23" t="n">
-        <v>97674</v>
+        <v>83058</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492599</v>
+        <v>492194</v>
       </c>
       <c r="R23" t="n">
-        <v>7134962</v>
+        <v>7135150</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3959,49 +3959,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726722</v>
+        <v>129726737</v>
       </c>
       <c r="B31" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492376</v>
+        <v>492228</v>
       </c>
       <c r="R31" t="n">
-        <v>7135128</v>
+        <v>7135126</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4033,7 +4029,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4039,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,10 +4066,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726726</v>
+        <v>129726722</v>
       </c>
       <c r="B32" t="n">
-        <v>91778</v>
+        <v>98797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4081,34 +4077,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492285</v>
+        <v>492376</v>
       </c>
       <c r="R32" t="n">
-        <v>7135248</v>
+        <v>7135128</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,32 +4177,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726737</v>
+        <v>129726726</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>91778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492228</v>
+        <v>492285</v>
       </c>
       <c r="R33" t="n">
-        <v>7135126</v>
+        <v>7135248</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4804,45 +4804,65 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726720</v>
+        <v>129728243</v>
       </c>
       <c r="B39" t="n">
-        <v>78100</v>
+        <v>98797</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492458</v>
+        <v>492168</v>
       </c>
       <c r="R39" t="n">
-        <v>7135104</v>
+        <v>7135133</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4872,19 +4892,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:55</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4893,83 +4908,69 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129728243</v>
+        <v>129726720</v>
       </c>
       <c r="B40" t="n">
-        <v>98797</v>
+        <v>78100</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492168</v>
+        <v>492458</v>
       </c>
       <c r="R40" t="n">
-        <v>7135133</v>
+        <v>7135104</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4999,14 +5000,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 150 plantor och 5 vinterståndare inom ca 3 m2 yta i gammal granskog.</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5015,69 +5021,70 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726735</v>
+        <v>129728236</v>
       </c>
       <c r="B41" t="n">
-        <v>83053</v>
+        <v>80221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>310</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492209</v>
+        <v>492236</v>
       </c>
       <c r="R41" t="n">
-        <v>7135176</v>
+        <v>7135033</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5107,19 +5114,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:39</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:39</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På en klen levande sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5128,70 +5130,89 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129728236</v>
+        <v>129726735</v>
       </c>
       <c r="B42" t="n">
-        <v>80221</v>
+        <v>83053</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492236</v>
+        <v>492209</v>
       </c>
       <c r="R42" t="n">
-        <v>7135033</v>
+        <v>7135176</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5221,14 +5242,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en klen levande sälg.</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5237,44 +5263,18 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5946,45 +5946,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129728241</v>
+        <v>129728262</v>
       </c>
       <c r="B49" t="n">
-        <v>80220</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492451</v>
+        <v>492479</v>
       </c>
       <c r="R49" t="n">
-        <v>7134904</v>
+        <v>7134899</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6019,14 +6022,45 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran i gammal barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6043,7 +6077,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129728262</v>
+        <v>129726721</v>
       </c>
       <c r="B50" t="n">
         <v>79087</v>
@@ -6072,19 +6106,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492479</v>
+        <v>492421</v>
       </c>
       <c r="R50" t="n">
-        <v>7134899</v>
+        <v>7135113</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6114,14 +6145,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran i ga